--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -626,10 +626,10 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2083</v>
+        <v>2163</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -705,7 +705,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -857,7 +857,7 @@
         <v>5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -927,13 +927,13 @@
         <v>0.7</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -985,73 +985,73 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
+          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>52470</v>
+        <v>198000</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>174900</v>
+        <v>198000</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>6</v>
+        <v>1627</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>374</v>
+        <v>11240</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
+          <t>React, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>520</v>
+        <v>1254</v>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2025-11-19T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26T10:28:07.736Z</t>
+          <t>2026-08-18T03:54:49.011Z</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-embeddings</t>
+          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
         </is>
       </c>
     </row>
@@ -1061,73 +1061,73 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
+          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>198000</v>
+        <v>52470</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>198000</v>
+        <v>174900</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1625</v>
+        <v>6</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11237</v>
+        <v>378</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>React, 인공지능(AI), claude</t>
+          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1254</v>
+        <v>520</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2025-11-19T09:00:00.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T03:54:49.011Z</t>
+          <t>2026-08-26T10:28:07.736Z</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
+          <t>https://www.inflearn.com/course/building-embeddings</t>
         </is>
       </c>
     </row>
@@ -1137,73 +1137,73 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
+          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>440000</v>
+        <v>43560</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>440000</v>
+        <v>108900</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>41</v>
+        <v>381</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
+          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
+          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>1240</v>
+        <v>321</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T15:00:07.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T03:23:49.530Z</t>
+          <t>2026-08-29T06:47:12.230Z</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
+          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
         </is>
       </c>
     </row>
@@ -1213,73 +1213,73 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
+          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>43560</v>
+        <v>440000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>108900</v>
+        <v>440000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>368</v>
+        <v>43</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
+          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
+          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>321</v>
+        <v>1240</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-10-04T15:00:07.000Z</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29T06:47:12.230Z</t>
+          <t>2026-10-05T03:23:49.530Z</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
+          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
         </is>
       </c>
     </row>
@@ -1289,31 +1289,31 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
+          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>198000</v>
+        <v>88000</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>198000</v>
+        <v>88000</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>44</v>
+        <v>725</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>295</v>
+        <v>5693</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
@@ -1322,40 +1322,40 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>api, trading, codex, 바이브코딩</t>
+          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>628</v>
+        <v>2108</v>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09T01:30:06.000Z</t>
+          <t>2024-06-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T15:56:36.075Z</t>
+          <t>2026-10-01T14:55:46.048Z</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/create-an-automated</t>
+          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
         </is>
       </c>
     </row>
@@ -1365,73 +1365,73 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
+          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>퇴근후딴짓</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>37950</v>
+        <v>121000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>75900</v>
+        <v>121000</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>198</v>
+        <v>5996</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
+          <t>데이터 사이언스 자격증, 데이터 분석</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Docker, Jenkins, Kubernetes, CI/CD, backend, devops, argocd</t>
+          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>641</v>
+        <v>1560</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:30:06.000Z</t>
+          <t>2022-12-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T01:52:33.960Z</t>
+          <t>2026-10-06T00:43:26.587Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
+          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
         <v>694</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>13278</v>
+        <v>13293</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -1517,31 +1517,31 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
+          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>88000</v>
+        <v>198000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>88000</v>
+        <v>198000</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>725</v>
+        <v>45</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5691</v>
+        <v>297</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1550,40 +1550,40 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
+          <t>api, trading, codex, 바이브코딩</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2108</v>
+        <v>628</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2024-06-13T15:00:00.000Z</t>
+          <t>2026-09-09T01:30:06.000Z</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T14:55:46.048Z</t>
+          <t>2026-09-24T15:56:36.075Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
+          <t>https://www.inflearn.com/course/create-an-automated</t>
         </is>
       </c>
     </row>
@@ -1593,31 +1593,31 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>퇴근후딴짓</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>927</v>
+        <v>413</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>5992</v>
+        <v>4602</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
@@ -1626,40 +1626,38 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 데이터 분석</t>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>1560</v>
-      </c>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n"/>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2022-12-12T15:00:00.000Z</t>
+          <t>2026-01-27T10:00:00.000Z</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T00:43:26.587Z</t>
+          <t>2026-06-30T00:59:39.967Z</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
         </is>
       </c>
     </row>
@@ -1669,31 +1667,31 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0</v>
+        <v>89100</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>89100</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>413</v>
+        <v>236</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4589</v>
+        <v>1723</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1702,38 +1700,40 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n"/>
+          <t>security, CPPG(개인정보관리사)</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>727</v>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27T10:00:00.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T00:59:39.967Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -1743,73 +1743,73 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
+          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>440000</v>
+        <v>37950</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>484000</v>
+        <v>75900</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>14</v>
+        <v>199</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
+          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
+          <t>Docker, Jenkins, Kubernetes, CI/CD, backend, devops, argocd</t>
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>198</v>
+        <v>641</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T05:30:05.000Z</t>
+          <t>2026-09-28T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09T13:24:30.459Z</t>
+          <t>2026-09-29T01:52:33.960Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
+          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
         </is>
       </c>
     </row>
@@ -1819,73 +1819,73 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>nstyxn</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>198000</v>
+        <v>118800</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>198000</v>
+        <v>118800</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>169</v>
+        <v>86</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1601</v>
+        <v>958</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>보안, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>Forensic, 디지털포렌식전문가 2급</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1650</v>
+        <v>6530</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2022-11-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T06:48:11.122Z</t>
+          <t>2026-07-15T02:00:30.898Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
         </is>
       </c>
     </row>
@@ -1895,73 +1895,73 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>김영한의 실전 자바 - 기본편</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>89100</v>
+        <v>44000</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>89100</v>
+        <v>44000</v>
       </c>
       <c r="F19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>236</v>
+        <v>2399</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>1719</v>
+        <v>28213</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>727</v>
+        <v>1012</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2025-12-23T06:52:23.926Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
         </is>
       </c>
     </row>
@@ -1971,73 +1971,73 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Hiro Son</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>49500</v>
+        <v>88000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>198000</v>
+        <v>88000</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6</v>
+        <v>1352</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>150</v>
+        <v>309</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T17:30:06.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T00:53:13.219Z</t>
+          <t>2026-08-30T11:28:44.702Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -2047,31 +2047,31 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>초당 1,000,000++ RPS를 처리하는 네이버 개발자의 Valkey</t>
+          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>56760</v>
+        <v>49500</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>141900</v>
+        <v>99000</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
@@ -2080,40 +2080,40 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 알고리즘 · 자료구조, 데이터베이스</t>
+          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, 빅데이터, TypeScript, DBMS/RDBMS, Redis, MSA, 데이터 엔지니어링</t>
+          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>422</v>
+        <v>363</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-09-16T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29T21:47:01.350Z</t>
+          <t>2026-09-30T03:16:06.187Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/valkey-vs-redis-a-na</t>
+          <t>https://www.inflearn.com/course/ai-automated-trading</t>
         </is>
       </c>
     </row>
@@ -2123,31 +2123,31 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 기본편</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>44000</v>
+        <v>198000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>44000</v>
+        <v>198000</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2398</v>
+        <v>169</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28210</v>
+        <v>1602</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2156,40 +2156,40 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1012</v>
+        <v>1650</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23T06:52:23.926Z</t>
+          <t>2026-09-22T06:48:11.122Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -2199,22 +2199,22 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>MLE부터 AE·VAE 입문까지 | 디퓨전 강의 TTD 무료 공개</t>
+          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>Hiro Son</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
@@ -2223,49 +2223,49 @@
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝</t>
+          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>딥러닝</t>
+          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T23:30:06.000Z</t>
+          <t>2026-10-07T17:30:06.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T15:50:32.518Z</t>
+          <t>2026-10-10T00:53:13.219Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-mle-to-an-intro</t>
+          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
         </is>
       </c>
     </row>
@@ -2275,73 +2275,73 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>GPT는 어떻게 문장을 생성할까? | LLM·ViT 강의 ATT 무료 공개</t>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>37</v>
+        <v>1092</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>gpt, 딥러닝</t>
+          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>35</v>
+        <v>516</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T09:00:09.000Z</t>
+          <t>2026-05-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T17:04:49.947Z</t>
+          <t>2026-09-21T01:35:54.874Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-does-gpt-generat</t>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
         </is>
       </c>
     </row>
@@ -2351,31 +2351,31 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>초당 1,000,000++ RPS를 처리하는 네이버 개발자의 Valkey</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0</v>
+        <v>56760</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0</v>
+        <v>141900</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>304</v>
+        <v>6</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>3911</v>
+        <v>140</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
@@ -2384,40 +2384,40 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>백엔드, 알고리즘 · 자료구조, 데이터베이스</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>JavaScript, 빅데이터, TypeScript, DBMS/RDBMS, Redis, MSA, 데이터 엔지니어링</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>90</v>
+        <v>422</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2026-08-29T21:47:01.350Z</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/valkey-vs-redis-a-na</t>
         </is>
       </c>
     </row>
@@ -2427,73 +2427,73 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>시드니개발자의 영어PT</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>220000</v>
+        <v>330000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>220000</v>
+        <v>330000</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2196</v>
+        <v>525</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>외국어</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>49</v>
+        <v>1048</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2023-01-12T15:00:00.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T05:15:40.989Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -2503,73 +2503,73 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
+          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>330000</v>
+        <v>220000</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>330000</v>
+        <v>220000</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>523</v>
+        <v>2197</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>외국어</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>1048</v>
+        <v>49</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22T17:00:00.000Z</t>
+          <t>2023-01-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T22:53:04.634Z</t>
+          <t>2026-10-02T05:15:40.989Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
+          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
         </is>
       </c>
     </row>
@@ -2579,73 +2579,73 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>"AI 딸깍의 시대" 피할 수 없다면, 마주하라: 시스템을 지키는 암호학과 보안</t>
+          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>nhcodingstudio</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>40700</v>
+        <v>440000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>40700</v>
+        <v>484000</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>276</v>
+        <v>15</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, 웹 개발, 풀스택</t>
+          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, Python, Node.js, 네트워크, 컴퓨터 구조, backend, 인공지능(AI)</t>
+          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>534</v>
+        <v>198</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T21:30:05.000Z</t>
+          <t>2026-10-04T05:30:05.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T04:51:33.465Z</t>
+          <t>2026-10-09T13:24:30.459Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-era-of-ai-clicks-2</t>
+          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
         </is>
       </c>
     </row>
@@ -2655,73 +2655,73 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1348</v>
+        <v>3914</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>309</v>
+        <v>90</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:44.702Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -2731,19 +2731,19 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
+          <t>스프링 핵심 원리 - 기본편</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>nstyxn</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>118800</v>
+        <v>88000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>118800</v>
+        <v>88000</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
@@ -2752,52 +2752,52 @@
         <v>5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>86</v>
+        <v>4932</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>954</v>
+        <v>50475</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>보안, 보안 · 네트워크 자격증</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Forensic, 디지털포렌식전문가 2급</t>
+          <t>Spring, 객체지향</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>6530</v>
+        <v>725</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2022-11-13T15:00:00.000Z</t>
+          <t>2020-09-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T02:00:30.898Z</t>
+          <t>2025-06-04T15:00:00.555Z</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
         </is>
       </c>
     </row>
@@ -2828,10 +2828,10 @@
         <v>5</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>11780</v>
+        <v>11784</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -2883,19 +2883,19 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
+          <t>김영한의 실전 자바 - 중급 2편</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>0</v>
@@ -2904,52 +2904,52 @@
         <v>5</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>149</v>
+        <v>878</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1090</v>
+        <v>11019</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
+          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>516</v>
+        <v>1165</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12T00:00:00.000Z</t>
+          <t>2024-05-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T01:35:54.874Z</t>
+          <t>2025-11-24T10:17:13.631Z</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
         </is>
       </c>
     </row>
@@ -2959,31 +2959,31 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법)</t>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>나도코딩</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>4</v>
+        <v>1928</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>71</v>
+        <v>40176</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
@@ -2992,40 +2992,40 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2020-02-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2025-04-29T06:34:34.311Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
         </is>
       </c>
     </row>
@@ -3035,31 +3035,31 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
+          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>그랩</t>
+          <t>YoungJea Oh</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>198000</v>
+        <v>49500</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>198000</v>
+        <v>99000</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3068,40 +3068,40 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>896</v>
+        <v>370</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T04:50:00.000Z</t>
+          <t>2026-10-02T10:00:08.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T16:24:39.937Z</t>
+          <t>2026-10-02T07:55:47.247Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
+          <t>https://www.inflearn.com/course/mastering-the-latest</t>
         </is>
       </c>
     </row>
@@ -3111,19 +3111,19 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>홍정모의 따라하며 배우는 C++</t>
+          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>홍정모</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>176000</v>
+        <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>176000</v>
+        <v>0</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0</v>
@@ -3132,52 +3132,52 @@
         <v>4.9</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>7122</v>
+        <v>21146</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 게임 개발</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>컴퓨터 구조, 운영체제, 기술면접</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>2907</v>
+        <v>823</v>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>2018-09-30T15:00:00.000Z</t>
+          <t>2023-03-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2025-08-10T19:46:59.750Z</t>
+          <t>2025-04-29T09:43:24.787Z</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/following-c-plus</t>
+          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 2편</t>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0</v>
@@ -3208,14 +3208,14 @@
         <v>5</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>878</v>
+        <v>3136</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11018</v>
+        <v>57277</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3225,35 +3225,35 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1165</v>
+        <v>771</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2024-05-07T15:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2025-11-24T10:17:13.631Z</t>
+          <t>2026-01-28T11:59:57.298Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>RNN의 모든 것 | 트랜스포머 강의 TTT 무료 공개</t>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
@@ -3281,13 +3281,13 @@
         <v>0</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0</v>
+        <v>8113</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>29</v>
+        <v>123231</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
@@ -3296,40 +3296,40 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>RNN, 딥러닝</t>
+          <t>Java, Spring, MVC, Spring Boot</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>61</v>
+        <v>321</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T11:00:10.000Z</t>
+          <t>2020-07-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T17:01:56.962Z</t>
+          <t>2026-01-30T11:34:33.353Z</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/everything-about-rnn</t>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
+          <t>김영한의 실전 자바 - 중급 1편</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>77000</v>
+        <v>66000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>77000</v>
+        <v>66000</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>0</v>
@@ -3360,10 +3360,10 @@
         <v>5</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>348</v>
+        <v>1261</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5456</v>
+        <v>12536</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3377,35 +3377,35 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1001</v>
+        <v>1161</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2025-03-24T15:00:00.000Z</t>
+          <t>2024-03-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2025-09-14T05:27:02.800Z</t>
+          <t>2025-11-28T10:04:41.236Z</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
         </is>
       </c>
     </row>
@@ -3415,22 +3415,22 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
+          <t>GPT는 어떻게 문장을 생성할까? | LLM·ViT 강의 ATT 무료 공개</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
@@ -3448,40 +3448,40 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
+          <t>gpt, 딥러닝</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>370</v>
+        <v>35</v>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T10:00:08.000Z</t>
+          <t>2026-10-06T09:00:09.000Z</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T07:55:47.247Z</t>
+          <t>2026-10-06T17:04:49.947Z</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-latest</t>
+          <t>https://www.inflearn.com/course/how-does-gpt-generat</t>
         </is>
       </c>
     </row>
@@ -3491,31 +3491,31 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>코드바나나</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0</v>
+        <v>148500</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0</v>
+        <v>148500</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>8111</v>
+        <v>320</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>123230</v>
+        <v>3749</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3524,40 +3524,40 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>데브옵스 · 인프라, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, MVC, Spring Boot</t>
+          <t>AWS, 네트워크, AWS SAA</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>321</v>
+        <v>1450</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2020-07-19T15:00:00.000Z</t>
+          <t>2022-06-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T11:34:33.353Z</t>
+          <t>2026-08-02T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
         </is>
       </c>
     </row>
@@ -3567,73 +3567,73 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+          <t>홍정모의 따라하며 배우는 C++</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>홍정모</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0</v>
+        <v>176000</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0</v>
+        <v>176000</v>
       </c>
       <c r="F41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>3136</v>
+        <v>395</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>57275</v>
+        <v>7122</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 게임 개발</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>771</v>
+        <v>2907</v>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2018-09-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28T11:59:57.298Z</t>
+          <t>2025-08-10T19:46:59.750Z</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+          <t>https://www.inflearn.com/course/following-c-plus</t>
         </is>
       </c>
     </row>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+          <t>시스코 CCNA 함께 공부해요</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>ccie_pe_kim</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
@@ -3664,52 +3664,52 @@
         <v>4.9</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>458</v>
+        <v>55</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21144</v>
+        <v>1737</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+          <t>네트워크, CCNA, routing, tcpip</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>823</v>
+        <v>1213</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2023-03-02T15:00:00.000Z</t>
+          <t>2026-01-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T09:43:24.787Z</t>
+          <t>2026-03-25T09:44:13.272Z</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
         </is>
       </c>
     </row>
@@ -3719,31 +3719,31 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>[리뉴얼] 처음하는 파이썬 데이터 분석 (쉽게! 전처리, pandas, 시각화 전과정 익히기) [데이터분석/과학 Part1]</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>잔재미코딩 DaveLee</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>55000</v>
+        <v>88000</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>55000</v>
+        <v>88000</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>107</v>
+        <v>382</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>637</v>
+        <v>4449</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
@@ -3752,40 +3752,40 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>데이터 사이언스, AI 기술</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>데이터 분석, 딥러닝 · 머신러닝, 데이터 엔지니어링</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>Python, Pandas, Plotly</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>196</v>
+        <v>747</v>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2020-06-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2026-09-18T09:16:03.413Z</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/파이썬-데이터분석-전처리-판다스-시각화</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+          <t>MLE부터 AE·VAE 입문까지 | 디퓨전 강의 TTD 무료 공개</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>나도코딩</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
@@ -3813,55 +3813,55 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1927</v>
+        <v>0</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>40172</v>
+        <v>27</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>딥러닝 · 머신러닝</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>딥러닝</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>358</v>
+        <v>146</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2020-02-24T15:00:00.000Z</t>
+          <t>2026-10-06T23:30:06.000Z</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T06:34:34.311Z</t>
+          <t>2026-10-06T15:50:32.518Z</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+          <t>https://www.inflearn.com/course/from-mle-to-an-intro</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+          <t>한 입 크기로 잘라먹는 Next.js</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -3889,13 +3889,13 @@
         <v>0</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>1557</v>
+        <v>637</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>15616</v>
+        <v>6024</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
@@ -3914,30 +3914,30 @@
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>React, TypeScript, Next.js</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>1114</v>
+        <v>934</v>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>2022-01-26T15:00:00.000Z</t>
+          <t>2024-08-18T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13T00:57:34.805Z</t>
+          <t>2026-07-13T03:56:34.520Z</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-리액트</t>
+          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
         </is>
       </c>
     </row>
@@ -3947,31 +3947,31 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>시스코 CCNA 함께 공부해요</t>
+          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ccie_pe_kim</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55</v>
+        <v>4068</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1734</v>
+        <v>37224</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3980,40 +3980,40 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, routing, tcpip</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1213</v>
+        <v>341</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T15:00:00.000Z</t>
+          <t>2020-12-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25T09:44:13.272Z</t>
+          <t>2025-05-13T07:23:13.295Z</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
         </is>
       </c>
     </row>
@@ -4023,31 +4023,31 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
+          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>마일드코드</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>239800</v>
+        <v>33000</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>239800</v>
+        <v>44000</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>2</v>
+        <v>613</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>42</v>
+        <v>8402</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
@@ -4056,40 +4056,40 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
+          <t>개발 도구</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
+          <t>Git, GitHub, github-actions, git-commands</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>422</v>
+        <v>353</v>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-21T09:00:33.000Z</t>
+          <t>2022-01-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09T14:01:31.021Z</t>
+          <t>2026-06-03T09:18:28.574Z</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-for-non</t>
+          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
         </is>
       </c>
     </row>
@@ -4099,31 +4099,31 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 프론트엔드 개념 ②</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>66000</v>
+        <v>46200</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1261</v>
+        <v>0</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12535</v>
+        <v>3</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4137,35 +4137,35 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>프론트엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>React, Next.js, Nuxt.js, frontend, playwright, web-accessibility, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1161</v>
+        <v>509</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2026-10-10T13:00:07.000Z</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2026-10-10T11:20:50.801Z</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/essential-frontend-c</t>
         </is>
       </c>
     </row>
@@ -4175,31 +4175,31 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 Next.js</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>48400</v>
+        <v>44330</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>48400</v>
+        <v>68200</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>637</v>
+        <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>6024</v>
+        <v>3</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
@@ -4213,35 +4213,35 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>React, TypeScript, Next.js</t>
+          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>934</v>
+        <v>410</v>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>2024-08-18T15:00:00.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13T03:56:34.520Z</t>
+          <t>2026-10-10T12:02:44.178Z</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
+          <t>https://www.inflearn.com/course/database-concepts-yo</t>
         </is>
       </c>
     </row>
@@ -4251,22 +4251,22 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CNN 기초 제대로 이해하기 | Legend 13 무료 공개</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0</v>
+        <v>44330</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0</v>
+        <v>68200</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4284,40 +4284,40 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 컴퓨터 비전</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, CNN</t>
+          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>94</v>
+        <v>410</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T08:30:06.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T16:57:34.184Z</t>
+          <t>2026-10-10T11:44:45.232Z</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/understanding-cnn-fu</t>
+          <t>https://www.inflearn.com/course/essential-database-c</t>
         </is>
       </c>
     </row>
@@ -4327,31 +4327,31 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>RAG를 활용한 LLM Application 개발 (feat. LangChain)</t>
+          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="F51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>614</v>
+        <v>348</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>4983</v>
+        <v>5456</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
@@ -4360,40 +4360,40 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 개발 · 프로그래밍 기타</t>
+          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>LLM, RAG, LangChain, vector-database, openAI API</t>
+          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>217</v>
+        <v>1001</v>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>2024-06-27T15:00:00.000Z</t>
+          <t>2025-03-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2025-11-15T11:12:24.826Z</t>
+          <t>2025-09-14T05:27:02.800Z</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/rag-llm-application개발-langchain</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
         </is>
       </c>
     </row>
@@ -4403,31 +4403,31 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 타입스크립트(TypeScript)</t>
+          <t>RNN의 모든 것 | 트랜스포머 강의 TTT 무료 공개</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14559</v>
+        <v>30</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4436,40 +4436,40 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 프론트엔드</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>RNN, 딥러닝</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>632</v>
+        <v>61</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2023-05-21T15:00:00.000Z</t>
+          <t>2026-10-06T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16T00:41:51.879Z</t>
+          <t>2026-10-06T17:01:56.962Z</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-크기-타입스크립트</t>
+          <t>https://www.inflearn.com/course/everything-about-rnn</t>
         </is>
       </c>
     </row>
@@ -4479,31 +4479,31 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
+          <t>한 입 크기로 잘라먹는 타입스크립트(TypeScript)</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>33000</v>
+        <v>48400</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>66000</v>
+        <v>48400</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>4</v>
+        <v>780</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>261</v>
+        <v>14559</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
@@ -4512,40 +4512,40 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
+          <t>프로그래밍 언어, 웹 개발, 프론트엔드</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>Python, LLM, AI Agent, claude</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N53" s="7" t="n">
-        <v>305</v>
+        <v>632</v>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23T06:30:05.000Z</t>
+          <t>2023-05-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26T17:31:06.856Z</t>
+          <t>2026-04-16T00:41:51.879Z</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
+          <t>https://www.inflearn.com/course/한입-크기-타입스크립트</t>
         </is>
       </c>
     </row>
@@ -4555,31 +4555,31 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>그랩</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>88000</v>
+        <v>198000</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>88000</v>
+        <v>198000</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1437</v>
+        <v>326</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4588,40 +4588,40 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>368</v>
+        <v>896</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2026-07-23T04:50:00.000Z</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2026-08-01T16:24:39.937Z</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
         </is>
       </c>
     </row>
@@ -4631,73 +4631,73 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>AI 원리와 구조: ③ AI는 어떻게 배우고 달라지는가</t>
+          <t>대규모 트래픽 처리를 위한 부하테스트 입문/실전</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>테크브릿지</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>38500</v>
+        <v>77000</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>55000</v>
+        <v>77000</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>2</v>
+        <v>1093</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 딥러닝 · 머신러닝, AI 시작하기</t>
+          <t>데브옵스 · 인프라, 백엔드</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), Python, 딥러닝, LLM, RAG, 머신러닝</t>
+          <t>k6, infrastructure, performance-tuning, performance-test</t>
         </is>
       </c>
       <c r="N55" s="7" t="n">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T12:00:13.000Z</t>
+          <t>2024-12-17T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T05:39:24.096Z</t>
+          <t>2026-08-30T11:26:38.596Z</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/principles-and-struc-1</t>
+          <t>https://www.inflearn.com/course/대규모트래픽-부하테스트-입문-실전</t>
         </is>
       </c>
     </row>
@@ -4707,73 +4707,73 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>[취업폭격기] 공공기관 전산직 취업 치트키 : NCS·전공·PT면접까지 한 번에 뚫는 정규과정</t>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>취업폭격기</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>77000</v>
+        <v>48400</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>77000</v>
+        <v>48400</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>13</v>
+        <v>1557</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>625</v>
+        <v>15616</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>취업 · 이직, 커리어 · 자기계발 기타</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>면접, 이력서, 기술면접</t>
+          <t>JavaScript, React, Node.js</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1448</v>
+        <v>1114</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2023-08-08T15:00:00.000Z</t>
+          <t>2022-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T12:40:18.174Z</t>
+          <t>2026-06-13T00:57:34.805Z</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/취업폭격기-전산직-취업준비</t>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
         </is>
       </c>
     </row>
@@ -4783,22 +4783,22 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>AI Agent·LLM을 위한 Decision AI 실전: Laya 판단 모델과 Human-in-the-Loop</t>
+          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>피엠인사이드</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>19800</v>
+        <v>330000</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>33000</v>
+        <v>330000</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>0</v>
@@ -4807,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
@@ -4816,40 +4816,40 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
+          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
+          <t>프로젝트 관리, PMP</t>
         </is>
       </c>
       <c r="N57" s="7" t="n">
-        <v>109</v>
+        <v>2475</v>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T05:00:08.000Z</t>
+          <t>2026-10-01T13:00:08.000Z</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T21:14:06.144Z</t>
+          <t>2026-10-09T13:57:34.626Z</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-decision-a</t>
+          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
         </is>
       </c>
     </row>
@@ -4859,31 +4859,31 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>74250</v>
+        <v>0</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>895</v>
+        <v>6150</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4892,40 +4892,40 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
+          <t>네트워크, tcpip, routing</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>657</v>
+        <v>779</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T05:00:00.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04T00:33:30.437Z</t>
+          <t>2025-04-29T09:27:31.006Z</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/codex-true-education</t>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
         </is>
       </c>
     </row>
@@ -4935,19 +4935,19 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>154000</v>
+        <v>55000</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>154000</v>
+        <v>55000</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>0</v>
@@ -4956,52 +4956,52 @@
         <v>5</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>2045</v>
+        <v>637</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 풀스택</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N59" s="7" t="n">
-        <v>1270</v>
+        <v>196</v>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28T00:00:00.000Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -5011,73 +5011,73 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>남박사</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>68200</v>
+        <v>88000</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>68200</v>
+        <v>88000</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>287</v>
+        <v>191</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3402</v>
+        <v>1438</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
+          <t>업무 생산성, wiki, obsidian, claude</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1143</v>
+        <v>368</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2025-05-06T15:00:00.000Z</t>
+          <t>2026-04-25T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12T11:29:01.075Z</t>
+          <t>2026-10-08T14:26:56.788Z</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
         </is>
       </c>
     </row>
@@ -5087,19 +5087,19 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
+          <t>노베이스를 위한 ADsP 생존 가이드</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="F61" s="10" t="n">
         <v>0</v>
@@ -5108,52 +5108,52 @@
         <v>5</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>603</v>
+        <v>22</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>9774</v>
+        <v>738</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, thread, multithread, 동시성</t>
+          <t>SQL, R, ADsP</t>
         </is>
       </c>
       <c r="N61" s="7" t="n">
-        <v>1249</v>
+        <v>303</v>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>2024-07-14T15:00:00.000Z</t>
+          <t>2025-11-11T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>2025-11-18T01:46:58.908Z</t>
+          <t>2025-11-11T09:14:53.120Z</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
+          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
         </is>
       </c>
     </row>
@@ -5163,73 +5163,73 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>LangGraph를 활용한 AI Agent 개발 (feat. MCP)</t>
+          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>69300</v>
+        <v>74250</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>69300</v>
+        <v>99000</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>262</v>
+        <v>136</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2946</v>
+        <v>895</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>프롬프트엔지니어링, LLM, AI Agent, LangGraph, MCP</t>
+          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
-        <v>381</v>
+        <v>657</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2025-01-19T15:00:00.000Z</t>
+          <t>2026-07-20T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:57:36.230Z</t>
+          <t>2026-09-04T00:33:30.437Z</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/랭그래프-활용한-llm에이전트-개발</t>
+          <t>https://www.inflearn.com/course/codex-true-education</t>
         </is>
       </c>
     </row>
@@ -5239,19 +5239,19 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 기본편</t>
+          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>마일드코드</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>88000</v>
+        <v>239800</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>88000</v>
+        <v>239800</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>0</v>
@@ -5260,52 +5260,52 @@
         <v>5</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>513</v>
+        <v>3</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>5387</v>
+        <v>43</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N63" s="7" t="n">
-        <v>821</v>
+        <v>422</v>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2026-09-21T09:00:33.000Z</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06T12:14:20.961Z</t>
+          <t>2026-10-09T14:01:31.021Z</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
+          <t>https://www.inflearn.com/course/claude-code-for-non</t>
         </is>
       </c>
     </row>
@@ -5315,73 +5315,73 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>[AI 리터러시 저자직강] 모든 직장인이 활용할 수 있는 올인원 AI 활용법(26년 6월 전체 리뉴얼)</t>
+          <t>AI 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>김용성</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>110000</v>
+        <v>19800</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>110000</v>
+        <v>33000</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1094</v>
+        <v>13</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, 영상제작, 서비스 기획, 인공지능(AI)</t>
+          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N64" s="2" t="n">
-        <v>274</v>
+        <v>109</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09T09:30:00.000Z</t>
+          <t>2026-10-06T05:00:08.000Z</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07T08:14:11.781Z</t>
+          <t>2026-10-07T21:14:06.144Z</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-리터러시-저자직강-모든-직장인이</t>
+          <t>https://www.inflearn.com/course/practical-decision-a</t>
         </is>
       </c>
     </row>
@@ -5391,31 +5391,31 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 2편, I/O, 네트워크, 리플렉션</t>
+          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>77000</v>
+        <v>79200</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>77000</v>
+        <v>79200</v>
       </c>
       <c r="F65" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>394</v>
+        <v>228</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>7217</v>
+        <v>6750</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
@@ -5424,40 +5424,40 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>Java, 네트워크, 객체지향</t>
+          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
         </is>
       </c>
       <c r="N65" s="7" t="n">
-        <v>1296</v>
+        <v>357</v>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>2024-10-06T15:00:00.000Z</t>
+          <t>2025-07-11T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>2025-06-08T10:29:28.205Z</t>
+          <t>2025-11-10T22:31:31.977Z</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-2</t>
+          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
         </is>
       </c>
     </row>
@@ -5467,73 +5467,73 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>피그마(Figma)를 활용한 UI디자인 입문부터 실전까지 A to Z</t>
+          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>에릭</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>82500</v>
+        <v>33000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>82500</v>
+        <v>66000</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>517</v>
+        <v>4</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3675</v>
+        <v>262</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>디자인 · 아트</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>UX/UI, 그래픽 디자인</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Figma, 웹 디자인, 모바일 디자인, 프로덕트디자인</t>
+          <t>Python, LLM, AI Agent, claude</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>545</v>
+        <v>305</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2020-11-04T15:00:00.000Z</t>
+          <t>2026-09-23T06:30:05.000Z</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04T11:22:20.563Z</t>
+          <t>2026-09-26T17:31:06.856Z</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/피그마-ui디자인</t>
+          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
         </is>
       </c>
     </row>
@@ -5543,73 +5543,73 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>피엠인사이드</t>
+          <t>인프런</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>330000</v>
+        <v>33000</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>330000</v>
+        <v>33000</v>
       </c>
       <c r="F67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0</v>
+        <v>1397</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>13</v>
+        <v>34379</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 관리, PMP</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N67" s="7" t="n">
-        <v>2475</v>
+        <v>857</v>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T13:00:08.000Z</t>
+          <t>2019-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09T13:57:34.626Z</t>
+          <t>2026-09-18T05:48:10.725Z</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -5695,12 +5695,12 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>노베이스를 위한 ADsP 생존 가이드</t>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
@@ -5713,13 +5713,13 @@
         <v>0</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>733</v>
+        <v>1075</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
@@ -5728,40 +5728,38 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>SQL, R, ADsP</t>
-        </is>
-      </c>
-      <c r="N69" s="7" t="n">
-        <v>303</v>
-      </c>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="n"/>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T11:00:00.000Z</t>
+          <t>2026-06-27T04:00:06.000Z</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T09:14:53.120Z</t>
+          <t>2026-06-30T07:01:04.312Z</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
         </is>
       </c>
     </row>
@@ -5771,73 +5769,73 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>토비의 클린 스프링 - 도메인 모델 패턴과 헥사고날 아키텍처 Part 1</t>
+          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>토비</t>
+          <t>멍슨상</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>121000</v>
+        <v>36300</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>121000</v>
+        <v>48400</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>318</v>
+        <v>8</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2569</v>
+        <v>309</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>백엔드</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, Spring Boot, JPA, hexagonal-architecture, 리팩터링, DDD</t>
+          <t>Python, Java, C, 정보처리기사, database</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>872</v>
+        <v>1547</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2025-06-18T15:00:00.000Z</t>
+          <t>2025-09-24T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2025-10-23T07:53:22.134Z</t>
+          <t>2026-10-11T05:08:47.602Z</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/토비-클린스프링-도메인모델패턴-헥사고날-part1</t>
+          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
         </is>
       </c>
     </row>
@@ -5847,31 +5845,31 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>BHPT - 호스트 기반 모의해킹 기초</t>
+          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>레드라쿤</t>
+          <t>숀김</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>198000</v>
+        <v>55000</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>198000</v>
+        <v>86900</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>0</v>
+        <v>0.3670886075949367</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>1158</v>
+        <v>17</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
@@ -5880,40 +5878,40 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>보안, 시스템 · 운영체제, 네트워크</t>
+          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>모의해킹, 오펜시브 시큐리티, 네트워크, kali-linux</t>
+          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
         </is>
       </c>
       <c r="N71" s="7" t="n">
-        <v>1031</v>
+        <v>541</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>2024-01-01T15:00:00.000Z</t>
+          <t>2026-09-23T02:30:05.000Z</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>2026-03-30T05:39:15.743Z</t>
+          <t>2026-09-29T15:07:55.641Z</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/호스트-기반-모의해킹-기초</t>
+          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
         </is>
       </c>
     </row>
@@ -5923,31 +5921,31 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 설계 1편, 현대적 데이터 모델링 완전 정복</t>
+          <t>웹 개발자와 정보보안 입문자가 꼭 알아야 할 웹 해킹 &amp; 시큐어 코딩</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>크리핵티브</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>99000</v>
+        <v>55000</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>99000</v>
+        <v>55000</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>4180</v>
+        <v>2357</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5956,40 +5954,40 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
+          <t>인젝션, 모의해킹</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2025-09-15T15:00:00.000Z</t>
+          <t>2020-06-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09T09:36:10.311Z</t>
+          <t>2025-05-13T07:44:01.802Z</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계1편</t>
+          <t>https://www.inflearn.com/course/웹해킹-보안-시큐어코딩</t>
         </is>
       </c>
     </row>
@@ -5999,31 +5997,31 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
+          <t>대세는 쿠버네티스 (초급~중급편)</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>55000</v>
+        <v>44000</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>86900</v>
+        <v>44000</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>0.3670886075949367</v>
+        <v>0</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>16</v>
+        <v>8487</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
@@ -6032,40 +6030,40 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
+          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
         </is>
       </c>
       <c r="N73" s="7" t="n">
-        <v>541</v>
+        <v>425</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23T02:30:05.000Z</t>
+          <t>2019-09-10T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T15:07:55.641Z</t>
+          <t>2025-11-19T05:23:15.024Z</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
         </is>
       </c>
     </row>
@@ -6075,73 +6073,73 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
+          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>최원영</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6748</v>
+        <v>1551</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
+          <t>인공지능(AI)</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>357</v>
+        <v>32</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2025-07-11T02:00:00.000Z</t>
+          <t>2026-02-27T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10T22:31:31.977Z</t>
+          <t>2026-02-27T06:18:36.692Z</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
+          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
         </is>
       </c>
     </row>
@@ -6151,19 +6149,19 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>파이썬 알고리즘 문제풀이 입문(코딩테스트 대비)</t>
+          <t>RAG를 활용한 LLM Application 개발 (feat. LangChain)</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>김태원</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>77000</v>
+        <v>66000</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>77000</v>
+        <v>66000</v>
       </c>
       <c r="F75" s="10" t="n">
         <v>0</v>
@@ -6172,52 +6170,52 @@
         <v>4.9</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>216</v>
+        <v>615</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>6876</v>
+        <v>4983</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>알고리즘 · 자료구조, 프로그래밍 언어</t>
+          <t>AI에이전트 개발, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>Python, 코딩 테스트</t>
+          <t>LLM, RAG, LangChain, vector-database, openAI API</t>
         </is>
       </c>
       <c r="N75" s="7" t="n">
-        <v>1609</v>
+        <v>217</v>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>2019-11-10T15:00:00.000Z</t>
+          <t>2024-06-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:45:10.808Z</t>
+          <t>2025-11-15T11:12:24.826Z</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/파이썬-알고리즘-문제풀이-코딩테스트</t>
+          <t>https://www.inflearn.com/course/rag-llm-application개발-langchain</t>
         </is>
       </c>
     </row>
@@ -6227,73 +6225,73 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>이득우의 언리얼 프로그래밍 Part2 - 언리얼 게임 프레임웍의 이해</t>
+          <t>정보처리기사 자격증 대비 교육(실기)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>이득우</t>
+          <t>국립안동대학교 SW융합교육원</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>317</v>
+        <v>55</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1986</v>
+        <v>2205</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>게임 개발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>게임 프로그래밍</t>
+          <t>개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Unreal Engine, 언리얼 C++, UE Blueprint</t>
+          <t>정보처리기사</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>621</v>
+        <v>1532</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2023-04-26T15:00:00.000Z</t>
+          <t>2024-08-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:30:24.800Z</t>
+          <t>2024-08-14T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/이득우-언리얼-프로그래밍-part-2</t>
+          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6301,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 기본편</t>
+          <t>스프링 MVC 2편 - 백엔드 웹 개발 활용 기술</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -6312,10 +6310,10 @@
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="F77" s="10" t="n">
         <v>0</v>
@@ -6324,10 +6322,10 @@
         <v>5</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>4932</v>
+        <v>1321</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>50474</v>
+        <v>26183</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
@@ -6346,30 +6344,30 @@
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>Spring, 객체지향</t>
+          <t>MVC, Spring</t>
         </is>
       </c>
       <c r="N77" s="7" t="n">
-        <v>725</v>
+        <v>1266</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>2020-09-20T15:00:00.000Z</t>
+          <t>2021-06-23T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2025-06-04T15:00:00.555Z</t>
+          <t>2026-02-09T13:51:44.094Z</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
+          <t>https://www.inflearn.com/course/스프링-mvc-2</t>
         </is>
       </c>
     </row>
@@ -6379,31 +6377,31 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>자바 개발자를 위한 코틀린 입문(Java to Kotlin Starter Guide)</t>
+          <t>38군데 합격 비법, 2026 코딩테스트 필수 알고리즘</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>최태현</t>
+          <t>딩코딩코</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>55000</v>
+        <v>165000</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>55000</v>
+        <v>165000</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>356</v>
+        <v>451</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3920</v>
+        <v>2884</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6412,40 +6410,40 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드</t>
+          <t>알고리즘 · 자료구조, 취업 · 이직</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Kotlin, Java, 객체지향</t>
+          <t>Python, 코딩 테스트, 알고리즘, data-structure</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>313</v>
+        <v>934</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2022-05-12T15:00:00.000Z</t>
+          <t>2024-11-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:39:53.983Z</t>
+          <t>2026-09-10T05:18:11.523Z</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/java-to-kotlin</t>
+          <t>https://www.inflearn.com/course/38군데-합격비법-코테-필수-알고리즘</t>
         </is>
       </c>
     </row>
@@ -6455,73 +6453,73 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>AI 원리와 구조: ② AI는 무엇을 보고 판단하는가</t>
+          <t>Windows System 프로그래밍</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>테크브릿지</t>
+          <t>megayuchi</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>38500</v>
+        <v>165000</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>55000</v>
+        <v>165000</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>3</v>
+        <v>121</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 엔지니어링, AI 시작하기</t>
+          <t>데스크톱 앱 개발, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, 딥러닝, 인공지능(AI), LLM, RAG</t>
+          <t>windows-programming, C++, microsoft-visual-c++, 운영체제, system-programming</t>
         </is>
       </c>
       <c r="N79" s="7" t="n">
-        <v>261</v>
+        <v>708</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T16:30:06.000Z</t>
+          <t>2025-02-04T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T10:18:47.578Z</t>
+          <t>2026-01-13T00:22:55.653Z</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/principles-and-struc</t>
+          <t>https://www.inflearn.com/course/windows-system-programming</t>
         </is>
       </c>
     </row>
@@ -6531,19 +6529,19 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>3D 모델링 입문을 위한 라이노(Rhino) '꿀팁' Part.1</t>
+          <t>구현하며 배우는 Transformer</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>soobaksee</t>
+          <t>권 철민</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>0</v>
@@ -6552,52 +6550,52 @@
         <v>5</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>279</v>
+        <v>368</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>디자인 · 아트</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>CAD · 3D 모델링, UX/UI, 그래픽 디자인</t>
+          <t>자연어 처리, 딥러닝 · 머신러닝, 인공지능 기타</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Rhino, 3d-modelling, 3d</t>
+          <t>딥러닝, PyTorch, encoder-decoder, bert, transformer</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>705</v>
+        <v>1690</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2022-06-21T15:00:00.000Z</t>
+          <t>2025-10-16T16:00:00.000Z</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17T11:36:09.828Z</t>
+          <t>2026-07-26T06:29:54.291Z</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/입문-꿀팁-라이노-제품-모델링-1</t>
+          <t>https://www.inflearn.com/course/구현하며-배우는-transformer</t>
         </is>
       </c>
     </row>
@@ -6607,73 +6605,73 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+          <t>이득우의 언리얼 프로그래밍 Part1 - 언리얼 C++의 이해</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>이득우</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0</v>
+        <v>132000</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>0</v>
+        <v>132000</v>
       </c>
       <c r="F81" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>185</v>
+        <v>388</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>6147</v>
+        <v>2569</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>게임 개발</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>게임 프로그래밍</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, routing</t>
+          <t>언리얼 C++, Unreal Engine</t>
         </is>
       </c>
       <c r="N81" s="7" t="n">
-        <v>779</v>
+        <v>596</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2023-04-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:27:31.006Z</t>
+          <t>2025-05-13T07:43:00.937Z</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+          <t>https://www.inflearn.com/course/이득우-언리얼-프로그래밍-part-1</t>
         </is>
       </c>
     </row>
@@ -6683,19 +6681,19 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+          <t>홍정모의 따라하며 배우는 C언어</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>홍정모</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0</v>
@@ -6704,10 +6702,10 @@
         <v>4.9</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>97</v>
+        <v>457</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1069</v>
+        <v>6048</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6716,38 +6714,40 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="n"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>3066</v>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T04:00:06.000Z</t>
+          <t>2019-12-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T07:01:04.312Z</t>
+          <t>2025-08-10T19:48:02.565Z</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+          <t>https://www.inflearn.com/course/following-c</t>
         </is>
       </c>
     </row>
@@ -6757,73 +6757,73 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>대세는 쿠버네티스 (초급~중급편)</t>
+          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>44000</v>
+        <v>154000</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>44000</v>
+        <v>154000</v>
       </c>
       <c r="F83" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>626</v>
+        <v>45</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>8487</v>
+        <v>2045</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>데이터베이스, 데이터 분석, 풀스택</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
+          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
         </is>
       </c>
       <c r="N83" s="7" t="n">
-        <v>425</v>
+        <v>1270</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>2019-09-10T15:00:00.000Z</t>
+          <t>2026-07-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T05:23:15.024Z</t>
+          <t>2026-07-28T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
         </is>
       </c>
     </row>
@@ -6833,19 +6833,19 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>비전공자도 이해할 수 있는 AWS 입문/실전</t>
+          <t>LangGraph를 활용한 AI Agent 개발 (feat. MCP)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>77000</v>
+        <v>69300</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>77000</v>
+        <v>69300</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0</v>
@@ -6854,52 +6854,52 @@
         <v>4.9</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>388</v>
+        <v>262</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>3364</v>
+        <v>2946</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 백엔드, 클라우드</t>
+          <t>AI에이전트 개발</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>AWS, aws-elb, aws-rds, ec2, s3</t>
+          <t>프롬프트엔지니어링, LLM, AI Agent, LangGraph, MCP</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>257</v>
+        <v>381</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2023-11-29T15:00:00.000Z</t>
+          <t>2025-01-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:39.884Z</t>
+          <t>2026-06-23T10:57:36.230Z</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-이해할수있는-aws-입문실전</t>
+          <t>https://www.inflearn.com/course/랭그래프-활용한-llm에이전트-개발</t>
         </is>
       </c>
     </row>
@@ -6909,73 +6909,73 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
+          <t>Claude로 끝내는 실무 업무자동화: 엑셀·문서·PPT부터 Skills·Obsidian까지</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>HappyAI</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="F85" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>573</v>
+        <v>104</v>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
+          <t>data-analysis, data-processing, n8n, 프롬프트엔지니어링, claude</t>
         </is>
       </c>
       <c r="N85" s="7" t="n">
-        <v>924</v>
+        <v>229</v>
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>2025-10-03T09:30:00.000Z</t>
+          <t>2026-08-01T09:00:05.000Z</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>2025-11-10T10:01:12.921Z</t>
+          <t>2026-09-19T02:33:41.290Z</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
+          <t>https://www.inflearn.com/course/mastering-practical-2</t>
         </is>
       </c>
     </row>
@@ -6985,73 +6985,73 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>비전공자도 쉽게 배우는 클로드 디자인</t>
+          <t>스프링 MVC 1편 - 백엔드 웹 개발 핵심 기술</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>범쌤</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>31</v>
+        <v>2616</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>357</v>
+        <v>31291</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 디자인 · 아트, 업무 생산성</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>AI 크리에이티브, UX/UI, 생산성 도구</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Figma, terminal, figma-plugin, AI Agent, claude</t>
+          <t>MVC, Spring</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>249</v>
+        <v>923</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T12:00:00.000Z</t>
+          <t>2021-03-06T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T08:13:15.389Z</t>
+          <t>2025-04-29T07:20:11.745Z</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-design-for-no</t>
+          <t>https://www.inflearn.com/course/스프링-mvc-1</t>
         </is>
       </c>
     </row>
@@ -7061,19 +7061,19 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>회로설계 입문자를 위한 디지털, 아날로그 설계와 실무 Project</t>
+          <t>20년 경력자의 알기 쉬운 컴퓨터네트워크</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>회로설계 멘토 삼코치</t>
+          <t>넷가이버</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>99000</v>
+        <v>137500</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>99000</v>
+        <v>137500</v>
       </c>
       <c r="F87" s="10" t="n">
         <v>0</v>
@@ -7082,52 +7082,52 @@
         <v>4.9</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>484</v>
+        <v>1229</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>반도체, 컴퓨터 구조</t>
+          <t>네트워크, 보안 · 네트워크 기타, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>Verilog HDL, FPGA, amp, circuit</t>
+          <t>네트워크, CCNA, networking, router, switch</t>
         </is>
       </c>
       <c r="N87" s="7" t="n">
-        <v>603</v>
+        <v>789</v>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>2024-11-07T15:00:00.000Z</t>
+          <t>2021-03-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20T10:07:10.396Z</t>
+          <t>2026-06-12T17:19:53.582Z</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/회로설계-입문자-디지털-아날로그설계</t>
+          <t>https://www.inflearn.com/course/패킷트레이서-네트워크</t>
         </is>
       </c>
     </row>
@@ -7137,31 +7137,31 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Vue3 완벽 마스터: 기초부터 실전까지 - "기본편"</t>
+          <t>CNN 기초 제대로 이해하기 | Legend 13 무료 공개</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>3154</v>
+        <v>24</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7170,40 +7170,40 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>딥러닝 · 머신러닝, 컴퓨터 비전</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Vue.js</t>
+          <t>딥러닝, CNN</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>469</v>
+        <v>94</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2022-06-08T15:00:00.000Z</t>
+          <t>2026-10-06T08:30:06.000Z</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2025-06-23T12:18:30.185Z</t>
+          <t>2026-10-06T16:57:34.184Z</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/vue-완벽-기본</t>
+          <t>https://www.inflearn.com/course/understanding-cnn-fu</t>
         </is>
       </c>
     </row>
@@ -7213,31 +7213,31 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
+          <t>[AI 리터러시 저자직강] 모든 직장인이 활용할 수 있는 올인원 AI 활용법(26년 6월 전체 리뉴얼)</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>멍슨상</t>
+          <t>김용성</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>36300</v>
+        <v>110000</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>48400</v>
+        <v>110000</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>8</v>
+        <v>211</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>308</v>
+        <v>1096</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
@@ -7246,40 +7246,40 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, database</t>
+          <t>업무 생산성, 영상제작, 서비스 기획, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N89" s="7" t="n">
-        <v>1547</v>
+        <v>274</v>
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>2025-09-24T07:00:00.000Z</t>
+          <t>2025-09-09T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30T13:31:46.755Z</t>
+          <t>2026-06-07T08:14:11.781Z</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
+          <t>https://www.inflearn.com/course/ai-리터러시-저자직강-모든-직장인이</t>
         </is>
       </c>
     </row>
@@ -7289,31 +7289,31 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>리눅스 소개와 리눅스 커널 Overview [저자직강 1부-1]</t>
+          <t>[취업폭격기] 공공기관 전산직 취업 치트키 : NCS·전공·PT면접까지 한 번에 뚫는 정규과정</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>김동현 (Austin Kim)</t>
+          <t>취업폭격기</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>33000</v>
+        <v>77000</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>33000</v>
+        <v>77000</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2547</v>
+        <v>625</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7322,40 +7322,40 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 하드웨어</t>
+          <t>커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>시스템 · 운영체제, 임베디드 · IoT, 반도체</t>
+          <t>취업 · 이직, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Linux, 운영체제, linux-kernel</t>
+          <t>면접, 이력서, 기술면접</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>505</v>
+        <v>1448</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2024-02-28T15:00:00.000Z</t>
+          <t>2023-08-08T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2025-11-01T13:27:49.983Z</t>
+          <t>2026-09-03T12:40:18.174Z</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/리눅스-커널-overview-1</t>
+          <t>https://www.inflearn.com/course/취업폭격기-전산직-취업준비</t>
         </is>
       </c>
     </row>
@@ -7365,31 +7365,31 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>단 60분! 파이썬 핵심 개념 초압축 강의 - 이론보다 이해 중심</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>딩코딩코</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>4.9</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>613</v>
+        <v>484</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>8400</v>
+        <v>7087</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
@@ -7403,35 +7403,35 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
-        <v>353</v>
+        <v>64</v>
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2024-09-22T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2026-06-10T00:47:07.734Z</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/파이썬-핵심개념-압축강의</t>
         </is>
       </c>
     </row>
@@ -7441,19 +7441,19 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
+          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>38500</v>
+        <v>77000</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>38500</v>
+        <v>77000</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>0</v>
@@ -7462,52 +7462,52 @@
         <v>5</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>2</v>
+        <v>603</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>56</v>
+        <v>9774</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>SQL, Oracle, database, modeling, SQLD</t>
+          <t>Java, 객체지향, thread, multithread, 동시성</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>923</v>
+        <v>1249</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T03:00:00.000Z</t>
+          <t>2024-07-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T00:00:00.000Z</t>
+          <t>2025-11-18T01:46:58.908Z</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
         </is>
       </c>
     </row>
@@ -7517,73 +7517,73 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Vue3 완벽 마스터: 기초부터 실전까지 - "실전편"</t>
+          <t>클로드코드-비개발자 위한 기초 업무 자동화 (카드뉴스, 상세페이지, 영상, 마케팅, Aside 연동 등) 사용법</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>강슬기</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>88000</v>
+        <v>66000</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>88000</v>
+        <v>66000</v>
       </c>
       <c r="F93" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H93" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="I93" s="7" t="n">
+        <v>519</v>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>입문</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
+        </is>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
+        </is>
+      </c>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t>콘텐츠 마케팅, claude, 바이브코딩, AX(에이전트 경험), 마케팅 자동화</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="n">
         <v>191</v>
       </c>
-      <c r="I93" s="7" t="n">
-        <v>2370</v>
-      </c>
-      <c r="J93" s="7" t="inlineStr">
-        <is>
-          <t>초급</t>
-        </is>
-      </c>
-      <c r="K93" s="7" t="inlineStr">
-        <is>
-          <t>개발 · 프로그래밍</t>
-        </is>
-      </c>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>프론트엔드, 웹 개발</t>
-        </is>
-      </c>
-      <c r="M93" s="7" t="inlineStr">
-        <is>
-          <t>Vue.js</t>
-        </is>
-      </c>
-      <c r="N93" s="7" t="n">
-        <v>403</v>
-      </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>2022-06-08T15:00:00.000Z</t>
+          <t>2026-03-23T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:33:50.428Z</t>
+          <t>2026-09-07T01:42:38.618Z</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/vue-완벽-실전</t>
+          <t>https://www.inflearn.com/course/claude-code-basic-ta</t>
         </is>
       </c>
     </row>
@@ -7593,19 +7593,19 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>PMSM 벡터제어 완전정복 - 이론, Matlab, STM32 실습까지!</t>
+          <t>피그마(Figma)를 활용한 UI디자인 입문부터 실전까지 A to Z</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>제어쟁이</t>
+          <t>에릭</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>1100000</v>
+        <v>82500</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1100000</v>
+        <v>82500</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>0</v>
@@ -7614,52 +7614,52 @@
         <v>4.9</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>14</v>
+        <v>517</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>154</v>
+        <v>3675</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>하드웨어, 개발 · 프로그래밍</t>
+          <t>디자인 · 아트</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 개발 · 프로그래밍 기타, 모빌리티</t>
+          <t>UX/UI, 그래픽 디자인</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>stm32, motordriver</t>
+          <t>Figma, 웹 디자인, 모바일 디자인, 프로덕트디자인</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>1297</v>
+        <v>545</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24T01:30:00.000Z</t>
+          <t>2020-11-04T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31T16:14:23.116Z</t>
+          <t>2026-05-04T11:22:20.563Z</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmsm-벡터제어-완전정복-이론-ma</t>
+          <t>https://www.inflearn.com/course/피그마-ui디자인</t>
         </is>
       </c>
     </row>
@@ -7669,31 +7669,31 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
+          <t>코딩을 몰라도 만드는 AI 엑셀 매크로 실무 프로젝트</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>칼퇴자동화연구소</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>44000</v>
+        <v>14850</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>44000</v>
+        <v>49500</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>4067</v>
+        <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>37223</v>
+        <v>8</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
@@ -7702,40 +7702,40 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>업무 생산성, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
+          <t>오피스, 업무 자동화, AI 실무 활용</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>Excel, VBA, ChatGPT, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
-        <v>341</v>
+        <v>146</v>
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>2020-12-19T15:00:00.000Z</t>
+          <t>2026-09-27T16:30:04.000Z</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:23:13.295Z</t>
+          <t>2026-09-27T14:21:29.601Z</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
+          <t>https://www.inflearn.com/course/practical-ai-excel-m</t>
         </is>
       </c>
     </row>
@@ -7745,73 +7745,73 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
+          <t>스프링 DB 1편 - 데이터 접근 핵심 원리</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>최원영</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>86</v>
+        <v>1073</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1548</v>
+        <v>20129</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI)</t>
+          <t>Spring, MVC, spring-jdbc</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>32</v>
+        <v>605</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27T05:00:00.000Z</t>
+          <t>2022-04-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27T06:18:36.692Z</t>
+          <t>2025-05-13T07:21:40.827Z</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
+          <t>https://www.inflearn.com/course/스프링-db-1</t>
         </is>
       </c>
     </row>
@@ -7821,73 +7821,73 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>Docker가 쉬워지는 운영체제 이야기</t>
+          <t>AI 에이전트 엔지니어링</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>민혁</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F97" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>944</v>
+        <v>2043</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 시스템 · 운영체제, 클라우드</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>네트워크, Linux, Docker, 운영체제, linux-containers, cloud-computing</t>
+          <t>Python, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N97" s="7" t="n">
-        <v>723</v>
+        <v>322</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30T04:00:57.000Z</t>
+          <t>2026-04-07T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04T00:38:47.888Z</t>
+          <t>2026-04-07T02:58:08.781Z</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/operating-system-sto</t>
+          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
         </is>
       </c>
     </row>
@@ -7897,73 +7897,73 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
+          <t>김영한의 실전 자바 - 고급 2편, I/O, 네트워크, 리플렉션</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>128700</v>
+        <v>77000</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>128700</v>
+        <v>77000</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>38</v>
+        <v>394</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>569</v>
+        <v>7217</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 오피스, 업무 자동화</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
+          <t>Java, 네트워크, 객체지향</t>
         </is>
       </c>
       <c r="N98" s="2" t="n">
-        <v>832</v>
+        <v>1296</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05T16:00:00.000Z</t>
+          <t>2024-10-06T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T06:36:11.731Z</t>
+          <t>2025-06-08T10:29:28.205Z</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/starting-with-claude</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-2</t>
         </is>
       </c>
     </row>
@@ -7973,12 +7973,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>AI 에이전트 개발 오리엔테이션</t>
+          <t>기초부터 따라하는 디지털포렌식</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>승귤</t>
+          <t>훈지손</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
@@ -7994,10 +7994,10 @@
         <v>4.9</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>237</v>
+        <v>148</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>2008</v>
+        <v>6197</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
@@ -8006,40 +8006,40 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>Python, adk, AI Agent</t>
+          <t>Forensic</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
-        <v>45</v>
+        <v>545</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>2025-08-01T04:00:00.000Z</t>
+          <t>2022-02-22T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>2025-08-01T07:44:13.361Z</t>
+          <t>2022-05-31T11:24:15.993Z</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-에이전트-개발-오리엔테이션</t>
+          <t>https://www.inflearn.com/course/기초-디지털-포렌식</t>
         </is>
       </c>
     </row>
@@ -8049,31 +8049,31 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>현대적 자연어 처리 : Transformer 구조 이해에서 LLM 실전 파인튜닝 까지</t>
+          <t>스프링 핵심 원리 - 고급편</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>31</v>
+        <v>879</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>604</v>
+        <v>21007</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -8082,40 +8082,40 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>자연어 처리, 딥러닝 · 머신러닝, 인공지능 기타</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, NLP, 인공지능(AI), LLM</t>
+          <t>Spring, 디자인 패턴</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>1120</v>
+        <v>1004</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2022-12-05T15:00:00.000Z</t>
+          <t>2021-10-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T11:00:05.505Z</t>
+          <t>2025-12-21T11:02:33.060Z</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/딥러닝-활용-자연어-처리</t>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-고급편</t>
         </is>
       </c>
     </row>
@@ -8125,73 +8125,73 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>인공지능 지도학습의 학습과정과 회귀, 분류 알아보기</t>
+          <t>비개발자 직장인을 위한 Claude (Cowork + N8N + Claude Design)</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>경남대학교 SW중심대학사업단</t>
+          <t>딩코딩코</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>19</v>
+        <v>566</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 대학 교육</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, AI 시작하기, 공학</t>
+          <t>AI 실무 활용, 업무 자동화</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI)</t>
+          <t>claude, 인공지능(AI), AI Agent, n8n</t>
         </is>
       </c>
       <c r="N101" s="7" t="n">
-        <v>474</v>
+        <v>694</v>
       </c>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T12:30:06.000Z</t>
+          <t>2026-04-26T02:30:00.000Z</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T10:20:01.470Z</t>
+          <t>2026-07-24T14:36:39.327Z</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/understanding-the-tr</t>
+          <t>https://www.inflearn.com/course/claude-for-non-devel</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-10T14:54:57+09:00</t>
+          <t>2026-10-11T14:49:30+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -626,10 +626,10 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2163</v>
+        <v>2291</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -681,31 +681,31 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
+          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>49500</v>
+        <v>84700</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>99000</v>
+        <v>121000</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -714,40 +714,40 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라</t>
+          <t>AI 실무 활용, 업무 자동화</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>Linux, AWS, bash, ubuntu, nginx</t>
+          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>731</v>
+        <v>8</v>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T07:00:10.000Z</t>
+          <t>2026-10-04T09:30:05.000Z</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T15:15:20.997Z</t>
+          <t>2026-10-07T14:30:36.470Z</t>
         </is>
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
+          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
         </is>
       </c>
     </row>
@@ -757,31 +757,31 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
+          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>84700</v>
+        <v>49500</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>121000</v>
+        <v>99000</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -790,40 +790,40 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화</t>
+          <t>데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
+          <t>Linux, AWS, bash, ubuntu, nginx</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>8</v>
+        <v>730</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T09:30:05.000Z</t>
+          <t>2026-10-06T07:00:10.000Z</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T14:30:36.470Z</t>
+          <t>2026-10-12T04:00:41.911Z</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
+          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
         </is>
       </c>
     </row>
@@ -833,31 +833,31 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
+          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>64900</v>
+        <v>52470</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>64900</v>
+        <v>174900</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>772</v>
+        <v>405</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
@@ -866,40 +866,40 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
+          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>1266</v>
+        <v>520</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07T05:00:33.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T02:47:16.149Z</t>
+          <t>2026-08-26T10:28:07.736Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-llm-servic</t>
+          <t>https://www.inflearn.com/course/building-embeddings</t>
         </is>
       </c>
     </row>
@@ -909,31 +909,31 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
+          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>한조각</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>19800</v>
+        <v>43560</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>66000</v>
+        <v>108900</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>207</v>
+        <v>409</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -942,40 +942,40 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
+          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
+          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>538</v>
+        <v>321</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T20:30:05.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T18:51:20.390Z</t>
+          <t>2026-08-29T06:47:12.230Z</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-service-deploym</t>
+          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
         </is>
       </c>
     </row>
@@ -985,73 +985,73 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
+          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>한조각</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>198000</v>
+        <v>19800</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>198000</v>
+        <v>66000</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1627</v>
+        <v>2</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11240</v>
+        <v>221</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, AI 기술</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>React, 인공지능(AI), claude</t>
+          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>1254</v>
+        <v>538</v>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T09:00:00.000Z</t>
+          <t>2026-09-29T20:30:05.000Z</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18T03:54:49.011Z</t>
+          <t>2026-09-29T18:51:20.390Z</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
+          <t>https://www.inflearn.com/course/from-service-deploym</t>
         </is>
       </c>
     </row>
@@ -1061,31 +1061,31 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
+          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>52470</v>
+        <v>64900</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>174900</v>
+        <v>64900</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>378</v>
+        <v>776</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1094,40 +1094,40 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
+          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
+          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>520</v>
+        <v>1266</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-09-07T05:00:33.000Z</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T10:28:07.736Z</t>
+          <t>2026-10-02T02:47:16.149Z</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-embeddings</t>
+          <t>https://www.inflearn.com/course/practical-llm-servic</t>
         </is>
       </c>
     </row>
@@ -1137,73 +1137,73 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
+          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>43560</v>
+        <v>198000</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>108900</v>
+        <v>198000</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>4.9</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>9</v>
+        <v>1630</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>381</v>
+        <v>11254</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
+          <t>React, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>321</v>
+        <v>1254</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2025-11-19T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29T06:47:12.230Z</t>
+          <t>2026-08-18T03:54:49.011Z</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
+          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
         </is>
       </c>
     </row>
@@ -1213,73 +1213,73 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
+          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>440000</v>
+        <v>88000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>440000</v>
+        <v>88000</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>727</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>43</v>
+        <v>5700</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
+          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1240</v>
+        <v>2108</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T15:00:07.000Z</t>
+          <t>2024-06-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T03:23:49.530Z</t>
+          <t>2026-10-01T14:55:46.048Z</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
+          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
         </is>
       </c>
     </row>
@@ -1289,31 +1289,31 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
+          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>퇴근후딴짓</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>725</v>
+        <v>927</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>5693</v>
+        <v>6002</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
@@ -1322,40 +1322,40 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>데이터 사이언스 자격증, 데이터 분석</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
+          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>2108</v>
+        <v>1560</v>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>2024-06-13T15:00:00.000Z</t>
+          <t>2022-12-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T14:55:46.048Z</t>
+          <t>2026-10-06T00:43:26.587Z</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
+          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
+          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>퇴근후딴짓</t>
+          <t>한빛미디어</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
@@ -1386,10 +1386,10 @@
         <v>4.9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>927</v>
+        <v>698</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5996</v>
+        <v>13325</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1398,40 +1398,40 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 데이터 분석</t>
+          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
+          <t>인공지능(AI), 바이브코딩</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1560</v>
+        <v>259</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2022-12-12T15:00:00.000Z</t>
+          <t>2025-12-22T08:00:00.000Z</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T00:43:26.587Z</t>
+          <t>2026-01-07T07:20:44.145Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
+          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
         </is>
       </c>
     </row>
@@ -1441,73 +1441,73 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
+          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>한빛미디어</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0</v>
+        <v>440000</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0</v>
+        <v>440000</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>694</v>
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>13293</v>
+        <v>44</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
+          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), 바이브코딩</t>
+          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>259</v>
+        <v>1240</v>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>2025-12-22T08:00:00.000Z</t>
+          <t>2026-10-04T15:00:07.000Z</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-01-07T07:20:44.145Z</t>
+          <t>2026-10-05T03:23:49.530Z</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
+          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
         </is>
       </c>
     </row>
@@ -1538,10 +1538,10 @@
         <v>4.9</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:56:36.075Z</t>
+          <t>2026-10-11T08:59:09.803Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -1617,7 +1617,7 @@
         <v>413</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>4602</v>
+        <v>4623</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
@@ -1667,19 +1667,19 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>89100</v>
+        <v>88000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>89100</v>
+        <v>88000</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
@@ -1688,52 +1688,52 @@
         <v>4.9</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1723</v>
+        <v>1357</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>727</v>
+        <v>309</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2026-08-30T11:28:44.702Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -1743,73 +1743,73 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>37950</v>
+        <v>89100</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>75900</v>
+        <v>89100</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>199</v>
+        <v>1728</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>Docker, Jenkins, Kubernetes, CI/CD, backend, devops, argocd</t>
+          <t>security, CPPG(개인정보관리사)</t>
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>641</v>
+        <v>727</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-28T10:30:06.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T01:52:33.960Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -1819,73 +1819,73 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
+          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>nstyxn</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>118800</v>
+        <v>37950</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>118800</v>
+        <v>75900</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>958</v>
+        <v>203</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>보안, 보안 · 네트워크 자격증</t>
+          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Forensic, 디지털포렌식전문가 2급</t>
+          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>6530</v>
+        <v>641</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2022-11-13T15:00:00.000Z</t>
+          <t>2026-09-28T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T02:00:30.898Z</t>
+          <t>2026-09-29T01:52:33.960Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
+          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
         </is>
       </c>
     </row>
@@ -1895,73 +1895,73 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 기본편</t>
+          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>Hiro Son</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>44000</v>
+        <v>49500</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>44000</v>
+        <v>198000</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>2399</v>
+        <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>28213</v>
+        <v>12</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>1012</v>
+        <v>150</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-10-07T17:30:06.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2025-12-23T06:52:23.926Z</t>
+          <t>2026-10-10T00:53:13.219Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
         </is>
       </c>
     </row>
@@ -1971,31 +1971,31 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>88000</v>
+        <v>69300</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>88000</v>
+        <v>99000</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1352</v>
+        <v>42</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -2004,40 +2004,40 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>309</v>
+        <v>73</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2026-10-08T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:44.702Z</t>
+          <t>2026-10-11T17:09:46.044Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
         </is>
       </c>
     </row>
@@ -2047,31 +2047,31 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법)</t>
+          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>nstyxn</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>49500</v>
+        <v>118800</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>99000</v>
+        <v>118800</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>74</v>
+        <v>958</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
@@ -2080,40 +2080,40 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>보안, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>Forensic, 디지털포렌식전문가 2급</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>363</v>
+        <v>6530</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2022-11-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2026-07-15T02:00:30.898Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
         </is>
       </c>
     </row>
@@ -2123,31 +2123,31 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>김영한의 실전 자바 - 기본편</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>198000</v>
+        <v>44000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>198000</v>
+        <v>44000</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>169</v>
+        <v>2399</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1602</v>
+        <v>28216</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2156,40 +2156,40 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1650</v>
+        <v>1012</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T06:48:11.122Z</t>
+          <t>2025-12-23T06:52:23.926Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
         </is>
       </c>
     </row>
@@ -2199,31 +2199,31 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
+          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Hiro Son</t>
+          <t>시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>49500</v>
+        <v>220000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>198000</v>
+        <v>220000</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>8</v>
+        <v>2199</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
@@ -2232,40 +2232,40 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
+          <t>외국어</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T17:30:06.000Z</t>
+          <t>2023-01-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T00:53:13.219Z</t>
+          <t>2026-10-02T05:15:40.989Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
+          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
         </is>
       </c>
     </row>
@@ -2275,31 +2275,31 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
+          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>99000</v>
+        <v>49500</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>99000</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>149</v>
+        <v>4</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1092</v>
+        <v>78</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2308,40 +2308,40 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
+          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>516</v>
+        <v>363</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12T00:00:00.000Z</t>
+          <t>2026-09-16T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T01:35:54.874Z</t>
+          <t>2026-09-30T03:16:06.187Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
+          <t>https://www.inflearn.com/course/ai-automated-trading</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
         <v>6</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -2427,19 +2427,19 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>330000</v>
+        <v>99000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>330000</v>
+        <v>99000</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>0</v>
@@ -2448,52 +2448,52 @@
         <v>5</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>525</v>
+        <v>1098</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1048</v>
+        <v>516</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T17:00:00.000Z</t>
+          <t>2026-05-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T22:53:04.634Z</t>
+          <t>2026-09-21T01:35:54.874Z</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
         </is>
       </c>
     </row>
@@ -2503,31 +2503,31 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>시드니개발자의 영어PT</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>63</v>
+        <v>306</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>2197</v>
+        <v>3935</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
@@ -2536,40 +2536,40 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>외국어</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>2023-01-12T15:00:00.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T05:15:40.989Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -2579,73 +2579,73 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>440000</v>
+        <v>550000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>484000</v>
+        <v>550000</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>15</v>
+        <v>603</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
+          <t>임베디드 · IoT, 모빌리티</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>198</v>
+        <v>1017</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T05:30:05.000Z</t>
+          <t>2025-06-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T13:24:30.459Z</t>
+          <t>2026-09-13T09:06:49.556Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
         </is>
       </c>
     </row>
@@ -2655,73 +2655,73 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>304</v>
+        <v>171</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>3914</v>
+        <v>1604</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>90</v>
+        <v>1650</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2026-09-22T06:48:11.122Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -2731,73 +2731,73 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 기본편</t>
+          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>88000</v>
+        <v>440000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>88000</v>
+        <v>484000</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4932</v>
+        <v>4</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>50475</v>
+        <v>16</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Spring, 객체지향</t>
+          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>725</v>
+        <v>204</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2020-09-20T15:00:00.000Z</t>
+          <t>2026-10-04T05:30:05.000Z</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04T15:00:00.555Z</t>
+          <t>2026-10-11T15:08:50.737Z</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
+          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
         </is>
       </c>
     </row>
@@ -2828,10 +2828,10 @@
         <v>5</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>11784</v>
+        <v>11799</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -2883,31 +2883,31 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 2편</t>
+          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>YoungJea Oh</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>66000</v>
+        <v>49500</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>66000</v>
+        <v>99000</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>878</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11019</v>
+        <v>21</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2916,40 +2916,40 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1165</v>
+        <v>370</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2024-05-07T15:00:00.000Z</t>
+          <t>2026-10-02T10:00:08.000Z</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2025-11-24T10:17:13.631Z</t>
+          <t>2026-10-02T07:55:47.247Z</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+          <t>https://www.inflearn.com/course/mastering-the-latest</t>
         </is>
       </c>
     </row>
@@ -2959,73 +2959,73 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>나도코딩</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>1928</v>
+        <v>35</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>40176</v>
+        <v>527</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>358</v>
+        <v>1048</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2020-02-24T15:00:00.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T06:34:34.311Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -3035,31 +3035,31 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>49500</v>
+        <v>55000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>99000</v>
+        <v>55000</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20</v>
+        <v>645</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3068,40 +3068,40 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T10:00:08.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T07:55:47.247Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-latest</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>나도코딩</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
@@ -3132,10 +3132,10 @@
         <v>4.9</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>459</v>
+        <v>1930</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>21146</v>
+        <v>40184</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
@@ -3144,40 +3144,40 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>823</v>
+        <v>358</v>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>2023-03-02T15:00:00.000Z</t>
+          <t>2020-02-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:43:24.787Z</t>
+          <t>2025-04-29T06:34:34.311Z</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3208,14 +3208,14 @@
         <v>5</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3136</v>
+        <v>8116</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>57277</v>
+        <v>123242</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3225,35 +3225,35 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>Java, Spring, MVC, Spring Boot</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>771</v>
+        <v>321</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2020-07-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28T11:59:57.298Z</t>
+          <t>2026-01-30T11:34:33.353Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
@@ -3281,55 +3281,55 @@
         <v>0</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>8113</v>
+        <v>460</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>123231</v>
+        <v>21155</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, MVC, Spring Boot</t>
+          <t>컴퓨터 구조, 운영체제, 기술면접</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>321</v>
+        <v>823</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2020-07-19T15:00:00.000Z</t>
+          <t>2023-03-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2026-01-30T11:34:33.353Z</t>
+          <t>2025-04-29T09:43:24.787Z</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
         </is>
       </c>
     </row>
@@ -3339,31 +3339,31 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>클로드로 딸깍! 루프 엔지니어링으로 통합 자산관리 시스템 개발하기</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>66000</v>
+        <v>154000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>66000</v>
+        <v>154000</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1261</v>
+        <v>10</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>12536</v>
+        <v>422</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3372,40 +3372,40 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>AI 실무 활용, AI 코딩, 풀스택</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>인공지능(AI), 바이브코딩, AX(에이전트 경험), AI Agent, minio</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1161</v>
+        <v>795</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2026-06-23T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2026-07-05T22:46:00.597Z</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/one-click-with-claud</t>
         </is>
       </c>
     </row>
@@ -3415,22 +3415,22 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>GPT는 어떻게 문장을 생성할까? | LLM·ViT 강의 ATT 무료 공개</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 프론트엔드 개념 ②</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0</v>
+        <v>46200</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
@@ -3448,40 +3448,40 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>프론트엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>gpt, 딥러닝</t>
+          <t>React, Next.js, Nuxt.js, frontend, playwright, web-accessibility, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>35</v>
+        <v>509</v>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T09:00:09.000Z</t>
+          <t>2026-10-10T13:00:07.000Z</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T17:04:49.947Z</t>
+          <t>2026-10-10T11:20:50.801Z</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-does-gpt-generat</t>
+          <t>https://www.inflearn.com/course/essential-frontend-c</t>
         </is>
       </c>
     </row>
@@ -3491,73 +3491,73 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
+          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>코드바나나</t>
+          <t>마일드코드</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>148500</v>
+        <v>239800</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>148500</v>
+        <v>239800</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>320</v>
+        <v>3</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3749</v>
+        <v>47</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
+          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>AWS, 네트워크, AWS SAA</t>
+          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1450</v>
+        <v>455</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2022-06-21T15:00:00.000Z</t>
+          <t>2026-09-21T09:00:33.000Z</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T00:00:00.000Z</t>
+          <t>2026-10-12T00:30:58.863Z</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
+          <t>https://www.inflearn.com/course/claude-code-for-non</t>
         </is>
       </c>
     </row>
@@ -3567,31 +3567,31 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>홍정모의 따라하며 배우는 C++</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>홍정모</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>176000</v>
+        <v>44330</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>176000</v>
+        <v>68200</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>7122</v>
+        <v>4</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
@@ -3600,40 +3600,40 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 게임 개발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>2907</v>
+        <v>410</v>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>2018-09-30T15:00:00.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2025-08-10T19:46:59.750Z</t>
+          <t>2026-10-10T12:02:44.178Z</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/following-c-plus</t>
+          <t>https://www.inflearn.com/course/database-concepts-yo</t>
         </is>
       </c>
     </row>
@@ -3643,31 +3643,31 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>시스코 CCNA 함께 공부해요</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>ccie_pe_kim</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0</v>
+        <v>44330</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0</v>
+        <v>68200</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1737</v>
+        <v>3</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3676,40 +3676,40 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, routing, tcpip</t>
+          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1213</v>
+        <v>410</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T15:00:00.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25T09:44:13.272Z</t>
+          <t>2026-10-10T11:44:45.232Z</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+          <t>https://www.inflearn.com/course/essential-database-c</t>
         </is>
       </c>
     </row>
@@ -3719,31 +3719,31 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>[리뉴얼] 처음하는 파이썬 데이터 분석 (쉽게! 전처리, pandas, 시각화 전과정 익히기) [데이터분석/과학 Part1]</t>
+          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>잔재미코딩 DaveLee</t>
+          <t>숀김</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>88000</v>
+        <v>86900</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>0</v>
+        <v>0.3670886075949367</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>4449</v>
+        <v>19</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
@@ -3752,40 +3752,40 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스, AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 딥러닝 · 머신러닝, 데이터 엔지니어링</t>
+          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Python, Pandas, Plotly</t>
+          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>747</v>
+        <v>541</v>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>2020-06-21T15:00:00.000Z</t>
+          <t>2026-09-23T02:30:05.000Z</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18T09:16:03.413Z</t>
+          <t>2026-09-29T15:07:55.641Z</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/파이썬-데이터분석-전처리-판다스-시각화</t>
+          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
         </is>
       </c>
     </row>
@@ -3795,22 +3795,22 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MLE부터 AE·VAE 입문까지 | 디퓨전 강의 TTD 무료 공개</t>
+          <t>AI 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0</v>
+        <v>19800</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3828,40 +3828,40 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>딥러닝</t>
+          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T23:30:06.000Z</t>
+          <t>2026-10-06T05:00:08.000Z</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T15:50:32.518Z</t>
+          <t>2026-10-07T21:14:06.144Z</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-mle-to-an-intro</t>
+          <t>https://www.inflearn.com/course/practical-decision-a</t>
         </is>
       </c>
     </row>
@@ -3871,31 +3871,31 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 Next.js</t>
+          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>48400</v>
+        <v>33000</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>48400</v>
+        <v>66000</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>637</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>6024</v>
+        <v>264</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
@@ -3904,40 +3904,40 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>React, TypeScript, Next.js</t>
+          <t>Python, LLM, AI Agent, claude</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>934</v>
+        <v>305</v>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>2024-08-18T15:00:00.000Z</t>
+          <t>2026-09-23T06:30:05.000Z</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13T03:56:34.520Z</t>
+          <t>2026-09-26T17:31:06.856Z</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
+          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
+          <t>김영한의 실전 자바 - 중급 2편</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>5</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>4068</v>
+        <v>880</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>37224</v>
+        <v>11020</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3980,40 +3980,40 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>341</v>
+        <v>1165</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2020-12-19T15:00:00.000Z</t>
+          <t>2024-05-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:23:13.295Z</t>
+          <t>2025-11-24T10:17:13.631Z</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
         </is>
       </c>
     </row>
@@ -4023,31 +4023,31 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>613</v>
+        <v>186</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>8402</v>
+        <v>6160</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
@@ -4056,40 +4056,40 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>네트워크, tcpip, routing</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>353</v>
+        <v>779</v>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2025-04-29T09:27:31.006Z</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
         </is>
       </c>
     </row>
@@ -4099,31 +4099,31 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 프론트엔드 개념 ②</t>
+          <t>(AI 퀀트) 코드 한 줄 안 쓰고 주식 자동 분석 시스템 만들기 feat. Claude CLI</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>호두감자</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>46200</v>
+        <v>140250</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>77000</v>
+        <v>187000</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
+        <v>442</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4132,40 +4132,40 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>프론트엔드, AI 코딩</t>
+          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>React, Next.js, Nuxt.js, frontend, playwright, web-accessibility, 인공지능(AI)</t>
+          <t>Python, Flask, Next.js, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T13:00:07.000Z</t>
+          <t>2026-02-17T20:00:00.000Z</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T11:20:50.801Z</t>
+          <t>2026-07-12T14:59:08.440Z</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-frontend-c</t>
+          <t>https://www.inflearn.com/course/코드-한-줄-안-쓰고-주식-자동-분석</t>
         </is>
       </c>
     </row>
@@ -4175,31 +4175,31 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>44330</v>
+        <v>48400</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>68200</v>
+        <v>48400</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0</v>
+        <v>1557</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>3</v>
+        <v>15618</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
@@ -4213,35 +4213,35 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
+          <t>JavaScript, React, Node.js</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>410</v>
+        <v>1114</v>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2022-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T12:02:44.178Z</t>
+          <t>2026-06-13T00:57:34.805Z</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/database-concepts-yo</t>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
         </is>
       </c>
     </row>
@@ -4251,31 +4251,31 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
+          <t>시스코 CCNA 함께 공부해요</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>ccie_pe_kim</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>44330</v>
+        <v>0</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>68200</v>
+        <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
+        <v>1741</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4284,40 +4284,40 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
+          <t>네트워크, CCNA, routing, tcpip</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>410</v>
+        <v>1213</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2026-01-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T11:44:45.232Z</t>
+          <t>2026-03-25T09:44:13.272Z</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-database-c</t>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="F51" s="10" t="n">
         <v>0</v>
@@ -4348,14 +4348,14 @@
         <v>5</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>348</v>
+        <v>3137</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>5456</v>
+        <v>57283</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
@@ -4365,35 +4365,35 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>1001</v>
+        <v>771</v>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>2025-03-24T15:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2025-09-14T05:27:02.800Z</t>
+          <t>2026-01-28T11:59:57.298Z</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
         </is>
       </c>
     </row>
@@ -4403,31 +4403,31 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>RNN의 모든 것 | 트랜스포머 강의 TTT 무료 공개</t>
+          <t>토비의 스프링 6 - 이해와 원리</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>토비</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>30</v>
+        <v>3540</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4436,40 +4436,40 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>백엔드</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>RNN, 딥러닝</t>
+          <t>Java, Spring</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>61</v>
+        <v>747</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T11:00:10.000Z</t>
+          <t>2024-06-23T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T17:01:56.962Z</t>
+          <t>2025-05-13T07:27:36.161Z</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/everything-about-rnn</t>
+          <t>https://www.inflearn.com/course/토비의-스프링6-이해와-원리</t>
         </is>
       </c>
     </row>
@@ -4479,73 +4479,73 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 타입스크립트(TypeScript)</t>
+          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>48400</v>
+        <v>74250</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>48400</v>
+        <v>99000</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>780</v>
+        <v>137</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>14559</v>
+        <v>898</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 프론트엔드</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
         </is>
       </c>
       <c r="N53" s="7" t="n">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>2023-05-21T15:00:00.000Z</t>
+          <t>2026-07-20T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>2026-04-16T00:41:51.879Z</t>
+          <t>2026-10-11T06:39:46.390Z</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-크기-타입스크립트</t>
+          <t>https://www.inflearn.com/course/codex-true-education</t>
         </is>
       </c>
     </row>
@@ -4555,73 +4555,71 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>그랩</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>326</v>
+        <v>1084</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>896</v>
-      </c>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T04:50:00.000Z</t>
+          <t>2026-06-27T04:00:06.000Z</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T16:24:39.937Z</t>
+          <t>2026-06-30T07:01:04.312Z</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
         </is>
       </c>
     </row>
@@ -4631,31 +4629,31 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>대규모 트래픽 처리를 위한 부하테스트 입문/실전</t>
+          <t>데이터 드리븐 그로스 마케팅 - 고객 중심의 문제 해결력 업그레이드</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>서현직</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>77000</v>
+        <v>132000</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>77000</v>
+        <v>132000</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>1093</v>
+        <v>512</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
@@ -4664,40 +4662,40 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 백엔드</t>
+          <t>마케팅, 기획 · PM· PO</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>k6, infrastructure, performance-tuning, performance-test</t>
+          <t>그로스해킹, 마케팅 이론, 퍼포먼스 마케팅, 디지털 마케팅</t>
         </is>
       </c>
       <c r="N55" s="7" t="n">
-        <v>208</v>
+        <v>618</v>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>2024-12-17T15:00:00.000Z</t>
+          <t>2024-03-06T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:38.596Z</t>
+          <t>2026-03-21T11:50:42.713Z</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/대규모트래픽-부하테스트-입문-실전</t>
+          <t>https://www.inflearn.com/course/그로스-마케팅-101</t>
         </is>
       </c>
     </row>
@@ -4707,35 +4705,35 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>48400</v>
+        <v>33000</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>48400</v>
+        <v>44000</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1557</v>
+        <v>614</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15616</v>
+        <v>8406</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4745,35 +4743,35 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>개발 도구</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>Git, GitHub, github-actions, git-commands</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1114</v>
+        <v>353</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2022-01-26T15:00:00.000Z</t>
+          <t>2022-01-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13T00:57:34.805Z</t>
+          <t>2026-06-03T09:18:28.574Z</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-리액트</t>
+          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
         </is>
       </c>
     </row>
@@ -4783,31 +4781,31 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
+          <t>독하게 시작하는 C 프로그래밍</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>피엠인사이드</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>330000</v>
+        <v>99000</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>330000</v>
+        <v>99000</v>
       </c>
       <c r="F57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>14</v>
+        <v>3144</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
@@ -4816,40 +4814,40 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
+          <t>프로그래밍 언어, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 관리, PMP</t>
+          <t>C, 컴퓨터 구조, assembly-language, vc++</t>
         </is>
       </c>
       <c r="N57" s="7" t="n">
-        <v>2475</v>
+        <v>1739</v>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T13:00:08.000Z</t>
+          <t>2023-09-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09T13:57:34.626Z</t>
+          <t>2025-05-13T07:29:20.937Z</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
+          <t>https://www.inflearn.com/course/독하게-시작하는-c프로그래밍</t>
         </is>
       </c>
     </row>
@@ -4859,31 +4857,31 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+          <t>[백문이불여일타] 데이터 분석을 위한 기초 SQL</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>데이터리안</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>185</v>
+        <v>1283</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>6150</v>
+        <v>6475</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4892,40 +4890,40 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>데이터 분석, 데이터베이스</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, routing</t>
+          <t>SQL, MySQL</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>779</v>
+        <v>86</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2020-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T09:27:31.006Z</t>
+          <t>2025-11-27T07:28:10.999Z</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+          <t>https://www.inflearn.com/course/백문이불여일타-데이터-분석-기초-sql</t>
         </is>
       </c>
     </row>
@@ -4935,31 +4933,31 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>정보처리기사 자격증 대비 교육(실기)</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>국립안동대학교 SW융합교육원</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>637</v>
+        <v>2217</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
@@ -4968,40 +4966,40 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>정보처리기사</t>
         </is>
       </c>
       <c r="N59" s="7" t="n">
-        <v>196</v>
+        <v>1532</v>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2024-08-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2024-08-14T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
         </is>
       </c>
     </row>
@@ -5011,12 +5009,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>스프링 핵심 원리 - 기본편</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
@@ -5029,13 +5027,13 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>191</v>
+        <v>4932</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1438</v>
+        <v>50475</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5044,40 +5042,40 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>Spring, 객체지향</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>368</v>
+        <v>725</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2020-09-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2025-06-04T15:00:00.555Z</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
         </is>
       </c>
     </row>
@@ -5087,73 +5085,73 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>노베이스를 위한 ADsP 생존 가이드</t>
+          <t>[백문이불여일타] 데이터 분석을 위한 중급 SQL</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>데이터리안</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="F61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>22</v>
+        <v>996</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>738</v>
+        <v>5698</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
+          <t>데이터 분석, 데이터베이스</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>SQL, R, ADsP</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="N61" s="7" t="n">
-        <v>303</v>
+        <v>140</v>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T11:00:00.000Z</t>
+          <t>2020-02-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T09:14:53.120Z</t>
+          <t>2025-11-27T07:45:36.152Z</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
+          <t>https://www.inflearn.com/course/데이터-분석-중급-sql</t>
         </is>
       </c>
     </row>
@@ -5163,73 +5161,73 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
+          <t>자바 개발자를 위한 코틀린 입문(Java to Kotlin Starter Guide)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>최태현</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>74250</v>
+        <v>55000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>99000</v>
+        <v>55000</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>136</v>
+        <v>356</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>895</v>
+        <v>3921</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>프로그래밍 언어, 백엔드</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
+          <t>Kotlin, Java, 객체지향</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
-        <v>657</v>
+        <v>313</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T05:00:00.000Z</t>
+          <t>2022-05-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04T00:33:30.437Z</t>
+          <t>2025-05-13T07:39:53.983Z</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/codex-true-education</t>
+          <t>https://www.inflearn.com/course/java-to-kotlin</t>
         </is>
       </c>
     </row>
@@ -5239,73 +5237,73 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
+          <t>GPT는 어떻게 문장을 생성할까? | LLM·ViT 강의 ATT 무료 공개</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>마일드코드</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>239800</v>
+        <v>0</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>239800</v>
+        <v>0</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
+          <t>gpt, 딥러닝</t>
         </is>
       </c>
       <c r="N63" s="7" t="n">
-        <v>422</v>
+        <v>35</v>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-21T09:00:33.000Z</t>
+          <t>2026-10-06T09:00:09.000Z</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09T14:01:31.021Z</t>
+          <t>2026-10-06T17:04:49.947Z</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-for-non</t>
+          <t>https://www.inflearn.com/course/how-does-gpt-generat</t>
         </is>
       </c>
     </row>
@@ -5315,73 +5313,73 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>AI 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
+          <t>노베이스를 위한 ADsP 생존 가이드</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>19800</v>
+        <v>0</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>13</v>
+        <v>748</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
+          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
+          <t>SQL, R, ADsP</t>
         </is>
       </c>
       <c r="N64" s="2" t="n">
-        <v>109</v>
+        <v>303</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T05:00:08.000Z</t>
+          <t>2025-11-11T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T21:14:06.144Z</t>
+          <t>2025-11-11T09:14:53.120Z</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-decision-a</t>
+          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
         </is>
       </c>
     </row>
@@ -5391,31 +5389,31 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
+          <t>대세는 쿠버네티스 (초급~중급편)</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>79200</v>
+        <v>44000</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>79200</v>
+        <v>44000</v>
       </c>
       <c r="F65" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>228</v>
+        <v>626</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>6750</v>
+        <v>8492</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
@@ -5424,40 +5422,40 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
+          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
         </is>
       </c>
       <c r="N65" s="7" t="n">
-        <v>357</v>
+        <v>425</v>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>2025-07-11T02:00:00.000Z</t>
+          <t>2019-09-10T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>2025-11-10T22:31:31.977Z</t>
+          <t>2025-11-19T05:23:15.024Z</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
         </is>
       </c>
     </row>
@@ -5467,31 +5465,31 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
+          <t>[유니티6] 타워 디펜스 리팩토링과 확장 - 신규 타워 4종과 맵 제작 자동화</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>고박사</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>33000</v>
+        <v>39600</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>66000</v>
+        <v>39600</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5500,40 +5498,40 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>게임 개발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
+          <t>게임 프로그래밍, 프로그래밍 언어, 게임 개발 기타</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Python, LLM, AI Agent, claude</t>
+          <t>C#, Unity, scriptable-object, unity2d, 유니티6</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T06:30:05.000Z</t>
+          <t>2026-09-26T14:30:05.000Z</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T17:31:06.856Z</t>
+          <t>2026-10-01T15:33:53.455Z</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
+          <t>https://www.inflearn.com/course/unity-6-tower-defens</t>
         </is>
       </c>
     </row>
@@ -5543,19 +5541,19 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
+          <t>맥킨지 출신 김재성의 AI로 앞서가는 문제 해결력 &amp; 리서치 전략</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>인프런</t>
+          <t>Jaesung Kim</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>33000</v>
+        <v>330000</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>33000</v>
+        <v>330000</v>
       </c>
       <c r="F67" s="10" t="n">
         <v>0</v>
@@ -5564,10 +5562,10 @@
         <v>4.8</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>1397</v>
+        <v>45</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>34379</v>
+        <v>391</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
@@ -5576,40 +5574,40 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>기획 · 경영 · 마케팅, AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>경영 · 전략, AI 실무 활용, 취업 · 이직</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>경영노하우, 인공지능(AI), ChatGPT, 컨설팅, 문제해결능력</t>
         </is>
       </c>
       <c r="N67" s="7" t="n">
-        <v>857</v>
+        <v>508</v>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>2019-06-01T15:00:00.000Z</t>
+          <t>2025-09-22T06:18:00.000Z</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18T05:48:10.725Z</t>
+          <t>2026-08-05T05:45:09.557Z</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
+          <t>https://www.inflearn.com/course/맥킨지-출신-김재성의-ai로-앞서가는</t>
         </is>
       </c>
     </row>
@@ -5619,31 +5617,31 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>[유니티6] 타워 디펜스 리팩토링과 확장 - 신규 타워 4종과 맵 제작 자동화</t>
+          <t>C개발자를 위한 최소한의 C++</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>고박사</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>39600</v>
+        <v>99000</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>39600</v>
+        <v>99000</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19</v>
+        <v>1126</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5652,40 +5650,40 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>게임 개발, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>게임 프로그래밍, 프로그래밍 언어, 게임 개발 기타</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>C#, Unity, scriptable-object, unity2d, 유니티6</t>
+          <t>C++, 객체지향, Microsoft Windows, 디자인 패턴</t>
         </is>
       </c>
       <c r="N68" s="2" t="n">
-        <v>335</v>
+        <v>969</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T14:30:05.000Z</t>
+          <t>2023-12-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T15:33:53.455Z</t>
+          <t>2025-05-13T07:39:13.654Z</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/unity-6-tower-defens</t>
+          <t>https://www.inflearn.com/course/c개발자를-위한-최소한의-cpp</t>
         </is>
       </c>
     </row>
@@ -5695,12 +5693,12 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+          <t>RNN의 모든 것 | 트랜스포머 강의 TTT 무료 공개</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
@@ -5713,53 +5711,55 @@
         <v>0</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>1075</v>
+        <v>36</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N69" s="7" t="n"/>
+          <t>RNN, 딥러닝</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="n">
+        <v>61</v>
+      </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-27T04:00:06.000Z</t>
+          <t>2026-10-06T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30T07:01:04.312Z</t>
+          <t>2026-10-06T17:01:56.962Z</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+          <t>https://www.inflearn.com/course/everything-about-rnn</t>
         </is>
       </c>
     </row>
@@ -5769,73 +5769,73 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
+          <t>MLE부터 AE·VAE 입문까지 | 디퓨전 강의 TTD 무료 공개</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>멍슨상</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>36300</v>
+        <v>0</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>딥러닝 · 머신러닝</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, database</t>
+          <t>딥러닝</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1547</v>
+        <v>146</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2025-09-24T07:00:00.000Z</t>
+          <t>2026-10-06T23:30:06.000Z</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T05:08:47.602Z</t>
+          <t>2026-10-06T15:50:32.518Z</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
+          <t>https://www.inflearn.com/course/from-mle-to-an-intro</t>
         </is>
       </c>
     </row>
@@ -5845,31 +5845,31 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
+          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>55000</v>
+        <v>99000</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>86900</v>
+        <v>99000</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>0.3670886075949367</v>
+        <v>0</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>17</v>
+        <v>578</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
@@ -5878,40 +5878,40 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
+          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
         </is>
       </c>
       <c r="N71" s="7" t="n">
-        <v>541</v>
+        <v>924</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23T02:30:05.000Z</t>
+          <t>2025-10-03T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T15:07:55.641Z</t>
+          <t>2025-11-10T10:01:12.921Z</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
+          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
         </is>
       </c>
     </row>
@@ -5921,31 +5921,31 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>웹 개발자와 정보보안 입문자가 꼭 알아야 할 웹 해킹 &amp; 시큐어 코딩</t>
+          <t>한 입 크기로 잘라먹는 타입스크립트(TypeScript)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>크리핵티브</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>55000</v>
+        <v>48400</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>55000</v>
+        <v>48400</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>264</v>
+        <v>780</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2357</v>
+        <v>14560</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5954,40 +5954,40 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>프로그래밍 언어, 웹 개발, 프론트엔드</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>인젝션, 모의해킹</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>993</v>
+        <v>632</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2020-06-16T15:00:00.000Z</t>
+          <t>2023-05-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:44:01.802Z</t>
+          <t>2026-04-16T00:41:51.879Z</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/웹해킹-보안-시큐어코딩</t>
+          <t>https://www.inflearn.com/course/한입-크기-타입스크립트</t>
         </is>
       </c>
     </row>
@@ -5997,31 +5997,31 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>대세는 쿠버네티스 (초급~중급편)</t>
+          <t>실전에서 바로 써먹는 Kafka 입문</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>44000</v>
+        <v>88000</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>44000</v>
+        <v>88000</v>
       </c>
       <c r="F73" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>626</v>
+        <v>103</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>8487</v>
+        <v>781</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
@@ -6035,35 +6035,35 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>백엔드, 데브옵스 · 인프라, 클라우드</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
+          <t>Kafka, EDA, MSA, devops, infrastructure</t>
         </is>
       </c>
       <c r="N73" s="7" t="n">
-        <v>425</v>
+        <v>314</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>2019-09-10T15:00:00.000Z</t>
+          <t>2025-07-28T06:00:00.000Z</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T05:23:15.024Z</t>
+          <t>2026-08-30T11:26:37.287Z</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+          <t>https://www.inflearn.com/course/실전에서-바로-써먹는-kafka-입문</t>
         </is>
       </c>
     </row>
@@ -6073,31 +6073,31 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
+          <t>실리콘밸리 엔지니어가 가르치는 파이썬 기초부터 고급까지</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>최원영</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>0</v>
+        <v>90750</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1551</v>
+        <v>7798</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6106,40 +6106,40 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>프로그래밍 언어, 백엔드, 풀스택</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI)</t>
+          <t>Python, 알고리즘</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>32</v>
+        <v>818</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27T05:00:00.000Z</t>
+          <t>2022-12-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27T06:18:36.692Z</t>
+          <t>2026-10-07T05:39:05.304Z</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
+          <t>https://www.inflearn.com/course/실리콘밸리-파이썬-기초부터-고급까지</t>
         </is>
       </c>
     </row>
@@ -6149,31 +6149,31 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>RAG를 활용한 LLM Application 개발 (feat. LangChain)</t>
+          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>피엠인사이드</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>66000</v>
+        <v>330000</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>66000</v>
+        <v>330000</v>
       </c>
       <c r="F75" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>4983</v>
+        <v>15</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
@@ -6182,40 +6182,40 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 개발 · 프로그래밍 기타</t>
+          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>LLM, RAG, LangChain, vector-database, openAI API</t>
+          <t>프로젝트 관리, PMP</t>
         </is>
       </c>
       <c r="N75" s="7" t="n">
-        <v>217</v>
+        <v>2458</v>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>2024-06-27T15:00:00.000Z</t>
+          <t>2026-10-01T13:00:08.000Z</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2025-11-15T11:12:24.826Z</t>
+          <t>2026-10-11T13:00:23.847Z</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/rag-llm-application개발-langchain</t>
+          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
         </is>
       </c>
     </row>
@@ -6225,31 +6225,31 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>정보처리기사 자격증 대비 교육(실기)</t>
+          <t>코딩을 몰라도 만드는 AI 엑셀 매크로 실무 프로젝트</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>국립안동대학교 SW융합교육원</t>
+          <t>칼퇴자동화연구소</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2205</v>
+        <v>9</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6258,40 +6258,40 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>업무 생산성, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증</t>
+          <t>오피스, 업무 자동화, AI 실무 활용</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>정보처리기사</t>
+          <t>Excel, VBA, ChatGPT, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>1532</v>
+        <v>146</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2024-08-13T15:00:00.000Z</t>
+          <t>2026-09-27T16:30:04.000Z</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2024-08-14T00:00:00.000Z</t>
+          <t>2026-09-27T14:21:29.601Z</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
+          <t>https://www.inflearn.com/course/practical-ai-excel-m</t>
         </is>
       </c>
     </row>
@@ -6301,19 +6301,19 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>스프링 MVC 2편 - 백엔드 웹 개발 활용 기술</t>
+          <t>시스템 디자인 첫걸음: 면접에서 돋보이는 백엔드 아키텍처 설계하기</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>성장랜턴</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>121000</v>
+        <v>44000</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>121000</v>
+        <v>44000</v>
       </c>
       <c r="F77" s="10" t="n">
         <v>0</v>
@@ -6322,10 +6322,10 @@
         <v>5</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>1321</v>
+        <v>55</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>26183</v>
+        <v>743</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
@@ -6334,40 +6334,40 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>개발 · 프로그래밍 기타, 웹 개발, 백엔드, 취업 · 이직</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>MVC, Spring</t>
+          <t>아키텍처, backend, 소프트웨어 설계, 시스템 디자인, 면접</t>
         </is>
       </c>
       <c r="N77" s="7" t="n">
-        <v>1266</v>
+        <v>299</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>2021-06-23T15:00:00.000Z</t>
+          <t>2025-05-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09T13:51:44.094Z</t>
+          <t>2025-08-01T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-mvc-2</t>
+          <t>https://www.inflearn.com/course/시스템-디자인-첫걸음</t>
         </is>
       </c>
     </row>
@@ -6377,19 +6377,19 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>38군데 합격 비법, 2026 코딩테스트 필수 알고리즘</t>
+          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>딩코딩코</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>165000</v>
+        <v>77000</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>165000</v>
+        <v>77000</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>5</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>451</v>
+        <v>349</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2884</v>
+        <v>5458</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6410,40 +6410,40 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>알고리즘 · 자료구조, 취업 · 이직</t>
+          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Python, 코딩 테스트, 알고리즘, data-structure</t>
+          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>934</v>
+        <v>1001</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2024-11-12T15:00:00.000Z</t>
+          <t>2025-03-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T05:18:11.523Z</t>
+          <t>2025-09-14T05:27:02.800Z</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/38군데-합격비법-코테-필수-알고리즘</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
         </is>
       </c>
     </row>
@@ -6453,31 +6453,31 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Windows System 프로그래밍</t>
+          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>megayuchi</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>165000</v>
+        <v>44000</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>165000</v>
+        <v>44000</v>
       </c>
       <c r="F79" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>17</v>
+        <v>4070</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>121</v>
+        <v>37224</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
@@ -6491,35 +6491,35 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>데스크톱 앱 개발, 시스템 · 운영체제</t>
+          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>windows-programming, C++, microsoft-visual-c++, 운영체제, system-programming</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="N79" s="7" t="n">
-        <v>708</v>
+        <v>341</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>2025-02-04T15:00:00.000Z</t>
+          <t>2020-12-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13T00:22:55.653Z</t>
+          <t>2025-05-13T07:23:13.295Z</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/windows-system-programming</t>
+          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
         </is>
       </c>
     </row>
@@ -6529,19 +6529,19 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>구현하며 배우는 Transformer</t>
+          <t>김영한의 실전 자바 - 중급 1편</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>권 철민</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>77000</v>
+        <v>66000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>77000</v>
+        <v>66000</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>0</v>
@@ -6550,52 +6550,52 @@
         <v>5</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>26</v>
+        <v>1263</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>368</v>
+        <v>12539</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>자연어 처리, 딥러닝 · 머신러닝, 인공지능 기타</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, PyTorch, encoder-decoder, bert, transformer</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1690</v>
+        <v>1161</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2025-10-16T16:00:00.000Z</t>
+          <t>2024-03-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26T06:29:54.291Z</t>
+          <t>2025-11-28T10:04:41.236Z</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/구현하며-배우는-transformer</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
         </is>
       </c>
     </row>
@@ -6605,73 +6605,73 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>이득우의 언리얼 프로그래밍 Part1 - 언리얼 C++의 이해</t>
+          <t>한 입 크기로 잘라먹는 Next.js</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>이득우</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>132000</v>
+        <v>48400</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>132000</v>
+        <v>48400</v>
       </c>
       <c r="F81" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>388</v>
+        <v>638</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>2569</v>
+        <v>6026</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>게임 개발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>게임 프로그래밍</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>언리얼 C++, Unreal Engine</t>
+          <t>React, TypeScript, Next.js</t>
         </is>
       </c>
       <c r="N81" s="7" t="n">
-        <v>596</v>
+        <v>934</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>2023-04-12T15:00:00.000Z</t>
+          <t>2024-08-18T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:43:00.937Z</t>
+          <t>2026-07-13T03:56:34.520Z</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/이득우-언리얼-프로그래밍-part-1</t>
+          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
         </is>
       </c>
     </row>
@@ -6681,35 +6681,35 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>홍정모의 따라하며 배우는 C언어</t>
+          <t>토비의 클린 스프링 - 도메인 모델 패턴과 헥사고날 아키텍처 Part 2</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>홍정모</t>
+          <t>토비</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>154000</v>
+        <v>99000</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>154000</v>
+        <v>99000</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>457</v>
+        <v>34</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>6048</v>
+        <v>627</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6719,35 +6719,35 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>백엔드</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Java, Spring, Spring Boot, JPA, 리팩터링, DDD, hexagonal-architecture</t>
         </is>
       </c>
       <c r="N82" s="2" t="n">
-        <v>3066</v>
+        <v>779</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2019-12-01T15:00:00.000Z</t>
+          <t>2026-07-16T08:12:00.000Z</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2025-08-10T19:48:02.565Z</t>
+          <t>2026-07-16T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/following-c</t>
+          <t>https://www.inflearn.com/course/tobys-clean-spring-d</t>
         </is>
       </c>
     </row>
@@ -6757,19 +6757,19 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
+          <t>비전공자도 이해할 수 있는 MySQL 성능 최적화 입문/실전 (SQL 튜닝편)</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>154000</v>
+        <v>88000</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>154000</v>
+        <v>88000</v>
       </c>
       <c r="F83" s="10" t="n">
         <v>0</v>
@@ -6778,52 +6778,52 @@
         <v>5</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>2045</v>
+        <v>1354</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 풀스택</t>
+          <t>데이터베이스, 백엔드</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
+          <t>MySQL, DBMS/RDBMS, query-tuning, SQL</t>
         </is>
       </c>
       <c r="N83" s="7" t="n">
-        <v>1270</v>
+        <v>163</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00.000Z</t>
+          <t>2024-07-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28T00:00:00.000Z</t>
+          <t>2026-08-30T11:26:39.344Z</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
+          <t>https://www.inflearn.com/course/비전공자-mysql-성능최정확-sql튜닝</t>
         </is>
       </c>
     </row>
@@ -6833,19 +6833,19 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>LangGraph를 활용한 AI Agent 개발 (feat. MCP)</t>
+          <t>CAN 통신 - 자동차 신입이 알아야 할 모든 것</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>존버매니아</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>69300</v>
+        <v>77000</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>69300</v>
+        <v>77000</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0</v>
@@ -6854,52 +6854,52 @@
         <v>4.9</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2946</v>
+        <v>1864</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>하드웨어, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발</t>
+          <t>모빌리티, 임베디드 · IoT, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>프롬프트엔지니어링, LLM, AI Agent, LangGraph, MCP</t>
+          <t>CAN, uds</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>381</v>
+        <v>256</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2025-01-19T15:00:00.000Z</t>
+          <t>2022-09-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:57:36.230Z</t>
+          <t>2025-05-30T14:52:11.295Z</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/랭그래프-활용한-llm에이전트-개발</t>
+          <t>https://www.inflearn.com/course/자동차-신입-can통신</t>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Claude로 끝내는 실무 업무자동화: 엑셀·문서·PPT부터 Skills·Obsidian까지</t>
+          <t>Docker가 쉬워지는 운영체제 이야기</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>HappyAI</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
@@ -6927,55 +6927,55 @@
         <v>0</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>104</v>
+        <v>946</v>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>데브옵스 · 인프라, 시스템 · 운영체제, 클라우드</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>data-analysis, data-processing, n8n, 프롬프트엔지니어링, claude</t>
+          <t>네트워크, Linux, Docker, 운영체제, linux-containers, cloud-computing</t>
         </is>
       </c>
       <c r="N85" s="7" t="n">
-        <v>229</v>
+        <v>723</v>
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01T09:00:05.000Z</t>
+          <t>2026-07-30T04:00:57.000Z</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-19T02:33:41.290Z</t>
+          <t>2026-08-04T00:38:47.888Z</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-practical-2</t>
+          <t>https://www.inflearn.com/course/operating-system-sto</t>
         </is>
       </c>
     </row>
@@ -6985,73 +6985,73 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>스프링 MVC 1편 - 백엔드 웹 개발 핵심 기술</t>
+          <t>공업수학을 위한 중학, 고교수학</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>지식탐험단</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>99000</v>
+        <v>121000</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>99000</v>
+        <v>121000</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>2616</v>
+        <v>20</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>31291</v>
+        <v>479</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>대학 교육</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>수학</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>MVC, Spring</t>
+          <t>대수학, mathematics, functions, 행렬, vectors, factorization, equations</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>923</v>
+        <v>3131</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2021-03-06T15:00:00.000Z</t>
+          <t>2023-12-17T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T07:20:11.745Z</t>
+          <t>2025-07-02T04:39:15.776Z</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-mvc-1</t>
+          <t>https://www.inflearn.com/course/중등-고등-수학-공업수학</t>
         </is>
       </c>
     </row>
@@ -7061,19 +7061,19 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>20년 경력자의 알기 쉬운 컴퓨터네트워크</t>
+          <t>대규모 트래픽 처리를 위한 부하테스트 입문/실전</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>넷가이버</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>137500</v>
+        <v>77000</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>137500</v>
+        <v>77000</v>
       </c>
       <c r="F87" s="10" t="n">
         <v>0</v>
@@ -7082,52 +7082,52 @@
         <v>4.9</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>1229</v>
+        <v>1094</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>네트워크, 보안 · 네트워크 기타, 보안 · 네트워크 자격증</t>
+          <t>데브옵스 · 인프라, 백엔드</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, networking, router, switch</t>
+          <t>k6, infrastructure, performance-tuning, performance-test</t>
         </is>
       </c>
       <c r="N87" s="7" t="n">
-        <v>789</v>
+        <v>208</v>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>2021-03-15T15:00:00.000Z</t>
+          <t>2024-12-17T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12T17:19:53.582Z</t>
+          <t>2026-08-30T11:26:38.596Z</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/패킷트레이서-네트워크</t>
+          <t>https://www.inflearn.com/course/대규모트래픽-부하테스트-입문-실전</t>
         </is>
       </c>
     </row>
@@ -7137,31 +7137,31 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>CNN 기초 제대로 이해하기 | Legend 13 무료 공개</t>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>24</v>
+        <v>1446</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7170,40 +7170,40 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 컴퓨터 비전</t>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, CNN</t>
+          <t>업무 생산성, wiki, obsidian, claude</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>94</v>
+        <v>368</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T08:30:06.000Z</t>
+          <t>2026-04-25T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T16:57:34.184Z</t>
+          <t>2026-10-08T14:26:56.788Z</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/understanding-cnn-fu</t>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
         </is>
       </c>
     </row>
@@ -7213,19 +7213,19 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>[AI 리터러시 저자직강] 모든 직장인이 활용할 수 있는 올인원 AI 활용법(26년 6월 전체 리뉴얼)</t>
+          <t>회사에서 바로 쓰는 챗GPT 실전 가이드_2026</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>김용성</t>
+          <t>포레스트소프트</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>110000</v>
+        <v>55000</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>110000</v>
+        <v>55000</v>
       </c>
       <c r="F89" s="10" t="n">
         <v>0</v>
@@ -7234,10 +7234,10 @@
         <v>4.8</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>1096</v>
+        <v>133</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
@@ -7251,35 +7251,35 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
+          <t>AI 실무 활용, AI 시작하기, 오피스</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, 영상제작, 서비스 기획, 인공지능(AI)</t>
+          <t>gemini, 인공지능(AI), ChatGPT, Microsoft Copilot, AI Agent</t>
         </is>
       </c>
       <c r="N89" s="7" t="n">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>2025-09-09T09:30:00.000Z</t>
+          <t>2025-12-04T05:30:00.000Z</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07T08:14:11.781Z</t>
+          <t>2025-12-04T06:33:12.706Z</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-리터러시-저자직강-모든-직장인이</t>
+          <t>https://www.inflearn.com/course/회사에서-바로-쓰는-챗gpt-실전-가</t>
         </is>
       </c>
     </row>
@@ -7289,19 +7289,19 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>[취업폭격기] 공공기관 전산직 취업 치트키 : NCS·전공·PT면접까지 한 번에 뚫는 정규과정</t>
+          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>취업폭격기</t>
+          <t>그랩</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>77000</v>
+        <v>198000</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>77000</v>
+        <v>198000</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>0</v>
@@ -7310,52 +7310,52 @@
         <v>5</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>625</v>
+        <v>326</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>취업 · 이직, 커리어 · 자기계발 기타</t>
+          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>면접, 이력서, 기술면접</t>
+          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>1448</v>
+        <v>896</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2023-08-08T15:00:00.000Z</t>
+          <t>2026-07-23T04:50:00.000Z</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T12:40:18.174Z</t>
+          <t>2026-08-01T16:24:39.937Z</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/취업폭격기-전산직-취업준비</t>
+          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
         </is>
       </c>
     </row>
@@ -7365,19 +7365,19 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>단 60분! 파이썬 핵심 개념 초압축 강의 - 이론보다 이해 중심</t>
+          <t>홍정모의 따라하며 배우는 C++</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>딩코딩코</t>
+          <t>홍정모</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0</v>
+        <v>176000</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>0</v>
+        <v>176000</v>
       </c>
       <c r="F91" s="10" t="n">
         <v>0</v>
@@ -7386,52 +7386,52 @@
         <v>4.9</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>484</v>
+        <v>395</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>7087</v>
+        <v>7125</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 게임 개발</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
-        <v>64</v>
+        <v>2907</v>
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>2024-09-22T15:00:00.000Z</t>
+          <t>2018-09-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10T00:47:07.734Z</t>
+          <t>2025-08-10T19:46:59.750Z</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/파이썬-핵심개념-압축강의</t>
+          <t>https://www.inflearn.com/course/following-c-plus</t>
         </is>
       </c>
     </row>
@@ -7441,31 +7441,31 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
+          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>코드바나나</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>77000</v>
+        <v>148500</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>77000</v>
+        <v>148500</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>603</v>
+        <v>320</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>9774</v>
+        <v>3750</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7474,40 +7474,40 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>데브옵스 · 인프라, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향, thread, multithread, 동시성</t>
+          <t>AWS, 네트워크, AWS SAA</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>1249</v>
+        <v>1450</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2024-07-14T15:00:00.000Z</t>
+          <t>2022-06-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2025-11-18T01:46:58.908Z</t>
+          <t>2026-10-12T03:07:28.063Z</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
+          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
         </is>
       </c>
     </row>
@@ -7517,31 +7517,31 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>클로드코드-비개발자 위한 기초 업무 자동화 (카드뉴스, 상세페이지, 영상, 마케팅, Aside 연동 등) 사용법</t>
+          <t>기초부터 따라하는 디지털포렌식</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>강슬기</t>
+          <t>훈지손</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F93" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>519</v>
+        <v>6202</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
@@ -7550,40 +7550,40 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>콘텐츠 마케팅, claude, 바이브코딩, AX(에이전트 경험), 마케팅 자동화</t>
+          <t>Forensic</t>
         </is>
       </c>
       <c r="N93" s="7" t="n">
-        <v>191</v>
+        <v>545</v>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>2026-03-23T18:30:00.000Z</t>
+          <t>2022-02-22T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07T01:42:38.618Z</t>
+          <t>2022-05-31T11:24:15.993Z</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-basic-ta</t>
+          <t>https://www.inflearn.com/course/기초-디지털-포렌식</t>
         </is>
       </c>
     </row>
@@ -7593,31 +7593,31 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>피그마(Figma)를 활용한 UI디자인 입문부터 실전까지 A to Z</t>
+          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>에릭</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>82500</v>
+        <v>38500</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>82500</v>
+        <v>38500</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>517</v>
+        <v>2</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3675</v>
+        <v>59</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7626,40 +7626,40 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>디자인 · 아트</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>UX/UI, 그래픽 디자인</t>
+          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Figma, 웹 디자인, 모바일 디자인, 프로덕트디자인</t>
+          <t>SQL, Oracle, database, modeling, SQLD</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>545</v>
+        <v>923</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2020-11-04T15:00:00.000Z</t>
+          <t>2026-09-02T03:00:00.000Z</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04T11:22:20.563Z</t>
+          <t>2026-09-02T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/피그마-ui디자인</t>
+          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
         </is>
       </c>
     </row>
@@ -7669,73 +7669,73 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>코딩을 몰라도 만드는 AI 엑셀 매크로 실무 프로젝트</t>
+          <t>2,000++억건 데이터를 다루는 실리콘 밸리 AI 개발자의 PostgreSQL</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>칼퇴자동화연구소</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>14850</v>
+        <v>152900</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>49500</v>
+        <v>152900</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>8</v>
+        <v>590</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX)</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>오피스, 업무 자동화, AI 실무 활용</t>
+          <t>자연어 처리, 데이터베이스, 백엔드</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>Excel, VBA, ChatGPT, 인공지능(AI)</t>
+          <t>MySQL, PostgreSQL, Oracle, DBMS/RDBMS, database</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
-        <v>146</v>
+        <v>567</v>
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27T16:30:04.000Z</t>
+          <t>2026-05-03T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27T14:21:29.601Z</t>
+          <t>2026-05-08T00:41:41.637Z</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-ai-excel-m</t>
+          <t>https://www.inflearn.com/course/postgresql-from-a-si</t>
         </is>
       </c>
     </row>
@@ -7745,31 +7745,31 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>스프링 DB 1편 - 데이터 접근 핵심 원리</t>
+          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>77000</v>
+        <v>79200</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>77000</v>
+        <v>79200</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>1073</v>
+        <v>228</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20129</v>
+        <v>6753</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7778,40 +7778,40 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Spring, MVC, spring-jdbc</t>
+          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>605</v>
+        <v>357</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2022-04-11T15:00:00.000Z</t>
+          <t>2025-07-11T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:21:40.827Z</t>
+          <t>2025-11-10T22:31:31.977Z</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-db-1</t>
+          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
         </is>
       </c>
     </row>
@@ -7821,73 +7821,73 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>AI 에이전트 엔지니어링</t>
+          <t>카카오 면접관과 함께하는 워크플로우 기반의 대용량 트래픽 처리 기법</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>민혁</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0</v>
+        <v>79200</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>0</v>
+        <v>79200</v>
       </c>
       <c r="F97" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>2043</v>
+        <v>562</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>백엔드, 데이터베이스, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>Python, 인공지능(AI), RAG, AI Agent</t>
+          <t>Spring, Kotlin, MySQL, Kafka</t>
         </is>
       </c>
       <c r="N97" s="7" t="n">
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07T05:00:00.000Z</t>
+          <t>2025-09-07T07:30:00.000Z</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07T02:58:08.781Z</t>
+          <t>2025-09-07T02:26:23.175Z</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
+          <t>https://www.inflearn.com/course/카카오-개발자와-함께하는-워크플로우</t>
         </is>
       </c>
     </row>
@@ -7897,31 +7897,31 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 2편, I/O, 네트워크, 리플렉션</t>
+          <t>[리뉴얼] 처음하는 파이썬 데이터 분석 (쉽게! 전처리, pandas, 시각화 전과정 익히기) [데이터분석/과학 Part1]</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>잔재미코딩 DaveLee</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>77000</v>
+        <v>88000</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>77000</v>
+        <v>88000</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>7217</v>
+        <v>4449</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7930,40 +7930,40 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스, AI 기술</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>데이터 분석, 딥러닝 · 머신러닝, 데이터 엔지니어링</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Java, 네트워크, 객체지향</t>
+          <t>Python, Pandas, Plotly</t>
         </is>
       </c>
       <c r="N98" s="2" t="n">
-        <v>1296</v>
+        <v>747</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2024-10-06T15:00:00.000Z</t>
+          <t>2020-06-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2025-06-08T10:29:28.205Z</t>
+          <t>2026-09-18T09:16:03.413Z</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-2</t>
+          <t>https://www.inflearn.com/course/파이썬-데이터분석-전처리-판다스-시각화</t>
         </is>
       </c>
     </row>
@@ -7973,12 +7973,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>기초부터 따라하는 디지털포렌식</t>
+          <t>AI 에이전트 엔지니어링</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>훈지손</t>
+          <t>민혁</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
@@ -7991,55 +7991,55 @@
         <v>0</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>6197</v>
+        <v>2049</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>Forensic</t>
+          <t>Python, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
-        <v>545</v>
+        <v>322</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>2022-02-22T15:00:00.000Z</t>
+          <t>2026-04-07T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>2022-05-31T11:24:15.993Z</t>
+          <t>2026-04-07T02:58:08.781Z</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/기초-디지털-포렌식</t>
+          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
         </is>
       </c>
     </row>
@@ -8049,73 +8049,73 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 고급편</t>
+          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>121000</v>
+        <v>82500</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>121000</v>
+        <v>82500</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>879</v>
+        <v>788</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>21007</v>
+        <v>2908</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Spring, 디자인 패턴</t>
+          <t>Kubernetes, devops, argocd, container, helm</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>1004</v>
+        <v>669</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2021-10-26T15:00:00.000Z</t>
+          <t>2023-09-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21T11:02:33.060Z</t>
+          <t>2026-05-27T08:15:25.352Z</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-고급편</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
         </is>
       </c>
     </row>
@@ -8125,73 +8125,73 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>비개발자 직장인을 위한 Claude (Cowork + N8N + Claude Design)</t>
+          <t>기초 탄탄! 독하게 시작하는 Java - Part 2 : OOP와 JVM</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>딩코딩코</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>165000</v>
+        <v>66000</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>165000</v>
+        <v>66000</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>566</v>
+        <v>5976</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화</t>
+          <t>프로그래밍 언어, 백엔드</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>claude, 인공지능(AI), AI Agent, n8n</t>
+          <t>Java, 객체지향, jvm, data-structure</t>
         </is>
       </c>
       <c r="N101" s="7" t="n">
-        <v>694</v>
+        <v>1215</v>
       </c>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>2026-04-26T02:30:00.000Z</t>
+          <t>2024-11-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24T14:36:39.327Z</t>
+          <t>2025-07-09T04:47:07.588Z</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-for-non-devel</t>
+          <t>https://www.inflearn.com/course/독하게-시작하는-java-part2</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-11T14:49:30+09:00</t>
+          <t>2026-10-12T15:00:49+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -605,31 +605,31 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Claude Code 실전 업무 자동화 : 코드 없이 나만의 AI 에이전트 만들기</t>
+          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>일잘러 장피엠</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>84700</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2291</v>
+        <v>232</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -643,35 +643,35 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
+          <t>AI 실무 활용, 업무 자동화</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>claude, codex, MCP, No-code</t>
+          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T05:00:08.000Z</t>
+          <t>2026-10-04T09:30:05.000Z</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T01:55:19.117Z</t>
+          <t>2026-10-07T14:30:36.470Z</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-workflow-a</t>
+          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
         </is>
       </c>
     </row>
@@ -681,31 +681,31 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
+          <t>Claude Code 실전 업무 자동화 : 코드 없이 나만의 AI 에이전트 만들기</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>일잘러 장피엠</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>84700</v>
+        <v>0</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>193</v>
+        <v>2404</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -719,35 +719,35 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화</t>
+          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
+          <t>claude, codex, MCP, No-code</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T09:30:05.000Z</t>
+          <t>2026-10-01T05:00:08.000Z</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T14:30:36.470Z</t>
+          <t>2026-10-05T01:55:19.117Z</t>
         </is>
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
+          <t>https://www.inflearn.com/course/practical-workflow-a</t>
         </is>
       </c>
     </row>
@@ -757,73 +757,73 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
+          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>49500</v>
+        <v>43560</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>99000</v>
+        <v>108900</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>132</v>
+        <v>432</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라</t>
+          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Linux, AWS, bash, ubuntu, nginx</t>
+          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>730</v>
+        <v>321</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T07:00:10.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T04:00:41.911Z</t>
+          <t>2026-08-29T06:47:12.230Z</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
+          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
         </is>
       </c>
     </row>
@@ -833,73 +833,73 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
+          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>52470</v>
+        <v>49500</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>174900</v>
+        <v>99000</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>405</v>
+        <v>141</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
+          <t>데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
+          <t>Linux, AWS, bash, ubuntu, nginx</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>520</v>
+        <v>728</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-10-06T07:00:10.000Z</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26T10:28:07.736Z</t>
+          <t>2026-10-13T03:16:22.539Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-embeddings</t>
+          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
+          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>43560</v>
+        <v>52470</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>108900</v>
+        <v>174900</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -947,16 +947,16 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
+          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>321</v>
+        <v>520</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -965,17 +965,17 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29T06:47:12.230Z</t>
+          <t>2026-08-26T10:28:07.736Z</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
+          <t>https://www.inflearn.com/course/building-embeddings</t>
         </is>
       </c>
     </row>
@@ -985,73 +985,73 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
+          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>한조각</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>19800</v>
+        <v>198000</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>66000</v>
+        <v>198000</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2</v>
+        <v>1633</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>221</v>
+        <v>11274</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
+          <t>React, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>538</v>
+        <v>1254</v>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T20:30:05.000Z</t>
+          <t>2025-11-19T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T18:51:20.390Z</t>
+          <t>2026-08-18T03:54:49.011Z</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-service-deploym</t>
+          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
         </is>
       </c>
     </row>
@@ -1061,31 +1061,31 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
+          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>한조각</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>64900</v>
+        <v>19800</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>64900</v>
+        <v>66000</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>776</v>
+        <v>232</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1094,40 +1094,40 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, AI 기술</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
+          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
+          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1266</v>
+        <v>538</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T05:00:33.000Z</t>
+          <t>2026-09-29T20:30:05.000Z</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T02:47:16.149Z</t>
+          <t>2026-09-29T18:51:20.390Z</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-llm-servic</t>
+          <t>https://www.inflearn.com/course/from-service-deploym</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
+          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>198000</v>
+        <v>88000</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>198000</v>
+        <v>88000</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1630</v>
+        <v>729</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>11254</v>
+        <v>5710</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
@@ -1170,40 +1170,40 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>React, 인공지능(AI), claude</t>
+          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>1254</v>
+        <v>2108</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T09:00:00.000Z</t>
+          <t>2024-06-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18T03:54:49.011Z</t>
+          <t>2026-10-01T14:55:46.048Z</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
+          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
         </is>
       </c>
     </row>
@@ -1213,31 +1213,31 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
+          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>퇴근후딴짓</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>727</v>
+        <v>927</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5700</v>
+        <v>6010</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1246,40 +1246,40 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>데이터 사이언스 자격증, 데이터 분석</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
+          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2108</v>
+        <v>1560</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2024-06-13T15:00:00.000Z</t>
+          <t>2022-12-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T14:55:46.048Z</t>
+          <t>2026-10-06T00:43:26.587Z</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
+          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
         </is>
       </c>
     </row>
@@ -1289,73 +1289,73 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
+          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>퇴근후딴짓</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>121000</v>
+        <v>64900</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>121000</v>
+        <v>64900</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>927</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>6002</v>
+        <v>780</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 데이터 분석</t>
+          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
+          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>1560</v>
+        <v>1266</v>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>2022-12-12T15:00:00.000Z</t>
+          <t>2026-09-07T05:00:33.000Z</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T00:43:26.587Z</t>
+          <t>2026-10-02T02:47:16.149Z</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
+          <t>https://www.inflearn.com/course/practical-llm-servic</t>
         </is>
       </c>
     </row>
@@ -1386,10 +1386,10 @@
         <v>4.9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13325</v>
+        <v>13376</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -1441,73 +1441,73 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>440000</v>
+        <v>89100</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>440000</v>
+        <v>89100</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>44</v>
+        <v>1731</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
+          <t>security, CPPG(개인정보관리사)</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>1240</v>
+        <v>727</v>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T15:00:07.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T03:23:49.530Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -1517,73 +1517,73 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
+          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>198000</v>
+        <v>37950</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>198000</v>
+        <v>75900</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>301</v>
+        <v>211</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
+          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>api, trading, codex, 바이브코딩</t>
+          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T01:30:06.000Z</t>
+          <t>2026-09-28T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T08:59:09.803Z</t>
+          <t>2026-09-29T01:52:33.960Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/create-an-automated</t>
+          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
         </is>
       </c>
     </row>
@@ -1593,31 +1593,31 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>Hiro Son</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>4623</v>
+        <v>15</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
@@ -1626,38 +1626,40 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n"/>
+          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27T10:00:00.000Z</t>
+          <t>2026-10-07T17:30:06.000Z</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30T00:59:39.967Z</t>
+          <t>2026-10-10T00:53:13.219Z</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
         </is>
       </c>
     </row>
@@ -1667,73 +1669,71 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>266</v>
+        <v>414</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1357</v>
+        <v>4634</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>309</v>
-      </c>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2026-01-27T10:00:00.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:44.702Z</t>
+          <t>2026-06-30T00:59:39.967Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
         </is>
       </c>
     </row>
@@ -1743,19 +1743,19 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>89100</v>
+        <v>198000</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>89100</v>
+        <v>198000</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0</v>
@@ -1764,10 +1764,10 @@
         <v>4.9</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>236</v>
+        <v>50</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1728</v>
+        <v>303</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
@@ -1776,40 +1776,40 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
+          <t>api, trading, codex, 바이브코딩</t>
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>727</v>
+        <v>628</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2026-09-09T01:30:06.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2026-10-11T08:59:09.803Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/create-an-automated</t>
         </is>
       </c>
     </row>
@@ -1819,22 +1819,22 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
+          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>37950</v>
+        <v>69300</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>75900</v>
+        <v>99000</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>203</v>
+        <v>47</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1852,40 +1852,40 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
+          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
+          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>641</v>
+        <v>73</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:30:06.000Z</t>
+          <t>2026-10-08T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T01:52:33.960Z</t>
+          <t>2026-10-11T17:09:46.044Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
+          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
         </is>
       </c>
     </row>
@@ -1895,31 +1895,31 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
+          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법)</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Hiro Son</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
         <v>49500</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>198000</v>
+        <v>99000</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
@@ -1928,40 +1928,40 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
+          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T17:30:06.000Z</t>
+          <t>2026-09-16T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T00:53:13.219Z</t>
+          <t>2026-09-30T03:16:06.187Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
+          <t>https://www.inflearn.com/course/ai-automated-trading</t>
         </is>
       </c>
     </row>
@@ -1971,31 +1971,31 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>69300</v>
+        <v>88000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>42</v>
+        <v>1360</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -2004,40 +2004,40 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>73</v>
+        <v>309</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T11:00:10.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T17:09:46.044Z</t>
+          <t>2026-08-30T11:28:44.702Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -2047,19 +2047,19 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
+          <t>김영한의 실전 자바 - 기본편</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>nstyxn</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>118800</v>
+        <v>44000</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>118800</v>
+        <v>44000</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>0</v>
@@ -2068,52 +2068,52 @@
         <v>5</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>86</v>
+        <v>2402</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>958</v>
+        <v>28220</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>보안, 보안 · 네트워크 자격증</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Forensic, 디지털포렌식전문가 2급</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>6530</v>
+        <v>1012</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2022-11-13T15:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15T02:00:30.898Z</t>
+          <t>2025-12-23T06:52:23.926Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
         </is>
       </c>
     </row>
@@ -2123,19 +2123,19 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 기본편</t>
+          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>마일드코드</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>44000</v>
+        <v>239800</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>44000</v>
+        <v>239800</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
@@ -2144,52 +2144,52 @@
         <v>5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2399</v>
+        <v>3</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28216</v>
+        <v>51</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1012</v>
+        <v>475</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-09-21T09:00:33.000Z</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23T06:52:23.926Z</t>
+          <t>2026-10-12T23:33:09.769Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+          <t>https://www.inflearn.com/course/claude-code-for-non</t>
         </is>
       </c>
     </row>
@@ -2199,73 +2199,73 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
+          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>시드니개발자의 영어PT</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>220000</v>
+        <v>440000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>220000</v>
+        <v>440000</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>2199</v>
+        <v>49</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>외국어</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>49</v>
+        <v>1240</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2023-01-12T15:00:00.000Z</t>
+          <t>2026-10-04T15:00:07.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T05:15:40.989Z</t>
+          <t>2026-10-05T03:23:49.530Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
+          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
         </is>
       </c>
     </row>
@@ -2275,73 +2275,73 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법)</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>49500</v>
+        <v>198000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>99000</v>
+        <v>198000</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>4</v>
+        <v>172</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>78</v>
+        <v>1610</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>363</v>
+        <v>1650</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2026-09-22T06:48:11.122Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -2351,31 +2351,31 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>초당 1,000,000++ RPS를 처리하는 네이버 개발자의 Valkey</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>56760</v>
+        <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>141900</v>
+        <v>0</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>6</v>
+        <v>307</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>143</v>
+        <v>3956</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
@@ -2384,40 +2384,40 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 알고리즘 · 자료구조, 데이터베이스</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, 빅데이터, TypeScript, DBMS/RDBMS, Redis, MSA, 데이터 엔지니어링</t>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>422</v>
+        <v>90</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29T21:47:01.350Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/valkey-vs-redis-a-na</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -2427,31 +2427,31 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
+          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>99000</v>
+        <v>440000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>99000</v>
+        <v>484000</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1098</v>
+        <v>18</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2460,40 +2460,40 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
+          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>516</v>
+        <v>204</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12T00:00:00.000Z</t>
+          <t>2026-10-04T05:30:05.000Z</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T01:35:54.874Z</t>
+          <t>2026-10-11T15:08:50.737Z</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
+          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
         </is>
       </c>
     </row>
@@ -2503,31 +2503,31 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>306</v>
+        <v>140</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>3935</v>
+        <v>902</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
@@ -2536,40 +2536,40 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>90</v>
+        <v>657</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2026-07-20T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2026-10-11T06:39:46.390Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/codex-true-education</t>
         </is>
       </c>
     </row>
@@ -2579,19 +2579,19 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
+          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>제어쟁이</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>550000</v>
+        <v>44000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>550000</v>
+        <v>44000</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0</v>
@@ -2600,52 +2600,52 @@
         <v>4.9</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>83</v>
+        <v>616</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>603</v>
+        <v>8411</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 모빌리티</t>
+          <t>개발 도구</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>임베디드, stm32, hardware, motordriver, artwork</t>
+          <t>Git, GitHub, github-actions, git-commands</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1017</v>
+        <v>353</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2025-06-15T15:00:00.000Z</t>
+          <t>2022-01-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T09:06:49.556Z</t>
+          <t>2026-06-03T09:18:28.574Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
+          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
         </is>
       </c>
     </row>
@@ -2655,73 +2655,73 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>nstyxn</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>198000</v>
+        <v>118800</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>198000</v>
+        <v>118800</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>171</v>
+        <v>87</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1604</v>
+        <v>958</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>보안, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>Forensic, 디지털포렌식전문가 2급</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>1650</v>
+        <v>6530</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2022-11-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T06:48:11.122Z</t>
+          <t>2026-07-15T02:00:30.898Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
         </is>
       </c>
     </row>
@@ -2731,73 +2731,73 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>440000</v>
+        <v>55000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>484000</v>
+        <v>55000</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16</v>
+        <v>651</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T05:30:05.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:50.737Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
+          <t>김영한의 실전 자바 - 중급 1편</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0</v>
@@ -2828,52 +2828,52 @@
         <v>5</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>747</v>
+        <v>1263</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>11799</v>
+        <v>12542</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>517</v>
+        <v>1161</v>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2024-03-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2025-08-31T09:28:51.006Z</t>
+          <t>2025-11-28T10:04:41.236Z</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
         </is>
       </c>
     </row>
@@ -2883,31 +2883,31 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
+          <t>홍정모의 따라하며 배우는 C++</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>홍정모</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>49500</v>
+        <v>176000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>99000</v>
+        <v>176000</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>21</v>
+        <v>7125</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2916,40 +2916,40 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 게임 개발</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>370</v>
+        <v>2907</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T10:00:08.000Z</t>
+          <t>2018-09-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T07:55:47.247Z</t>
+          <t>2025-08-10T19:46:59.750Z</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-latest</t>
+          <t>https://www.inflearn.com/course/following-c-plus</t>
         </is>
       </c>
     </row>
@@ -2959,73 +2959,73 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
+          <t>Decision AI로 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>330000</v>
+        <v>22000</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>330000</v>
+        <v>22000</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>527</v>
+        <v>18</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>1048</v>
+        <v>109</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22T17:00:00.000Z</t>
+          <t>2026-10-06T05:00:08.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T22:53:04.634Z</t>
+          <t>2026-10-12T19:46:29.290Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
+          <t>https://www.inflearn.com/course/practical-decision-a</t>
         </is>
       </c>
     </row>
@@ -3035,19 +3035,19 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>회로설계 멘토 삼코치</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>55000</v>
+        <v>269500</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>55000</v>
+        <v>269500</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>0</v>
@@ -3056,52 +3056,52 @@
         <v>5</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>645</v>
+        <v>697</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>임베디드 · IoT, 반도체</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>196</v>
+        <v>918</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2025-03-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2026-09-11T13:20:57.892Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
         </is>
       </c>
     </row>
@@ -3111,73 +3111,73 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>나도코딩</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>1930</v>
+        <v>194</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>40184</v>
+        <v>1450</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>업무 생산성, wiki, obsidian, claude</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>2020-02-24T15:00:00.000Z</t>
+          <t>2026-04-25T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T06:34:34.311Z</t>
+          <t>2026-10-08T14:26:56.788Z</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3208,52 +3208,52 @@
         <v>5</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>8116</v>
+        <v>747</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>123242</v>
+        <v>11814</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, MVC, Spring Boot</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>321</v>
+        <v>517</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2020-07-19T15:00:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T11:34:33.353Z</t>
+          <t>2025-08-31T09:28:51.006Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
         </is>
       </c>
     </row>
@@ -3263,73 +3263,73 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>YoungJea Oh</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>21155</v>
+        <v>26</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>823</v>
+        <v>370</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2023-03-02T15:00:00.000Z</t>
+          <t>2026-10-02T10:00:08.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:43:24.787Z</t>
+          <t>2026-10-02T07:55:47.247Z</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+          <t>https://www.inflearn.com/course/mastering-the-latest</t>
         </is>
       </c>
     </row>
@@ -3339,19 +3339,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>클로드로 딸깍! 루프 엔지니어링으로 통합 자산관리 시스템 개발하기</t>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>나도코딩</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>154000</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>154000</v>
+        <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>0</v>
@@ -3360,52 +3360,52 @@
         <v>4.9</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10</v>
+        <v>1930</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>422</v>
+        <v>40201</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 코딩, 풀스택</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), 바이브코딩, AX(에이전트 경험), AI Agent, minio</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>795</v>
+        <v>358</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T05:00:00.000Z</t>
+          <t>2020-02-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05T22:46:00.597Z</t>
+          <t>2025-04-29T06:34:34.311Z</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/one-click-with-claud</t>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
         </is>
       </c>
     </row>
@@ -3415,35 +3415,35 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 프론트엔드 개념 ②</t>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>인프런</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>46200</v>
+        <v>33000</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>77000</v>
+        <v>33000</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0</v>
+        <v>1399</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>3</v>
+        <v>34387</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
@@ -3453,35 +3453,35 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, AI 코딩</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>React, Next.js, Nuxt.js, frontend, playwright, web-accessibility, 인공지능(AI)</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>509</v>
+        <v>857</v>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T13:00:07.000Z</t>
+          <t>2019-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T11:20:50.801Z</t>
+          <t>2026-09-18T05:48:10.725Z</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-frontend-c</t>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
         </is>
       </c>
     </row>
@@ -3491,73 +3491,73 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
+          <t>AI를 위한 미적분 — 도함수, 그래디언트, 그리고 신경망이 학습하는 원리</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>마일드코드</t>
+          <t>코딩맥스 CodingMax</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>239800</v>
+        <v>99000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>239800</v>
+        <v>99000</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
+          <t>AI 기술, 대학 교육</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
+          <t>딥러닝 · 머신러닝, 수학</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
+          <t>머신러닝, 딥러닝, 인공신경망, 선형대수학, 미적분, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>455</v>
+        <v>1093</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:00:33.000Z</t>
+          <t>2026-09-13T08:00:08.000Z</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T00:30:58.863Z</t>
+          <t>2026-09-13T05:41:38.564Z</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-for-non</t>
+          <t>https://www.inflearn.com/course/calculus-for-ai-deri</t>
         </is>
       </c>
     </row>
@@ -3567,73 +3567,73 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
+          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>44330</v>
+        <v>220000</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>68200</v>
+        <v>220000</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>4</v>
+        <v>2199</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>외국어</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>410</v>
+        <v>49</v>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2023-01-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T12:02:44.178Z</t>
+          <t>2026-10-02T05:15:40.989Z</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/database-concepts-yo</t>
+          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
         </is>
       </c>
     </row>
@@ -3643,73 +3643,73 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>44330</v>
+        <v>550000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>68200</v>
+        <v>550000</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
+        <v>603</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>임베디드 · IoT, 모빌리티</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>410</v>
+        <v>1017</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2025-06-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T11:44:45.232Z</t>
+          <t>2026-09-13T09:06:49.556Z</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-database-c</t>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
         </is>
       </c>
     </row>
@@ -3719,73 +3719,73 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
+          <t>노베이스를 위한 ADsP 생존 가이드</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>86900</v>
+        <v>0</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>0.3670886075949367</v>
+        <v>0</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>19</v>
+        <v>757</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
+          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
+          <t>SQL, R, ADsP</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>541</v>
+        <v>303</v>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23T02:30:05.000Z</t>
+          <t>2025-11-11T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T15:07:55.641Z</t>
+          <t>2025-11-11T09:14:53.120Z</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
+          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
         </is>
       </c>
     </row>
@@ -3795,31 +3795,31 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>AI 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
+          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>19800</v>
+        <v>99000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>33000</v>
+        <v>99000</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14</v>
+        <v>578</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3828,40 +3828,40 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
+          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>109</v>
+        <v>924</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T05:00:08.000Z</t>
+          <t>2025-10-03T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T21:14:06.144Z</t>
+          <t>2025-11-10T10:01:12.921Z</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-decision-a</t>
+          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
         </is>
       </c>
     </row>
@@ -3871,31 +3871,31 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
+          <t>김영한의 실전 자바 - 중급 2편</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>33000</v>
+        <v>66000</v>
       </c>
       <c r="E45" s="9" t="n">
         <v>66000</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>4</v>
+        <v>880</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>264</v>
+        <v>11023</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
@@ -3904,40 +3904,40 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>Python, LLM, AI Agent, claude</t>
+          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>305</v>
+        <v>1165</v>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23T06:30:05.000Z</t>
+          <t>2024-05-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26T17:31:06.856Z</t>
+          <t>2025-11-24T10:17:13.631Z</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
         </is>
       </c>
     </row>
@@ -3947,31 +3947,31 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 2편</t>
+          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>숀김</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>66000</v>
+        <v>55000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>66000</v>
+        <v>86900</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0</v>
+        <v>0.3670886075949367</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11020</v>
+        <v>20</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3985,35 +3985,35 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1165</v>
+        <v>541</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2024-05-07T15:00:00.000Z</t>
+          <t>2026-09-23T02:30:05.000Z</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2025-11-24T10:17:13.631Z</t>
+          <t>2026-09-29T15:07:55.641Z</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
         </is>
       </c>
     </row>
@@ -4023,73 +4023,73 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="F47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>186</v>
+        <v>1557</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>6160</v>
+        <v>15624</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, routing</t>
+          <t>JavaScript, React, Node.js</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>779</v>
+        <v>1114</v>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2022-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:27:31.006Z</t>
+          <t>2026-06-13T00:57:34.805Z</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
         </is>
       </c>
     </row>
@@ -4099,31 +4099,31 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>(AI 퀀트) 코드 한 줄 안 쓰고 주식 자동 분석 시스템 만들기 feat. Claude CLI</t>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>호두감자</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>140250</v>
+        <v>0</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>187000</v>
+        <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>63</v>
+        <v>8117</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>442</v>
+        <v>123250</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4132,40 +4132,40 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Python, Flask, Next.js, 인공지능(AI)</t>
+          <t>Java, Spring, MVC, Spring Boot</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>458</v>
+        <v>321</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17T20:00:00.000Z</t>
+          <t>2020-07-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12T14:59:08.440Z</t>
+          <t>2026-01-30T11:34:33.353Z</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/코드-한-줄-안-쓰고-주식-자동-분석</t>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
         </is>
       </c>
     </row>
@@ -4175,35 +4175,35 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="F49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>1557</v>
+        <v>3140</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>15618</v>
+        <v>57297</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
@@ -4213,35 +4213,35 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>1114</v>
+        <v>771</v>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>2022-01-26T15:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13T00:57:34.805Z</t>
+          <t>2026-01-28T11:59:57.298Z</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-리액트</t>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
         </is>
       </c>
     </row>
@@ -4251,19 +4251,19 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>시스코 CCNA 함께 공부해요</t>
+          <t>대세는 쿠버네티스 (초급~중급편)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>ccie_pe_kim</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0</v>
@@ -4272,10 +4272,10 @@
         <v>4.9</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>56</v>
+        <v>626</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1741</v>
+        <v>8493</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4284,40 +4284,40 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, routing, tcpip</t>
+          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1213</v>
+        <v>425</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T15:00:00.000Z</t>
+          <t>2019-09-10T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25T09:44:13.272Z</t>
+          <t>2025-11-19T05:23:15.024Z</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+          <t>정보처리기사 자격증 대비 교육(실기)</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>국립안동대학교 SW융합교육원</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
@@ -4345,17 +4345,17 @@
         <v>0</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>3137</v>
+        <v>55</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>57283</v>
+        <v>2227</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
@@ -4365,35 +4365,35 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>정보처리기사</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>771</v>
+        <v>1532</v>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2024-08-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28T11:59:57.298Z</t>
+          <t>2024-08-14T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
         </is>
       </c>
     </row>
@@ -4403,31 +4403,31 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>토비의 스프링 6 - 이해와 원리</t>
+          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>토비</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>121000</v>
+        <v>79200</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>121000</v>
+        <v>79200</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3540</v>
+        <v>6756</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4436,40 +4436,40 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>백엔드</t>
+          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring</t>
+          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>747</v>
+        <v>357</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2024-06-23T15:00:00.000Z</t>
+          <t>2025-07-11T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:27:36.161Z</t>
+          <t>2025-11-10T22:31:31.977Z</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/토비의-스프링6-이해와-원리</t>
+          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
         </is>
       </c>
     </row>
@@ -4479,31 +4479,31 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
+          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>74250</v>
+        <v>0</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>4.9</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>137</v>
+        <v>460</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>898</v>
+        <v>21158</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
@@ -4512,40 +4512,40 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
+          <t>컴퓨터 구조, 운영체제, 기술면접</t>
         </is>
       </c>
       <c r="N53" s="7" t="n">
-        <v>657</v>
+        <v>823</v>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20T05:00:00.000Z</t>
+          <t>2023-03-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T06:39:46.390Z</t>
+          <t>2025-04-29T09:43:24.787Z</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/codex-true-education</t>
+          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
         </is>
       </c>
     </row>
@@ -4555,71 +4555,73 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+          <t>한 입 크기로 잘라먹는 Next.js</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>97</v>
+        <v>638</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1084</v>
+        <v>6027</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="n"/>
+          <t>React, TypeScript, Next.js</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>934</v>
+      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T04:00:06.000Z</t>
+          <t>2024-08-18T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T07:01:04.312Z</t>
+          <t>2026-07-13T03:56:34.520Z</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
         </is>
       </c>
     </row>
@@ -4629,73 +4631,73 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>데이터 드리븐 그로스 마케팅 - 고객 중심의 문제 해결력 업그레이드</t>
+          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>서현직</t>
+          <t>알고런 데이터코드 연구소</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>132000</v>
+        <v>79200</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>132000</v>
+        <v>79200</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>512</v>
+        <v>586</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>마케팅, 기획 · PM· PO</t>
+          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>그로스해킹, 마케팅 이론, 퍼포먼스 마케팅, 디지털 마케팅</t>
+          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
         </is>
       </c>
       <c r="N55" s="7" t="n">
-        <v>618</v>
+        <v>785</v>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>2024-03-06T15:00:00.000Z</t>
+          <t>2025-04-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21T11:50:42.713Z</t>
+          <t>2026-07-02T07:40:07.999Z</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/그로스-마케팅-101</t>
+          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
         </is>
       </c>
     </row>
@@ -4705,35 +4707,35 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>33000</v>
+        <v>44330</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>44000</v>
+        <v>68200</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>8406</v>
+        <v>5</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4743,35 +4745,35 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2026-10-10T12:02:44.178Z</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/database-concepts-yo</t>
         </is>
       </c>
     </row>
@@ -4781,31 +4783,31 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>독하게 시작하는 C 프로그래밍</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>99000</v>
+        <v>44330</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>99000</v>
+        <v>68200</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>3144</v>
+        <v>4</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
@@ -4814,40 +4816,40 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 시스템 · 운영체제</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>C, 컴퓨터 구조, assembly-language, vc++</t>
+          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
         </is>
       </c>
       <c r="N57" s="7" t="n">
-        <v>1739</v>
+        <v>410</v>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>2023-09-26T15:00:00.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:29:20.937Z</t>
+          <t>2026-10-10T11:44:45.232Z</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/독하게-시작하는-c프로그래밍</t>
+          <t>https://www.inflearn.com/course/essential-database-c</t>
         </is>
       </c>
     </row>
@@ -4857,31 +4859,31 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>[백문이불여일타] 데이터 분석을 위한 기초 SQL</t>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>데이터리안</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>16500</v>
+        <v>99000</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>16500</v>
+        <v>99000</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1283</v>
+        <v>151</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>6475</v>
+        <v>1099</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4890,40 +4892,40 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터베이스</t>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL</t>
+          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>86</v>
+        <v>516</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2020-01-26T15:00:00.000Z</t>
+          <t>2026-05-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2025-11-27T07:28:10.999Z</t>
+          <t>2026-09-21T01:35:54.874Z</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/백문이불여일타-데이터-분석-기초-sql</t>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
         </is>
       </c>
     </row>
@@ -4933,31 +4935,31 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>정보처리기사 자격증 대비 교육(실기)</t>
+          <t>클로드로 딸깍! 루프 엔지니어링으로 통합 자산관리 시스템 개발하기</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>국립안동대학교 SW융합교육원</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>2217</v>
+        <v>423</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
@@ -4966,40 +4968,40 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증</t>
+          <t>AI 실무 활용, AI 코딩, 풀스택</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>정보처리기사</t>
+          <t>인공지능(AI), 바이브코딩, AX(에이전트 경험), AI Agent, minio</t>
         </is>
       </c>
       <c r="N59" s="7" t="n">
-        <v>1532</v>
+        <v>795</v>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>2024-08-13T15:00:00.000Z</t>
+          <t>2026-06-23T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>2024-08-14T00:00:00.000Z</t>
+          <t>2026-07-05T22:46:00.597Z</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
+          <t>https://www.inflearn.com/course/one-click-with-claud</t>
         </is>
       </c>
     </row>
@@ -5009,31 +5011,31 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 기본편</t>
+          <t>시스코 CCNA 함께 공부해요</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>ccie_pe_kim</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>4932</v>
+        <v>58</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>50475</v>
+        <v>1751</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5042,40 +5044,40 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Spring, 객체지향</t>
+          <t>네트워크, CCNA, routing, tcpip</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>725</v>
+        <v>1213</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2020-09-20T15:00:00.000Z</t>
+          <t>2026-01-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04T15:00:00.555Z</t>
+          <t>2026-03-25T09:44:13.272Z</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
         </is>
       </c>
     </row>
@@ -5085,31 +5087,31 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>[백문이불여일타] 데이터 분석을 위한 중급 SQL</t>
+          <t>면접 전에 알고 가면 좋을 것들 - 신입 Java 백엔드 개발자편</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>데이터리안</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>38500</v>
+        <v>66000</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>38500</v>
+        <v>66000</v>
       </c>
       <c r="F61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>996</v>
+        <v>69</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>5698</v>
+        <v>1627</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
@@ -5118,40 +5120,40 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터베이스</t>
+          <t>취업 · 이직, 웹 개발, 백엔드, 풀스택</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>기술면접, 이력서, DBMS/RDBMS, tcpip</t>
         </is>
       </c>
       <c r="N61" s="7" t="n">
-        <v>140</v>
+        <v>306</v>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>2020-02-02T15:00:00.000Z</t>
+          <t>2023-08-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>2025-11-27T07:45:36.152Z</t>
+          <t>2025-05-13T07:42:51.608Z</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/데이터-분석-중급-sql</t>
+          <t>https://www.inflearn.com/course/면접-신입-java-백앤드-개발자</t>
         </is>
       </c>
     </row>
@@ -5161,73 +5163,73 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>자바 개발자를 위한 코틀린 입문(Java to Kotlin Starter Guide)</t>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>최태현</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>356</v>
+        <v>187</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3921</v>
+        <v>6165</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Kotlin, Java, 객체지향</t>
+          <t>네트워크, tcpip, routing</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
-        <v>313</v>
+        <v>779</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2022-05-12T15:00:00.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:39:53.983Z</t>
+          <t>2025-04-29T09:27:31.006Z</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/java-to-kotlin</t>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
         </is>
       </c>
     </row>
@@ -5237,73 +5239,73 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>GPT는 어떻게 문장을 생성할까? | LLM·ViT 강의 ATT 무료 공개</t>
+          <t>Claude로 끝내는 실무 업무자동화: 엑셀·문서·PPT부터 Skills·Obsidian까지</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>HappyAI</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>gpt, 딥러닝</t>
+          <t>data-analysis, data-processing, n8n, 프롬프트엔지니어링, claude</t>
         </is>
       </c>
       <c r="N63" s="7" t="n">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T09:00:09.000Z</t>
+          <t>2026-08-01T09:00:05.000Z</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T17:04:49.947Z</t>
+          <t>2026-10-12T00:06:16.136Z</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-does-gpt-generat</t>
+          <t>https://www.inflearn.com/course/mastering-practical-2</t>
         </is>
       </c>
     </row>
@@ -5313,19 +5315,19 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>노베이스를 위한 ADsP 생존 가이드</t>
+          <t>스프링 핵심 원리 - 기본편</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>0</v>
@@ -5334,52 +5336,52 @@
         <v>5</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>22</v>
+        <v>4932</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>748</v>
+        <v>50478</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SQL, R, ADsP</t>
+          <t>Spring, 객체지향</t>
         </is>
       </c>
       <c r="N64" s="2" t="n">
-        <v>303</v>
+        <v>725</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11T11:00:00.000Z</t>
+          <t>2020-09-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11T09:14:53.120Z</t>
+          <t>2025-06-04T15:00:00.555Z</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
         </is>
       </c>
     </row>
@@ -5389,19 +5391,19 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>대세는 쿠버네티스 (초급~중급편)</t>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="F65" s="10" t="n">
         <v>0</v>
@@ -5410,52 +5412,50 @@
         <v>4.9</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>626</v>
+        <v>97</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>8492</v>
+        <v>1089</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="n">
-        <v>425</v>
-      </c>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="n"/>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>2019-09-10T15:00:00.000Z</t>
+          <t>2026-06-27T04:00:06.000Z</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T05:23:15.024Z</t>
+          <t>2026-06-30T07:01:04.312Z</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
         </is>
       </c>
     </row>
@@ -5465,31 +5465,31 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>[유니티6] 타워 디펜스 리팩토링과 확장 - 신규 타워 4종과 맵 제작 자동화</t>
+          <t>MFC Windows 프로그래밍 - 기본</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>고박사</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>39600</v>
+        <v>99000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>39600</v>
+        <v>99000</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20</v>
+        <v>565</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5498,40 +5498,40 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>게임 개발, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 게임 개발</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>게임 프로그래밍, 프로그래밍 언어, 게임 개발 기타</t>
+          <t>데스크톱 앱 개발, 개발 도구, 프로그래밍 언어, 게임 개발 기타</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>C#, Unity, scriptable-object, unity2d, 유니티6</t>
+          <t>mfc, vc++, C++, win32api, sdi, gdi</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>335</v>
+        <v>997</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T14:30:05.000Z</t>
+          <t>2024-02-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T15:33:53.455Z</t>
+          <t>2025-05-13T07:41:58.198Z</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/unity-6-tower-defens</t>
+          <t>https://www.inflearn.com/course/mfc-programming-basic</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>맥킨지 출신 김재성의 AI로 앞서가는 문제 해결력 &amp; 리서치 전략</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Jaesung Kim</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
@@ -5559,55 +5559,55 @@
         <v>0</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>391</v>
+        <v>532</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅, AI 활용(AX), 커리어 · 자기계발</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>경영 · 전략, AI 실무 활용, 취업 · 이직</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>경영노하우, 인공지능(AI), ChatGPT, 컨설팅, 문제해결능력</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N67" s="7" t="n">
-        <v>508</v>
+        <v>1048</v>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>2025-09-22T06:18:00.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05T05:45:09.557Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/맥킨지-출신-김재성의-ai로-앞서가는</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -5617,31 +5617,31 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>C개발자를 위한 최소한의 C++</t>
+          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>99000</v>
+        <v>33000</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1126</v>
+        <v>265</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5650,40 +5650,40 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>C++, 객체지향, Microsoft Windows, 디자인 패턴</t>
+          <t>Python, LLM, AI Agent, claude</t>
         </is>
       </c>
       <c r="N68" s="2" t="n">
-        <v>969</v>
+        <v>305</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2023-12-21T15:00:00.000Z</t>
+          <t>2026-09-23T06:30:05.000Z</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:39:13.654Z</t>
+          <t>2026-09-26T17:31:06.856Z</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/c개발자를-위한-최소한의-cpp</t>
+          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
         </is>
       </c>
     </row>
@@ -5693,31 +5693,31 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>RNN의 모든 것 | 트랜스포머 강의 TTT 무료 공개</t>
+          <t>독하게 시작하는 C 프로그래밍</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>36</v>
+        <v>3144</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
@@ -5726,40 +5726,40 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>프로그래밍 언어, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>RNN, 딥러닝</t>
+          <t>C, 컴퓨터 구조, assembly-language, vc++</t>
         </is>
       </c>
       <c r="N69" s="7" t="n">
-        <v>61</v>
+        <v>1739</v>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T11:00:10.000Z</t>
+          <t>2023-09-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T17:01:56.962Z</t>
+          <t>2025-05-13T07:29:20.937Z</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/everything-about-rnn</t>
+          <t>https://www.inflearn.com/course/독하게-시작하는-c프로그래밍</t>
         </is>
       </c>
     </row>
@@ -5769,73 +5769,73 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>MLE부터 AE·VAE 입문까지 | 디퓨전 강의 TTD 무료 공개</t>
+          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>멍슨상</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>0</v>
+        <v>36300</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>30</v>
+        <v>314</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>딥러닝</t>
+          <t>Python, Java, C, 정보처리기사, database</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>146</v>
+        <v>1553</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T23:30:06.000Z</t>
+          <t>2025-09-24T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T15:50:32.518Z</t>
+          <t>2026-10-11T06:06:52.494Z</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-mle-to-an-intro</t>
+          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
         </is>
       </c>
     </row>
@@ -5845,73 +5845,73 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
+          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>99000</v>
+        <v>38500</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>99000</v>
+        <v>38500</v>
       </c>
       <c r="F71" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>578</v>
+        <v>61</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
+          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
+          <t>SQL, Oracle, database, modeling, SQLD</t>
         </is>
       </c>
       <c r="N71" s="7" t="n">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>2025-10-03T09:30:00.000Z</t>
+          <t>2026-09-02T03:00:00.000Z</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>2025-11-10T10:01:12.921Z</t>
+          <t>2026-09-02T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
+          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
         </is>
       </c>
     </row>
@@ -5921,73 +5921,73 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 타입스크립트(TypeScript)</t>
+          <t>디지털포렌식전문가 2급 필기 핵심 요약집[전자책]</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>훈지손</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>48400</v>
+        <v>38500</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>48400</v>
+        <v>38500</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>780</v>
+        <v>79</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14560</v>
+        <v>1342</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 프론트엔드</t>
+          <t>보안, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Forensic, 디지털포렌식전문가 2급</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>632</v>
+        <v>13</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2023-05-21T15:00:00.000Z</t>
+          <t>2023-02-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16T00:41:51.879Z</t>
+          <t>2026-01-05T15:57:52.306Z</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-크기-타입스크립트</t>
+          <t>https://www.inflearn.com/course/디지털포렌식전문가-2급-필기-전자책</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>실전에서 바로 써먹는 Kafka 입문</t>
+          <t>비전공자도 이해할 수 있는 Docker 입문/실전</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -6015,13 +6015,13 @@
         <v>0</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>103</v>
+        <v>692</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>781</v>
+        <v>14639</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
@@ -6035,35 +6035,35 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 데브옵스 · 인프라, 클라우드</t>
+          <t>데브옵스 · 인프라, 백엔드, 클라우드</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>Kafka, EDA, MSA, devops, infrastructure</t>
+          <t>Docker, container, docker-compose, docker-volume, ecr, docker-image</t>
         </is>
       </c>
       <c r="N73" s="7" t="n">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>2025-07-28T06:00:00.000Z</t>
+          <t>2024-06-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:37.287Z</t>
+          <t>2026-08-30T11:26:39.530Z</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/실전에서-바로-써먹는-kafka-입문</t>
+          <t>https://www.inflearn.com/course/비전공자-docker-입문-실전</t>
         </is>
       </c>
     </row>
@@ -6073,31 +6073,31 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 엔지니어가 가르치는 파이썬 기초부터 고급까지</t>
+          <t>[2026] 유니티 엔진 입문 올인원</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>90750</v>
+        <v>165000</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>121000</v>
+        <v>165000</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7798</v>
+        <v>135</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6106,40 +6106,40 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>게임 개발</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 풀스택</t>
+          <t>게임 프로그래밍</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Python, 알고리즘</t>
+          <t>game-programming, 유니티6</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>818</v>
+        <v>1159</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2022-12-01T15:00:00.000Z</t>
+          <t>2026-06-11T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T05:39:05.304Z</t>
+          <t>2026-06-11T02:13:13.639Z</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/실리콘밸리-파이썬-기초부터-고급까지</t>
+          <t>https://www.inflearn.com/course/2026-unity-engine-be</t>
         </is>
       </c>
     </row>
@@ -6149,73 +6149,73 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
+          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>피엠인사이드</t>
+          <t>최원영</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="F75" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>15</v>
+        <v>1560</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 관리, PMP</t>
+          <t>인공지능(AI)</t>
         </is>
       </c>
       <c r="N75" s="7" t="n">
-        <v>2458</v>
+        <v>32</v>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T13:00:08.000Z</t>
+          <t>2026-02-27T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T13:00:23.847Z</t>
+          <t>2026-02-27T06:18:36.692Z</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
+          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
         </is>
       </c>
     </row>
@@ -6225,31 +6225,31 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>코딩을 몰라도 만드는 AI 엑셀 매크로 실무 프로젝트</t>
+          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>칼퇴자동화연구소</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>49500</v>
+        <v>44000</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>49500</v>
+        <v>44000</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0</v>
+        <v>4071</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9</v>
+        <v>37227</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6258,40 +6258,40 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>오피스, 업무 자동화, AI 실무 활용</t>
+          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Excel, VBA, ChatGPT, 인공지능(AI)</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>146</v>
+        <v>341</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T16:30:04.000Z</t>
+          <t>2020-12-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T14:21:29.601Z</t>
+          <t>2025-05-13T07:23:13.295Z</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-ai-excel-m</t>
+          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>시스템 디자인 첫걸음: 면접에서 돋보이는 백엔드 아키텍처 설계하기</t>
+          <t>대규모 언어 모델, 핵심만 빠르게!</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>성장랜턴</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
@@ -6319,55 +6319,55 @@
         <v>0</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>743</v>
+        <v>138</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 웹 개발, 백엔드, 취업 · 이직</t>
+          <t>인공지능 기타, 자연어 처리, 딥러닝 · 머신러닝</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>아키텍처, backend, 소프트웨어 설계, 시스템 디자인, 면접</t>
+          <t>인공신경망, PyTorch, LLM, Fine-Tuning, RNN</t>
         </is>
       </c>
       <c r="N77" s="7" t="n">
-        <v>299</v>
+        <v>476</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>2025-05-27T15:00:00.000Z</t>
+          <t>2025-11-12T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2025-08-01T00:00:00.000Z</t>
+          <t>2026-01-31T09:31:50.184Z</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스템-디자인-첫걸음</t>
+          <t>https://www.inflearn.com/course/대규모-언어-모델-핵심만-빠르게</t>
         </is>
       </c>
     </row>
@@ -6377,73 +6377,73 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
+          <t>머신러닝, 핵심만 빠르게!</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>77000</v>
+        <v>44000</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>77000</v>
+        <v>44000</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>349</v>
+        <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5458</v>
+        <v>192</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
+          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 인공지능 기타</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
+          <t>인공신경망, CNN, linear-regression, RNN, ensembles</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>1001</v>
+        <v>382</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2025-03-24T15:00:00.000Z</t>
+          <t>2025-11-11T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2025-09-14T05:27:02.800Z</t>
+          <t>2026-01-12T09:18:24.857Z</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
+          <t>https://www.inflearn.com/course/머신러닝-핵심만-빠르게</t>
         </is>
       </c>
     </row>
@@ -6453,73 +6453,73 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
+          <t>초당 1,000,000++ RPS를 처리하는 네이버 개발자의 Valkey</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>44000</v>
+        <v>56760</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>44000</v>
+        <v>141900</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>4070</v>
+        <v>6</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>37224</v>
+        <v>143</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
+          <t>백엔드, 알고리즘 · 자료구조, 데이터베이스</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>JavaScript, 빅데이터, TypeScript, DBMS/RDBMS, Redis, MSA, 데이터 엔지니어링</t>
         </is>
       </c>
       <c r="N79" s="7" t="n">
-        <v>341</v>
+        <v>422</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>2020-12-19T15:00:00.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:23:13.295Z</t>
+          <t>2026-08-29T21:47:01.350Z</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
+          <t>https://www.inflearn.com/course/valkey-vs-redis-a-na</t>
         </is>
       </c>
     </row>
@@ -6529,31 +6529,31 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>비전공자도 이해할 수 있는 쿠버네티스 입문/실전</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>66000</v>
+        <v>88000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>66000</v>
+        <v>88000</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>1263</v>
+        <v>204</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12539</v>
+        <v>1676</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6562,40 +6562,40 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>데브옵스 · 인프라, 백엔드, 클라우드</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>Kubernetes, Docker, infrastructure, MSA, container</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1161</v>
+        <v>287</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2024-11-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2026-08-30T11:26:38.775Z</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/비전공자-쿠버네티스-입문-실전</t>
         </is>
       </c>
     </row>
@@ -6605,31 +6605,31 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 Next.js</t>
+          <t>클로드코드 Harness 와 Mods, Graph Engineering 심화 CLI 하네스 엔지니어링 실무</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>미국달팽이</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>48400</v>
+        <v>66000</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>48400</v>
+        <v>88000</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>638</v>
+        <v>62</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>6026</v>
+        <v>781</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
@@ -6638,40 +6638,40 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>AI 개발 활용, 풀스택, AI 실무 활용</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>React, TypeScript, Next.js</t>
+          <t>인공지능(AI), claude, 바이브코딩, 하네스</t>
         </is>
       </c>
       <c r="N81" s="7" t="n">
-        <v>934</v>
+        <v>503</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>2024-08-18T15:00:00.000Z</t>
+          <t>2026-04-24T22:00:00.000Z</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13T03:56:34.520Z</t>
+          <t>2026-10-09T19:56:24.049Z</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
+          <t>https://www.inflearn.com/course/claude-code-harness</t>
         </is>
       </c>
     </row>
@@ -6681,31 +6681,31 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>토비의 클린 스프링 - 도메인 모델 패턴과 헥사고날 아키텍처 Part 2</t>
+          <t>RNN의 모든 것 | 트랜스포머 강의 TTT 무료 공개</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>토비</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>627</v>
+        <v>37</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6714,40 +6714,40 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>백엔드</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, Spring Boot, JPA, 리팩터링, DDD, hexagonal-architecture</t>
+          <t>RNN, 딥러닝</t>
         </is>
       </c>
       <c r="N82" s="2" t="n">
-        <v>779</v>
+        <v>61</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T08:12:00.000Z</t>
+          <t>2026-10-06T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T00:00:00.000Z</t>
+          <t>2026-10-06T17:01:56.962Z</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/tobys-clean-spring-d</t>
+          <t>https://www.inflearn.com/course/everything-about-rnn</t>
         </is>
       </c>
     </row>
@@ -6757,31 +6757,31 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>비전공자도 이해할 수 있는 MySQL 성능 최적화 입문/실전 (SQL 튜닝편)</t>
+          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>88000</v>
+        <v>82500</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>88000</v>
+        <v>82500</v>
       </c>
       <c r="F83" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>153</v>
+        <v>789</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>1354</v>
+        <v>2910</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
@@ -6790,40 +6790,40 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>MySQL, DBMS/RDBMS, query-tuning, SQL</t>
+          <t>Kubernetes, devops, argocd, container, helm</t>
         </is>
       </c>
       <c r="N83" s="7" t="n">
-        <v>163</v>
+        <v>669</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>2024-07-14T15:00:00.000Z</t>
+          <t>2023-09-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:39.344Z</t>
+          <t>2026-05-27T08:15:25.352Z</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-mysql-성능최정확-sql튜닝</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
         </is>
       </c>
     </row>
@@ -6833,19 +6833,19 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>CAN 통신 - 자동차 신입이 알아야 할 모든 것</t>
+          <t>기초부터 따라하는 디지털포렌식</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>존버매니아</t>
+          <t>훈지손</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0</v>
@@ -6854,10 +6854,10 @@
         <v>4.9</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>259</v>
+        <v>148</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1864</v>
+        <v>6205</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6866,40 +6866,40 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>하드웨어, 보안 · 네트워크</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>모빌리티, 임베디드 · IoT, 보안 · 네트워크 기타</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>CAN, uds</t>
+          <t>Forensic</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>256</v>
+        <v>545</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2022-09-20T15:00:00.000Z</t>
+          <t>2022-02-22T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2025-05-30T14:52:11.295Z</t>
+          <t>2022-05-31T11:24:15.993Z</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/자동차-신입-can통신</t>
+          <t>https://www.inflearn.com/course/기초-디지털-포렌식</t>
         </is>
       </c>
     </row>
@@ -6909,31 +6909,31 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Docker가 쉬워지는 운영체제 이야기</t>
+          <t>헤르메스, 코덱스, LLM Wiki로 익히는 실무형 AI 하네스 엔지니어링</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>Masocampus</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>88000</v>
+        <v>48510</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>88000</v>
+        <v>69300</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>946</v>
+        <v>32</v>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
@@ -6942,40 +6942,40 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 시스템 · 운영체제, 클라우드</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>네트워크, Linux, Docker, 운영체제, linux-containers, cloud-computing</t>
+          <t>인공지능(AI), AI Agent, AX(에이전트 경험), LLM, wiki, 하네스, 프롬프트엔지니어링</t>
         </is>
       </c>
       <c r="N85" s="7" t="n">
-        <v>723</v>
+        <v>244</v>
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30T04:00:57.000Z</t>
+          <t>2026-09-17T06:00:06.000Z</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04T00:38:47.888Z</t>
+          <t>2026-09-11T06:33:52.548Z</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/operating-system-sto</t>
+          <t>https://www.inflearn.com/course/hands-on-ai-harness</t>
         </is>
       </c>
     </row>
@@ -6985,73 +6985,73 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>공업수학을 위한 중학, 고교수학</t>
+          <t>기초 탄탄! 독하게 시작하는 Java - Part 2 : OOP와 JVM</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>지식탐험단</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>121000</v>
+        <v>66000</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>121000</v>
+        <v>66000</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>479</v>
+        <v>5976</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>대학 교육</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>프로그래밍 언어, 백엔드</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>대수학, mathematics, functions, 행렬, vectors, factorization, equations</t>
+          <t>Java, 객체지향, jvm, data-structure</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>3131</v>
+        <v>1215</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2023-12-17T15:00:00.000Z</t>
+          <t>2024-11-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02T04:39:15.776Z</t>
+          <t>2025-07-09T04:47:07.588Z</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/중등-고등-수학-공업수학</t>
+          <t>https://www.inflearn.com/course/독하게-시작하는-java-part2</t>
         </is>
       </c>
     </row>
@@ -7061,19 +7061,19 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>대규모 트래픽 처리를 위한 부하테스트 입문/실전</t>
+          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>77000</v>
+        <v>128700</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>77000</v>
+        <v>128700</v>
       </c>
       <c r="F87" s="10" t="n">
         <v>0</v>
@@ -7082,52 +7082,52 @@
         <v>4.9</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>1094</v>
+        <v>573</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 백엔드</t>
+          <t>AI 실무 활용, 오피스, 업무 자동화</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>k6, infrastructure, performance-tuning, performance-test</t>
+          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N87" s="7" t="n">
-        <v>208</v>
+        <v>832</v>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>2024-12-17T15:00:00.000Z</t>
+          <t>2026-06-05T16:00:00.000Z</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:38.596Z</t>
+          <t>2026-08-07T06:36:11.731Z</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/대규모트래픽-부하테스트-입문-실전</t>
+          <t>https://www.inflearn.com/course/starting-with-claude</t>
         </is>
       </c>
     </row>
@@ -7137,31 +7137,31 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>GPT는 어떻게 문장을 생성할까? | LLM·ViT 강의 ATT 무료 공개</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>192</v>
+        <v>2</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1446</v>
+        <v>42</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7170,40 +7170,40 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>gpt, 딥러닝</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>368</v>
+        <v>35</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2026-10-06T09:00:09.000Z</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2026-10-06T17:04:49.947Z</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/how-does-gpt-generat</t>
         </is>
       </c>
     </row>
@@ -7213,73 +7213,73 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>회사에서 바로 쓰는 챗GPT 실전 가이드_2026</t>
+          <t>AI 에이전트 엔지니어링</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>포레스트소프트</t>
+          <t>민혁</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="F89" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>133</v>
+        <v>2056</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 시작하기, 오피스</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>gemini, 인공지능(AI), ChatGPT, Microsoft Copilot, AI Agent</t>
+          <t>Python, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N89" s="7" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>2025-12-04T05:30:00.000Z</t>
+          <t>2026-04-07T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>2025-12-04T06:33:12.706Z</t>
+          <t>2026-04-07T02:58:08.781Z</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/회사에서-바로-쓰는-챗gpt-실전-가</t>
+          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
         </is>
       </c>
     </row>
@@ -7289,73 +7289,73 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
+          <t>실리콘 밸리 엔지니어와 함께하는 Local LLM 완전 정복 (LM Studio &amp; Ollama &amp; Ollaya)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>그랩</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>198000</v>
+        <v>41250</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>198000</v>
+        <v>55000</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>326</v>
+        <v>684</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>인공지능(AI), LLM, AI Agent</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>896</v>
+        <v>270</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T04:50:00.000Z</t>
+          <t>2026-04-17T18:00:00.000Z</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T16:24:39.937Z</t>
+          <t>2026-10-01T05:15:20.298Z</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
+          <t>https://www.inflearn.com/course/mastering-local-llm</t>
         </is>
       </c>
     </row>
@@ -7365,19 +7365,19 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>홍정모의 따라하며 배우는 C++</t>
+          <t>단 60분! 파이썬 핵심 개념 초압축 강의 - 이론보다 이해 중심</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>홍정모</t>
+          <t>딩코딩코</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>176000</v>
+        <v>0</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>176000</v>
+        <v>0</v>
       </c>
       <c r="F91" s="10" t="n">
         <v>0</v>
@@ -7386,52 +7386,52 @@
         <v>4.9</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>395</v>
+        <v>484</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>7125</v>
+        <v>7095</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 게임 개발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
-        <v>2907</v>
+        <v>64</v>
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>2018-09-30T15:00:00.000Z</t>
+          <t>2024-09-22T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>2025-08-10T19:46:59.750Z</t>
+          <t>2026-06-10T00:47:07.734Z</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/following-c-plus</t>
+          <t>https://www.inflearn.com/course/파이썬-핵심개념-압축강의</t>
         </is>
       </c>
     </row>
@@ -7441,19 +7441,19 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
+          <t>외워서 끝내는 네트워크 핵심이론 - 기초</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>코드바나나</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>148500</v>
+        <v>77000</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>148500</v>
+        <v>77000</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>0</v>
@@ -7462,52 +7462,52 @@
         <v>4.9</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>320</v>
+        <v>797</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3750</v>
+        <v>8577</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
+          <t>네트워크, 개발 · 프로그래밍 기타, 웹 개발</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>AWS, 네트워크, AWS SAA</t>
+          <t>네트워크, 프로토콜</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>1450</v>
+        <v>431</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2022-06-21T15:00:00.000Z</t>
+          <t>2022-09-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T03:07:28.063Z</t>
+          <t>2025-05-13T07:25:51.956Z</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
+          <t>https://www.inflearn.com/course/네트워크-핵심이론-기초</t>
         </is>
       </c>
     </row>
@@ -7517,12 +7517,12 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>기초부터 따라하는 디지털포렌식</t>
+          <t>MLE부터 AE·VAE 입문까지 | 디퓨전 강의 TTD 무료 공개</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>훈지손</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
@@ -7535,55 +7535,55 @@
         <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>6202</v>
+        <v>31</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>딥러닝 · 머신러닝</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>Forensic</t>
+          <t>딥러닝</t>
         </is>
       </c>
       <c r="N93" s="7" t="n">
-        <v>545</v>
+        <v>146</v>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>2022-02-22T15:00:00.000Z</t>
+          <t>2026-10-06T23:30:06.000Z</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>2022-05-31T11:24:15.993Z</t>
+          <t>2026-10-06T15:50:32.518Z</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/기초-디지털-포렌식</t>
+          <t>https://www.inflearn.com/course/from-mle-to-an-intro</t>
         </is>
       </c>
     </row>
@@ -7593,31 +7593,31 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
+          <t>이야기로 배우는 1on1: 팀장을 위한 면담 대화법</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>오픈러닝랩</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>38500</v>
+        <v>18150</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>38500</v>
+        <v>36300</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7626,40 +7626,40 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>SQL, Oracle, database, modeling, SQLD</t>
+          <t>커뮤니케이션</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>923</v>
+        <v>226</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T03:00:00.000Z</t>
+          <t>2026-10-07T02:00:12.000Z</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T00:00:00.000Z</t>
+          <t>2026-10-06T03:17:00.759Z</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
+          <t>https://www.inflearn.com/course/learning-1-on-1s-thr</t>
         </is>
       </c>
     </row>
@@ -7669,73 +7669,73 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2,000++억건 데이터를 다루는 실리콘 밸리 AI 개발자의 PostgreSQL</t>
+          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>152900</v>
+        <v>154000</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>152900</v>
+        <v>154000</v>
       </c>
       <c r="F95" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>590</v>
+        <v>2048</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>자연어 처리, 데이터베이스, 백엔드</t>
+          <t>데이터베이스, 데이터 분석, 풀스택</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>MySQL, PostgreSQL, Oracle, DBMS/RDBMS, database</t>
+          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
-        <v>567</v>
+        <v>1270</v>
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>2026-05-03T11:00:00.000Z</t>
+          <t>2026-07-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08T00:41:41.637Z</t>
+          <t>2026-07-28T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/postgresql-from-a-si</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
         </is>
       </c>
     </row>
@@ -7745,73 +7745,73 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
+          <t>하루만에 끝내는 Herdr: 멀티플렉서, 에이전트, SSH 맥미니-모바일 원격 접속</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>79200</v>
+        <v>77000</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>79200</v>
+        <v>77000</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>228</v>
+        <v>9</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>6753</v>
+        <v>119</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
+          <t>개발 도구, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
+          <t>tmux, claude, codex, terminal, AI Agent, macOS, Git</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>357</v>
+        <v>248</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2025-07-11T02:00:00.000Z</t>
+          <t>2026-09-13T12:00:06.000Z</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10T22:31:31.977Z</t>
+          <t>2026-09-27T09:02:14.111Z</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
+          <t>https://www.inflearn.com/course/herdr-in-one-day-mul</t>
         </is>
       </c>
     </row>
@@ -7821,19 +7821,19 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>카카오 면접관과 함께하는 워크플로우 기반의 대용량 트래픽 처리 기법</t>
+          <t>오브젝트 - 기초편</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>조영호</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>79200</v>
+        <v>110000</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>79200</v>
+        <v>110000</v>
       </c>
       <c r="F97" s="10" t="n">
         <v>0</v>
@@ -7842,14 +7842,14 @@
         <v>5</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>562</v>
+        <v>1829</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
@@ -7859,35 +7859,35 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 데이터베이스, 개발 · 프로그래밍 자격증</t>
+          <t>개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>Spring, Kotlin, MySQL, Kafka</t>
+          <t>소프트웨어 설계, 객체지향</t>
         </is>
       </c>
       <c r="N97" s="7" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>2025-09-07T07:30:00.000Z</t>
+          <t>2024-07-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>2025-09-07T02:26:23.175Z</t>
+          <t>2025-11-19T23:18:05.849Z</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/카카오-개발자와-함께하는-워크플로우</t>
+          <t>https://www.inflearn.com/course/오브젝트-기초편-객체지향</t>
         </is>
       </c>
     </row>
@@ -7897,73 +7897,73 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>[리뉴얼] 처음하는 파이썬 데이터 분석 (쉽게! 전처리, pandas, 시각화 전과정 익히기) [데이터분석/과학 Part1]</t>
+          <t>실무에 바로 적용하는 Spring AI: Spring 서비스에 챗봇·RAG·MCP 도입하기</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>잔재미코딩 DaveLee</t>
+          <t>JSCODE 시니</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>88000</v>
+        <v>61600</v>
       </c>
       <c r="E98" s="4" t="n">
         <v>88000</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>382</v>
+        <v>45</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>4449</v>
+        <v>586</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스, AI 기술</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석, 딥러닝 · 머신러닝, 데이터 엔지니어링</t>
+          <t>AI 실무 활용, 백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Python, Pandas, Plotly</t>
+          <t>Spring Boot, Elasticsearch, vector-database, LLM, RAG, Spring AI, MCP</t>
         </is>
       </c>
       <c r="N98" s="2" t="n">
-        <v>747</v>
+        <v>439</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2020-06-21T15:00:00.000Z</t>
+          <t>2026-06-12T23:30:00.000Z</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T09:16:03.413Z</t>
+          <t>2026-08-30T11:28:43.252Z</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/파이썬-데이터분석-전처리-판다스-시각화</t>
+          <t>https://www.inflearn.com/course/spring-ai-in-practic</t>
         </is>
       </c>
     </row>
@@ -7973,73 +7973,73 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>AI 에이전트 엔지니어링</t>
+          <t>토비의 클린 스프링 - 도메인 모델 패턴과 헥사고날 아키텍처 Part 1</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>민혁</t>
+          <t>토비</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>39</v>
+        <v>318</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>2049</v>
+        <v>2570</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>백엔드</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>Python, 인공지능(AI), RAG, AI Agent</t>
+          <t>Java, Spring, Spring Boot, JPA, hexagonal-architecture, 리팩터링, DDD</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
-        <v>322</v>
+        <v>872</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07T05:00:00.000Z</t>
+          <t>2025-06-18T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07T02:58:08.781Z</t>
+          <t>2025-10-23T07:53:22.134Z</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
+          <t>https://www.inflearn.com/course/토비-클린스프링-도메인모델패턴-헥사고날-part1</t>
         </is>
       </c>
     </row>
@@ -8049,31 +8049,31 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
+          <t>[Rookiss] 클로드 하네스 입문 (인터랙티브 교재)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>82500</v>
+        <v>99000</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>82500</v>
+        <v>99000</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>788</v>
+        <v>5</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2908</v>
+        <v>112</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -8082,40 +8082,40 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, argocd, container, helm</t>
+          <t>Python, 인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>669</v>
+        <v>225</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2023-09-11T15:00:00.000Z</t>
+          <t>2026-07-24T09:30:06.000Z</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27T08:15:25.352Z</t>
+          <t>2026-08-04T05:39:18.684Z</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
+          <t>https://www.inflearn.com/course/rookiss-introduction-2</t>
         </is>
       </c>
     </row>
@@ -8125,31 +8125,31 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>기초 탄탄! 독하게 시작하는 Java - Part 2 : OOP와 JVM</t>
+          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>66000</v>
+        <v>44550</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>66000</v>
+        <v>59400</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>5976</v>
+        <v>224</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
@@ -8158,40 +8158,40 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, jvm, data-structure</t>
+          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
         </is>
       </c>
       <c r="N101" s="7" t="n">
-        <v>1215</v>
+        <v>311</v>
       </c>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>2024-11-20T15:00:00.000Z</t>
+          <t>2026-07-31T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>2025-07-09T04:47:07.588Z</t>
+          <t>2026-08-12T14:30:32.966Z</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/독하게-시작하는-java-part2</t>
+          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12T15:00:49+09:00</t>
+          <t>2026-10-13T15:48:21+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -702,10 +702,10 @@
         <v>5</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>2404</v>
+        <v>2475</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
+          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>43560</v>
+        <v>52470</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>108900</v>
+        <v>174900</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -795,16 +795,16 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
+          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>321</v>
+        <v>520</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29T06:47:12.230Z</t>
+          <t>2026-08-26T10:28:07.736Z</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
+          <t>https://www.inflearn.com/course/building-embeddings</t>
         </is>
       </c>
     </row>
@@ -833,73 +833,73 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
+          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>49500</v>
+        <v>43560</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>99000</v>
+        <v>108900</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라</t>
+          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>Linux, AWS, bash, ubuntu, nginx</t>
+          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>728</v>
+        <v>321</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T07:00:10.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T03:16:22.539Z</t>
+          <t>2026-08-29T06:47:12.230Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
+          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
         </is>
       </c>
     </row>
@@ -909,73 +909,73 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
+          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>52470</v>
+        <v>49500</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>174900</v>
+        <v>99000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>430</v>
+        <v>147</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
+          <t>데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
+          <t>Linux, AWS, bash, ubuntu, nginx</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>520</v>
+        <v>726</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-10-06T07:00:10.000Z</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T10:28:07.736Z</t>
+          <t>2026-10-14T02:24:25.825Z</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-embeddings</t>
+          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
         </is>
       </c>
     </row>
@@ -1006,10 +1006,10 @@
         <v>4.9</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11274</v>
+        <v>11286</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1061,73 +1061,73 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
+          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>한조각</t>
+          <t>퇴근후딴짓</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>19800</v>
+        <v>121000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>66000</v>
+        <v>121000</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2</v>
+        <v>929</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>232</v>
+        <v>6017</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
+          <t>데이터 사이언스 자격증, 데이터 분석</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
+          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>538</v>
+        <v>1560</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T20:30:05.000Z</t>
+          <t>2022-12-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T18:51:20.390Z</t>
+          <t>2026-10-06T00:43:26.587Z</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-service-deploym</t>
+          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
         </is>
       </c>
     </row>
@@ -1137,73 +1137,73 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
+          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>한조각</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>88000</v>
+        <v>19800</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>88000</v>
+        <v>66000</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>729</v>
+        <v>3</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>5710</v>
+        <v>235</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍, AI 기술</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
+          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>2108</v>
+        <v>538</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2024-06-13T15:00:00.000Z</t>
+          <t>2026-09-29T20:30:05.000Z</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T14:55:46.048Z</t>
+          <t>2026-09-29T18:51:20.390Z</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
+          <t>https://www.inflearn.com/course/from-service-deploym</t>
         </is>
       </c>
     </row>
@@ -1213,31 +1213,31 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
+          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>퇴근후딴짓</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>121000</v>
+        <v>88000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>121000</v>
+        <v>88000</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>927</v>
+        <v>730</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6010</v>
+        <v>5715</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1246,40 +1246,40 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 데이터 분석</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
+          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1560</v>
+        <v>2108</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2022-12-12T15:00:00.000Z</t>
+          <t>2024-06-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T00:43:26.587Z</t>
+          <t>2026-10-01T14:55:46.048Z</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
+          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
         </is>
       </c>
     </row>
@@ -1289,73 +1289,73 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
+          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>한빛미디어</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>5</v>
+        <v>715</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>780</v>
+        <v>13420</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
+          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
+          <t>인공지능(AI), 바이브코딩</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>1266</v>
+        <v>259</v>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07T05:00:33.000Z</t>
+          <t>2025-12-22T08:00:00.000Z</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T02:47:16.149Z</t>
+          <t>2026-01-07T07:20:44.145Z</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-llm-servic</t>
+          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
         </is>
       </c>
     </row>
@@ -1365,73 +1365,73 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
+          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>한빛미디어</t>
+          <t>김대현</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13376</v>
+        <v>8</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
+          <t>백엔드, 풀스택, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), 바이브코딩</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>259</v>
+        <v>89</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22T08:00:00.000Z</t>
+          <t>2026-10-13T05:00:07.000Z</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07T07:20:44.145Z</t>
+          <t>2026-10-13T02:52:17.360Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
+          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
         </is>
       </c>
     </row>
@@ -1441,73 +1441,73 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>진짜! 타입스크립트 - 타입 설계부터 타입 레벨 프로그래밍까지</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>코딩맥스 CodingMax</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>89100</v>
+        <v>49500</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>89100</v>
+        <v>99000</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1731</v>
+        <v>5</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
+          <t>JavaScript, 함수형 프로그래밍, TypeScript, Node.js</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>727</v>
+        <v>3475</v>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2026-10-13T01:00:07.000Z</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2026-10-13T01:50:40.027Z</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/really-typescript-fr</t>
         </is>
       </c>
     </row>
@@ -1517,73 +1517,73 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
+          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>37950</v>
+        <v>198000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>75900</v>
+        <v>198000</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>211</v>
+        <v>305</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
+          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
+          <t>api, trading, codex, 바이브코딩</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:30:06.000Z</t>
+          <t>2026-09-09T01:30:06.000Z</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T01:52:33.960Z</t>
+          <t>2026-10-11T08:59:09.803Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
+          <t>https://www.inflearn.com/course/create-an-automated</t>
         </is>
       </c>
     </row>
@@ -1593,22 +1593,22 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
+          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Hiro Son</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>49500</v>
+        <v>37950</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>198000</v>
+        <v>75900</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>0</v>
@@ -1617,49 +1617,49 @@
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>15</v>
+        <v>212</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
+          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>150</v>
+        <v>641</v>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T17:30:06.000Z</t>
+          <t>2026-09-28T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T00:53:13.219Z</t>
+          <t>2026-09-29T01:52:33.960Z</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
+          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
         </is>
       </c>
     </row>
@@ -1669,71 +1669,73 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>414</v>
+        <v>268</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4634</v>
+        <v>1363</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n"/>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>309</v>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27T10:00:00.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T00:59:39.967Z</t>
+          <t>2026-08-30T11:28:44.702Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -1743,31 +1745,31 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>50</v>
+        <v>414</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>303</v>
+        <v>4649</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
@@ -1776,40 +1778,38 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>api, trading, codex, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>628</v>
-      </c>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n"/>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09T01:30:06.000Z</t>
+          <t>2026-01-27T10:00:00.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T08:59:09.803Z</t>
+          <t>2026-06-30T00:59:39.967Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/create-an-automated</t>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
         </is>
       </c>
     </row>
@@ -1819,73 +1819,73 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>69300</v>
+        <v>89100</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>99000</v>
+        <v>89100</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>47</v>
+        <v>1734</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
+          <t>security, CPPG(개인정보관리사)</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>73</v>
+        <v>727</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T11:00:10.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T17:09:46.044Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -1895,31 +1895,31 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법)</t>
+          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>Hiro Son</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
         <v>49500</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>99000</v>
+        <v>198000</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
@@ -1928,40 +1928,40 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>363</v>
+        <v>150</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2026-10-07T17:30:06.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2026-10-10T00:53:13.219Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
         </is>
       </c>
     </row>
@@ -1971,19 +1971,19 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>88000</v>
+        <v>198000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>88000</v>
+        <v>198000</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>4.9</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>267</v>
+        <v>173</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1360</v>
+        <v>1613</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -2004,40 +2004,40 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>309</v>
+        <v>1650</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:44.702Z</t>
+          <t>2026-10-14T02:26:30.439Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -2047,73 +2047,73 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 기본편</t>
+          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>44000</v>
+        <v>49500</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>44000</v>
+        <v>99000</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H21" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="7" t="n">
-        <v>2402</v>
-      </c>
       <c r="I21" s="7" t="n">
-        <v>28220</v>
+        <v>83</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>1012</v>
+        <v>363</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-09-16T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2025-12-23T06:52:23.926Z</t>
+          <t>2026-09-30T03:16:06.187Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+          <t>https://www.inflearn.com/course/ai-automated-trading</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T23:33:09.769Z</t>
+          <t>2026-10-13T14:25:37.776Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -2199,73 +2199,73 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>49</v>
+        <v>3978</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>1240</v>
+        <v>90</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T15:00:07.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T03:23:49.530Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -2275,19 +2275,19 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>198000</v>
+        <v>44000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>198000</v>
+        <v>44000</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
@@ -2296,52 +2296,52 @@
         <v>4.9</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>172</v>
+        <v>616</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1610</v>
+        <v>8416</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>개발 도구</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>Git, GitHub, github-actions, git-commands</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1650</v>
+        <v>353</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2022-01-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T06:48:11.122Z</t>
+          <t>2026-06-03T09:18:28.574Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
         </is>
       </c>
     </row>
@@ -2351,73 +2351,73 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>김영한의 실전 자바 - 기본편</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>307</v>
+        <v>2403</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>3956</v>
+        <v>28222</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>90</v>
+        <v>1012</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2025-12-23T06:52:23.926Z</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
         </is>
       </c>
     </row>
@@ -2427,73 +2427,73 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>440000</v>
+        <v>330000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>484000</v>
+        <v>330000</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18</v>
+        <v>533</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>204</v>
+        <v>1048</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T05:30:05.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:50.737Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>99000</v>
+        <v>48400</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>99000</v>
+        <v>48400</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
@@ -2524,52 +2524,52 @@
         <v>4.9</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>140</v>
+        <v>1559</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>902</v>
+        <v>15626</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
+          <t>JavaScript, React, Node.js</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>657</v>
+        <v>1114</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20T05:00:00.000Z</t>
+          <t>2022-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T06:39:46.390Z</t>
+          <t>2026-06-13T00:57:34.805Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/codex-true-education</t>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
         </is>
       </c>
     </row>
@@ -2579,73 +2579,73 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>44000</v>
+        <v>55000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>44000</v>
+        <v>55000</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>616</v>
+        <v>110</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8411</v>
+        <v>656</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>353</v>
+        <v>196</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -2655,73 +2655,73 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>nstyxn</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>118800</v>
+        <v>550000</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>118800</v>
+        <v>550000</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>958</v>
+        <v>605</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>보안, 보안 · 네트워크 자격증</t>
+          <t>임베디드 · IoT, 모빌리티</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>Forensic, 디지털포렌식전문가 2급</t>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>6530</v>
+        <v>1017</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2022-11-13T15:00:00.000Z</t>
+          <t>2025-06-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15T02:00:30.898Z</t>
+          <t>2026-09-13T09:06:49.556Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
         </is>
       </c>
     </row>
@@ -2731,19 +2731,19 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>회로설계 멘토 삼코치</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>55000</v>
+        <v>269500</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>55000</v>
+        <v>269500</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
@@ -2752,52 +2752,52 @@
         <v>5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>651</v>
+        <v>699</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>임베디드 · IoT, 반도체</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>196</v>
+        <v>918</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2025-03-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2026-09-11T13:20:57.892Z</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
         </is>
       </c>
     </row>
@@ -2807,73 +2807,73 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>66000</v>
+        <v>440000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>66000</v>
+        <v>440000</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>1263</v>
+        <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>12542</v>
+        <v>50</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>1161</v>
+        <v>1240</v>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2026-10-04T15:00:07.000Z</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2026-10-05T03:23:49.530Z</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
         </is>
       </c>
     </row>
@@ -2883,19 +2883,19 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>홍정모의 따라하며 배우는 C++</t>
+          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>홍정모</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>176000</v>
+        <v>99000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>176000</v>
+        <v>99000</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>0</v>
@@ -2904,52 +2904,52 @@
         <v>4.9</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>395</v>
+        <v>143</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7125</v>
+        <v>903</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 게임 개발</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2907</v>
+        <v>657</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2018-09-30T15:00:00.000Z</t>
+          <t>2026-07-20T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2025-08-10T19:46:59.750Z</t>
+          <t>2026-10-11T06:39:46.390Z</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/following-c-plus</t>
+          <t>https://www.inflearn.com/course/codex-true-education</t>
         </is>
       </c>
     </row>
@@ -2959,22 +2959,22 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Decision AI로 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
+          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>22000</v>
+        <v>69300</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>22000</v>
+        <v>99000</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>0</v>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
@@ -2992,40 +2992,40 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
+          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
+          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T05:00:08.000Z</t>
+          <t>2026-10-08T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T19:46:29.290Z</t>
+          <t>2026-10-11T17:09:46.044Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-decision-a</t>
+          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
         </is>
       </c>
     </row>
@@ -3035,73 +3035,73 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
+          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>회로설계 멘토 삼코치</t>
+          <t>YoungJea Oh</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>269500</v>
+        <v>49500</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>269500</v>
+        <v>99000</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>697</v>
+        <v>27</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 반도체</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
+          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>918</v>
+        <v>370</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2025-03-25T15:00:00.000Z</t>
+          <t>2026-10-02T10:00:08.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:20:57.892Z</t>
+          <t>2026-10-02T07:55:47.247Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
+          <t>https://www.inflearn.com/course/mastering-the-latest</t>
         </is>
       </c>
     </row>
@@ -3111,73 +3111,73 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>194</v>
+        <v>747</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1450</v>
+        <v>11823</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>368</v>
+        <v>517</v>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2025-08-31T09:28:51.006Z</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
         </is>
       </c>
     </row>
@@ -3187,31 +3187,31 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
+          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0</v>
+        <v>440000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0</v>
+        <v>484000</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>747</v>
+        <v>4</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11814</v>
+        <v>18</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3220,40 +3220,40 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>517</v>
+        <v>204</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2026-10-04T05:30:05.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2025-08-31T09:28:51.006Z</t>
+          <t>2026-10-11T15:08:50.737Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
+          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
         </is>
       </c>
     </row>
@@ -3263,73 +3263,73 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
+          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>알고런 데이터코드 연구소</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>49500</v>
+        <v>79200</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>99000</v>
+        <v>79200</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>26</v>
+        <v>589</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
+          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>370</v>
+        <v>785</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T10:00:08.000Z</t>
+          <t>2025-04-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T07:55:47.247Z</t>
+          <t>2026-07-02T07:40:07.999Z</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-latest</t>
+          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>나도코딩</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
@@ -3357,13 +3357,13 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1930</v>
+        <v>3141</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>40201</v>
+        <v>57306</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3377,35 +3377,35 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>358</v>
+        <v>771</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2020-02-24T15:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T06:34:34.311Z</t>
+          <t>2026-01-28T11:59:57.298Z</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
         </is>
       </c>
     </row>
@@ -3415,31 +3415,31 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>인프런</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>33000</v>
+        <v>99000</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>33000</v>
+        <v>99000</v>
       </c>
       <c r="F39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>1399</v>
+        <v>152</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>34387</v>
+        <v>1102</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
@@ -3448,40 +3448,40 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>857</v>
+        <v>516</v>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>2019-06-01T15:00:00.000Z</t>
+          <t>2026-05-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18T05:48:10.725Z</t>
+          <t>2026-09-21T01:35:54.874Z</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
         </is>
       </c>
     </row>
@@ -3491,31 +3491,31 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>AI를 위한 미적분 — 도함수, 그래디언트, 그리고 신경망이 학습하는 원리</t>
+          <t>김영한의 실전 자바 - 중급 1편</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>코딩맥스 CodingMax</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0</v>
+        <v>1263</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>32</v>
+        <v>12542</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3524,40 +3524,40 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 대학 교육</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 수학</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>머신러닝, 딥러닝, 인공신경망, 선형대수학, 미적분, 인공지능(AI)</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1093</v>
+        <v>1161</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T08:00:08.000Z</t>
+          <t>2024-03-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T05:41:38.564Z</t>
+          <t>2025-11-28T10:04:41.236Z</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/calculus-for-ai-deri</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
         </is>
       </c>
     </row>
@@ -3567,31 +3567,31 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>시드니개발자의 영어PT</t>
+          <t>인프런</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>220000</v>
+        <v>33000</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>220000</v>
+        <v>33000</v>
       </c>
       <c r="F41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>63</v>
+        <v>1401</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>2199</v>
+        <v>34390</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
@@ -3600,40 +3600,40 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>외국어</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>49</v>
+        <v>857</v>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>2023-01-12T15:00:00.000Z</t>
+          <t>2019-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T05:15:40.989Z</t>
+          <t>2026-09-18T05:48:10.725Z</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
         </is>
       </c>
     </row>
@@ -3643,19 +3643,19 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>제어쟁이</t>
+          <t>나도코딩</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>0</v>
@@ -3664,52 +3664,52 @@
         <v>4.9</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>83</v>
+        <v>1931</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>603</v>
+        <v>40206</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 모빌리티</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>임베디드, stm32, hardware, motordriver, artwork</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1017</v>
+        <v>358</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2025-06-15T15:00:00.000Z</t>
+          <t>2020-02-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T09:06:49.556Z</t>
+          <t>2025-04-29T06:34:34.311Z</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
         </is>
       </c>
     </row>
@@ -3719,73 +3719,73 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>노베이스를 위한 ADsP 생존 가이드</t>
+          <t>대세는 쿠버네티스 (초급~중급편)</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>22</v>
+        <v>626</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>757</v>
+        <v>8497</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>SQL, R, ADsP</t>
+          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>303</v>
+        <v>425</v>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T11:00:00.000Z</t>
+          <t>2019-09-10T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T09:14:53.120Z</t>
+          <t>2025-11-19T05:23:15.024Z</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
         </is>
       </c>
     </row>
@@ -3795,73 +3795,73 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>26</v>
+        <v>188</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>578</v>
+        <v>6173</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
+          <t>네트워크, tcpip, routing</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>924</v>
+        <v>779</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2025-10-03T09:30:00.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10T10:01:12.921Z</t>
+          <t>2025-04-29T09:27:31.006Z</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 2편</t>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F45" s="10" t="n">
         <v>0</v>
@@ -3892,10 +3892,10 @@
         <v>5</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>880</v>
+        <v>8118</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>11023</v>
+        <v>123262</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
@@ -3909,35 +3909,35 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+          <t>Java, Spring, MVC, Spring Boot</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>1165</v>
+        <v>321</v>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>2024-05-07T15:00:00.000Z</t>
+          <t>2020-07-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2025-11-24T10:17:13.631Z</t>
+          <t>2026-01-30T11:34:33.353Z</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
         </is>
       </c>
     </row>
@@ -3947,73 +3947,73 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
+          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>nstyxn</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>55000</v>
+        <v>118800</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>86900</v>
+        <v>118800</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.3670886075949367</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20</v>
+        <v>958</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
+          <t>보안, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
+          <t>Forensic, 디지털포렌식전문가 2급</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>541</v>
+        <v>6530</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T02:30:05.000Z</t>
+          <t>2022-11-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T15:07:55.641Z</t>
+          <t>2026-07-15T02:00:30.898Z</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
+          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
         </is>
       </c>
     </row>
@@ -4023,31 +4023,31 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>피엠인사이드</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>48400</v>
+        <v>330000</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>48400</v>
+        <v>330000</v>
       </c>
       <c r="F47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>1557</v>
+        <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>15624</v>
+        <v>17</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
@@ -4056,40 +4056,40 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>프로젝트 관리, PMP</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>1114</v>
+        <v>2405</v>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>2022-01-26T15:00:00.000Z</t>
+          <t>2026-10-01T13:00:08.000Z</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13T00:57:34.805Z</t>
+          <t>2026-10-13T13:27:36.753Z</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-리액트</t>
+          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
         </is>
       </c>
     </row>
@@ -4099,19 +4099,19 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0</v>
+        <v>64900</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0</v>
+        <v>64900</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>0</v>
@@ -4120,10 +4120,10 @@
         <v>5</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>8117</v>
+        <v>5</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>123250</v>
+        <v>782</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4132,40 +4132,40 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, MVC, Spring Boot</t>
+          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>321</v>
+        <v>1266</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2020-07-19T15:00:00.000Z</t>
+          <t>2026-09-07T05:00:33.000Z</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T11:34:33.353Z</t>
+          <t>2026-10-13T22:16:49.715Z</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+          <t>https://www.inflearn.com/course/practical-llm-servic</t>
         </is>
       </c>
     </row>
@@ -4175,73 +4175,73 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+          <t>Decision AI로 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="F49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>3140</v>
+        <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>57297</v>
+        <v>19</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>771</v>
+        <v>109</v>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-10-06T05:00:08.000Z</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28T11:59:57.298Z</t>
+          <t>2026-10-12T19:46:29.290Z</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+          <t>https://www.inflearn.com/course/practical-decision-a</t>
         </is>
       </c>
     </row>
@@ -4251,31 +4251,31 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>대세는 쿠버네티스 (초급~중급편)</t>
+          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>44000</v>
+        <v>99000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>44000</v>
+        <v>99000</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>626</v>
+        <v>26</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8493</v>
+        <v>579</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4284,40 +4284,40 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
+          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>425</v>
+        <v>924</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2019-09-10T15:00:00.000Z</t>
+          <t>2025-10-03T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2025-11-19T05:23:15.024Z</t>
+          <t>2025-11-10T10:01:12.921Z</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>정보처리기사 자격증 대비 교육(실기)</t>
+          <t>시스코 CCNA 함께 공부해요</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>국립안동대학교 SW융합교육원</t>
+          <t>ccie_pe_kim</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
@@ -4345,13 +4345,13 @@
         <v>0</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>2227</v>
+        <v>1758</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
@@ -4360,40 +4360,40 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증</t>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>정보처리기사</t>
+          <t>네트워크, CCNA, routing, tcpip</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>1532</v>
+        <v>1213</v>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>2024-08-13T15:00:00.000Z</t>
+          <t>2026-01-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2024-08-14T00:00:00.000Z</t>
+          <t>2026-03-25T09:44:13.272Z</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
         </is>
       </c>
     </row>
@@ -4403,73 +4403,73 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
+          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>79200</v>
+        <v>128700</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>79200</v>
+        <v>128700</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>229</v>
+        <v>38</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6756</v>
+        <v>576</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
+          <t>AI 실무 활용, 오피스, 업무 자동화</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
+          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>357</v>
+        <v>832</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2025-07-11T02:00:00.000Z</t>
+          <t>2026-06-05T16:00:00.000Z</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10T22:31:31.977Z</t>
+          <t>2026-08-07T06:36:11.731Z</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
+          <t>https://www.inflearn.com/course/starting-with-claude</t>
         </is>
       </c>
     </row>
@@ -4479,73 +4479,73 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+          <t>김영한의 실전 자바 - 중급 2편</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="F53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>460</v>
+        <v>881</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>21158</v>
+        <v>11023</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
         </is>
       </c>
       <c r="N53" s="7" t="n">
-        <v>823</v>
+        <v>1165</v>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>2023-03-02T15:00:00.000Z</t>
+          <t>2024-05-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:43:24.787Z</t>
+          <t>2025-11-24T10:17:13.631Z</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
         </is>
       </c>
     </row>
@@ -4555,19 +4555,19 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 Next.js</t>
+          <t>노베이스를 위한 ADsP 생존 가이드</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0</v>
@@ -4576,52 +4576,52 @@
         <v>5</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>638</v>
+        <v>22</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>6027</v>
+        <v>759</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>React, TypeScript, Next.js</t>
+          <t>SQL, R, ADsP</t>
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>934</v>
+        <v>303</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2024-08-18T15:00:00.000Z</t>
+          <t>2025-11-11T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T03:56:34.520Z</t>
+          <t>2025-11-11T09:14:53.120Z</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
+          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
         </is>
       </c>
     </row>
@@ -4631,31 +4631,31 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
+          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>알고런 데이터코드 연구소</t>
+          <t>시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>79200</v>
+        <v>220000</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>79200</v>
+        <v>220000</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>586</v>
+        <v>2199</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
@@ -4664,40 +4664,40 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>외국어</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="N55" s="7" t="n">
-        <v>785</v>
+        <v>49</v>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>2025-04-07T15:00:00.000Z</t>
+          <t>2023-01-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02T07:40:07.999Z</t>
+          <t>2026-10-02T05:15:40.989Z</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
+          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
         </is>
       </c>
     </row>
@@ -4707,73 +4707,73 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
+          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>44330</v>
+        <v>0</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>68200</v>
+        <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>5</v>
+        <v>21161</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
+          <t>컴퓨터 구조, 운영체제, 기술면접</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>410</v>
+        <v>823</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2023-03-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T12:02:44.178Z</t>
+          <t>2025-04-29T09:43:24.787Z</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/database-concepts-yo</t>
+          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
         </is>
       </c>
     </row>
@@ -4783,31 +4783,31 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
+          <t>정보처리기사 자격증 대비 교육(실기)</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>국립안동대학교 SW융합교육원</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>44330</v>
+        <v>0</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>68200</v>
+        <v>0</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>4</v>
+        <v>2229</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
@@ -4821,35 +4821,35 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
+          <t>정보처리기사</t>
         </is>
       </c>
       <c r="N57" s="7" t="n">
-        <v>410</v>
+        <v>1532</v>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2024-08-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T11:44:45.232Z</t>
+          <t>2024-08-14T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-database-c</t>
+          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
         </is>
       </c>
     </row>
@@ -4859,73 +4859,73 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
+          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>99000</v>
+        <v>82500</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>99000</v>
+        <v>82500</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>151</v>
+        <v>789</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1099</v>
+        <v>2911</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
+          <t>Kubernetes, devops, argocd, container, helm</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>516</v>
+        <v>669</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12T00:00:00.000Z</t>
+          <t>2023-09-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T01:35:54.874Z</t>
+          <t>2026-05-27T08:15:25.352Z</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
         </is>
       </c>
     </row>
@@ -4935,19 +4935,19 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>클로드로 딸깍! 루프 엔지니어링으로 통합 자산관리 시스템 개발하기</t>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>154000</v>
+        <v>0</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>154000</v>
+        <v>0</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>0</v>
@@ -4956,52 +4956,50 @@
         <v>4.9</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>423</v>
+        <v>1099</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 코딩, 풀스택</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), 바이브코딩, AX(에이전트 경험), AI Agent, minio</t>
-        </is>
-      </c>
-      <c r="N59" s="7" t="n">
-        <v>795</v>
-      </c>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="n"/>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23T05:00:00.000Z</t>
+          <t>2026-06-27T04:00:06.000Z</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05T22:46:00.597Z</t>
+          <t>2026-06-30T07:01:04.312Z</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/one-click-with-claud</t>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
         </is>
       </c>
     </row>
@@ -5011,12 +5009,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>시스코 CCNA 함께 공부해요</t>
+          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>ccie_pe_kim</t>
+          <t>최원영</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
@@ -5029,55 +5027,55 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1751</v>
+        <v>1568</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, routing, tcpip</t>
+          <t>인공지능(AI)</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1213</v>
+        <v>32</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T15:00:00.000Z</t>
+          <t>2026-02-27T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25T09:44:13.272Z</t>
+          <t>2026-02-27T06:18:36.692Z</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
         </is>
       </c>
     </row>
@@ -5087,31 +5085,31 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>면접 전에 알고 가면 좋을 것들 - 신입 Java 백엔드 개발자편</t>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>66000</v>
+        <v>88000</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>66000</v>
+        <v>88000</v>
       </c>
       <c r="F61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>69</v>
+        <v>194</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>1627</v>
+        <v>1456</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
@@ -5120,40 +5118,40 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>취업 · 이직, 웹 개발, 백엔드, 풀스택</t>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>기술면접, 이력서, DBMS/RDBMS, tcpip</t>
+          <t>업무 생산성, wiki, obsidian, claude</t>
         </is>
       </c>
       <c r="N61" s="7" t="n">
-        <v>306</v>
+        <v>368</v>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>2023-08-30T15:00:00.000Z</t>
+          <t>2026-04-25T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:42:51.608Z</t>
+          <t>2026-10-08T14:26:56.788Z</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/면접-신입-java-백앤드-개발자</t>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
         </is>
       </c>
     </row>
@@ -5163,31 +5161,31 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+          <t>Claude로 끝내는 실무 업무자동화: 엑셀·문서·PPT부터 Skills·Obsidian까지</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>HappyAI</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6165</v>
+        <v>109</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5196,40 +5194,40 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, routing</t>
+          <t>data-analysis, data-processing, n8n, 프롬프트엔지니어링, claude</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
-        <v>779</v>
+        <v>229</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2026-08-01T09:00:05.000Z</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T09:27:31.006Z</t>
+          <t>2026-10-12T00:06:16.136Z</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+          <t>https://www.inflearn.com/course/mastering-practical-2</t>
         </is>
       </c>
     </row>
@@ -5239,73 +5237,73 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Claude로 끝내는 실무 업무자동화: 엑셀·문서·PPT부터 Skills·Obsidian까지</t>
+          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>HappyAI</t>
+          <t>숀김</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>88000</v>
+        <v>86900</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>0</v>
+        <v>0.3670886075949367</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>data-analysis, data-processing, n8n, 프롬프트엔지니어링, claude</t>
+          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
         </is>
       </c>
       <c r="N63" s="7" t="n">
-        <v>229</v>
+        <v>541</v>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01T09:00:05.000Z</t>
+          <t>2026-09-23T02:30:05.000Z</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T00:06:16.136Z</t>
+          <t>2026-09-29T15:07:55.641Z</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-practical-2</t>
+          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
         </is>
       </c>
     </row>
@@ -5315,31 +5313,31 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 기본편</t>
+          <t>AI를 위한 미적분 — 도함수, 그래디언트, 그리고 신경망이 학습하는 원리</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>코딩맥스 CodingMax</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>88000</v>
+        <v>99000</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>88000</v>
+        <v>99000</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>4932</v>
+        <v>0</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>50478</v>
+        <v>32</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5348,40 +5346,40 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 대학 교육</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>딥러닝 · 머신러닝, 수학</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Spring, 객체지향</t>
+          <t>머신러닝, 딥러닝, 인공신경망, 선형대수학, 미적분, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N64" s="2" t="n">
-        <v>725</v>
+        <v>1093</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2020-09-20T15:00:00.000Z</t>
+          <t>2026-09-13T08:00:08.000Z</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04T15:00:00.555Z</t>
+          <t>2026-09-13T05:41:38.564Z</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
+          <t>https://www.inflearn.com/course/calculus-for-ai-deri</t>
         </is>
       </c>
     </row>
@@ -5391,19 +5389,19 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+          <t>The 10x AI-Native Developer: 회사에서 AI로 압도적 성과를 내는 법</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>딩코딩코</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F65" s="10" t="n">
         <v>0</v>
@@ -5412,50 +5410,52 @@
         <v>4.9</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>1089</v>
+        <v>978</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>AI 개발 활용, 풀스택, AI 실무 활용</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="n"/>
+          <t>Spring Boot, Next.js, 인공지능(AI), claude</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="n">
+        <v>926</v>
+      </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-27T04:00:06.000Z</t>
+          <t>2025-10-01T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30T07:01:04.312Z</t>
+          <t>2026-05-17T14:48:39.414Z</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+          <t>https://www.inflearn.com/course/the-10x-ai-native-de</t>
         </is>
       </c>
     </row>
@@ -5465,19 +5465,19 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>MFC Windows 프로그래밍 - 기본</t>
+          <t>홍정모의 따라하며 배우는 C++</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>홍정모</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>99000</v>
+        <v>176000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>99000</v>
+        <v>176000</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>4.9</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>33</v>
+        <v>395</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>565</v>
+        <v>7125</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5503,35 +5503,35 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>데스크톱 앱 개발, 개발 도구, 프로그래밍 언어, 게임 개발 기타</t>
+          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>mfc, vc++, C++, win32api, sdi, gdi</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>997</v>
+        <v>2907</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2024-02-26T15:00:00.000Z</t>
+          <t>2018-09-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:41:58.198Z</t>
+          <t>2025-08-10T19:46:59.750Z</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mfc-programming-basic</t>
+          <t>https://www.inflearn.com/course/following-c-plus</t>
         </is>
       </c>
     </row>
@@ -5541,73 +5541,73 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
+          <t>[2026] 유니티 엔진 입문 올인원</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>330000</v>
+        <v>165000</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>330000</v>
+        <v>165000</v>
       </c>
       <c r="F67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>532</v>
+        <v>135</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>게임 개발</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>게임 프로그래밍</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>game-programming, 유니티6</t>
         </is>
       </c>
       <c r="N67" s="7" t="n">
-        <v>1048</v>
+        <v>1159</v>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22T17:00:00.000Z</t>
+          <t>2026-06-11T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T22:53:04.634Z</t>
+          <t>2026-06-11T02:13:13.639Z</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
+          <t>https://www.inflearn.com/course/2026-unity-engine-be</t>
         </is>
       </c>
     </row>
@@ -5617,73 +5617,73 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
+          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>남박사</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>33000</v>
+        <v>68200</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>66000</v>
+        <v>68200</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>4</v>
+        <v>287</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>265</v>
+        <v>3407</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
+          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Python, LLM, AI Agent, claude</t>
+          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N68" s="2" t="n">
-        <v>305</v>
+        <v>1143</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T06:30:05.000Z</t>
+          <t>2025-05-06T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T17:31:06.856Z</t>
+          <t>2026-06-12T11:29:01.075Z</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
+          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
         </is>
       </c>
     </row>
@@ -5693,31 +5693,31 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>독하게 시작하는 C 프로그래밍</t>
+          <t>[Unity6] 내가 연출하는 한 편의 이야기, 비주얼노벨 제작</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>Pinous</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>3144</v>
+        <v>113</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
@@ -5726,40 +5726,40 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>게임 개발</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 시스템 · 운영체제</t>
+          <t>게임 프로그래밍, 게임 기획, 게임 개발 기타</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>C, 컴퓨터 구조, assembly-language, vc++</t>
+          <t>C#, Unity, 유니티6</t>
         </is>
       </c>
       <c r="N69" s="7" t="n">
-        <v>1739</v>
+        <v>566</v>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>2023-09-26T15:00:00.000Z</t>
+          <t>2026-05-27T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:29:20.937Z</t>
+          <t>2026-06-16T11:01:40.099Z</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/독하게-시작하는-c프로그래밍</t>
+          <t>https://www.inflearn.com/course/unity6-creating-a-vi</t>
         </is>
       </c>
     </row>
@@ -5769,73 +5769,73 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
+          <t>비전공자도 이해할 수 있는 Docker 입문/실전</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>멍슨상</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>36300</v>
+        <v>88000</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>48400</v>
+        <v>88000</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>9</v>
+        <v>693</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>314</v>
+        <v>14640</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>데브옵스 · 인프라, 백엔드, 클라우드</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, database</t>
+          <t>Docker, container, docker-compose, docker-volume, ecr, docker-image</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1553</v>
+        <v>372</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2025-09-24T07:00:00.000Z</t>
+          <t>2024-06-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T06:06:52.494Z</t>
+          <t>2026-08-30T11:26:39.530Z</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
+          <t>https://www.inflearn.com/course/비전공자-docker-입문-실전</t>
         </is>
       </c>
     </row>
@@ -5845,19 +5845,19 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
+          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>그랩</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>38500</v>
+        <v>198000</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>38500</v>
+        <v>198000</v>
       </c>
       <c r="F71" s="10" t="n">
         <v>0</v>
@@ -5866,52 +5866,52 @@
         <v>5</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>61</v>
+        <v>332</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>SQL, Oracle, database, modeling, SQLD</t>
+          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N71" s="7" t="n">
-        <v>923</v>
+        <v>896</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02T03:00:00.000Z</t>
+          <t>2026-07-23T04:50:00.000Z</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02T00:00:00.000Z</t>
+          <t>2026-08-01T16:24:39.937Z</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
+          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
         </is>
       </c>
     </row>
@@ -5921,31 +5921,31 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>디지털포렌식전문가 2급 필기 핵심 요약집[전자책]</t>
+          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>훈지손</t>
+          <t>김형태</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>38500</v>
+        <v>138600</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>38500</v>
+        <v>198000</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1342</v>
+        <v>480</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5954,40 +5954,40 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>보안, 보안 · 네트워크 자격증</t>
+          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Forensic, 디지털포렌식전문가 2급</t>
+          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>13</v>
+        <v>483</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2023-02-16T15:00:00.000Z</t>
+          <t>2026-05-29T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05T15:57:52.306Z</t>
+          <t>2026-09-26T10:39:08.073Z</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/디지털포렌식전문가-2급-필기-전자책</t>
+          <t>https://www.inflearn.com/course/building-a-marketing</t>
         </is>
       </c>
     </row>
@@ -5997,19 +5997,19 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>비전공자도 이해할 수 있는 Docker 입문/실전</t>
+          <t>옵시디언 마스터 클래스: PKM·AI Second Brain·LLM WiKi 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>조영수(데이먼)</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>88000</v>
+        <v>132000</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>88000</v>
+        <v>132000</v>
       </c>
       <c r="F73" s="10" t="n">
         <v>0</v>
@@ -6018,52 +6018,52 @@
         <v>4.9</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>692</v>
+        <v>166</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>14639</v>
+        <v>1134</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>업무 생산성, 기획 · 경영 · 마케팅, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 백엔드, 클라우드</t>
+          <t>생산성 도구, 기획 · PM· PO, AI 실무 활용</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>Docker, container, docker-compose, docker-volume, ecr, docker-image</t>
+          <t>업무 생산성, obsidian</t>
         </is>
       </c>
       <c r="N73" s="7" t="n">
-        <v>372</v>
+        <v>455</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>2024-06-12T15:00:00.000Z</t>
+          <t>2025-06-25T12:30:00.000Z</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:39.530Z</t>
+          <t>2026-05-08T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-docker-입문-실전</t>
+          <t>https://www.inflearn.com/course/옵시디언-마스터-클래스생산성을-바꾸는-1</t>
         </is>
       </c>
     </row>
@@ -6073,31 +6073,31 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>[2026] 유니티 엔진 입문 올인원</t>
+          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>멍슨상</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>165000</v>
+        <v>36300</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>165000</v>
+        <v>48400</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>135</v>
+        <v>314</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6106,40 +6106,40 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>게임 개발</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>게임 프로그래밍</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>game-programming, 유니티6</t>
+          <t>Python, Java, C, 정보처리기사, database</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1159</v>
+        <v>1553</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11T04:00:00.000Z</t>
+          <t>2025-09-24T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11T02:13:13.639Z</t>
+          <t>2026-10-11T06:06:52.494Z</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/2026-unity-engine-be</t>
+          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
         </is>
       </c>
     </row>
@@ -6149,73 +6149,73 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
+          <t>PMP 합격을 완성하는 250문제 실전 풀이 코스!</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>최원영</t>
+          <t>피엠인사이드</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="F75" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>1560</v>
+        <v>39</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>기획 · PM· PO, 경영 · 전략, 기획 · 경영 · 마케팅 자격증</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI)</t>
+          <t>애자일, 프로젝트 관리, project, waterfall, PMP</t>
         </is>
       </c>
       <c r="N75" s="7" t="n">
-        <v>32</v>
+        <v>512</v>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27T05:00:00.000Z</t>
+          <t>2026-01-14T08:00:00.000Z</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27T06:18:36.692Z</t>
+          <t>2026-01-14T06:08:44.346Z</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
+          <t>https://www.inflearn.com/course/pmp-합격을-완성하는-250문제-실</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
+          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>44000</v>
+        <v>154000</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>44000</v>
+        <v>154000</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>0</v>
@@ -6246,52 +6246,52 @@
         <v>5</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>4071</v>
+        <v>48</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>37227</v>
+        <v>2050</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
+          <t>데이터베이스, 데이터 분석, 풀스택</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>341</v>
+        <v>1270</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2020-12-19T15:00:00.000Z</t>
+          <t>2026-07-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:23:13.295Z</t>
+          <t>2026-07-28T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
         </is>
       </c>
     </row>
@@ -6301,73 +6301,73 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>대규모 언어 모델, 핵심만 빠르게!</t>
+          <t>한 입 크기로 잘라먹는 Next.js</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>44000</v>
+        <v>48400</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>44000</v>
+        <v>48400</v>
       </c>
       <c r="F77" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>10</v>
+        <v>639</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>138</v>
+        <v>6028</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>인공지능 기타, 자연어 처리, 딥러닝 · 머신러닝</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>인공신경망, PyTorch, LLM, Fine-Tuning, RNN</t>
+          <t>React, TypeScript, Next.js</t>
         </is>
       </c>
       <c r="N77" s="7" t="n">
-        <v>476</v>
+        <v>934</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>2025-11-12T11:00:00.000Z</t>
+          <t>2024-08-18T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31T09:31:50.184Z</t>
+          <t>2026-07-13T03:56:34.520Z</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/대규모-언어-모델-핵심만-빠르게</t>
+          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
         </is>
       </c>
     </row>
@@ -6377,73 +6377,73 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>머신러닝, 핵심만 빠르게!</t>
+          <t>클로드로 딸깍! 루프 엔지니어링으로 통합 자산관리 시스템 개발하기</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>44000</v>
+        <v>154000</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>44000</v>
+        <v>154000</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>192</v>
+        <v>423</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 인공지능 기타</t>
+          <t>AI 실무 활용, AI 코딩, 풀스택</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>인공신경망, CNN, linear-regression, RNN, ensembles</t>
+          <t>인공지능(AI), 바이브코딩, AX(에이전트 경험), AI Agent, minio</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>382</v>
+        <v>795</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11T09:30:00.000Z</t>
+          <t>2026-06-23T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12T09:18:24.857Z</t>
+          <t>2026-07-05T22:46:00.597Z</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/머신러닝-핵심만-빠르게</t>
+          <t>https://www.inflearn.com/course/one-click-with-claud</t>
         </is>
       </c>
     </row>
@@ -6453,73 +6453,73 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>초당 1,000,000++ RPS를 처리하는 네이버 개발자의 Valkey</t>
+          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>코드바나나</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>56760</v>
+        <v>148500</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>141900</v>
+        <v>148500</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>143</v>
+        <v>3753</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 알고리즘 · 자료구조, 데이터베이스</t>
+          <t>데브옵스 · 인프라, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, 빅데이터, TypeScript, DBMS/RDBMS, Redis, MSA, 데이터 엔지니어링</t>
+          <t>AWS, 네트워크, AWS SAA</t>
         </is>
       </c>
       <c r="N79" s="7" t="n">
-        <v>422</v>
+        <v>1450</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2022-06-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29T21:47:01.350Z</t>
+          <t>2026-10-12T03:07:28.063Z</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/valkey-vs-redis-a-na</t>
+          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
         </is>
       </c>
     </row>
@@ -6529,31 +6529,31 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>비전공자도 이해할 수 있는 쿠버네티스 입문/실전</t>
+          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>88000</v>
+        <v>79200</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>88000</v>
+        <v>79200</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1676</v>
+        <v>6756</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6562,40 +6562,40 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 백엔드, 클라우드</t>
+          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Kubernetes, Docker, infrastructure, MSA, container</t>
+          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>287</v>
+        <v>357</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2024-11-21T15:00:00.000Z</t>
+          <t>2025-07-11T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:38.775Z</t>
+          <t>2025-11-10T22:31:31.977Z</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-쿠버네티스-입문-실전</t>
+          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
         </is>
       </c>
     </row>
@@ -6605,73 +6605,73 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>클로드코드 Harness 와 Mods, Graph Engineering 심화 CLI 하네스 엔지니어링 실무</t>
+          <t>하루만에 끝내는 Herdr: 멀티플렉서, 에이전트, SSH 맥미니-모바일 원격 접속</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>미국달팽이</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>88000</v>
+        <v>77000</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>781</v>
+        <v>120</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 풀스택, AI 실무 활용</t>
+          <t>개발 도구, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), claude, 바이브코딩, 하네스</t>
+          <t>tmux, claude, codex, terminal, AI Agent, macOS, Git</t>
         </is>
       </c>
       <c r="N81" s="7" t="n">
-        <v>503</v>
+        <v>248</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24T22:00:00.000Z</t>
+          <t>2026-09-13T12:00:06.000Z</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09T19:56:24.049Z</t>
+          <t>2026-09-27T09:02:14.111Z</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-harness</t>
+          <t>https://www.inflearn.com/course/herdr-in-one-day-mul</t>
         </is>
       </c>
     </row>
@@ -6681,31 +6681,31 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>RNN의 모든 것 | 트랜스포머 강의 TTT 무료 공개</t>
+          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>37</v>
+        <v>5459</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6714,40 +6714,40 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>RNN, 딥러닝</t>
+          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
         </is>
       </c>
       <c r="N82" s="2" t="n">
-        <v>61</v>
+        <v>1001</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T11:00:10.000Z</t>
+          <t>2025-03-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T17:01:56.962Z</t>
+          <t>2025-09-14T05:27:02.800Z</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/everything-about-rnn</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
         </is>
       </c>
     </row>
@@ -6757,19 +6757,19 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
+          <t>MATLAB/Simulink 자동차 MBD 실무 입문: 모델링부터 검증과 코드 생성까지</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>82500</v>
+        <v>129800</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>82500</v>
+        <v>129800</v>
       </c>
       <c r="F83" s="10" t="n">
         <v>0</v>
@@ -6778,10 +6778,10 @@
         <v>4.9</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>789</v>
+        <v>12</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>2910</v>
+        <v>99</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
@@ -6790,40 +6790,40 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>모빌리티, 임베디드 · IoT</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, argocd, container, helm</t>
+          <t>MATLAB</t>
         </is>
       </c>
       <c r="N83" s="7" t="n">
-        <v>669</v>
+        <v>376</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>2023-09-11T15:00:00.000Z</t>
+          <t>2026-06-27T10:30:05.000Z</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>2026-05-27T08:15:25.352Z</t>
+          <t>2026-08-05T12:40:21.603Z</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
+          <t>https://www.inflearn.com/course/introduction-to-prac</t>
         </is>
       </c>
     </row>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>기초부터 따라하는 디지털포렌식</t>
+          <t>AI 에이전트 엔지니어링</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>훈지손</t>
+          <t>민혁</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
@@ -6851,55 +6851,55 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6205</v>
+        <v>2059</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Forensic</t>
+          <t>Python, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>545</v>
+        <v>322</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2022-02-22T15:00:00.000Z</t>
+          <t>2026-04-07T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2022-05-31T11:24:15.993Z</t>
+          <t>2026-04-07T02:58:08.781Z</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/기초-디지털-포렌식</t>
+          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
         </is>
       </c>
     </row>
@@ -6909,73 +6909,73 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>헤르메스, 코덱스, LLM Wiki로 익히는 실무형 AI 하네스 엔지니어링</t>
+          <t>외워서 끝내는 네트워크 핵심이론 - 기초</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Masocampus</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>48510</v>
+        <v>77000</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>69300</v>
+        <v>77000</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>6</v>
+        <v>797</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>32</v>
+        <v>8577</v>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>네트워크, 개발 · 프로그래밍 기타, 웹 개발</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, AX(에이전트 경험), LLM, wiki, 하네스, 프롬프트엔지니어링</t>
+          <t>네트워크, 프로토콜</t>
         </is>
       </c>
       <c r="N85" s="7" t="n">
-        <v>244</v>
+        <v>431</v>
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17T06:00:06.000Z</t>
+          <t>2022-09-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11T06:33:52.548Z</t>
+          <t>2025-05-13T07:25:51.956Z</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hands-on-ai-harness</t>
+          <t>https://www.inflearn.com/course/네트워크-핵심이론-기초</t>
         </is>
       </c>
     </row>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>기초 탄탄! 독하게 시작하는 Java - Part 2 : OOP와 JVM</t>
+          <t>면접 전에 알고 가면 좋을 것들 - 신입 Java 백엔드 개발자편</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7006,10 +7006,10 @@
         <v>5</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5976</v>
+        <v>1627</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -7018,40 +7018,40 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드</t>
+          <t>취업 · 이직, 웹 개발, 백엔드, 풀스택</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향, jvm, data-structure</t>
+          <t>기술면접, 이력서, DBMS/RDBMS, tcpip</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>1215</v>
+        <v>306</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2024-11-20T15:00:00.000Z</t>
+          <t>2023-08-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2025-07-09T04:47:07.588Z</t>
+          <t>2025-05-13T07:42:51.608Z</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/독하게-시작하는-java-part2</t>
+          <t>https://www.inflearn.com/course/면접-신입-java-백앤드-개발자</t>
         </is>
       </c>
     </row>
@@ -7061,73 +7061,73 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
+          <t>스프링 핵심 원리 - 기본편</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>128700</v>
+        <v>88000</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>128700</v>
+        <v>88000</v>
       </c>
       <c r="F87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>38</v>
+        <v>4933</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>573</v>
+        <v>50478</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 오피스, 업무 자동화</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
+          <t>Spring, 객체지향</t>
         </is>
       </c>
       <c r="N87" s="7" t="n">
-        <v>832</v>
+        <v>725</v>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05T16:00:00.000Z</t>
+          <t>2020-09-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07T06:36:11.731Z</t>
+          <t>2025-06-04T15:00:00.555Z</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/starting-with-claude</t>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
         </is>
       </c>
     </row>
@@ -7137,19 +7137,19 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>GPT는 어떻게 문장을 생성할까? | LLM·ViT 강의 ATT 무료 공개</t>
+          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>0</v>
@@ -7158,52 +7158,52 @@
         <v>5</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>gpt, 딥러닝</t>
+          <t>SQL, Oracle, database, modeling, SQLD</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>35</v>
+        <v>923</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T09:00:09.000Z</t>
+          <t>2026-09-02T03:00:00.000Z</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T17:04:49.947Z</t>
+          <t>2026-09-02T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-does-gpt-generat</t>
+          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
         </is>
       </c>
     </row>
@@ -7213,73 +7213,73 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>AI 에이전트 엔지니어링</t>
+          <t>트래픽 급증을 견디는 서버 시스템 설계 - Coupon 발급 서비스</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>민혁</t>
+          <t>한조각</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0</v>
+        <v>41250</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>2056</v>
+        <v>810</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>백엔드, 웹 개발, 데이터베이스</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>Python, 인공지능(AI), RAG, AI Agent</t>
+          <t>Java, Kotlin, MySQL, Docker, Spring Boot, Kafka, Redis</t>
         </is>
       </c>
       <c r="N89" s="7" t="n">
-        <v>322</v>
+        <v>618</v>
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07T05:00:00.000Z</t>
+          <t>2026-08-09T17:00:05.000Z</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07T02:58:08.781Z</t>
+          <t>2026-08-27T15:21:43.118Z</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
+          <t>https://www.inflearn.com/course/designing-a-server-s</t>
         </is>
       </c>
     </row>
@@ -7289,31 +7289,31 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>실리콘 밸리 엔지니어와 함께하는 Local LLM 완전 정복 (LM Studio &amp; Ollama &amp; Ollaya)</t>
+          <t>AI 한달 구독료로 나만의 AI 에이전트 만들기 (feat. 인터넷 없이 내 PC에서 돌아가는)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>kmmom591</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>41250</v>
+        <v>16940</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>55000</v>
+        <v>24200</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>684</v>
+        <v>5</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7322,40 +7322,40 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
+          <t>AI 실무 활용, AI 크리에이티브, AI 시작하기</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), LLM, AI Agent</t>
+          <t>Python, 딥러닝, agents, 인공지능(AI), LLM, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17T18:00:00.000Z</t>
+          <t>2026-10-11T07:30:06.000Z</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T05:15:20.298Z</t>
+          <t>2026-10-11T08:58:31.423Z</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-local-llm</t>
+          <t>https://www.inflearn.com/course/build-your-own-ai-ag-1</t>
         </is>
       </c>
     </row>
@@ -7365,73 +7365,73 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>단 60분! 파이썬 핵심 개념 초압축 강의 - 이론보다 이해 중심</t>
+          <t>김영한의 실전 데이터베이스 - 기본편</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>딩코딩코</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F91" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>7095</v>
+        <v>5392</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
-        <v>64</v>
+        <v>821</v>
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>2024-09-22T15:00:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10T00:47:07.734Z</t>
+          <t>2026-08-06T12:14:20.961Z</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/파이썬-핵심개념-압축강의</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>외워서 끝내는 네트워크 핵심이론 - 기초</t>
+          <t>독하게 시작하는 C 프로그래밍</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>77000</v>
+        <v>99000</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>77000</v>
+        <v>99000</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>0</v>
@@ -7462,52 +7462,52 @@
         <v>4.9</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>797</v>
+        <v>242</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>8577</v>
+        <v>3144</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>네트워크, 개발 · 프로그래밍 기타, 웹 개발</t>
+          <t>프로그래밍 언어, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>네트워크, 프로토콜</t>
+          <t>C, 컴퓨터 구조, assembly-language, vc++</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>431</v>
+        <v>1739</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2022-09-26T15:00:00.000Z</t>
+          <t>2023-09-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:25:51.956Z</t>
+          <t>2025-05-13T07:29:20.937Z</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/네트워크-핵심이론-기초</t>
+          <t>https://www.inflearn.com/course/독하게-시작하는-c프로그래밍</t>
         </is>
       </c>
     </row>
@@ -7517,31 +7517,31 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>MLE부터 AE·VAE 입문까지 | 디퓨전 강의 TTD 무료 공개</t>
+          <t>타입스크립트로 배우는 리액트(React.js) : 기초부터 최신 기술까지 완벽하게</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>수코딩</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0</v>
+        <v>79200</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>31</v>
+        <v>622</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
@@ -7550,40 +7550,40 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝</t>
+          <t>프론트엔드, 웹 개발, 모바일 앱 개발</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>딥러닝</t>
+          <t>React, react-router, redux-toolkit, zustand, react.js</t>
         </is>
       </c>
       <c r="N93" s="7" t="n">
-        <v>146</v>
+        <v>1615</v>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T23:30:06.000Z</t>
+          <t>2025-06-08T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T15:50:32.518Z</t>
+          <t>2026-05-25T06:25:45.941Z</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-mle-to-an-intro</t>
+          <t>https://www.inflearn.com/course/typescript-react-perfect-course</t>
         </is>
       </c>
     </row>
@@ -7593,73 +7593,73 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>이야기로 배우는 1on1: 팀장을 위한 면담 대화법</t>
+          <t>절대강좌! 유니티 6 - TPS 게임으로 배우는 유니티 마스터클래스</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>오픈러닝랩</t>
+          <t>이재현</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>18150</v>
+        <v>99000</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>36300</v>
+        <v>99000</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>8</v>
+        <v>195</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발</t>
+          <t>게임 개발</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발 기타</t>
+          <t>게임 프로그래밍</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>커뮤니케이션</t>
+          <t>Unity, C#</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>226</v>
+        <v>979</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T02:00:12.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T03:17:00.759Z</t>
+          <t>2025-07-02T03:41:32.036Z</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/learning-1-on-1s-thr</t>
+          <t>https://www.inflearn.com/course/절대강좌-유니티6-tps</t>
         </is>
       </c>
     </row>
@@ -7669,73 +7669,73 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
+          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>154000</v>
+        <v>33000</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>154000</v>
+        <v>66000</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>2048</v>
+        <v>265</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 풀스택</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
+          <t>Python, LLM, AI Agent, claude</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
-        <v>1270</v>
+        <v>305</v>
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00.000Z</t>
+          <t>2026-09-23T06:30:05.000Z</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28T00:00:00.000Z</t>
+          <t>2026-09-26T17:31:06.856Z</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
+          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
         </is>
       </c>
     </row>
@@ -7745,73 +7745,73 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>하루만에 끝내는 Herdr: 멀티플렉서, 에이전트, SSH 맥미니-모바일 원격 접속</t>
+          <t>비개발자 4주만에 수익화 서비스 만들기: AI 바이브코딩 웹 + 앱 ALL IN ONE</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>딩코딩코</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>77000</v>
+        <v>165000</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>77000</v>
+        <v>165000</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>9</v>
+        <v>318</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>119</v>
+        <v>1908</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>개발 도구, AI에이전트 개발, AI 개발 활용</t>
+          <t>AI 실무 활용, AI에이전트 개발, 웹 개발, 모바일 앱 개발</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>tmux, claude, codex, terminal, AI Agent, macOS, Git</t>
+          <t>Flutter, Next.js, cursor, supabase, 바이브코딩</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>248</v>
+        <v>675</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:00:06.000Z</t>
+          <t>2025-07-19T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T09:02:14.111Z</t>
+          <t>2026-03-02T12:53:10.998Z</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/herdr-in-one-day-mul</t>
+          <t>https://www.inflearn.com/course/비개발자-4주만에-수익화-서비스-만들</t>
         </is>
       </c>
     </row>
@@ -7821,19 +7821,19 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>오브젝트 - 기초편</t>
+          <t>GPT는 어떻게 문장을 생성할까? | LLM·ViT 강의 ATT 무료 공개</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>조영호</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="F97" s="10" t="n">
         <v>0</v>
@@ -7842,10 +7842,10 @@
         <v>5</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>1829</v>
+        <v>47</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
@@ -7854,40 +7854,40 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>소프트웨어 설계, 객체지향</t>
+          <t>gpt, 딥러닝</t>
         </is>
       </c>
       <c r="N97" s="7" t="n">
-        <v>301</v>
+        <v>35</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>2024-07-25T15:00:00.000Z</t>
+          <t>2026-10-06T09:00:09.000Z</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T23:18:05.849Z</t>
+          <t>2026-10-06T17:04:49.947Z</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/오브젝트-기초편-객체지향</t>
+          <t>https://www.inflearn.com/course/how-does-gpt-generat</t>
         </is>
       </c>
     </row>
@@ -7897,31 +7897,31 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>실무에 바로 적용하는 Spring AI: Spring 서비스에 챗봇·RAG·MCP 도입하기</t>
+          <t>개발자 개념 장착 - 프로그래밍 개발에 필요한 필수 개념과 핵심 이론정리</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 시니</t>
+          <t>코딩하는기술사</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>61600</v>
+        <v>0</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>586</v>
+        <v>1632</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7930,40 +7930,38 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 백엔드, AI 코딩</t>
+          <t>개발 · 프로그래밍 기타, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Spring Boot, Elasticsearch, vector-database, LLM, RAG, Spring AI, MCP</t>
-        </is>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>439</v>
-      </c>
+          <t>아키텍처, 컴퓨터 구조, 기술면접, 소프트웨어 설계, 문제해결능력</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="n"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12T23:30:00.000Z</t>
+          <t>2026-01-19T13:00:00.000Z</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:43.252Z</t>
+          <t>2026-01-30T22:11:57.790Z</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/spring-ai-in-practic</t>
+          <t>https://www.inflearn.com/course/개발자-개념-장착-프로그래밍-개발에</t>
         </is>
       </c>
     </row>
@@ -7973,31 +7971,31 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>토비의 클린 스프링 - 도메인 모델 패턴과 헥사고날 아키텍처 Part 1</t>
+          <t>RNN의 모든 것 | 트랜스포머 강의 TTT 무료 공개</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>토비</t>
+          <t>혁펜하임</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>2570</v>
+        <v>39</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
@@ -8006,40 +8004,40 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>백엔드</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, Spring Boot, JPA, hexagonal-architecture, 리팩터링, DDD</t>
+          <t>RNN, 딥러닝</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
-        <v>872</v>
+        <v>61</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>2025-06-18T15:00:00.000Z</t>
+          <t>2026-10-06T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>2025-10-23T07:53:22.134Z</t>
+          <t>2026-10-06T17:01:56.962Z</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/토비-클린스프링-도메인모델패턴-헥사고날-part1</t>
+          <t>https://www.inflearn.com/course/everything-about-rnn</t>
         </is>
       </c>
     </row>
@@ -8049,31 +8047,31 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>[Rookiss] 클로드 하네스 입문 (인터랙티브 교재)</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>99000</v>
+        <v>44330</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>99000</v>
+        <v>68200</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -8082,40 +8080,40 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Python, 인공지능(AI), AI Agent</t>
+          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>225</v>
+        <v>410</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T09:30:06.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04T05:39:18.684Z</t>
+          <t>2026-10-10T12:02:44.178Z</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/rookiss-introduction-2</t>
+          <t>https://www.inflearn.com/course/database-concepts-yo</t>
         </is>
       </c>
     </row>
@@ -8125,31 +8123,31 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>44550</v>
+        <v>44330</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>59400</v>
+        <v>68200</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>224</v>
+        <v>5</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
@@ -8158,40 +8156,40 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
+          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
         </is>
       </c>
       <c r="N101" s="7" t="n">
-        <v>311</v>
+        <v>410</v>
       </c>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31T10:30:06.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12T14:30:32.966Z</t>
+          <t>2026-10-10T11:44:45.232Z</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
+          <t>https://www.inflearn.com/course/essential-database-c</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8346,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-13T15:48:21+09:00</t>
+          <t>2026-10-14T13:55:49+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -605,22 +605,22 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
+          <t>Spring AI LLM 비용 모니터링 — Actuator 한 줄로 만드는 토큰 대시보드</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>84700</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -629,49 +629,49 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>245</v>
+        <v>144</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화</t>
+          <t>AI 개발 활용, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
+          <t>Spring AI, Prometheus, grafana, spring-boot-actuator, 인공지능(AI), Spring Boot, IntelliJ IDEA</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T09:30:05.000Z</t>
+          <t>2026-10-13T23:30:05.000Z</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T14:30:36.470Z</t>
+          <t>2026-10-13T22:06:45.263Z</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
+          <t>https://www.inflearn.com/course/spring-ai-llm-cost-m</t>
         </is>
       </c>
     </row>
@@ -681,31 +681,31 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Claude Code 실전 업무 자동화 : 코드 없이 나만의 AI 에이전트 만들기</t>
+          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>일잘러 장피엠</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0</v>
+        <v>108900</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>2475</v>
+        <v>256</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -719,35 +719,35 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
+          <t>AI 실무 활용, 업무 자동화</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>claude, codex, MCP, No-code</t>
+          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T05:00:08.000Z</t>
+          <t>2026-10-04T09:30:05.000Z</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T01:55:19.117Z</t>
+          <t>2026-10-14T16:38:31.831Z</t>
         </is>
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-workflow-a</t>
+          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
         <v>6</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -833,73 +833,73 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
+          <t>Claude Code 실전 업무 자동화 : 코드 없이 나만의 AI 에이전트 만들기</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>일잘러 장피엠</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>43560</v>
+        <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>108900</v>
+        <v>0</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>446</v>
+        <v>2549</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
+          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
+          <t>claude, codex, MCP, No-code</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-10-01T05:00:08.000Z</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29T06:47:12.230Z</t>
+          <t>2026-10-05T01:55:19.117Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
+          <t>https://www.inflearn.com/course/practical-workflow-a</t>
         </is>
       </c>
     </row>
@@ -909,73 +909,73 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
+          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>49500</v>
+        <v>43560</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>99000</v>
+        <v>108900</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>147</v>
+        <v>451</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라</t>
+          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Linux, AWS, bash, ubuntu, nginx</t>
+          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>726</v>
+        <v>321</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T07:00:10.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T02:24:25.825Z</t>
+          <t>2026-08-29T06:47:12.230Z</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
+          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
         </is>
       </c>
     </row>
@@ -985,31 +985,31 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
+          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>198000</v>
+        <v>49500</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>198000</v>
+        <v>99000</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1636</v>
+        <v>9</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11286</v>
+        <v>156</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
@@ -1018,40 +1018,40 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>React, 인공지능(AI), claude</t>
+          <t>Linux, AWS, bash, ubuntu, nginx</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>1254</v>
+        <v>721</v>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T09:00:00.000Z</t>
+          <t>2026-10-06T07:00:10.000Z</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18T03:54:49.011Z</t>
+          <t>2026-10-15T03:53:50.016Z</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
+          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
         </is>
       </c>
     </row>
@@ -1061,19 +1061,19 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
+          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>퇴근후딴짓</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>121000</v>
+        <v>198000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>121000</v>
+        <v>198000</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>4.9</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>929</v>
+        <v>1641</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6017</v>
+        <v>11311</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1094,40 +1094,40 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 데이터 분석</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
+          <t>React, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1560</v>
+        <v>1254</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2022-12-12T15:00:00.000Z</t>
+          <t>2025-11-19T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T00:43:26.587Z</t>
+          <t>2026-08-18T03:54:49.011Z</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
+          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
         </is>
       </c>
     </row>
@@ -1137,73 +1137,73 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
+          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>한조각</t>
+          <t>퇴근후딴짓</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>19800</v>
+        <v>121000</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>66000</v>
+        <v>121000</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>3</v>
+        <v>929</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>235</v>
+        <v>6022</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
+          <t>데이터 사이언스 자격증, 데이터 분석</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
+          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>538</v>
+        <v>1576</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T20:30:05.000Z</t>
+          <t>2022-12-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T18:51:20.390Z</t>
+          <t>2026-10-14T10:04:18.317Z</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-service-deploym</t>
+          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
         </is>
       </c>
     </row>
@@ -1234,10 +1234,10 @@
         <v>4.8</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5715</v>
+        <v>5719</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -1310,10 +1310,10 @@
         <v>4.9</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>13420</v>
+        <v>13462</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -1365,73 +1365,73 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
+          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>김대현</t>
+          <t>한조각</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6600</v>
+        <v>19800</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>11000</v>
+        <v>66000</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>8</v>
+        <v>238</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 풀스택, 프로그래밍 언어</t>
+          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>89</v>
+        <v>538</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:00:07.000Z</t>
+          <t>2026-09-29T20:30:05.000Z</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T02:52:17.360Z</t>
+          <t>2026-09-29T18:51:20.390Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
+          <t>https://www.inflearn.com/course/from-service-deploym</t>
         </is>
       </c>
     </row>
@@ -1441,73 +1441,71 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>진짜! 타입스크립트 - 타입 설계부터 타입 레벨 프로그래밍까지</t>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>코딩맥스 CodingMax</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>5</v>
+        <v>4662</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, 함수형 프로그래밍, TypeScript, Node.js</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>3475</v>
-      </c>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n"/>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T01:00:07.000Z</t>
+          <t>2026-01-27T10:00:00.000Z</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T01:50:40.027Z</t>
+          <t>2026-06-30T00:59:39.967Z</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/really-typescript-fr</t>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
         </is>
       </c>
     </row>
@@ -1517,19 +1515,19 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>198000</v>
+        <v>88000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>198000</v>
+        <v>88000</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
@@ -1538,52 +1536,52 @@
         <v>4.9</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>50</v>
+        <v>269</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>305</v>
+        <v>1367</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>api, trading, codex, 바이브코딩</t>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>628</v>
+        <v>309</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T01:30:06.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T08:59:09.803Z</t>
+          <t>2026-08-30T11:28:44.702Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/create-an-automated</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -1593,73 +1591,73 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>37950</v>
+        <v>89100</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>75900</v>
+        <v>89100</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>212</v>
+        <v>1738</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
+          <t>security, CPPG(개인정보관리사)</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>641</v>
+        <v>727</v>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-28T10:30:06.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T01:52:33.960Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -1669,31 +1667,31 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>김영한의 실전 자바 - 기본편</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>268</v>
+        <v>2404</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1363</v>
+        <v>28224</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1707,35 +1705,35 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>309</v>
+        <v>1012</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:44.702Z</t>
+          <t>2025-12-23T06:52:23.926Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1743,12 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
@@ -1763,13 +1761,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>414</v>
+        <v>311</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>4649</v>
+        <v>3995</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
@@ -1778,38 +1776,40 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n"/>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27T10:00:00.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30T00:59:39.967Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -1819,31 +1819,31 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>89100</v>
+        <v>49500</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>89100</v>
+        <v>99000</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>236</v>
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1734</v>
+        <v>87</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1852,40 +1852,40 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
+          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>727</v>
+        <v>363</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2026-09-16T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2026-09-30T03:16:06.187Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/ai-automated-trading</t>
         </is>
       </c>
     </row>
@@ -1895,73 +1895,73 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Hiro Son</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>49500</v>
+        <v>198000</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>198000</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>18</v>
+        <v>1614</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>150</v>
+        <v>1650</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T17:30:06.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T00:53:13.219Z</t>
+          <t>2026-10-14T02:26:30.439Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -1971,73 +1971,73 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>김대현</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>198000</v>
+        <v>6600</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>198000</v>
+        <v>11000</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1613</v>
+        <v>9</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>백엔드, 풀스택, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1650</v>
+        <v>89</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2026-10-13T05:00:07.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T02:26:30.439Z</t>
+          <t>2026-10-13T02:52:17.360Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
         </is>
       </c>
     </row>
@@ -2047,73 +2047,73 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법)</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>49500</v>
+        <v>55000</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>99000</v>
+        <v>55000</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>83</v>
+        <v>659</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>363</v>
+        <v>196</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -2123,73 +2123,73 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
+          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>마일드코드</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>239800</v>
+        <v>37950</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>239800</v>
+        <v>75900</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>51</v>
+        <v>214</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
+          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
+          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>480</v>
+        <v>641</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:00:33.000Z</t>
+          <t>2026-09-28T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:25:37.776Z</t>
+          <t>2026-09-29T01:52:33.960Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-for-non</t>
+          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
         </is>
       </c>
     </row>
@@ -2199,73 +2199,73 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>진짜! 타입스크립트 - 타입 설계부터 타입 레벨 프로그래밍까지</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>코딩맥스 CodingMax</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>3978</v>
+        <v>6</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>JavaScript, 함수형 프로그래밍, TypeScript, Node.js</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>90</v>
+        <v>3475</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2026-10-13T01:00:07.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2026-10-13T01:50:40.027Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/really-typescript-fr</t>
         </is>
       </c>
     </row>
@@ -2275,31 +2275,31 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>Hiro Son</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>44000</v>
+        <v>49500</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>44000</v>
+        <v>198000</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8416</v>
+        <v>19</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2308,40 +2308,40 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>353</v>
+        <v>150</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2026-10-07T17:30:06.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2026-10-10T00:53:13.219Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
         </is>
       </c>
     </row>
@@ -2351,73 +2351,73 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 기본편</t>
+          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>44000</v>
+        <v>198000</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>44000</v>
+        <v>198000</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>2403</v>
+        <v>50</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>28222</v>
+        <v>305</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>api, trading, codex, 바이브코딩</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>1012</v>
+        <v>628</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-09-09T01:30:06.000Z</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2025-12-23T06:52:23.926Z</t>
+          <t>2026-10-11T08:59:09.803Z</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+          <t>https://www.inflearn.com/course/create-an-automated</t>
         </is>
       </c>
     </row>
@@ -2427,73 +2427,73 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
+          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>알고런 데이터코드 연구소</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>330000</v>
+        <v>79200</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>330000</v>
+        <v>79200</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>533</v>
+        <v>591</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1048</v>
+        <v>785</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T17:00:00.000Z</t>
+          <t>2025-04-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T22:53:04.634Z</t>
+          <t>2026-07-02T07:40:07.999Z</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
+          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -2512,64 +2512,64 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>48400</v>
+        <v>99000</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>48400</v>
+        <v>99000</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1559</v>
+        <v>153</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>15626</v>
+        <v>1107</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>1114</v>
+        <v>516</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>2022-01-26T15:00:00.000Z</t>
+          <t>2026-05-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13T00:57:34.805Z</t>
+          <t>2026-09-21T01:35:54.874Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-리액트</t>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
         </is>
       </c>
     </row>
@@ -2579,73 +2579,73 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>인프런</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>110</v>
+        <v>1401</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>656</v>
+        <v>34394</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>196</v>
+        <v>857</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2019-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2026-09-18T05:48:10.725Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
         </is>
       </c>
     </row>
@@ -2655,73 +2655,73 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>제어쟁이</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>550000</v>
+        <v>88000</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>550000</v>
+        <v>88000</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>605</v>
+        <v>1462</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 모빌리티</t>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>임베디드, stm32, hardware, motordriver, artwork</t>
+          <t>업무 생산성, wiki, obsidian, claude</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>1017</v>
+        <v>368</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2025-06-15T15:00:00.000Z</t>
+          <t>2026-04-25T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13T09:06:49.556Z</t>
+          <t>2026-10-08T14:26:56.788Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -2807,35 +2807,35 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
+          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0</v>
+        <v>747</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>50</v>
+        <v>11838</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -2845,35 +2845,35 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>1240</v>
+        <v>517</v>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T15:00:07.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T03:23:49.530Z</t>
+          <t>2025-08-31T09:28:51.006Z</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
         </is>
       </c>
     </row>
@@ -2883,19 +2883,19 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>99000</v>
+        <v>48400</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>99000</v>
+        <v>48400</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>0</v>
@@ -2904,52 +2904,52 @@
         <v>4.9</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>143</v>
+        <v>1560</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>903</v>
+        <v>15627</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
+          <t>JavaScript, React, Node.js</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>657</v>
+        <v>1114</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T05:00:00.000Z</t>
+          <t>2022-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T06:39:46.390Z</t>
+          <t>2026-06-13T00:57:34.805Z</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/codex-true-education</t>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
         </is>
       </c>
     </row>
@@ -2959,73 +2959,73 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
+          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>69300</v>
+        <v>440000</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>99000</v>
+        <v>484000</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>0.3</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
+          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
+          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08T11:00:10.000Z</t>
+          <t>2026-10-04T05:30:05.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T17:09:46.044Z</t>
+          <t>2026-10-11T15:08:50.737Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
+          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
         </is>
       </c>
     </row>
@@ -3035,73 +3035,73 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
+          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>마일드코드</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>49500</v>
+        <v>239800</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>99000</v>
+        <v>239800</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
+          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>370</v>
+        <v>480</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T10:00:08.000Z</t>
+          <t>2026-09-21T09:00:33.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T07:55:47.247Z</t>
+          <t>2026-10-13T14:25:37.776Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-latest</t>
+          <t>https://www.inflearn.com/course/claude-code-for-non</t>
         </is>
       </c>
     </row>
@@ -3111,19 +3111,19 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0</v>
@@ -3132,52 +3132,52 @@
         <v>5</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>747</v>
+        <v>38</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>11823</v>
+        <v>536</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>517</v>
+        <v>1048</v>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2025-08-31T09:28:51.006Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -3187,31 +3187,31 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
+          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>남박사</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>440000</v>
+        <v>68200</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>484000</v>
+        <v>68200</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>4</v>
+        <v>288</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18</v>
+        <v>3411</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3220,40 +3220,40 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
+          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
+          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>204</v>
+        <v>1143</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T05:30:05.000Z</t>
+          <t>2025-05-06T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:50.737Z</t>
+          <t>2026-06-12T11:29:01.075Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
+          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
         </is>
       </c>
     </row>
@@ -3263,31 +3263,31 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
+          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>알고런 데이터코드 연구소</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>79200</v>
+        <v>99000</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>79200</v>
+        <v>99000</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>589</v>
+        <v>904</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
@@ -3296,40 +3296,40 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
+          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>785</v>
+        <v>657</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2025-04-07T15:00:00.000Z</t>
+          <t>2026-07-20T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02T07:40:07.999Z</t>
+          <t>2026-10-11T06:39:46.390Z</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
+          <t>https://www.inflearn.com/course/codex-true-education</t>
         </is>
       </c>
     </row>
@@ -3339,31 +3339,31 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3141</v>
+        <v>616</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>57306</v>
+        <v>8417</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3377,35 +3377,35 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>개발 도구</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>Git, GitHub, github-actions, git-commands</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>771</v>
+        <v>353</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2022-01-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28T11:59:57.298Z</t>
+          <t>2026-06-03T09:18:28.574Z</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
         </is>
       </c>
     </row>
@@ -3415,73 +3415,73 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
+          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>99000</v>
+        <v>55000</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>99000</v>
+        <v>55000</v>
       </c>
       <c r="F39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>152</v>
+        <v>42</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1102</v>
+        <v>480</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
+          <t>SQLD, SQL, Oracle, MSSQL</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12T00:00:00.000Z</t>
+          <t>2026-01-13T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-21T01:35:54.874Z</t>
+          <t>2026-10-12T07:12:46.551Z</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
+          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0</v>
@@ -3512,14 +3512,14 @@
         <v>5</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1263</v>
+        <v>3141</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12542</v>
+        <v>57315</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3538,26 +3538,26 @@
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1161</v>
+        <v>771</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2026-01-28T11:59:57.298Z</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
         </is>
       </c>
     </row>
@@ -3567,73 +3567,73 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
+          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>인프런</t>
+          <t>YoungJea Oh</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>33000</v>
+        <v>49500</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>33000</v>
+        <v>99000</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>1401</v>
+        <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>34390</v>
+        <v>29</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>857</v>
+        <v>370</v>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>2019-06-01T15:00:00.000Z</t>
+          <t>2026-10-02T10:00:08.000Z</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18T05:48:10.725Z</t>
+          <t>2026-10-02T07:55:47.247Z</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
+          <t>https://www.inflearn.com/course/mastering-the-latest</t>
         </is>
       </c>
     </row>
@@ -3643,19 +3643,19 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>나도코딩</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>0</v>
@@ -3664,52 +3664,52 @@
         <v>4.9</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1931</v>
+        <v>84</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>40206</v>
+        <v>605</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>임베디드 · IoT, 모빌리티</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>358</v>
+        <v>1017</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2020-02-24T15:00:00.000Z</t>
+          <t>2025-06-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T06:34:34.311Z</t>
+          <t>2026-09-13T09:06:49.556Z</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
         </is>
       </c>
     </row>
@@ -3719,31 +3719,31 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>대세는 쿠버네티스 (초급~중급편)</t>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>626</v>
+        <v>8119</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>8497</v>
+        <v>123267</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
@@ -3752,40 +3752,40 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
+          <t>Java, Spring, MVC, Spring Boot</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>425</v>
+        <v>321</v>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>2019-09-10T15:00:00.000Z</t>
+          <t>2020-07-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T05:23:15.024Z</t>
+          <t>2026-01-30T11:34:33.353Z</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
         </is>
       </c>
     </row>
@@ -3795,31 +3795,31 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0</v>
+        <v>128700</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0</v>
+        <v>128700</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>188</v>
+        <v>40</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6173</v>
+        <v>579</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3828,40 +3828,40 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>AI 실무 활용, 오피스, 업무 자동화</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, routing</t>
+          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>779</v>
+        <v>832</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2026-06-05T16:00:00.000Z</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T09:27:31.006Z</t>
+          <t>2026-08-07T06:36:11.731Z</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+          <t>https://www.inflearn.com/course/starting-with-claude</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>나도코딩</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
@@ -3889,17 +3889,17 @@
         <v>0</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>8118</v>
+        <v>1932</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>123262</v>
+        <v>40215</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
@@ -3909,35 +3909,35 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, MVC, Spring Boot</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>2020-07-19T15:00:00.000Z</t>
+          <t>2020-02-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2026-01-30T11:34:33.353Z</t>
+          <t>2025-04-29T06:34:34.311Z</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
         </is>
       </c>
     </row>
@@ -3947,19 +3947,19 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
+          <t>김영한의 실전 데이터베이스 - 기본편</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>nstyxn</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>118800</v>
+        <v>88000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>118800</v>
+        <v>88000</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>0</v>
@@ -3968,52 +3968,52 @@
         <v>5</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>87</v>
+        <v>517</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>958</v>
+        <v>5396</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>보안, 보안 · 네트워크 자격증</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Forensic, 디지털포렌식전문가 2급</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>6530</v>
+        <v>821</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2022-11-13T15:00:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T02:00:30.898Z</t>
+          <t>2026-08-06T12:14:20.961Z</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
         </is>
       </c>
     </row>
@@ -4023,73 +4023,73 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>피엠인사이드</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="F47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>17</v>
+        <v>6179</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 관리, PMP</t>
+          <t>네트워크, tcpip, routing</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>2405</v>
+        <v>779</v>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T13:00:08.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T13:27:36.753Z</t>
+          <t>2025-04-29T09:27:31.006Z</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
         </is>
       </c>
     </row>
@@ -4099,73 +4099,71 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>782</v>
+        <v>1109</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>1266</v>
-      </c>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T05:00:33.000Z</t>
+          <t>2026-06-27T04:00:06.000Z</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T22:16:49.715Z</t>
+          <t>2026-06-30T07:01:04.312Z</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-llm-servic</t>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
         </is>
       </c>
     </row>
@@ -4175,19 +4173,19 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Decision AI로 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
+          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>22000</v>
+        <v>440000</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>22000</v>
+        <v>440000</v>
       </c>
       <c r="F49" s="10" t="n">
         <v>0</v>
@@ -4199,49 +4197,49 @@
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
+          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
+          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>109</v>
+        <v>1240</v>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T05:00:08.000Z</t>
+          <t>2026-10-04T15:00:07.000Z</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T19:46:29.290Z</t>
+          <t>2026-10-05T03:23:49.530Z</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-decision-a</t>
+          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
         </is>
       </c>
     </row>
@@ -4251,31 +4249,31 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
+          <t>BHPT - 호스트 기반 모의해킹 기초</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>레드라쿤</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>99000</v>
+        <v>198000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>99000</v>
+        <v>198000</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>579</v>
+        <v>1161</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4284,40 +4282,40 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
+          <t>보안, 시스템 · 운영체제, 네트워크</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
+          <t>모의해킹, 오펜시브 시큐리티, 네트워크, kali-linux</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>924</v>
+        <v>1031</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2025-10-03T09:30:00.000Z</t>
+          <t>2024-01-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10T10:01:12.921Z</t>
+          <t>2026-03-30T05:39:15.743Z</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
+          <t>https://www.inflearn.com/course/호스트-기반-모의해킹-기초</t>
         </is>
       </c>
     </row>
@@ -4327,31 +4325,31 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>시스코 CCNA 함께 공부해요</t>
+          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>ccie_pe_kim</t>
+          <t>피엠인사이드</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="F51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>1758</v>
+        <v>20</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
@@ -4360,40 +4358,40 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, routing, tcpip</t>
+          <t>프로젝트 관리, PMP</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>1213</v>
+        <v>2392</v>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>2026-01-30T15:00:00.000Z</t>
+          <t>2026-10-01T13:00:08.000Z</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25T09:44:13.272Z</t>
+          <t>2026-10-14T13:35:49.299Z</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
         </is>
       </c>
     </row>
@@ -4403,73 +4401,73 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
+          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>128700</v>
+        <v>154000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>128700</v>
+        <v>154000</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>576</v>
+        <v>2051</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 오피스, 업무 자동화</t>
+          <t>데이터베이스, 데이터 분석, 풀스택</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
+          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>832</v>
+        <v>1270</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05T16:00:00.000Z</t>
+          <t>2026-07-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T06:36:11.731Z</t>
+          <t>2026-07-28T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/starting-with-claude</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
         </is>
       </c>
     </row>
@@ -4479,19 +4477,19 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 2편</t>
+          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>66000</v>
+        <v>38500</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>66000</v>
+        <v>38500</v>
       </c>
       <c r="F53" s="10" t="n">
         <v>0</v>
@@ -4500,52 +4498,52 @@
         <v>5</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>881</v>
+        <v>3</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>11023</v>
+        <v>64</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+          <t>SQL, Oracle, database, modeling, SQLD</t>
         </is>
       </c>
       <c r="N53" s="7" t="n">
-        <v>1165</v>
+        <v>923</v>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>2024-05-07T15:00:00.000Z</t>
+          <t>2026-09-02T03:00:00.000Z</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>2025-11-24T10:17:13.631Z</t>
+          <t>2026-09-02T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4553,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>노베이스를 위한 ADsP 생존 가이드</t>
+          <t>[Chapter 1. 유치원생도 이해하는 파이썬 기초] 설치 없이 시작하는 파이썬 입문</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>숀김</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
@@ -4573,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>759</v>
+        <v>13</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4588,40 +4586,40 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
+          <t>AI 코딩, 프로그래밍 언어, AI 시작하기</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SQL, R, ADsP</t>
+          <t>algorithms, data-structure, functions, ioc, python3</t>
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>303</v>
+        <v>121</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11T11:00:00.000Z</t>
+          <t>2026-10-14T03:00:06.000Z</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11T09:14:53.120Z</t>
+          <t>2026-10-13T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
+          <t>https://www.inflearn.com/course/python-basics-even-k</t>
         </is>
       </c>
     </row>
@@ -4631,73 +4629,73 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
+          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>시드니개발자의 영어PT</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>220000</v>
+        <v>99000</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>220000</v>
+        <v>99000</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>2199</v>
+        <v>580</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>외국어</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
         </is>
       </c>
       <c r="N55" s="7" t="n">
-        <v>49</v>
+        <v>924</v>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>2023-01-12T15:00:00.000Z</t>
+          <t>2025-10-03T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T05:15:40.989Z</t>
+          <t>2025-11-10T10:01:12.921Z</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
+          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
         </is>
       </c>
     </row>
@@ -4707,73 +4705,73 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>0</v>
+        <v>69300</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21161</v>
+        <v>48</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>823</v>
+        <v>73</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2023-03-02T15:00:00.000Z</t>
+          <t>2026-10-08T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T09:43:24.787Z</t>
+          <t>2026-10-11T17:09:46.044Z</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
         </is>
       </c>
     </row>
@@ -4783,31 +4781,31 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>정보처리기사 자격증 대비 교육(실기)</t>
+          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>국립안동대학교 SW융합교육원</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0</v>
+        <v>64900</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>0</v>
+        <v>64900</v>
       </c>
       <c r="F57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>2229</v>
+        <v>785</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
@@ -4816,40 +4814,40 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증</t>
+          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>정보처리기사</t>
+          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
         </is>
       </c>
       <c r="N57" s="7" t="n">
-        <v>1532</v>
+        <v>1266</v>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>2024-08-13T15:00:00.000Z</t>
+          <t>2026-09-07T05:00:33.000Z</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>2024-08-14T00:00:00.000Z</t>
+          <t>2026-10-13T22:16:49.715Z</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
+          <t>https://www.inflearn.com/course/practical-llm-servic</t>
         </is>
       </c>
     </row>
@@ -4859,19 +4857,19 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
+          <t>시스코 CCNA 함께 공부해요</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>ccie_pe_kim</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>82500</v>
+        <v>0</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>82500</v>
+        <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
@@ -4880,10 +4878,10 @@
         <v>4.9</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>789</v>
+        <v>58</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2911</v>
+        <v>1765</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4892,40 +4890,40 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, argocd, container, helm</t>
+          <t>네트워크, CCNA, routing, tcpip</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>669</v>
+        <v>1213</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2023-09-11T15:00:00.000Z</t>
+          <t>2026-01-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27T08:15:25.352Z</t>
+          <t>2026-03-25T09:44:13.272Z</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
         </is>
       </c>
     </row>
@@ -4935,71 +4933,73 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+          <t>김영한의 실전 자바 - 중급 1편</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>97</v>
+        <v>1265</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>1099</v>
+        <v>12542</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N59" s="7" t="n"/>
+          <t>Java, 객체지향</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="n">
+        <v>1161</v>
+      </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-27T04:00:06.000Z</t>
+          <t>2024-03-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30T07:01:04.312Z</t>
+          <t>2025-11-28T10:04:41.236Z</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
+          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>최원영</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
@@ -5027,13 +5027,13 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>86</v>
+        <v>460</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1568</v>
+        <v>21165</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5042,40 +5042,40 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI)</t>
+          <t>컴퓨터 구조, 운영체제, 기술면접</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>32</v>
+        <v>823</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27T05:00:00.000Z</t>
+          <t>2023-03-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27T06:18:36.692Z</t>
+          <t>2025-04-29T09:43:24.787Z</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
+          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
         </is>
       </c>
     </row>
@@ -5085,31 +5085,31 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>정보처리기사 자격증 대비 교육(실기)</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>국립안동대학교 SW융합교육원</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>1456</v>
+        <v>2236</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
@@ -5118,40 +5118,40 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>정보처리기사</t>
         </is>
       </c>
       <c r="N61" s="7" t="n">
-        <v>368</v>
+        <v>1532</v>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2024-08-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2024-08-14T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
         </is>
       </c>
     </row>
@@ -5161,73 +5161,73 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Claude로 끝내는 실무 업무자동화: 엑셀·문서·PPT부터 Skills·Obsidian까지</t>
+          <t>타입스크립트로 배우는 리액트(React.js) : 기초부터 최신 기술까지 완벽하게</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>HappyAI</t>
+          <t>수코딩</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>88000</v>
+        <v>79200</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>88000</v>
+        <v>99000</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>109</v>
+        <v>624</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>프론트엔드, 웹 개발, 모바일 앱 개발</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>data-analysis, data-processing, n8n, 프롬프트엔지니어링, claude</t>
+          <t>React, react-router, redux-toolkit, zustand, react.js</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
-        <v>229</v>
+        <v>1615</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T09:00:05.000Z</t>
+          <t>2025-06-08T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T00:06:16.136Z</t>
+          <t>2026-05-25T06:25:45.941Z</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-practical-2</t>
+          <t>https://www.inflearn.com/course/typescript-react-perfect-course</t>
         </is>
       </c>
     </row>
@@ -5237,73 +5237,73 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
+          <t>실리콘밸리 AI 개발자의 LLM 서비스를 위한 RAG</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>55000</v>
+        <v>165000</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>86900</v>
+        <v>165000</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>0.3670886075949367</v>
+        <v>0</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>20</v>
+        <v>683</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
+          <t>JavaScript, Python, 인공지능(AI), ChatGPT, RAG</t>
         </is>
       </c>
       <c r="N63" s="7" t="n">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23T02:30:05.000Z</t>
+          <t>2026-08-14T08:00:08.000Z</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T15:07:55.641Z</t>
+          <t>2026-10-02T00:24:12.168Z</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
+          <t>https://www.inflearn.com/course/mastering-rag-as-tau</t>
         </is>
       </c>
     </row>
@@ -5313,22 +5313,22 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>AI를 위한 미적분 — 도함수, 그래디언트, 그리고 신경망이 학습하는 원리</t>
+          <t>AI에게 마음 놓고 맡기는 바이브코딩 : 망쳐도 한 문장으로 되돌리는 Git 버전 관리</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>코딩맥스 CodingMax</t>
+          <t>Masocampus</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>99000</v>
+        <v>34650</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>99000</v>
+        <v>49500</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>0</v>
@@ -5337,49 +5337,49 @@
         <v>0</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 대학 교육</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 수학</t>
+          <t>AI 실무 활용, AI 개발 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>머신러닝, 딥러닝, 인공신경망, 선형대수학, 미적분, 인공지능(AI)</t>
+          <t>인공지능(AI), Git, 바이브코딩, VSCode, codex, GitHub</t>
         </is>
       </c>
       <c r="N64" s="2" t="n">
-        <v>1093</v>
+        <v>119</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T08:00:08.000Z</t>
+          <t>2026-10-14T02:00:06.000Z</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T05:41:38.564Z</t>
+          <t>2026-10-12T02:14:59.154Z</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/calculus-for-ai-deri</t>
+          <t>https://www.inflearn.com/course/vibe-coding-you-can</t>
         </is>
       </c>
     </row>
@@ -5389,73 +5389,73 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>The 10x AI-Native Developer: 회사에서 AI로 압도적 성과를 내는 법</t>
+          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>딩코딩코</t>
+          <t>김형태</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>198000</v>
+        <v>138600</v>
       </c>
       <c r="E65" s="9" t="n">
         <v>198000</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>978</v>
+        <v>482</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 풀스택, AI 실무 활용</t>
+          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, Next.js, 인공지능(AI), claude</t>
+          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N65" s="7" t="n">
-        <v>926</v>
+        <v>483</v>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>2025-10-01T17:00:00.000Z</t>
+          <t>2026-05-29T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>2026-05-17T14:48:39.414Z</t>
+          <t>2026-09-26T10:39:08.073Z</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-10x-ai-native-de</t>
+          <t>https://www.inflearn.com/course/building-a-marketing</t>
         </is>
       </c>
     </row>
@@ -5465,19 +5465,19 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>홍정모의 따라하며 배우는 C++</t>
+          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>홍정모</t>
+          <t>시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>176000</v>
+        <v>220000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>176000</v>
+        <v>220000</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0</v>
@@ -5486,52 +5486,52 @@
         <v>4.9</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>395</v>
+        <v>63</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7125</v>
+        <v>2198</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 게임 개발</t>
+          <t>외국어</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>2907</v>
+        <v>49</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2018-09-30T15:00:00.000Z</t>
+          <t>2023-01-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2025-08-10T19:46:59.750Z</t>
+          <t>2026-10-02T05:15:40.989Z</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/following-c-plus</t>
+          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
         </is>
       </c>
     </row>
@@ -5541,31 +5541,31 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>[2026] 유니티 엔진 입문 올인원</t>
+          <t>노베이스를 위한 ADsP 생존 가이드</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="F67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>135</v>
+        <v>761</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
@@ -5574,40 +5574,40 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>게임 개발</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>게임 프로그래밍</t>
+          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>game-programming, 유니티6</t>
+          <t>SQL, R, ADsP</t>
         </is>
       </c>
       <c r="N67" s="7" t="n">
-        <v>1159</v>
+        <v>303</v>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11T04:00:00.000Z</t>
+          <t>2025-11-11T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11T02:13:13.639Z</t>
+          <t>2025-11-11T09:14:53.120Z</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/2026-unity-engine-be</t>
+          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
         </is>
       </c>
     </row>
@@ -5617,31 +5617,31 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
+          <t>실리콘 밸리 엔지니어와 함께하는 Local LLM 완전 정복 (LM Studio &amp; Ollama &amp; Ollaya)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>남박사</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>68200</v>
+        <v>41250</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>68200</v>
+        <v>55000</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>287</v>
+        <v>42</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>3407</v>
+        <v>688</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5650,40 +5650,40 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
+          <t>인공지능(AI), LLM, AI Agent</t>
         </is>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1143</v>
+        <v>270</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2025-05-06T15:00:00.000Z</t>
+          <t>2026-04-17T18:00:00.000Z</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12T11:29:01.075Z</t>
+          <t>2026-10-01T05:15:20.298Z</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
+          <t>https://www.inflearn.com/course/mastering-local-llm</t>
         </is>
       </c>
     </row>
@@ -5693,19 +5693,19 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>[Unity6] 내가 연출하는 한 편의 이야기, 비주얼노벨 제작</t>
+          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Pinous</t>
+          <t>그랩</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>77000</v>
+        <v>198000</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>77000</v>
+        <v>198000</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>0</v>
@@ -5714,10 +5714,10 @@
         <v>5</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>113</v>
+        <v>333</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
@@ -5726,40 +5726,40 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>게임 개발</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>게임 프로그래밍, 게임 기획, 게임 개발 기타</t>
+          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>C#, Unity, 유니티6</t>
+          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N69" s="7" t="n">
-        <v>566</v>
+        <v>896</v>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>2026-05-27T09:30:00.000Z</t>
+          <t>2026-07-23T04:50:00.000Z</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16T11:01:40.099Z</t>
+          <t>2026-08-01T16:24:39.937Z</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/unity6-creating-a-vi</t>
+          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
         </is>
       </c>
     </row>
@@ -5769,19 +5769,19 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>비전공자도 이해할 수 있는 Docker 입문/실전</t>
+          <t>대세는 쿠버네티스 (초급~중급편)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>0</v>
@@ -5790,10 +5790,10 @@
         <v>4.9</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>693</v>
+        <v>626</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14640</v>
+        <v>8498</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5807,35 +5807,35 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 백엔드, 클라우드</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Docker, container, docker-compose, docker-volume, ecr, docker-image</t>
+          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2024-06-12T15:00:00.000Z</t>
+          <t>2019-09-10T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:39.530Z</t>
+          <t>2025-11-19T05:23:15.024Z</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-docker-입문-실전</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
         </is>
       </c>
     </row>
@@ -5845,19 +5845,19 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
+          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>그랩</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>198000</v>
+        <v>77000</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>198000</v>
+        <v>77000</v>
       </c>
       <c r="F71" s="10" t="n">
         <v>0</v>
@@ -5866,10 +5866,10 @@
         <v>5</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>30</v>
+        <v>349</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>332</v>
+        <v>5460</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
@@ -5878,40 +5878,40 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
+          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
         </is>
       </c>
       <c r="N71" s="7" t="n">
-        <v>896</v>
+        <v>1001</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23T04:50:00.000Z</t>
+          <t>2025-03-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01T16:24:39.937Z</t>
+          <t>2025-09-14T05:27:02.800Z</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
         </is>
       </c>
     </row>
@@ -5921,73 +5921,73 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
+          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>김형태</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>138600</v>
+        <v>121000</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>198000</v>
+        <v>121000</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>480</v>
+        <v>2970</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
+          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>483</v>
+        <v>797</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29T02:00:00.000Z</t>
+          <t>2026-01-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T10:39:08.073Z</t>
+          <t>2026-02-09T09:50:03.741Z</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-a-marketing</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
         </is>
       </c>
     </row>
@@ -5997,73 +5997,73 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>옵시디언 마스터 클래스: PKM·AI Second Brain·LLM WiKi 기초부터 실전까지</t>
+          <t>Decision AI로 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>조영수(데이먼)</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>132000</v>
+        <v>22000</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>132000</v>
+        <v>22000</v>
       </c>
       <c r="F73" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>1134</v>
+        <v>20</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, 기획 · 경영 · 마케팅, AI 활용(AX)</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>생산성 도구, 기획 · PM· PO, AI 실무 활용</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, obsidian</t>
+          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N73" s="7" t="n">
-        <v>455</v>
+        <v>109</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>2025-06-25T12:30:00.000Z</t>
+          <t>2026-10-06T05:00:08.000Z</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08T00:00:00.000Z</t>
+          <t>2026-10-12T19:46:29.290Z</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/옵시디언-마스터-클래스생산성을-바꾸는-1</t>
+          <t>https://www.inflearn.com/course/practical-decision-a</t>
         </is>
       </c>
     </row>
@@ -6073,73 +6073,73 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
+          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>멍슨상</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>36300</v>
+        <v>44550</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>48400</v>
+        <v>59400</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>314</v>
+        <v>227</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, database</t>
+          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1553</v>
+        <v>311</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2025-09-24T07:00:00.000Z</t>
+          <t>2026-07-31T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T06:06:52.494Z</t>
+          <t>2026-08-12T14:30:32.966Z</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
+          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
         </is>
       </c>
     </row>
@@ -6149,19 +6149,19 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>PMP 합격을 완성하는 250문제 실전 풀이 코스!</t>
+          <t>김영한의 실전 자바 - 중급 2편</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>피엠인사이드</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>110000</v>
+        <v>66000</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>110000</v>
+        <v>66000</v>
       </c>
       <c r="F75" s="10" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>5</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>9</v>
+        <v>881</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>39</v>
+        <v>11023</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
@@ -6182,40 +6182,40 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>기획 · PM· PO, 경영 · 전략, 기획 · 경영 · 마케팅 자격증</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>애자일, 프로젝트 관리, project, waterfall, PMP</t>
+          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
         </is>
       </c>
       <c r="N75" s="7" t="n">
-        <v>512</v>
+        <v>1165</v>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14T08:00:00.000Z</t>
+          <t>2024-05-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14T06:08:44.346Z</t>
+          <t>2025-11-24T10:17:13.631Z</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmp-합격을-완성하는-250문제-실</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
         </is>
       </c>
     </row>
@@ -6225,73 +6225,73 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
+          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>154000</v>
+        <v>79200</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>154000</v>
+        <v>79200</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48</v>
+        <v>229</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2050</v>
+        <v>6760</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 풀스택</t>
+          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
+          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>1270</v>
+        <v>357</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00.000Z</t>
+          <t>2025-07-11T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28T00:00:00.000Z</t>
+          <t>2025-11-10T22:31:31.977Z</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
+          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
         </is>
       </c>
     </row>
@@ -6301,73 +6301,73 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 Next.js</t>
+          <t>리눅스 입문 - 개념으로 탄탄히!!</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>런잇(ProgCoach4U)</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>48400</v>
+        <v>77000</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>48400</v>
+        <v>77000</v>
       </c>
       <c r="F77" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>639</v>
+        <v>301</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>6028</v>
+        <v>3491</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>시스템 · 운영체제, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>React, TypeScript, Next.js</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="N77" s="7" t="n">
-        <v>934</v>
+        <v>757</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>2024-08-18T15:00:00.000Z</t>
+          <t>2021-06-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13T03:56:34.520Z</t>
+          <t>2025-05-13T07:44:10.964Z</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-크기-nextjs</t>
+          <t>https://www.inflearn.com/course/리눅스-입문</t>
         </is>
       </c>
     </row>
@@ -6377,73 +6377,73 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>클로드로 딸깍! 루프 엔지니어링으로 통합 자산관리 시스템 개발하기</t>
+          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>멍슨상</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>154000</v>
+        <v>36300</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>154000</v>
+        <v>48400</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>423</v>
+        <v>315</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 코딩, 풀스택</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), 바이브코딩, AX(에이전트 경험), AI Agent, minio</t>
+          <t>Python, Java, C, 정보처리기사, database</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>795</v>
+        <v>1553</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T05:00:00.000Z</t>
+          <t>2025-09-24T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05T22:46:00.597Z</t>
+          <t>2026-10-11T06:06:52.494Z</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/one-click-with-claud</t>
+          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
         </is>
       </c>
     </row>
@@ -6453,73 +6453,73 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
+          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>코드바나나</t>
+          <t>nstyxn</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>148500</v>
+        <v>118800</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>148500</v>
+        <v>118800</v>
       </c>
       <c r="F79" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>320</v>
+        <v>87</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>3753</v>
+        <v>959</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
+          <t>보안, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>AWS, 네트워크, AWS SAA</t>
+          <t>Forensic, 디지털포렌식전문가 2급</t>
         </is>
       </c>
       <c r="N79" s="7" t="n">
-        <v>1450</v>
+        <v>6530</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>2022-06-21T15:00:00.000Z</t>
+          <t>2022-11-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T03:07:28.063Z</t>
+          <t>2026-07-15T02:00:30.898Z</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
+          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
         </is>
       </c>
     </row>
@@ -6529,73 +6529,73 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
+          <t>2026년 완벽한 Claude AI 강좌: 프롬프트, 콘텐츠, SEO 및 비즈니스</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>Tanmoy Das</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>79200</v>
+        <v>15400</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>79200</v>
+        <v>22000</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6756</v>
+        <v>4</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
+          <t>AI 실무 활용, AI 크리에이티브, AI 시작하기</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
+          <t>인공지능(AI), claude, AI Agent, 블록체인, 보안 교육, AX(에이전트 경험), ChatGPT</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>357</v>
+        <v>827</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2025-07-11T02:00:00.000Z</t>
+          <t>2026-10-12T04:00:08.000Z</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10T22:31:31.977Z</t>
+          <t>2026-09-30T03:58:13.247Z</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
+          <t>https://www.inflearn.com/course/full-claude-ai-cours</t>
         </is>
       </c>
     </row>
@@ -6605,73 +6605,73 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>하루만에 끝내는 Herdr: 멀티플렉서, 에이전트, SSH 맥미니-모바일 원격 접속</t>
+          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>최원영</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="F81" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>120</v>
+        <v>1572</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>개발 도구, AI에이전트 개발, AI 개발 활용</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>tmux, claude, codex, terminal, AI Agent, macOS, Git</t>
+          <t>인공지능(AI)</t>
         </is>
       </c>
       <c r="N81" s="7" t="n">
-        <v>248</v>
+        <v>32</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13T12:00:06.000Z</t>
+          <t>2026-02-27T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27T09:02:14.111Z</t>
+          <t>2026-02-27T06:18:36.692Z</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/herdr-in-one-day-mul</t>
+          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
         </is>
       </c>
     </row>
@@ -6681,73 +6681,73 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
+          <t>AI 에이전트 엔지니어링</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>민혁</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>349</v>
+        <v>39</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>5459</v>
+        <v>2063</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
+          <t>Python, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1001</v>
+        <v>322</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2025-03-24T15:00:00.000Z</t>
+          <t>2026-04-07T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2025-09-14T05:27:02.800Z</t>
+          <t>2026-04-07T02:58:08.781Z</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
+          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
         </is>
       </c>
     </row>
@@ -6757,19 +6757,19 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>MATLAB/Simulink 자동차 MBD 실무 입문: 모델링부터 검증과 코드 생성까지</t>
+          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>제어쟁이</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>129800</v>
+        <v>82500</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>129800</v>
+        <v>82500</v>
       </c>
       <c r="F83" s="10" t="n">
         <v>0</v>
@@ -6778,10 +6778,10 @@
         <v>4.9</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>12</v>
+        <v>789</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>99</v>
+        <v>2912</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
@@ -6790,40 +6790,40 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>모빌리티, 임베디드 · IoT</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>MATLAB</t>
+          <t>Kubernetes, devops, argocd, container, helm</t>
         </is>
       </c>
       <c r="N83" s="7" t="n">
-        <v>376</v>
+        <v>669</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-27T10:30:05.000Z</t>
+          <t>2023-09-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05T12:40:21.603Z</t>
+          <t>2026-05-27T08:15:25.352Z</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/introduction-to-prac</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
         </is>
       </c>
     </row>
@@ -6833,35 +6833,35 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>AI 에이전트 엔지니어링</t>
+          <t>챗봇을 만들며 배우는 ai agent 개발의 모든것(fastapi, RAG, vector, LangChain, sLLM/파인튜닝)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>민혁</t>
+          <t>bradkim</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2059</v>
+        <v>336</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6871,35 +6871,35 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>AI에이전트 개발, 인공지능 기타, AI 개발 활용</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Python, 인공지능(AI), RAG, AI Agent</t>
+          <t>RAG, vector-database, FastAPI, LLM, Llama, Fine-Tuning, openAI API</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>322</v>
+        <v>507</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07T05:00:00.000Z</t>
+          <t>2026-07-01T06:30:06.000Z</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07T02:58:08.781Z</t>
+          <t>2026-07-01T07:03:29.747Z</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
+          <t>https://www.inflearn.com/course/everything-about-ai</t>
         </is>
       </c>
     </row>
@@ -6909,73 +6909,73 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>외워서 끝내는 네트워크 핵심이론 - 기초</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>77000</v>
+        <v>44330</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>77000</v>
+        <v>68200</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>797</v>
+        <v>0</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>8577</v>
+        <v>6</v>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>네트워크, 개발 · 프로그래밍 기타, 웹 개발</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>네트워크, 프로토콜</t>
+          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
         </is>
       </c>
       <c r="N85" s="7" t="n">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>2022-09-26T15:00:00.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:25:51.956Z</t>
+          <t>2026-10-10T12:02:44.178Z</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/네트워크-핵심이론-기초</t>
+          <t>https://www.inflearn.com/course/database-concepts-yo</t>
         </is>
       </c>
     </row>
@@ -6985,32 +6985,32 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>면접 전에 알고 가면 좋을 것들 - 신입 Java 백엔드 개발자편</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>66000</v>
+        <v>44330</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>66000</v>
+        <v>68200</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H86" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>1627</v>
-      </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
           <t>초급</t>
@@ -7018,40 +7018,40 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>취업 · 이직, 웹 개발, 백엔드, 풀스택</t>
+          <t>데이터베이스, AI 코딩</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>기술면접, 이력서, DBMS/RDBMS, tcpip</t>
+          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>306</v>
+        <v>410</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2023-08-30T15:00:00.000Z</t>
+          <t>2026-10-10T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:42:51.608Z</t>
+          <t>2026-10-10T11:44:45.232Z</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/면접-신입-java-백앤드-개발자</t>
+          <t>https://www.inflearn.com/course/essential-database-c</t>
         </is>
       </c>
     </row>
@@ -7061,73 +7061,73 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 기본편</t>
+          <t>실무에 바로 적용하는 Spring AI: Spring 서비스에 챗봇·RAG·MCP 도입하기</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>JSCODE 시니</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>88000</v>
+        <v>61600</v>
       </c>
       <c r="E87" s="9" t="n">
         <v>88000</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>4933</v>
+        <v>45</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>50478</v>
+        <v>588</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>AI 실무 활용, 백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>Spring, 객체지향</t>
+          <t>Spring Boot, Elasticsearch, vector-database, LLM, RAG, Spring AI, MCP</t>
         </is>
       </c>
       <c r="N87" s="7" t="n">
-        <v>725</v>
+        <v>439</v>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>2020-09-20T15:00:00.000Z</t>
+          <t>2026-06-12T23:30:00.000Z</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>2025-06-04T15:00:00.555Z</t>
+          <t>2026-08-30T11:28:43.252Z</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
+          <t>https://www.inflearn.com/course/spring-ai-in-practic</t>
         </is>
       </c>
     </row>
@@ -7137,73 +7137,73 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
+          <t>홍정모의 따라하며 배우는 C++</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>홍정모</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>38500</v>
+        <v>176000</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>38500</v>
+        <v>176000</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>3</v>
+        <v>395</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>61</v>
+        <v>7125</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 게임 개발</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>SQL, Oracle, database, modeling, SQLD</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>923</v>
+        <v>2907</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T03:00:00.000Z</t>
+          <t>2018-09-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T00:00:00.000Z</t>
+          <t>2025-08-10T19:46:59.750Z</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
+          <t>https://www.inflearn.com/course/following-c-plus</t>
         </is>
       </c>
     </row>
@@ -7213,31 +7213,31 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>트래픽 급증을 견디는 서버 시스템 설계 - Coupon 발급 서비스</t>
+          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>한조각</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>41250</v>
+        <v>77000</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>55000</v>
+        <v>77000</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>26</v>
+        <v>605</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>810</v>
+        <v>9780</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
@@ -7251,35 +7251,35 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데이터베이스</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>Java, Kotlin, MySQL, Docker, Spring Boot, Kafka, Redis</t>
+          <t>Java, 객체지향, thread, multithread, 동시성</t>
         </is>
       </c>
       <c r="N89" s="7" t="n">
-        <v>618</v>
+        <v>1249</v>
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09T17:00:05.000Z</t>
+          <t>2024-07-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27T15:21:43.118Z</t>
+          <t>2025-11-18T01:46:58.908Z</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/designing-a-server-s</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
         </is>
       </c>
     </row>
@@ -7289,22 +7289,22 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>AI 한달 구독료로 나만의 AI 에이전트 만들기 (feat. 인터넷 없이 내 PC에서 돌아가는)</t>
+          <t>#2-1 ComfyUI 마스터하기: 애니 2D 일러스트 제작 총집편 (SD 1.5 · SDXL · PonyXL)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>kmmom591</t>
+          <t>닭강정</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>16940</v>
+        <v>24750</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>24200</v>
+        <v>33000</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>0</v>
@@ -7313,49 +7313,49 @@
         <v>0</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 크리에이티브, AI 시작하기</t>
+          <t>AI 크리에이티브, 컴퓨터 비전, AI 시작하기</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Python, 딥러닝, agents, 인공지능(AI), LLM, AI Agent, AX(에이전트 경험)</t>
+          <t>InDesign, motion, animations, ui, us-ascii</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>78</v>
+        <v>349</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T07:30:06.000Z</t>
+          <t>2026-08-19T22:00:00.000Z</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T08:58:31.423Z</t>
+          <t>2026-08-20T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/build-your-own-ai-ag-1</t>
+          <t>https://www.inflearn.com/course/2-1-mastering-comfyu</t>
         </is>
       </c>
     </row>
@@ -7365,31 +7365,31 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 기본편</t>
+          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>코드바나나</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>88000</v>
+        <v>148500</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>88000</v>
+        <v>148500</v>
       </c>
       <c r="F91" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>5392</v>
+        <v>3755</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
@@ -7398,40 +7398,40 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>데브옵스 · 인프라, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>AWS, 네트워크, AWS SAA</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
-        <v>821</v>
+        <v>1450</v>
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2022-06-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06T12:14:20.961Z</t>
+          <t>2026-10-12T03:07:28.063Z</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
+          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>독하게 시작하는 C 프로그래밍</t>
+          <t>React 완벽 마스터: 기초 개념부터 린캔버스 프로젝트까지</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
@@ -7459,13 +7459,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>242</v>
+        <v>145</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3144</v>
+        <v>962</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7474,40 +7474,40 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 시스템 · 운영체제</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>C, 컴퓨터 구조, assembly-language, vc++</t>
+          <t>React, react-query, react-router, React Context, TailwindCSS</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>1739</v>
+        <v>1054</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2023-09-26T15:00:00.000Z</t>
+          <t>2024-09-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:29:20.937Z</t>
+          <t>2025-09-09T02:15:49.950Z</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/독하게-시작하는-c프로그래밍</t>
+          <t>https://www.inflearn.com/course/react-완벽가이드-기초-프로젝트</t>
         </is>
       </c>
     </row>
@@ -7517,31 +7517,31 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>타입스크립트로 배우는 리액트(React.js) : 기초부터 최신 기술까지 완벽하게</t>
+          <t>AI를 위한 미적분 — 도함수, 그래디언트, 그리고 신경망이 학습하는 원리</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>수코딩</t>
+          <t>코딩맥스 CodingMax</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>79200</v>
+        <v>99000</v>
       </c>
       <c r="E93" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>622</v>
+        <v>32</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
@@ -7550,40 +7550,40 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 대학 교육</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발, 모바일 앱 개발</t>
+          <t>딥러닝 · 머신러닝, 수학</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>React, react-router, redux-toolkit, zustand, react.js</t>
+          <t>머신러닝, 딥러닝, 인공신경망, 선형대수학, 미적분, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N93" s="7" t="n">
-        <v>1615</v>
+        <v>1093</v>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>2025-06-08T15:00:00.000Z</t>
+          <t>2026-09-13T08:00:08.000Z</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25T06:25:45.941Z</t>
+          <t>2026-09-13T05:41:38.564Z</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/typescript-react-perfect-course</t>
+          <t>https://www.inflearn.com/course/calculus-for-ai-deri</t>
         </is>
       </c>
     </row>
@@ -7593,73 +7593,73 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>절대강좌! 유니티 6 - TPS 게임으로 배우는 유니티 마스터클래스</t>
+          <t>비전공자들을 위한 실무 밀착 네이버 검색광고</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>이재현</t>
+          <t>그로스쿨</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>게임 개발</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>게임 프로그래밍</t>
+          <t>데이터 분석</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Unity, C#</t>
+          <t>네이버 키워드 검색</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>979</v>
+        <v>319</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2026-04-22T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2025-07-02T03:41:32.036Z</t>
+          <t>2026-04-23T00:40:58.257Z</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/절대강좌-유니티6-tps</t>
+          <t>https://www.inflearn.com/course/practical-naver-sa-f</t>
         </is>
       </c>
     </row>
@@ -7669,31 +7669,31 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
+          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>숀김</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>33000</v>
+        <v>55000</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>66000</v>
+        <v>86900</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3670886075949367</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
@@ -7702,40 +7702,40 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
+          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>Python, LLM, AI Agent, claude</t>
+          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
-        <v>305</v>
+        <v>541</v>
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23T06:30:05.000Z</t>
+          <t>2026-09-23T02:30:05.000Z</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26T17:31:06.856Z</t>
+          <t>2026-09-29T15:07:55.641Z</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
+          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
         </is>
       </c>
     </row>
@@ -7745,73 +7745,73 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>비개발자 4주만에 수익화 서비스 만들기: AI 바이브코딩 웹 + 앱 ALL IN ONE</t>
+          <t>베개투자법 완성: 아침이 설레는 AI 주식 완전 자동매매  Claude 바이브코딩</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>딩코딩코</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>165000</v>
+        <v>132000</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>165000</v>
+        <v>132000</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>318</v>
+        <v>34</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1908</v>
+        <v>277</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, 웹 개발, 모바일 앱 개발</t>
+          <t>AI 개발 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Flutter, Next.js, cursor, supabase, 바이브코딩</t>
+          <t>Python, 머신러닝, AWS, FastAPI, 퀀트, cloud-computing, claude</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>675</v>
+        <v>309</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2025-07-19T11:00:00.000Z</t>
+          <t>2026-05-17T08:30:00.000Z</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02T12:53:10.998Z</t>
+          <t>2026-06-29T05:27:04.296Z</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비개발자-4주만에-수익화-서비스-만들</t>
+          <t>https://www.inflearn.com/course/automated-trading-th</t>
         </is>
       </c>
     </row>
@@ -7821,31 +7821,31 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>GPT는 어떻게 문장을 생성할까? | LLM·ViT 강의 ATT 무료 공개</t>
+          <t>[2026] SQLD 문제가 어려운 당신을 위한 노랭이 176 문제 풀이</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>알고런 데이터코드 연구소</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0</v>
+        <v>39600</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>0</v>
+        <v>39600</v>
       </c>
       <c r="F97" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>47</v>
+        <v>245</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
@@ -7854,40 +7854,40 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>데이터 사이언스 자격증, 데이터 분석, 데이터 엔지니어링</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>gpt, 딥러닝</t>
+          <t>SQL, 빅데이터, Oracle, MSSQL, SQLD</t>
         </is>
       </c>
       <c r="N97" s="7" t="n">
-        <v>35</v>
+        <v>746</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T09:00:09.000Z</t>
+          <t>2025-02-17T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T17:04:49.947Z</t>
+          <t>2026-05-26T04:21:15.498Z</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-does-gpt-generat</t>
+          <t>https://www.inflearn.com/course/2025-sqld-올인원</t>
         </is>
       </c>
     </row>
@@ -7897,31 +7897,31 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>개발자 개념 장착 - 프로그래밍 개발에 필요한 필수 개념과 핵심 이론정리</t>
+          <t>[2026] 유니티 엔진 입문 올인원</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>코딩하는기술사</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1632</v>
+        <v>135</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7930,38 +7930,40 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>게임 개발</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 웹 개발, 백엔드</t>
+          <t>게임 프로그래밍</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>아키텍처, 컴퓨터 구조, 기술면접, 소프트웨어 설계, 문제해결능력</t>
-        </is>
-      </c>
-      <c r="N98" s="2" t="n"/>
+          <t>game-programming, 유니티6</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>1159</v>
+      </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2026-01-19T13:00:00.000Z</t>
+          <t>2026-06-11T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T22:11:57.790Z</t>
+          <t>2026-06-11T02:13:13.639Z</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-개념-장착-프로그래밍-개발에</t>
+          <t>https://www.inflearn.com/course/2026-unity-engine-be</t>
         </is>
       </c>
     </row>
@@ -7971,31 +7973,31 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>RNN의 모든 것 | 트랜스포머 강의 TTT 무료 공개</t>
+          <t>RAG를 활용한 LLM Application 개발 (feat. LangChain)</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>혁펜하임</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>39</v>
+        <v>4991</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
@@ -8004,40 +8006,40 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리</t>
+          <t>AI에이전트 개발, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>RNN, 딥러닝</t>
+          <t>LLM, RAG, LangChain, vector-database, openAI API</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T11:00:10.000Z</t>
+          <t>2024-06-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T17:01:56.962Z</t>
+          <t>2025-11-15T11:12:24.826Z</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/everything-about-rnn</t>
+          <t>https://www.inflearn.com/course/rag-llm-application개발-langchain</t>
         </is>
       </c>
     </row>
@@ -8047,73 +8049,73 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
+          <t>안티그래비티 CLI 하네스 엔지니어링</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>박조은</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>44330</v>
+        <v>77000</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>68200</v>
+        <v>77000</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>6</v>
+        <v>700</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>AI 실무 활용, 개발 도구, 데이터 분석</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
+          <t>Python, VSCode, gemini, 안티그래비티</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>410</v>
+        <v>584</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2025-12-03T06:00:00.000Z</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T12:02:44.178Z</t>
+          <t>2026-06-28T06:12:21.429Z</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/database-concepts-yo</t>
+          <t>https://www.inflearn.com/course/gemini-cli-딸깍으로-완성하는</t>
         </is>
       </c>
     </row>
@@ -8123,73 +8125,73 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
+          <t>Claude로 끝내는 실무 업무자동화: 엑셀·문서·PPT부터 Skills·Obsidian까지</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>HappyAI</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>44330</v>
+        <v>88000</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>68200</v>
+        <v>88000</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
+          <t>data-analysis, data-processing, n8n, 프롬프트엔지니어링, claude</t>
         </is>
       </c>
       <c r="N101" s="7" t="n">
-        <v>410</v>
+        <v>229</v>
       </c>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2026-08-01T09:00:05.000Z</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T11:44:45.232Z</t>
+          <t>2026-10-12T00:06:16.136Z</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-database-c</t>
+          <t>https://www.inflearn.com/course/mastering-practical-2</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8348,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:49+09:00</t>
+          <t>2026-10-15T13:42:03+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>144</v>
+        <v>218</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -681,73 +681,73 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
+          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>108900</v>
+        <v>52470</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>121000</v>
+        <v>174900</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>256</v>
+        <v>482</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
+          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>8</v>
+        <v>520</v>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T09:30:05.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T16:38:31.831Z</t>
+          <t>2026-08-26T10:28:07.736Z</t>
         </is>
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
+          <t>https://www.inflearn.com/course/building-embeddings</t>
         </is>
       </c>
     </row>
@@ -757,73 +757,73 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
+          <t>Claude Code 실전 업무 자동화 : 코드 없이 나만의 AI 에이전트 만들기</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>일잘러 장피엠</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>52470</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>174900</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>466</v>
+        <v>2633</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
+          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
+          <t>claude, codex, MCP, No-code</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>520</v>
+        <v>306</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-10-01T05:00:08.000Z</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T10:28:07.736Z</t>
+          <t>2026-10-05T01:55:19.117Z</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-embeddings</t>
+          <t>https://www.inflearn.com/course/practical-workflow-a</t>
         </is>
       </c>
     </row>
@@ -833,31 +833,31 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Claude Code 실전 업무 자동화 : 코드 없이 나만의 AI 에이전트 만들기</t>
+          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>일잘러 장피엠</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0</v>
+        <v>108900</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>2549</v>
+        <v>261</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
@@ -871,35 +871,35 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
+          <t>AI 실무 활용, 업무 자동화</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>claude, codex, MCP, No-code</t>
+          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>306</v>
+        <v>127</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T05:00:08.000Z</t>
+          <t>2026-10-04T09:30:05.000Z</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T01:55:19.117Z</t>
+          <t>2026-10-15T10:00:36.269Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-workflow-a</t>
+          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
         <v>10</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -985,31 +985,31 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
+          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>49500</v>
+        <v>198000</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>99000</v>
+        <v>198000</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>9</v>
+        <v>1649</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>156</v>
+        <v>11330</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
@@ -1018,40 +1018,40 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>Linux, AWS, bash, ubuntu, nginx</t>
+          <t>React, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>721</v>
+        <v>1254</v>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T07:00:10.000Z</t>
+          <t>2025-11-19T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T03:53:50.016Z</t>
+          <t>2026-08-18T03:54:49.011Z</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
+          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
         </is>
       </c>
     </row>
@@ -1061,19 +1061,19 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
+          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>퇴근후딴짓</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>198000</v>
+        <v>121000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>198000</v>
+        <v>121000</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>4.9</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1641</v>
+        <v>931</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11311</v>
+        <v>6031</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1094,40 +1094,40 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>데이터 사이언스 자격증, 데이터 분석</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>React, 인공지능(AI), claude</t>
+          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1254</v>
+        <v>1576</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2025-11-19T09:00:00.000Z</t>
+          <t>2022-12-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T03:54:49.011Z</t>
+          <t>2026-10-14T10:04:18.317Z</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
+          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
+          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>퇴근후딴짓</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>121000</v>
+        <v>49500</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>121000</v>
+        <v>99000</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>929</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>6022</v>
+        <v>162</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
@@ -1170,40 +1170,40 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 데이터 분석</t>
+          <t>데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
+          <t>Linux, AWS, bash, ubuntu, nginx</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>1576</v>
+        <v>716</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2022-12-12T15:00:00.000Z</t>
+          <t>2026-10-06T07:00:10.000Z</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T10:04:18.317Z</t>
+          <t>2026-10-16T00:06:15.984Z</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
+          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
         <v>732</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5719</v>
+        <v>5726</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -1310,10 +1310,10 @@
         <v>4.9</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>13462</v>
+        <v>13498</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0</v>
@@ -1462,10 +1462,10 @@
         <v>4.6</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>415</v>
+        <v>5</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>4662</v>
+        <v>92</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
@@ -1474,38 +1474,40 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="n"/>
+          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>363</v>
+      </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27T10:00:00.000Z</t>
+          <t>2026-09-16T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30T00:59:39.967Z</t>
+          <t>2026-09-30T03:16:06.187Z</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+          <t>https://www.inflearn.com/course/ai-automated-trading</t>
         </is>
       </c>
     </row>
@@ -1515,31 +1517,31 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1367</v>
+        <v>662</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1548,40 +1550,40 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>309</v>
+        <v>196</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:44.702Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -1591,31 +1593,31 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>89100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>89100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>236</v>
+        <v>416</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1738</v>
+        <v>4683</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
@@ -1624,40 +1626,38 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>727</v>
-      </c>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n"/>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2026-01-27T10:00:00.000Z</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2026-06-30T00:59:39.967Z</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
         </is>
       </c>
     </row>
@@ -1667,73 +1667,73 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 기본편</t>
+          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>알고런 데이터코드 연구소</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>44000</v>
+        <v>79200</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>44000</v>
+        <v>79200</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2404</v>
+        <v>77</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28224</v>
+        <v>598</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1012</v>
+        <v>785</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2025-04-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23T06:52:23.926Z</t>
+          <t>2026-07-02T07:40:07.999Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
         </is>
       </c>
     </row>
@@ -1743,73 +1743,73 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>3995</v>
+        <v>1369</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>90</v>
+        <v>309</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2026-08-30T11:28:44.702Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -1819,31 +1819,31 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
+          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>49500</v>
+        <v>440000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>99000</v>
+        <v>484000</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.5</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1852,40 +1852,40 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>363</v>
+        <v>224</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2026-10-04T05:30:05.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2026-10-16T04:14:58.414Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
         </is>
       </c>
     </row>
@@ -1895,73 +1895,73 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="F19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>173</v>
+        <v>314</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>1614</v>
+        <v>4022</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>1650</v>
+        <v>90</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T02:26:30.439Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -1971,31 +1971,31 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
+          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>김대현</t>
+          <t>회로설계 멘토 삼코치</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>6600</v>
+        <v>269500</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>11000</v>
+        <v>269500</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9</v>
+        <v>702</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -2004,40 +2004,40 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 풀스택, 프로그래밍 언어</t>
+          <t>임베디드 · IoT, 반도체</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>89</v>
+        <v>918</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:00:07.000Z</t>
+          <t>2025-03-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T02:52:17.360Z</t>
+          <t>2026-09-11T13:20:57.892Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
+          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
         </is>
       </c>
     </row>
@@ -2047,31 +2047,31 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>55000</v>
+        <v>37950</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>55000</v>
+        <v>75900</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>659</v>
+        <v>218</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
@@ -2080,40 +2080,40 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>196</v>
+        <v>641</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2026-09-28T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2026-09-29T01:52:33.960Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
         </is>
       </c>
     </row>
@@ -2123,73 +2123,73 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>37950</v>
+        <v>89100</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>75900</v>
+        <v>89100</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>214</v>
+        <v>1738</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
+          <t>security, CPPG(개인정보관리사)</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>641</v>
+        <v>727</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:30:06.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T01:52:33.960Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -2199,22 +2199,22 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>진짜! 타입스크립트 - 타입 설계부터 타입 레벨 프로그래밍까지</t>
+          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>코딩맥스 CodingMax</t>
+          <t>YoungJea Oh</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
@@ -2232,40 +2232,40 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, 함수형 프로그래밍, TypeScript, Node.js</t>
+          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>3475</v>
+        <v>370</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T01:00:07.000Z</t>
+          <t>2026-10-02T10:00:08.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T01:50:40.027Z</t>
+          <t>2026-10-02T07:55:47.247Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/really-typescript-fr</t>
+          <t>https://www.inflearn.com/course/mastering-the-latest</t>
         </is>
       </c>
     </row>
@@ -2275,22 +2275,22 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
+          <t>기획자·마케터를 위한 피그마 배리어블로 SNS 템플릿 제작법</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Hiro Son</t>
+          <t>알라딘 아카데미</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>49500</v>
+        <v>33000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>198000</v>
+        <v>110000</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -2299,49 +2299,49 @@
         <v>0</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
+          <t>디자인 · 아트, 기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
+          <t>그래픽 디자인, UX/UI, 마케팅</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+          <t>콘텐츠 마케팅, Figma, 콘텐츠 제작, autolayout, figma variable</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T17:30:06.000Z</t>
+          <t>2026-10-15T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T00:53:13.219Z</t>
+          <t>2026-10-15T08:49:08.171Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
+          <t>https://www.inflearn.com/course/how-to-create-sns-te</t>
         </is>
       </c>
     </row>
@@ -2351,19 +2351,19 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
+          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>198000</v>
+        <v>128700</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>198000</v>
+        <v>128700</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
         <v>4.9</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>305</v>
+        <v>581</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
@@ -2384,40 +2384,40 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
+          <t>AI 실무 활용, 오피스, 업무 자동화</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>api, trading, codex, 바이브코딩</t>
+          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>628</v>
+        <v>832</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09T01:30:06.000Z</t>
+          <t>2026-06-05T16:00:00.000Z</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T08:59:09.803Z</t>
+          <t>2026-08-07T06:36:11.731Z</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/create-an-automated</t>
+          <t>https://www.inflearn.com/course/starting-with-claude</t>
         </is>
       </c>
     </row>
@@ -2427,73 +2427,73 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
+          <t>김영한의 실전 자바 - 기본편</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>알고런 데이터코드 연구소</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>79200</v>
+        <v>44000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>79200</v>
+        <v>44000</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>77</v>
+        <v>2404</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>591</v>
+        <v>28224</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>785</v>
+        <v>1012</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2025-04-07T15:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T07:40:07.999Z</t>
+          <t>2025-12-23T06:52:23.926Z</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
+          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
@@ -2524,10 +2524,10 @@
         <v>5</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>153</v>
+        <v>747</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1107</v>
+        <v>11849</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
@@ -2536,40 +2536,40 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12T00:00:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-21T01:35:54.874Z</t>
+          <t>2025-08-31T09:28:51.006Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
         </is>
       </c>
     </row>
@@ -2579,73 +2579,73 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>인프런</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>33000</v>
+        <v>198000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>33000</v>
+        <v>198000</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1401</v>
+        <v>173</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>34394</v>
+        <v>1618</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>857</v>
+        <v>1649</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2019-06-01T15:00:00.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T05:48:10.725Z</t>
+          <t>2026-10-15T09:10:56.894Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -2655,73 +2655,73 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>[Chapter 1. 유치원생도 이해하는 파이썬 기초] 설치 없이 시작하는 파이썬 입문</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>숀김</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1462</v>
+        <v>16</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>AI 코딩, 프로그래밍 언어, AI 시작하기</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>algorithms, data-structure, functions, ioc, python3</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>368</v>
+        <v>121</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2026-10-14T03:00:06.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2026-10-13T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/python-basics-even-k</t>
         </is>
       </c>
     </row>
@@ -2731,19 +2731,19 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
+          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>회로설계 멘토 삼코치</t>
+          <t>마일드코드</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>269500</v>
+        <v>239800</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>269500</v>
+        <v>239800</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
@@ -2752,52 +2752,52 @@
         <v>5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>699</v>
+        <v>52</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 반도체</t>
+          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
+          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>918</v>
+        <v>480</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2025-03-25T15:00:00.000Z</t>
+          <t>2026-09-21T09:00:33.000Z</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:20:57.892Z</t>
+          <t>2026-10-13T14:25:37.776Z</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
+          <t>https://www.inflearn.com/course/claude-code-for-non</t>
         </is>
       </c>
     </row>
@@ -2807,31 +2807,31 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>인프런</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>747</v>
+        <v>1402</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>11838</v>
+        <v>34397</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
@@ -2840,40 +2840,40 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>517</v>
+        <v>857</v>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2019-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2025-08-31T09:28:51.006Z</t>
+          <t>2026-09-18T05:48:10.725Z</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2892,64 +2892,64 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>48400</v>
+        <v>99000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>48400</v>
+        <v>99000</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1560</v>
+        <v>154</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15627</v>
+        <v>1110</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1114</v>
+        <v>516</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2022-01-26T15:00:00.000Z</t>
+          <t>2026-05-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13T00:57:34.805Z</t>
+          <t>2026-09-21T01:35:54.874Z</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-리액트</t>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
         </is>
       </c>
     </row>
@@ -2959,73 +2959,73 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>440000</v>
+        <v>550000</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>484000</v>
+        <v>550000</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>20</v>
+        <v>606</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
+          <t>임베디드 · IoT, 모빌리티</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>204</v>
+        <v>1017</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T05:30:05.000Z</t>
+          <t>2025-06-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:50.737Z</t>
+          <t>2026-09-13T09:06:49.556Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
         </is>
       </c>
     </row>
@@ -3035,31 +3035,31 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
+          <t>조회수 터지는 AI 강아지 영상만들기</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>마일드코드</t>
+          <t>마이업AI</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>239800</v>
+        <v>0</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>239800</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3068,40 +3068,40 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
+          <t>AI 크리에이티브, AI 시작하기, 창업 · 부업</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
+          <t>인공지능(AI), gemini, gpt, 영상제작, AI 영상, AI 이미지</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>480</v>
+        <v>10</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:00:33.000Z</t>
+          <t>2026-10-14T08:00:07.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:25:37.776Z</t>
+          <t>2026-10-14T05:45:43.069Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-for-non</t>
+          <t>https://www.inflearn.com/course/creating-ai-dog-vide</t>
         </is>
       </c>
     </row>
@@ -3111,73 +3111,73 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>330000</v>
+        <v>48400</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>330000</v>
+        <v>48400</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>38</v>
+        <v>1560</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>536</v>
+        <v>15629</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>JavaScript, React, Node.js</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>1048</v>
+        <v>1114</v>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22T17:00:00.000Z</t>
+          <t>2022-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T22:53:04.634Z</t>
+          <t>2026-06-13T00:57:34.805Z</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
         </is>
       </c>
     </row>
@@ -3187,73 +3187,73 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
+          <t>김영한의 실전 데이터베이스 - 기본편</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>남박사</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>68200</v>
+        <v>88000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>68200</v>
+        <v>88000</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>288</v>
+        <v>517</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3411</v>
+        <v>5399</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1143</v>
+        <v>821</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2025-05-06T15:00:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12T11:29:01.075Z</t>
+          <t>2026-08-06T12:14:20.961Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
         </is>
       </c>
     </row>
@@ -3263,73 +3263,73 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
+          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>99000</v>
+        <v>154000</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>99000</v>
+        <v>154000</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>144</v>
+        <v>50</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>904</v>
+        <v>2052</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>데이터베이스, 데이터 분석, 풀스택</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
+          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>657</v>
+        <v>1270</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20T05:00:00.000Z</t>
+          <t>2026-07-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T06:39:46.390Z</t>
+          <t>2026-07-28T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/codex-true-education</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>44000</v>
+        <v>198000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>44000</v>
+        <v>198000</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>0</v>
@@ -3360,10 +3360,10 @@
         <v>4.9</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>616</v>
+        <v>51</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>8417</v>
+        <v>306</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3372,40 +3372,40 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>api, trading, codex, 바이브코딩</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>353</v>
+        <v>628</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2026-09-09T01:30:06.000Z</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2026-10-11T08:59:09.803Z</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/create-an-automated</t>
         </is>
       </c>
     </row>
@@ -3415,31 +3415,31 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>55000</v>
+        <v>88000</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>55000</v>
+        <v>88000</v>
       </c>
       <c r="F39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>480</v>
+        <v>1465</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
@@ -3448,40 +3448,40 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>SQLD, SQL, Oracle, MSSQL</t>
+          <t>업무 생산성, wiki, obsidian, claude</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>501</v>
+        <v>368</v>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13T09:30:00.000Z</t>
+          <t>2026-04-25T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T07:12:46.551Z</t>
+          <t>2026-10-08T14:26:56.788Z</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
         </is>
       </c>
     </row>
@@ -3491,31 +3491,31 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>김형태</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>3141</v>
+        <v>32</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>57315</v>
+        <v>485</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3524,40 +3524,40 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>771</v>
+        <v>483</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-05-29T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28T11:59:57.298Z</t>
+          <t>2026-09-26T10:39:08.073Z</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+          <t>https://www.inflearn.com/course/building-a-marketing</t>
         </is>
       </c>
     </row>
@@ -3567,22 +3567,22 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
+          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>49500</v>
+        <v>440000</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>99000</v>
+        <v>440000</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>0</v>
@@ -3591,49 +3591,49 @@
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
+          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>370</v>
+        <v>1240</v>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T10:00:08.000Z</t>
+          <t>2026-10-04T15:00:07.000Z</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T07:55:47.247Z</t>
+          <t>2026-10-05T03:23:49.530Z</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-latest</t>
+          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
         </is>
       </c>
     </row>
@@ -3643,73 +3643,73 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
+          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>제어쟁이</t>
+          <t>Hiro Son</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>550000</v>
+        <v>49500</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>550000</v>
+        <v>198000</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>605</v>
+        <v>22</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 모빌리티</t>
+          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>임베디드, stm32, hardware, motordriver, artwork</t>
+          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1017</v>
+        <v>184</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2025-06-15T15:00:00.000Z</t>
+          <t>2026-10-07T17:30:06.000Z</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T09:06:49.556Z</t>
+          <t>2026-10-15T07:17:43.638Z</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
+          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
         </is>
       </c>
     </row>
@@ -3719,19 +3719,19 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>그랩</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>0</v>
@@ -3740,10 +3740,10 @@
         <v>5</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>8119</v>
+        <v>30</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>123267</v>
+        <v>335</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
@@ -3752,40 +3752,40 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, MVC, Spring Boot</t>
+          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>321</v>
+        <v>896</v>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>2020-07-19T15:00:00.000Z</t>
+          <t>2026-07-23T04:50:00.000Z</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2026-01-30T11:34:33.353Z</t>
+          <t>2026-08-01T16:24:39.937Z</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
         </is>
       </c>
     </row>
@@ -3795,73 +3795,73 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>128700</v>
+        <v>0</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>128700</v>
+        <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>40</v>
+        <v>8119</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>579</v>
+        <v>123272</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 오피스, 업무 자동화</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
+          <t>Java, Spring, MVC, Spring Boot</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>832</v>
+        <v>321</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05T16:00:00.000Z</t>
+          <t>2020-07-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T06:36:11.731Z</t>
+          <t>2026-01-30T11:34:33.353Z</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/starting-with-claude</t>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>나도코딩</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
@@ -3889,13 +3889,13 @@
         <v>0</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>1932</v>
+        <v>3141</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>40215</v>
+        <v>57316</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
@@ -3909,35 +3909,35 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>358</v>
+        <v>771</v>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>2020-02-24T15:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T06:34:34.311Z</t>
+          <t>2026-01-28T11:59:57.298Z</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
         </is>
       </c>
     </row>
@@ -3947,73 +3947,73 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 기본편</t>
+          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>517</v>
+        <v>617</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5396</v>
+        <v>8419</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>개발 도구</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>Git, GitHub, github-actions, git-commands</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>821</v>
+        <v>353</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2022-01-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06T12:14:20.961Z</t>
+          <t>2026-06-03T09:18:28.574Z</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
+          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
         </is>
       </c>
     </row>
@@ -4023,31 +4023,31 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>6179</v>
+        <v>907</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
@@ -4056,40 +4056,40 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, routing</t>
+          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>779</v>
+        <v>657</v>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2026-07-20T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:27:31.006Z</t>
+          <t>2026-10-11T06:39:46.390Z</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+          <t>https://www.inflearn.com/course/codex-true-education</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>나도코딩</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
@@ -4120,10 +4120,10 @@
         <v>4.9</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>98</v>
+        <v>1933</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1109</v>
+        <v>40221</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4132,38 +4132,40 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="n"/>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>358</v>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T04:00:06.000Z</t>
+          <t>2020-02-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T07:01:04.312Z</t>
+          <t>2025-04-29T06:34:34.311Z</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
         </is>
       </c>
     </row>
@@ -4173,73 +4175,73 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>51</v>
+        <v>6184</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
+          <t>네트워크, tcpip, routing</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>1240</v>
+        <v>779</v>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T15:00:07.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T03:23:49.530Z</t>
+          <t>2025-04-29T09:27:31.006Z</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
         </is>
       </c>
     </row>
@@ -4249,31 +4251,31 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>BHPT - 호스트 기반 모의해킹 기초</t>
+          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>레드라쿤</t>
+          <t>피엠인사이드</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>198000</v>
+        <v>330000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>198000</v>
+        <v>330000</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1161</v>
+        <v>20</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4282,40 +4284,40 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>보안, 시스템 · 운영체제, 네트워크</t>
+          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>모의해킹, 오펜시브 시큐리티, 네트워크, kali-linux</t>
+          <t>프로젝트 관리, PMP</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1031</v>
+        <v>2379</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2024-01-01T15:00:00.000Z</t>
+          <t>2026-10-01T13:00:08.000Z</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-03-30T05:39:15.743Z</t>
+          <t>2026-10-16T03:05:49.547Z</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/호스트-기반-모의해킹-기초</t>
+          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
         </is>
       </c>
     </row>
@@ -4325,31 +4327,31 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
+          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>피엠인사이드</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>330000</v>
+        <v>55000</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>330000</v>
+        <v>55000</v>
       </c>
       <c r="F51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>20</v>
+        <v>481</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
@@ -4358,40 +4360,40 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
+          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 관리, PMP</t>
+          <t>SQLD, SQL, Oracle, MSSQL</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>2392</v>
+        <v>501</v>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T13:00:08.000Z</t>
+          <t>2026-01-13T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T13:35:49.299Z</t>
+          <t>2026-10-12T07:12:46.551Z</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
+          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4403,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
+          <t>실전! 스프링 부트와 JPA 활용2 - API 개발과 성능 최적화</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4410,10 +4412,10 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>154000</v>
+        <v>88000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>154000</v>
+        <v>88000</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
@@ -4422,10 +4424,10 @@
         <v>5</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48</v>
+        <v>1404</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2051</v>
+        <v>21971</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4434,40 +4436,40 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 풀스택</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
+          <t>Java, Spring, Spring Boot, JPA</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1270</v>
+        <v>395</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00.000Z</t>
+          <t>2019-10-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28T00:00:00.000Z</t>
+          <t>2025-05-13T07:23:46.889Z</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
+          <t>https://www.inflearn.com/course/스프링부트-JPA-API개발-성능최적화</t>
         </is>
       </c>
     </row>
@@ -4477,73 +4479,73 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
+          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>김대현</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>38500</v>
+        <v>6600</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>38500</v>
+        <v>11000</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>백엔드, 풀스택, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>SQL, Oracle, database, modeling, SQLD</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N53" s="7" t="n">
-        <v>923</v>
+        <v>89</v>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02T03:00:00.000Z</t>
+          <t>2026-10-13T05:00:07.000Z</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02T00:00:00.000Z</t>
+          <t>2026-10-13T02:52:17.360Z</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
+          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
         </is>
       </c>
     </row>
@@ -4553,73 +4555,73 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>[Chapter 1. 유치원생도 이해하는 파이썬 기초] 설치 없이 시작하는 파이썬 입문</t>
+          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13</v>
+        <v>2973</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, 프로그래밍 언어, AI 시작하기</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>algorithms, data-structure, functions, ioc, python3</t>
+          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>121</v>
+        <v>797</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T03:00:06.000Z</t>
+          <t>2026-01-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T00:00:00.000Z</t>
+          <t>2026-02-09T09:50:03.741Z</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/python-basics-even-k</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
         </is>
       </c>
     </row>
@@ -4629,73 +4631,73 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>99000</v>
+        <v>330000</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>99000</v>
+        <v>330000</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>580</v>
+        <v>538</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N55" s="7" t="n">
-        <v>924</v>
+        <v>1048</v>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>2025-10-03T09:30:00.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2025-11-10T10:01:12.921Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -4705,22 +4707,22 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
+          <t>진짜! 타입스크립트 - 타입 설계부터 타입 레벨 프로그래밍까지</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>코딩맥스 CodingMax</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>69300</v>
+        <v>49500</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>99000</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
@@ -4729,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4738,40 +4740,40 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
+          <t>JavaScript, 함수형 프로그래밍, TypeScript, Node.js</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>73</v>
+        <v>3475</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T11:00:10.000Z</t>
+          <t>2026-10-13T01:00:07.000Z</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T17:09:46.044Z</t>
+          <t>2026-10-13T01:50:40.027Z</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
+          <t>https://www.inflearn.com/course/really-typescript-fr</t>
         </is>
       </c>
     </row>
@@ -4781,73 +4783,71 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="F57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>785</v>
+        <v>1115</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
-        </is>
-      </c>
-      <c r="N57" s="7" t="n">
-        <v>1266</v>
-      </c>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="n"/>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07T05:00:33.000Z</t>
+          <t>2026-06-27T04:00:06.000Z</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T22:16:49.715Z</t>
+          <t>2026-06-30T07:01:04.312Z</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-llm-servic</t>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
         </is>
       </c>
     </row>
@@ -4857,19 +4857,19 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>시스코 CCNA 함께 공부해요</t>
+          <t>베개투자법 완성: 아침이 설레는 AI 주식 완전 자동매매  Claude 바이브코딩</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ccie_pe_kim</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>0</v>
+        <v>132000</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0</v>
+        <v>132000</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
@@ -4878,10 +4878,10 @@
         <v>4.9</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1765</v>
+        <v>279</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4890,40 +4890,40 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+          <t>AI 개발 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, routing, tcpip</t>
+          <t>Python, 머신러닝, AWS, FastAPI, 퀀트, cloud-computing, claude</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>1213</v>
+        <v>309</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T15:00:00.000Z</t>
+          <t>2026-05-17T08:30:00.000Z</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25T09:44:13.272Z</t>
+          <t>2026-06-29T05:27:04.296Z</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+          <t>https://www.inflearn.com/course/automated-trading-th</t>
         </is>
       </c>
     </row>
@@ -4933,19 +4933,19 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>66000</v>
+        <v>64900</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>66000</v>
+        <v>64900</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>0</v>
@@ -4954,10 +4954,10 @@
         <v>5</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>1265</v>
+        <v>5</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>12542</v>
+        <v>787</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
@@ -4966,40 +4966,40 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
         </is>
       </c>
       <c r="N59" s="7" t="n">
-        <v>1161</v>
+        <v>1266</v>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2026-09-07T05:00:33.000Z</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2026-10-13T22:16:49.715Z</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/practical-llm-servic</t>
         </is>
       </c>
     </row>
@@ -5009,31 +5009,31 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>멍슨상</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>0</v>
+        <v>36300</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>460</v>
+        <v>9</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21165</v>
+        <v>317</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5042,40 +5042,40 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+          <t>Python, Java, C, 정보처리기사, database</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>823</v>
+        <v>1553</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2023-03-02T15:00:00.000Z</t>
+          <t>2025-09-24T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T09:43:24.787Z</t>
+          <t>2026-10-11T06:06:52.494Z</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>정보처리기사 자격증 대비 교육(실기)</t>
+          <t>시스코 CCNA 함께 공부해요</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>국립안동대학교 SW융합교육원</t>
+          <t>ccie_pe_kim</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
@@ -5103,13 +5103,13 @@
         <v>0</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>2236</v>
+        <v>1770</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
@@ -5118,40 +5118,40 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증</t>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>정보처리기사</t>
+          <t>네트워크, CCNA, routing, tcpip</t>
         </is>
       </c>
       <c r="N61" s="7" t="n">
-        <v>1532</v>
+        <v>1213</v>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>2024-08-13T15:00:00.000Z</t>
+          <t>2026-01-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>2024-08-14T00:00:00.000Z</t>
+          <t>2026-03-25T09:44:13.272Z</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
         </is>
       </c>
     </row>
@@ -5161,73 +5161,73 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>타입스크립트로 배우는 리액트(React.js) : 기초부터 최신 기술까지 완벽하게</t>
+          <t>리눅스 입문 - 개념으로 탄탄히!!</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>수코딩</t>
+          <t>런잇(ProgCoach4U)</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>79200</v>
+        <v>77000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>86</v>
+        <v>301</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>624</v>
+        <v>3495</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발, 모바일 앱 개발</t>
+          <t>시스템 · 운영체제, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>React, react-router, redux-toolkit, zustand, react.js</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
-        <v>1615</v>
+        <v>757</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2025-06-08T15:00:00.000Z</t>
+          <t>2021-06-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25T06:25:45.941Z</t>
+          <t>2025-05-13T07:44:10.964Z</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/typescript-react-perfect-course</t>
+          <t>https://www.inflearn.com/course/리눅스-입문</t>
         </is>
       </c>
     </row>
@@ -5237,19 +5237,19 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 AI 개발자의 LLM 서비스를 위한 RAG</t>
+          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>남박사</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>165000</v>
+        <v>68200</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>165000</v>
+        <v>68200</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>0</v>
@@ -5258,10 +5258,10 @@
         <v>4.8</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>14</v>
+        <v>288</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>683</v>
+        <v>3414</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
@@ -5270,40 +5270,40 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
+          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, Python, 인공지능(AI), ChatGPT, RAG</t>
+          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N63" s="7" t="n">
-        <v>531</v>
+        <v>1143</v>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14T08:00:08.000Z</t>
+          <t>2025-05-06T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T00:24:12.168Z</t>
+          <t>2026-06-12T11:29:01.075Z</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-rag-as-tau</t>
+          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
         </is>
       </c>
     </row>
@@ -5313,73 +5313,73 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>AI에게 마음 놓고 맡기는 바이브코딩 : 망쳐도 한 문장으로 되돌리는 Git 버전 관리</t>
+          <t>스프링 핵심 원리 - 고급편</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Masocampus</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>34650</v>
+        <v>121000</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>49500</v>
+        <v>121000</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
+        <v>21012</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI에이전트 개발</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), Git, 바이브코딩, VSCode, codex, GitHub</t>
+          <t>Spring, 디자인 패턴</t>
         </is>
       </c>
       <c r="N64" s="2" t="n">
-        <v>119</v>
+        <v>1004</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T02:00:06.000Z</t>
+          <t>2021-10-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T02:14:59.154Z</t>
+          <t>2025-12-21T11:02:33.060Z</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/vibe-coding-you-can</t>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-고급편</t>
         </is>
       </c>
     </row>
@@ -5389,73 +5389,73 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
+          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>김형태</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>138600</v>
+        <v>69300</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>198000</v>
+        <v>99000</v>
       </c>
       <c r="F65" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>482</v>
+        <v>48</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
+          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
+          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
         </is>
       </c>
       <c r="N65" s="7" t="n">
-        <v>483</v>
+        <v>73</v>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>2026-05-29T02:00:00.000Z</t>
+          <t>2026-10-08T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26T10:39:08.073Z</t>
+          <t>2026-10-11T17:09:46.044Z</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-a-marketing</t>
+          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
         </is>
       </c>
     </row>
@@ -5465,31 +5465,31 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
+          <t>베개 투자법: 자면서 돈 버는 AI 주식 자동 매매 머신</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>시드니개발자의 영어PT</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>220000</v>
+        <v>99000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>220000</v>
+        <v>99000</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2198</v>
+        <v>611</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5498,40 +5498,40 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>외국어</t>
+          <t>AI 기술, 커리어 · 자기계발, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>AI에이전트 개발, 금융 ·  재테크, 데이터 분석</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>Python, 딥러닝, 데이터 엔지니어링, FastAPI, 빅데이터</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>49</v>
+        <v>349</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2023-01-12T15:00:00.000Z</t>
+          <t>2025-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T05:15:40.989Z</t>
+          <t>2026-09-30T03:37:05.105Z</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
+          <t>https://www.inflearn.com/course/베개투자법-ai주식-자동매매머신</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>노베이스를 위한 ADsP 생존 가이드</t>
+          <t>정보처리기사 자격증 대비 교육(실기)</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>국립안동대학교 SW융합교육원</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
@@ -5559,55 +5559,55 @@
         <v>0</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>761</v>
+        <v>2239</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
+          <t>개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>SQL, R, ADsP</t>
+          <t>정보처리기사</t>
         </is>
       </c>
       <c r="N67" s="7" t="n">
-        <v>303</v>
+        <v>1532</v>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T11:00:00.000Z</t>
+          <t>2024-08-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T09:14:53.120Z</t>
+          <t>2024-08-14T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
+          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
         </is>
       </c>
     </row>
@@ -5617,73 +5617,73 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>실리콘 밸리 엔지니어와 함께하는 Local LLM 완전 정복 (LM Studio &amp; Ollama &amp; Ollaya)</t>
+          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>41250</v>
+        <v>99000</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>55000</v>
+        <v>99000</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>688</v>
+        <v>580</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
+          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), LLM, AI Agent</t>
+          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
         </is>
       </c>
       <c r="N68" s="2" t="n">
-        <v>270</v>
+        <v>924</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17T18:00:00.000Z</t>
+          <t>2025-10-03T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T05:15:20.298Z</t>
+          <t>2025-11-10T10:01:12.921Z</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-local-llm</t>
+          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
         </is>
       </c>
     </row>
@@ -5693,19 +5693,19 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
+          <t>한국에서 제일 쉬운 리눅스 커널 강의</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>그랩</t>
+          <t>ojtube5</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>198000</v>
+        <v>110000</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>198000</v>
+        <v>110000</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>0</v>
@@ -5714,10 +5714,10 @@
         <v>5</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>333</v>
+        <v>537</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
@@ -5726,40 +5726,40 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>하드웨어, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
+          <t>임베디드 · IoT, 컴퓨터 구조, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>Linux, 운영체제, asm, C, Raspberry Pi, ARM Architecture</t>
         </is>
       </c>
       <c r="N69" s="7" t="n">
-        <v>896</v>
+        <v>1231</v>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23T04:50:00.000Z</t>
+          <t>2024-10-08T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01T16:24:39.937Z</t>
+          <t>2025-05-13T07:41:48.813Z</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
+          <t>https://www.inflearn.com/course/한국에서-제일쉬운-리눅스커널-강의</t>
         </is>
       </c>
     </row>
@@ -5769,19 +5769,19 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>대세는 쿠버네티스 (초급~중급편)</t>
+          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>0</v>
@@ -5790,52 +5790,52 @@
         <v>4.9</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>626</v>
+        <v>460</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8498</v>
+        <v>21174</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
+          <t>컴퓨터 구조, 운영체제, 기술면접</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>425</v>
+        <v>823</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2019-09-10T15:00:00.000Z</t>
+          <t>2023-03-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2025-11-19T05:23:15.024Z</t>
+          <t>2025-04-29T09:43:24.787Z</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
         </is>
       </c>
     </row>
@@ -5845,31 +5845,31 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
+          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>77000</v>
+        <v>82500</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>77000</v>
+        <v>82500</v>
       </c>
       <c r="F71" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>349</v>
+        <v>790</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>5460</v>
+        <v>2912</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
@@ -5878,40 +5878,40 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
+          <t>Kubernetes, devops, argocd, container, helm</t>
         </is>
       </c>
       <c r="N71" s="7" t="n">
-        <v>1001</v>
+        <v>669</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>2025-03-24T15:00:00.000Z</t>
+          <t>2023-09-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>2025-09-14T05:27:02.800Z</t>
+          <t>2026-05-27T08:15:25.352Z</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
         </is>
       </c>
     </row>
@@ -5921,31 +5921,31 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
+          <t>AI 에이전트로 구현하는 RAG 시스템(w. LangGraph)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>판다스 스튜디오</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>121000</v>
+        <v>99000</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>121000</v>
+        <v>99000</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2970</v>
+        <v>8047</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5954,40 +5954,40 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>AI에이전트 개발</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
+          <t>AI Agent, LangGraph, RAG, LLM, LangChain</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>797</v>
+        <v>405</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27T15:00:00.000Z</t>
+          <t>2024-10-22T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09T09:50:03.741Z</t>
+          <t>2026-03-04T03:56:05.522Z</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
+          <t>https://www.inflearn.com/course/ai에이전트-구현-rag시스템-랭그래프</t>
         </is>
       </c>
     </row>
@@ -5997,31 +5997,31 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Decision AI로 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
+          <t>BHPT - 호스트 기반 모의해킹 기초</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>레드라쿤</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>22000</v>
+        <v>198000</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>22000</v>
+        <v>198000</v>
       </c>
       <c r="F73" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>20</v>
+        <v>1161</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
@@ -6030,40 +6030,40 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
+          <t>보안, 시스템 · 운영체제, 네트워크</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
+          <t>모의해킹, 오펜시브 시큐리티, 네트워크, kali-linux</t>
         </is>
       </c>
       <c r="N73" s="7" t="n">
-        <v>109</v>
+        <v>1031</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T05:00:08.000Z</t>
+          <t>2024-01-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T19:46:29.290Z</t>
+          <t>2026-03-30T05:39:15.743Z</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-decision-a</t>
+          <t>https://www.inflearn.com/course/호스트-기반-모의해킹-기초</t>
         </is>
       </c>
     </row>
@@ -6073,31 +6073,31 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
+          <t>토비의 클린 스프링 - 도메인 모델 패턴과 헥사고날 아키텍처 Part 2</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>토비</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>44550</v>
+        <v>99000</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>59400</v>
+        <v>99000</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>227</v>
+        <v>630</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6106,40 +6106,40 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
+          <t>백엔드</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
+          <t>Java, Spring, Spring Boot, JPA, 리팩터링, DDD, hexagonal-architecture</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>311</v>
+        <v>779</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T10:30:06.000Z</t>
+          <t>2026-07-16T08:12:00.000Z</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T14:30:32.966Z</t>
+          <t>2026-07-16T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
+          <t>https://www.inflearn.com/course/tobys-clean-spring-d</t>
         </is>
       </c>
     </row>
@@ -6149,31 +6149,31 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 2편</t>
+          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>66000</v>
+        <v>44550</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>66000</v>
+        <v>59400</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>881</v>
+        <v>23</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>11023</v>
+        <v>229</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
@@ -6182,40 +6182,40 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
         </is>
       </c>
       <c r="N75" s="7" t="n">
-        <v>1165</v>
+        <v>311</v>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>2024-05-07T15:00:00.000Z</t>
+          <t>2026-07-31T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2025-11-24T10:17:13.631Z</t>
+          <t>2026-08-12T14:30:32.966Z</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
         </is>
       </c>
     </row>
@@ -6225,31 +6225,31 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
+          <t>Decision AI로 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>79200</v>
+        <v>22000</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>79200</v>
+        <v>22000</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6760</v>
+        <v>20</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6258,40 +6258,40 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
+          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>357</v>
+        <v>109</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2025-07-11T02:00:00.000Z</t>
+          <t>2026-10-06T05:00:08.000Z</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10T22:31:31.977Z</t>
+          <t>2026-10-12T19:46:29.290Z</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
+          <t>https://www.inflearn.com/course/practical-decision-a</t>
         </is>
       </c>
     </row>
@@ -6301,19 +6301,19 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>리눅스 입문 - 개념으로 탄탄히!!</t>
+          <t>대세는 쿠버네티스 (초급~중급편)</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>런잇(ProgCoach4U)</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>77000</v>
+        <v>44000</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>77000</v>
+        <v>44000</v>
       </c>
       <c r="F77" s="10" t="n">
         <v>0</v>
@@ -6322,52 +6322,52 @@
         <v>4.9</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>301</v>
+        <v>626</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>3491</v>
+        <v>8499</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>시스템 · 운영체제, 데브옵스 · 인프라</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
         </is>
       </c>
       <c r="N77" s="7" t="n">
-        <v>757</v>
+        <v>425</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>2021-06-02T15:00:00.000Z</t>
+          <t>2019-09-10T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:44:10.964Z</t>
+          <t>2025-11-19T05:23:15.024Z</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/리눅스-입문</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
         </is>
       </c>
     </row>
@@ -6377,31 +6377,31 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
+          <t>[AI 리터러시 저자직강] 모든 직장인이 활용할 수 있는 올인원 AI 활용법(26년 6월 전체 리뉴얼)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>멍슨상</t>
+          <t>김용성</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>36300</v>
+        <v>110000</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>48400</v>
+        <v>110000</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>315</v>
+        <v>1138</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6410,40 +6410,40 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, database</t>
+          <t>업무 생산성, 영상제작, 서비스 기획, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>1553</v>
+        <v>274</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2025-09-24T07:00:00.000Z</t>
+          <t>2025-09-09T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T06:06:52.494Z</t>
+          <t>2026-06-07T08:14:11.781Z</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
+          <t>https://www.inflearn.com/course/ai-리터러시-저자직강-모든-직장인이</t>
         </is>
       </c>
     </row>
@@ -6453,19 +6453,19 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
+          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>nstyxn</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>118800</v>
+        <v>77000</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>118800</v>
+        <v>77000</v>
       </c>
       <c r="F79" s="10" t="n">
         <v>0</v>
@@ -6474,52 +6474,52 @@
         <v>5</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>87</v>
+        <v>605</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>959</v>
+        <v>9781</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>보안, 보안 · 네트워크 자격증</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>Forensic, 디지털포렌식전문가 2급</t>
+          <t>Java, 객체지향, thread, multithread, 동시성</t>
         </is>
       </c>
       <c r="N79" s="7" t="n">
-        <v>6530</v>
+        <v>1249</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>2022-11-13T15:00:00.000Z</t>
+          <t>2024-07-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15T02:00:30.898Z</t>
+          <t>2025-11-18T01:46:58.908Z</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
         </is>
       </c>
     </row>
@@ -6529,73 +6529,73 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>2026년 완벽한 Claude AI 강좌: 프롬프트, 콘텐츠, SEO 및 비즈니스</t>
+          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Tanmoy Das</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>15400</v>
+        <v>79200</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>22000</v>
+        <v>79200</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4</v>
+        <v>6762</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 크리에이티브, AI 시작하기</t>
+          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), claude, AI Agent, 블록체인, 보안 교육, AX(에이전트 경험), ChatGPT</t>
+          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>827</v>
+        <v>357</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T04:00:08.000Z</t>
+          <t>2025-07-11T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T03:58:13.247Z</t>
+          <t>2025-11-10T22:31:31.977Z</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/full-claude-ai-cours</t>
+          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
         </is>
       </c>
     </row>
@@ -6605,31 +6605,31 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
+          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>최원영</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="F81" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>1572</v>
+        <v>64</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
@@ -6638,40 +6638,40 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI)</t>
+          <t>SQL, Oracle, database, modeling, SQLD</t>
         </is>
       </c>
       <c r="N81" s="7" t="n">
-        <v>32</v>
+        <v>923</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27T05:00:00.000Z</t>
+          <t>2026-09-02T03:00:00.000Z</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27T06:18:36.692Z</t>
+          <t>2026-09-02T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
+          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
         </is>
       </c>
     </row>
@@ -6681,73 +6681,73 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>AI 에이전트 엔지니어링</t>
+          <t>React 완벽 마스터: 기초 개념부터 린캔버스 프로젝트까지</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>민혁</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2063</v>
+        <v>963</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Python, 인공지능(AI), RAG, AI Agent</t>
+          <t>React, react-query, react-router, React Context, TailwindCSS</t>
         </is>
       </c>
       <c r="N82" s="2" t="n">
-        <v>322</v>
+        <v>1054</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07T05:00:00.000Z</t>
+          <t>2024-09-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07T02:58:08.781Z</t>
+          <t>2025-09-09T02:15:49.950Z</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
+          <t>https://www.inflearn.com/course/react-완벽가이드-기초-프로젝트</t>
         </is>
       </c>
     </row>
@@ -6757,31 +6757,31 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
+          <t>김영한의 실전 자바 - 중급 1편</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>82500</v>
+        <v>66000</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>82500</v>
+        <v>66000</v>
       </c>
       <c r="F83" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>789</v>
+        <v>1265</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>2912</v>
+        <v>12542</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
@@ -6790,40 +6790,40 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, argocd, container, helm</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N83" s="7" t="n">
-        <v>669</v>
+        <v>1161</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>2023-09-11T15:00:00.000Z</t>
+          <t>2024-03-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>2026-05-27T08:15:25.352Z</t>
+          <t>2025-11-28T10:04:41.236Z</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
         </is>
       </c>
     </row>
@@ -6833,19 +6833,19 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>챗봇을 만들며 배우는 ai agent 개발의 모든것(fastapi, RAG, vector, LangChain, sLLM/파인튜닝)</t>
+          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>bradkim</t>
+          <t>nstyxn</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>88000</v>
+        <v>118800</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>88000</v>
+        <v>118800</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0</v>
@@ -6854,10 +6854,10 @@
         <v>5</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>336</v>
+        <v>959</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6866,40 +6866,40 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 인공지능 기타, AI 개발 활용</t>
+          <t>보안, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>RAG, vector-database, FastAPI, LLM, Llama, Fine-Tuning, openAI API</t>
+          <t>Forensic, 디지털포렌식전문가 2급</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>507</v>
+        <v>6530</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T06:30:06.000Z</t>
+          <t>2022-11-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T07:03:29.747Z</t>
+          <t>2026-07-15T02:00:30.898Z</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/everything-about-ai</t>
+          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
         </is>
       </c>
     </row>
@@ -6909,31 +6909,31 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ②</t>
+          <t>알고리즘 트레이딩의 비밀, AI가 주가를 맞추는 법</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>44330</v>
+        <v>47300</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>68200</v>
+        <v>47300</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>6</v>
+        <v>484</v>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
@@ -6942,40 +6942,40 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스, AI 기술, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>데이터 분석, 데이터 엔지니어링, 딥러닝 · 머신러닝, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL, MongoDB, DBMS/RDBMS, Redis, NoSQL, 인공지능(AI), dynamodb</t>
+          <t>딥러닝, Python, transformer, lstm, 재테크</t>
         </is>
       </c>
       <c r="N85" s="7" t="n">
-        <v>410</v>
+        <v>119</v>
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2025-02-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10T12:02:44.178Z</t>
+          <t>2025-08-25T04:22:21.430Z</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/database-concepts-yo</t>
+          <t>https://www.inflearn.com/course/ai딥러닝기반-미국주식-분석</t>
         </is>
       </c>
     </row>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 데이터베이스 개념 ①</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ②</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6994,13 +6994,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>44330</v>
+        <v>33000</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>68200</v>
+        <v>66000</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>0</v>
@@ -7009,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -7023,35 +7023,35 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, AI 코딩</t>
+          <t>백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>SQL, PostgreSQL, DBMS/RDBMS, 동시성, database, 인공지능(AI), database-modeling</t>
+          <t>네트워크, Docker, backend, devops, 인공지능(AI), RAG</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>410</v>
+        <v>461</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T13:30:05.000Z</t>
+          <t>2026-09-18T04:30:06.000Z</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T11:44:45.232Z</t>
+          <t>2026-09-17T22:23:02.274Z</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-database-c</t>
+          <t>https://www.inflearn.com/course/essential-backend-co-1</t>
         </is>
       </c>
     </row>
@@ -7061,73 +7061,73 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>실무에 바로 적용하는 Spring AI: Spring 서비스에 챗봇·RAG·MCP 도입하기</t>
+          <t>AI 에이전트 엔지니어링</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 시니</t>
+          <t>민혁</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>61600</v>
+        <v>0</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>588</v>
+        <v>2070</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 백엔드, AI 코딩</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, Elasticsearch, vector-database, LLM, RAG, Spring AI, MCP</t>
+          <t>Python, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N87" s="7" t="n">
-        <v>439</v>
+        <v>322</v>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12T23:30:00.000Z</t>
+          <t>2026-04-07T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:43.252Z</t>
+          <t>2026-04-07T02:58:08.781Z</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/spring-ai-in-practic</t>
+          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
         </is>
       </c>
     </row>
@@ -7137,73 +7137,73 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>홍정모의 따라하며 배우는 C++</t>
+          <t>서비스기획 &amp; 프로덕트 매니저(PM)의 첫걸음[입문]</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>홍정모</t>
+          <t>레브(Reve)</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>176000</v>
+        <v>49500</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>176000</v>
+        <v>55000</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>395</v>
+        <v>42</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>7125</v>
+        <v>300</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 게임 개발</t>
+          <t>기획 · 경영 · 마케팅, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
+          <t>기획 · PM· PO, 취업 · 이직</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>서비스 기획, Figma, 프로젝트 관리, 포트폴리오</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>2907</v>
+        <v>321</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2018-09-30T15:00:00.000Z</t>
+          <t>2025-02-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2025-08-10T19:46:59.750Z</t>
+          <t>2025-08-13T23:51:26.711Z</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/following-c-plus</t>
+          <t>https://www.inflearn.com/course/프로덕트-매니저-본질</t>
         </is>
       </c>
     </row>
@@ -7213,12 +7213,12 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
+          <t>[리뉴얼] 처음하는 SQL과 데이터베이스(MySQL) 부트캠프 [입문부터 활용까지]</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>잔재미코딩 DaveLee</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
@@ -7231,13 +7231,13 @@
         <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>605</v>
+        <v>328</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>9780</v>
+        <v>4363</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
@@ -7246,40 +7246,40 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>데이터베이스, 데이터 분석</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, thread, multithread, 동시성</t>
+          <t>Python, SQL, MySQL, DBMS/RDBMS, 데이터 엔지니어링</t>
         </is>
       </c>
       <c r="N89" s="7" t="n">
-        <v>1249</v>
+        <v>528</v>
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>2024-07-14T15:00:00.000Z</t>
+          <t>2019-09-08T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>2025-11-18T01:46:58.908Z</t>
+          <t>2026-08-27T04:47:42.744Z</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
+          <t>https://www.inflearn.com/course/sql-db-mysql-파이썬-데이터분석</t>
         </is>
       </c>
     </row>
@@ -7289,31 +7289,31 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>#2-1 ComfyUI 마스터하기: 애니 2D 일러스트 제작 총집편 (SD 1.5 · SDXL · PonyXL)</t>
+          <t>38군데 합격 비법, 2026 코딩테스트 필수 알고리즘</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>닭강정</t>
+          <t>딩코딩코</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>24750</v>
+        <v>165000</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>33000</v>
+        <v>165000</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>56</v>
+        <v>2887</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7322,40 +7322,40 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>AI 크리에이티브, 컴퓨터 비전, AI 시작하기</t>
+          <t>알고리즘 · 자료구조, 취업 · 이직</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>InDesign, motion, animations, ui, us-ascii</t>
+          <t>Python, 코딩 테스트, 알고리즘, data-structure</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>349</v>
+        <v>934</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19T22:00:00.000Z</t>
+          <t>2024-11-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T00:00:00.000Z</t>
+          <t>2026-09-10T05:18:11.523Z</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/2-1-mastering-comfyu</t>
+          <t>https://www.inflearn.com/course/38군데-합격비법-코테-필수-알고리즘</t>
         </is>
       </c>
     </row>
@@ -7365,73 +7365,73 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
+          <t>노베이스를 위한 ADsP 생존 가이드</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>코드바나나</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>148500</v>
+        <v>0</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>148500</v>
+        <v>0</v>
       </c>
       <c r="F91" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>320</v>
+        <v>22</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>3755</v>
+        <v>767</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
+          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>AWS, 네트워크, AWS SAA</t>
+          <t>SQL, R, ADsP</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
-        <v>1450</v>
+        <v>303</v>
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>2022-06-21T15:00:00.000Z</t>
+          <t>2025-11-11T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T03:07:28.063Z</t>
+          <t>2025-11-11T09:14:53.120Z</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
+          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
         </is>
       </c>
     </row>
@@ -7441,73 +7441,73 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>React 완벽 마스터: 기초 개념부터 린캔버스 프로젝트까지</t>
+          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>최원영</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>145</v>
+        <v>86</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>962</v>
+        <v>1576</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>React, react-query, react-router, React Context, TailwindCSS</t>
+          <t>인공지능(AI)</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>1054</v>
+        <v>32</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2024-09-11T15:00:00.000Z</t>
+          <t>2026-02-27T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09T02:15:49.950Z</t>
+          <t>2026-02-27T06:18:36.692Z</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/react-완벽가이드-기초-프로젝트</t>
+          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
         </is>
       </c>
     </row>
@@ -7517,31 +7517,31 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>AI를 위한 미적분 — 도함수, 그래디언트, 그리고 신경망이 학습하는 원리</t>
+          <t>타입스크립트로 배우는 리액트(React.js) : 기초부터 최신 기술까지 완벽하게</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>코딩맥스 CodingMax</t>
+          <t>수코딩</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>99000</v>
+        <v>79200</v>
       </c>
       <c r="E93" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>32</v>
+        <v>624</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
@@ -7550,40 +7550,40 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 대학 교육</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 수학</t>
+          <t>프론트엔드, 웹 개발, 모바일 앱 개발</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>머신러닝, 딥러닝, 인공신경망, 선형대수학, 미적분, 인공지능(AI)</t>
+          <t>React, react-router, redux-toolkit, zustand, react.js</t>
         </is>
       </c>
       <c r="N93" s="7" t="n">
-        <v>1093</v>
+        <v>1615</v>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13T08:00:08.000Z</t>
+          <t>2025-06-08T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13T05:41:38.564Z</t>
+          <t>2026-05-25T06:25:45.941Z</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/calculus-for-ai-deri</t>
+          <t>https://www.inflearn.com/course/typescript-react-perfect-course</t>
         </is>
       </c>
     </row>
@@ -7593,31 +7593,31 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>비전공자들을 위한 실무 밀착 네이버 검색광고</t>
+          <t>실리콘밸리 AI 개발자의 LLM 서비스를 위한 RAG</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>그로스쿨</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>77000</v>
+        <v>165000</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>77000</v>
+        <v>165000</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>224</v>
+        <v>684</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7626,40 +7626,40 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>네이버 키워드 검색</t>
+          <t>JavaScript, Python, 인공지능(AI), ChatGPT, RAG</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>319</v>
+        <v>531</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22T06:30:00.000Z</t>
+          <t>2026-08-14T08:00:08.000Z</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:40:58.257Z</t>
+          <t>2026-10-02T00:24:12.168Z</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-naver-sa-f</t>
+          <t>https://www.inflearn.com/course/mastering-rag-as-tau</t>
         </is>
       </c>
     </row>
@@ -7669,31 +7669,31 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>스프링 부트 4, Spring Boot 4 완전 정복: 새 기능부터 3.x 마이그레이션까지</t>
+          <t>나만의 Claude Code  하네스 (SPEC·TDD·CI로 짓는 AI 개발 워크플로우)</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>프롱트</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>55000</v>
+        <v>49500</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>86900</v>
+        <v>66000</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>0.3670886075949367</v>
+        <v>0.25</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>20</v>
+        <v>575</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
@@ -7702,40 +7702,40 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 프로그래밍 언어</t>
+          <t>AI에이전트 개발, 웹 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, flyway, open-telemetry, es5, virtual thread</t>
+          <t>React, TDD, AI Agent, claude, 하네스</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
-        <v>541</v>
+        <v>438</v>
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23T02:30:05.000Z</t>
+          <t>2026-05-06T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T15:07:55.641Z</t>
+          <t>2026-05-21T16:24:41.523Z</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-spring-boo</t>
+          <t>https://www.inflearn.com/course/my-own-claude-code-h</t>
         </is>
       </c>
     </row>
@@ -7745,73 +7745,73 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>베개투자법 완성: 아침이 설레는 AI 주식 완전 자동매매  Claude 바이브코딩</t>
+          <t>실리콘 밸리 엔지니어와 함께하는 Local LLM 완전 정복 (LM Studio &amp; Ollama &amp; Ollaya)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>132000</v>
+        <v>55000</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>132000</v>
+        <v>55000</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>277</v>
+        <v>690</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, FastAPI, 퀀트, cloud-computing, claude</t>
+          <t>인공지능(AI), LLM, AI Agent</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T08:30:00.000Z</t>
+          <t>2026-04-17T18:00:00.000Z</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T05:27:04.296Z</t>
+          <t>2026-10-01T05:15:20.298Z</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/automated-trading-th</t>
+          <t>https://www.inflearn.com/course/mastering-local-llm</t>
         </is>
       </c>
     </row>
@@ -7821,31 +7821,31 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>[2026] SQLD 문제가 어려운 당신을 위한 노랭이 176 문제 풀이</t>
+          <t>독하게 시작하는 C 프로그래밍</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>알고런 데이터코드 연구소</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>39600</v>
+        <v>99000</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>39600</v>
+        <v>99000</v>
       </c>
       <c r="F97" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>245</v>
+        <v>3145</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
@@ -7854,40 +7854,40 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 데이터 분석, 데이터 엔지니어링</t>
+          <t>프로그래밍 언어, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>SQL, 빅데이터, Oracle, MSSQL, SQLD</t>
+          <t>C, 컴퓨터 구조, assembly-language, vc++</t>
         </is>
       </c>
       <c r="N97" s="7" t="n">
-        <v>746</v>
+        <v>1739</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>2025-02-17T15:00:00.000Z</t>
+          <t>2023-09-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>2026-05-26T04:21:15.498Z</t>
+          <t>2025-05-13T07:29:20.937Z</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/2025-sqld-올인원</t>
+          <t>https://www.inflearn.com/course/독하게-시작하는-c프로그래밍</t>
         </is>
       </c>
     </row>
@@ -7897,31 +7897,31 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>[2026] 유니티 엔진 입문 올인원</t>
+          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>시드니개발자의 영어PT</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>165000</v>
+        <v>220000</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>165000</v>
+        <v>220000</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>135</v>
+        <v>2198</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7930,40 +7930,40 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>게임 개발</t>
+          <t>외국어</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>게임 프로그래밍</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>game-programming, 유니티6</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="N98" s="2" t="n">
-        <v>1159</v>
+        <v>49</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11T04:00:00.000Z</t>
+          <t>2023-01-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11T02:13:13.639Z</t>
+          <t>2026-10-02T05:15:40.989Z</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/2026-unity-engine-be</t>
+          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
         </is>
       </c>
     </row>
@@ -7973,19 +7973,19 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>RAG를 활용한 LLM Application 개발 (feat. LangChain)</t>
+          <t>외워서 끝내는 네트워크 핵심이론 - 기초</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>0</v>
@@ -7994,52 +7994,52 @@
         <v>4.9</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>615</v>
+        <v>798</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>4991</v>
+        <v>8579</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 개발 · 프로그래밍 기타</t>
+          <t>네트워크, 개발 · 프로그래밍 기타, 웹 개발</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>LLM, RAG, LangChain, vector-database, openAI API</t>
+          <t>네트워크, 프로토콜</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
-        <v>217</v>
+        <v>431</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>2024-06-27T15:00:00.000Z</t>
+          <t>2022-09-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>2025-11-15T11:12:24.826Z</t>
+          <t>2025-05-13T07:25:51.956Z</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/rag-llm-application개발-langchain</t>
+          <t>https://www.inflearn.com/course/네트워크-핵심이론-기초</t>
         </is>
       </c>
     </row>
@@ -8049,73 +8049,73 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>안티그래비티 CLI 하네스 엔지니어링</t>
+          <t>자바 ORM 표준 JPA 프로그래밍 - 기본편</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>박조은</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>77000</v>
+        <v>121000</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>77000</v>
+        <v>121000</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>67</v>
+        <v>2154</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>700</v>
+        <v>25680</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 개발 도구, 데이터 분석</t>
+          <t>백엔드, 웹 개발, 데이터베이스</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Python, VSCode, gemini, 안티그래비티</t>
+          <t>Java, JPA</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>584</v>
+        <v>963</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2025-12-03T06:00:00.000Z</t>
+          <t>2019-06-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T06:12:21.429Z</t>
+          <t>2025-04-29T09:40:24.471Z</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/gemini-cli-딸깍으로-완성하는</t>
+          <t>https://www.inflearn.com/course/ORM-JPA-Basic</t>
         </is>
       </c>
     </row>
@@ -8125,73 +8125,73 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>Claude로 끝내는 실무 업무자동화: 엑셀·문서·PPT부터 Skills·Obsidian까지</t>
+          <t>실습으로 손에 잡히는 SQLD(2과목)</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>HappyAI</t>
+          <t>땃지</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>88000</v>
+        <v>49500</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>88000</v>
+        <v>49500</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>110</v>
+        <v>913</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>데이터 사이언스 자격증, 개발 · 프로그래밍 자격증, 데이터 분석</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>data-analysis, data-processing, n8n, 프롬프트엔지니어링, claude</t>
+          <t>SQL, Oracle, MSSQL, SQLD</t>
         </is>
       </c>
       <c r="N101" s="7" t="n">
-        <v>229</v>
+        <v>518</v>
       </c>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01T09:00:05.000Z</t>
+          <t>2024-07-17T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T00:06:16.136Z</t>
+          <t>2026-02-27T14:29:36.409Z</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-practical-2</t>
+          <t>https://www.inflearn.com/course/sqld-완성-2과목</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-15T13:42:03+09:00</t>
+          <t>2026-10-16T13:34:20+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -705,7 +705,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -775,13 +775,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2633</v>
+        <v>2661</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
@@ -889,12 +889,12 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T10:00:36.269Z</t>
+          <t>2026-10-16T15:43:03.831Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -933,7 +933,7 @@
         <v>10</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -1006,10 +1006,10 @@
         <v>4.9</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1649</v>
+        <v>1654</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11330</v>
+        <v>11346</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1085,7 +1085,7 @@
         <v>931</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -1137,31 +1137,31 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
+          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>49500</v>
+        <v>88000</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>9</v>
+        <v>732</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>162</v>
+        <v>5731</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
@@ -1170,40 +1170,40 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>Linux, AWS, bash, ubuntu, nginx</t>
+          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>716</v>
+        <v>2108</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T07:00:10.000Z</t>
+          <t>2024-06-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T00:06:15.984Z</t>
+          <t>2026-10-01T14:55:46.048Z</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
+          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
         </is>
       </c>
     </row>
@@ -1213,31 +1213,31 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
+          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>88000</v>
+        <v>49500</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>88000</v>
+        <v>99000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>732</v>
+        <v>10</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5726</v>
+        <v>165</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1246,40 +1246,40 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
+          <t>Linux, AWS, bash, ubuntu, nginx</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2108</v>
+        <v>712</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2024-06-13T15:00:00.000Z</t>
+          <t>2026-10-06T07:00:10.000Z</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T14:55:46.048Z</t>
+          <t>2026-10-17T00:04:40.038Z</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
+          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
         </is>
       </c>
     </row>
@@ -1310,10 +1310,10 @@
         <v>4.9</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>13498</v>
+        <v>13515</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -1441,31 +1441,31 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
+          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>99000</v>
+        <v>440000</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>99000</v>
+        <v>484000</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>5</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
@@ -1474,40 +1474,40 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>363</v>
+        <v>224</v>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2026-10-04T05:30:05.000Z</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2026-10-16T04:14:58.414Z</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
         </is>
       </c>
     </row>
@@ -1517,31 +1517,31 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>55000</v>
+        <v>198000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>55000</v>
+        <v>198000</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>662</v>
+        <v>1620</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1550,40 +1550,40 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>196</v>
+        <v>1649</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2026-10-15T09:10:56.894Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
@@ -1611,13 +1611,13 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>416</v>
+        <v>316</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>4683</v>
+        <v>4039</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
@@ -1626,38 +1626,40 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n"/>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27T10:00:00.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30T00:59:39.967Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -1667,31 +1669,31 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>알고런 데이터코드 연구소</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>77</v>
+        <v>416</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>598</v>
+        <v>4692</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1700,40 +1702,38 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>785</v>
-      </c>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2025-04-07T15:00:00.000Z</t>
+          <t>2026-01-27T10:00:00.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T07:40:07.999Z</t>
+          <t>2026-06-30T00:59:39.967Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
         </is>
       </c>
     </row>
@@ -1743,73 +1743,73 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>알고런 데이터코드 연구소</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>88000</v>
+        <v>79200</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>88000</v>
+        <v>79200</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1369</v>
+        <v>600</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>309</v>
+        <v>785</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2025-04-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:44.702Z</t>
+          <t>2026-07-02T07:40:07.999Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
         </is>
       </c>
     </row>
@@ -1819,73 +1819,73 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
+          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>440000</v>
+        <v>37950</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>484000</v>
+        <v>75900</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
+          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
+          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>224</v>
+        <v>641</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T05:30:05.000Z</t>
+          <t>2026-09-28T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T04:14:58.414Z</t>
+          <t>2026-09-29T01:52:33.960Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
+          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
         </is>
       </c>
     </row>
@@ -1895,31 +1895,31 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>Hiro Son</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>4022</v>
+        <v>24</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
@@ -1928,40 +1928,40 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2026-10-07T17:30:06.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2026-10-17T02:35:12.680Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
         </is>
       </c>
     </row>
@@ -1971,19 +1971,19 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>회로설계 멘토 삼코치</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>269500</v>
+        <v>55000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>269500</v>
+        <v>55000</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0</v>
@@ -1992,52 +1992,52 @@
         <v>5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>702</v>
+        <v>662</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 반도체</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>918</v>
+        <v>196</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2025-03-25T15:00:00.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:20:57.892Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -2047,31 +2047,31 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>37950</v>
+        <v>88000</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>75900</v>
+        <v>88000</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>218</v>
+        <v>1369</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
@@ -2085,35 +2085,35 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>641</v>
+        <v>309</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-28T10:30:06.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T01:52:33.960Z</t>
+          <t>2026-08-30T11:28:44.702Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -2123,31 +2123,31 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>89100</v>
+        <v>99000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>89100</v>
+        <v>99000</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>236</v>
+        <v>5</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1738</v>
+        <v>91</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2156,40 +2156,40 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
+          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>727</v>
+        <v>363</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2026-09-16T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2026-09-30T03:16:06.187Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/ai-automated-trading</t>
         </is>
       </c>
     </row>
@@ -2199,73 +2199,73 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>99000</v>
+        <v>89100</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>99000</v>
+        <v>89100</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>32</v>
+        <v>1740</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
+          <t>security, CPPG(개인정보관리사)</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>370</v>
+        <v>727</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T10:00:08.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T07:55:47.247Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-latest</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -2275,73 +2275,73 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>기획자·마케터를 위한 피그마 배리어블로 SNS 템플릿 제작법</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>알라딘 아카데미</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>33000</v>
+        <v>330000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>110000</v>
+        <v>330000</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>539</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>디자인 · 아트, 기획 · 경영 · 마케팅</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>그래픽 디자인, UX/UI, 마케팅</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>콘텐츠 마케팅, Figma, 콘텐츠 제작, autolayout, figma variable</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>183</v>
+        <v>1048</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T10:30:06.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:49:08.171Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-sns-te</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -2351,73 +2351,73 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
+          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>회로설계 멘토 삼코치</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>128700</v>
+        <v>269500</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>128700</v>
+        <v>269500</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>581</v>
+        <v>702</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 오피스, 업무 자동화</t>
+          <t>임베디드 · IoT, 반도체</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
+          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>832</v>
+        <v>918</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05T16:00:00.000Z</t>
+          <t>2025-03-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07T06:36:11.731Z</t>
+          <t>2026-09-11T13:20:57.892Z</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/starting-with-claude</t>
+          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
         <v>2404</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28224</v>
+        <v>28226</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
+          <t>김영한의 실전 데이터베이스 - 기본편</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
@@ -2524,14 +2524,14 @@
         <v>5</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>747</v>
+        <v>518</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>11849</v>
+        <v>5400</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>517</v>
+        <v>821</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
@@ -2559,17 +2559,17 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2025-08-31T09:28:51.006Z</t>
+          <t>2026-08-06T12:14:20.961Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
         </is>
       </c>
     </row>
@@ -2579,73 +2579,73 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>김대현</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>198000</v>
+        <v>6600</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>198000</v>
+        <v>11000</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1618</v>
+        <v>12</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>백엔드, 풀스택, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1649</v>
+        <v>89</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2026-10-13T05:00:07.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T09:10:56.894Z</t>
+          <t>2026-10-13T02:52:17.360Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
         </is>
       </c>
     </row>
@@ -2655,73 +2655,73 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>[Chapter 1. 유치원생도 이해하는 파이썬 기초] 설치 없이 시작하는 파이썬 입문</t>
+          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>YoungJea Oh</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, 프로그래밍 언어, AI 시작하기</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>algorithms, data-structure, functions, ioc, python3</t>
+          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>121</v>
+        <v>370</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T03:00:06.000Z</t>
+          <t>2026-10-02T10:00:08.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T00:00:00.000Z</t>
+          <t>2026-10-02T07:55:47.247Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/python-basics-even-k</t>
+          <t>https://www.inflearn.com/course/mastering-the-latest</t>
         </is>
       </c>
     </row>
@@ -2731,19 +2731,19 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
+          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>마일드코드</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>239800</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>239800</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
@@ -2752,10 +2752,10 @@
         <v>5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>3</v>
+        <v>747</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>52</v>
+        <v>11851</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2764,40 +2764,40 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:00:33.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:25:37.776Z</t>
+          <t>2025-08-31T09:28:51.006Z</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-for-non</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
         </is>
       </c>
     </row>
@@ -2807,35 +2807,35 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
+          <t>자바 ORM 표준 JPA 프로그래밍 - 기본편</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>인프런</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>33000</v>
+        <v>121000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>33000</v>
+        <v>121000</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>1402</v>
+        <v>2154</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>34397</v>
+        <v>25681</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -2845,35 +2845,35 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>백엔드, 웹 개발, 데이터베이스</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java, JPA</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>857</v>
+        <v>963</v>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>2019-06-01T15:00:00.000Z</t>
+          <t>2019-06-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18T05:48:10.725Z</t>
+          <t>2025-04-29T09:40:24.471Z</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
+          <t>https://www.inflearn.com/course/ORM-JPA-Basic</t>
         </is>
       </c>
     </row>
@@ -2904,10 +2904,10 @@
         <v>5</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -2959,73 +2959,73 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>제어쟁이</t>
+          <t>인프런</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>550000</v>
+        <v>33000</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>550000</v>
+        <v>33000</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>84</v>
+        <v>1403</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>606</v>
+        <v>34402</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 모빌리티</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>임베디드, stm32, hardware, motordriver, artwork</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>1017</v>
+        <v>857</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2025-06-15T15:00:00.000Z</t>
+          <t>2019-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13T09:06:49.556Z</t>
+          <t>2026-09-18T05:48:10.725Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
         </is>
       </c>
     </row>
@@ -3035,19 +3035,19 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>조회수 터지는 AI 강아지 영상만들기</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ①</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>마이업AI</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>0</v>
@@ -3059,49 +3059,49 @@
         <v>0</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>AI 크리에이티브, AI 시작하기, 창업 · 부업</t>
+          <t>백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), gemini, gpt, 영상제작, AI 영상, AI 이미지</t>
+          <t>네트워크, REST API, DBMS/RDBMS, 동시성, JWT, backend, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>10</v>
+        <v>461</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T08:00:07.000Z</t>
+          <t>2026-09-17T02:01:06.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T05:45:43.069Z</t>
+          <t>2026-09-17T15:11:35.275Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/creating-ai-dog-vide</t>
+          <t>https://www.inflearn.com/course/essential-backend-co</t>
         </is>
       </c>
     </row>
@@ -3111,73 +3111,73 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>48400</v>
+        <v>154000</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>48400</v>
+        <v>154000</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>1560</v>
+        <v>50</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>15629</v>
+        <v>2053</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>데이터베이스, 데이터 분석, 풀스택</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>1114</v>
+        <v>1270</v>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>2022-01-26T15:00:00.000Z</t>
+          <t>2026-07-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13T00:57:34.805Z</t>
+          <t>2026-07-28T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-리액트</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
         </is>
       </c>
     </row>
@@ -3187,73 +3187,73 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 기본편</t>
+          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>88000</v>
+        <v>128700</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>88000</v>
+        <v>128700</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>517</v>
+        <v>42</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5399</v>
+        <v>581</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>AI 실무 활용, 오피스, 업무 자동화</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>821</v>
+        <v>832</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2026-06-05T16:00:00.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06T12:14:20.961Z</t>
+          <t>2026-08-07T06:36:11.731Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
+          <t>https://www.inflearn.com/course/starting-with-claude</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
+          <t>스프링 핵심 원리 - 기본편</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>154000</v>
+        <v>88000</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>154000</v>
+        <v>88000</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>0</v>
@@ -3284,52 +3284,52 @@
         <v>5</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>50</v>
+        <v>4934</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>2052</v>
+        <v>50483</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 풀스택</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
+          <t>Spring, 객체지향</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>1270</v>
+        <v>725</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00.000Z</t>
+          <t>2020-09-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28T00:00:00.000Z</t>
+          <t>2025-06-04T15:00:00.555Z</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
         </is>
       </c>
     </row>
@@ -3339,19 +3339,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>198000</v>
+        <v>48400</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>198000</v>
+        <v>48400</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>0</v>
@@ -3360,52 +3360,52 @@
         <v>4.9</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51</v>
+        <v>1561</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>306</v>
+        <v>15631</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>api, trading, codex, 바이브코딩</t>
+          <t>JavaScript, React, Node.js</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>628</v>
+        <v>1114</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T01:30:06.000Z</t>
+          <t>2022-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T08:59:09.803Z</t>
+          <t>2026-06-13T00:57:34.805Z</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/create-an-automated</t>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
         </is>
       </c>
     </row>
@@ -3415,73 +3415,73 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>김형태</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>88000</v>
+        <v>138600</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>88000</v>
+        <v>198000</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>195</v>
+        <v>32</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1465</v>
+        <v>486</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>368</v>
+        <v>483</v>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2026-05-29T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2026-09-26T10:39:08.073Z</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/building-a-marketing</t>
         </is>
       </c>
     </row>
@@ -3491,73 +3491,73 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>김형태</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>138600</v>
+        <v>88000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>198000</v>
+        <v>88000</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>32</v>
+        <v>195</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>485</v>
+        <v>1467</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
+          <t>업무 생산성, wiki, obsidian, claude</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>483</v>
+        <v>368</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29T02:00:00.000Z</t>
+          <t>2026-04-25T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T10:39:08.073Z</t>
+          <t>2026-10-08T14:26:56.788Z</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-a-marketing</t>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
         </is>
       </c>
     </row>
@@ -3567,73 +3567,73 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
+          <t>조회수 터지는 AI 강아지 영상만들기</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>마이업AI</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="F41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
+          <t>AI 크리에이티브, AI 시작하기, 창업 · 부업</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
+          <t>인공지능(AI), gemini, gpt, 영상제작, AI 영상, AI 이미지</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>1240</v>
+        <v>10</v>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T15:00:07.000Z</t>
+          <t>2026-10-14T08:00:07.000Z</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T03:23:49.530Z</t>
+          <t>2026-10-14T05:45:43.069Z</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
+          <t>https://www.inflearn.com/course/creating-ai-dog-vide</t>
         </is>
       </c>
     </row>
@@ -3643,31 +3643,31 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
+          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Hiro Son</t>
+          <t>마일드코드</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>49500</v>
+        <v>239800</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>198000</v>
+        <v>239800</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3676,40 +3676,40 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
+          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>184</v>
+        <v>480</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T17:30:06.000Z</t>
+          <t>2026-09-21T09:00:33.000Z</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:17:43.638Z</t>
+          <t>2026-10-13T14:25:37.776Z</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
+          <t>https://www.inflearn.com/course/claude-code-for-non</t>
         </is>
       </c>
     </row>
@@ -3719,19 +3719,19 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>그랩</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>0</v>
@@ -3740,52 +3740,52 @@
         <v>5</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>30</v>
+        <v>3142</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>335</v>
+        <v>57319</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>896</v>
+        <v>771</v>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23T04:50:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01T16:24:39.937Z</t>
+          <t>2026-01-28T11:59:57.298Z</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
         </is>
       </c>
     </row>
@@ -3795,73 +3795,73 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>8119</v>
+        <v>144</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>123272</v>
+        <v>908</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, MVC, Spring Boot</t>
+          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>321</v>
+        <v>657</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2020-07-19T15:00:00.000Z</t>
+          <t>2026-07-20T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T11:34:33.353Z</t>
+          <t>2026-10-11T06:39:46.390Z</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+          <t>https://www.inflearn.com/course/codex-true-education</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>나도코딩</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
@@ -3889,13 +3889,13 @@
         <v>0</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>3141</v>
+        <v>1933</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>57316</v>
+        <v>40225</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
@@ -3909,35 +3909,35 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>771</v>
+        <v>358</v>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2020-02-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28T11:59:57.298Z</t>
+          <t>2025-04-29T06:34:34.311Z</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
         </is>
       </c>
     </row>
@@ -3947,35 +3947,35 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ②</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>44000</v>
+        <v>33000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>617</v>
+        <v>0</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8419</v>
+        <v>35</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3985,35 +3985,35 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>네트워크, Docker, backend, devops, 인공지능(AI), RAG</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>353</v>
+        <v>461</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2026-09-18T04:30:06.000Z</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2026-09-17T22:23:02.274Z</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/essential-backend-co-1</t>
         </is>
       </c>
     </row>
@@ -4023,19 +4023,19 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
+          <t>블렌더 리부트 베이직: AI와 새로운 UI로 다시 시작하는 블렌더</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>런타임</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>99000</v>
+        <v>148500</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>99000</v>
+        <v>148500</v>
       </c>
       <c r="F47" s="10" t="n">
         <v>0</v>
@@ -4044,10 +4044,10 @@
         <v>4.9</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>907</v>
+        <v>435</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
@@ -4056,40 +4056,40 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 디자인 · 아트</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>AI 실무 활용, CAD · 3D 모델링, AI 크리에이티브</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
+          <t>Blender, 콘텐츠 제작, 3d-modeling, 인공지능(AI), ChatGPT, MCP, claude</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>657</v>
+        <v>568</v>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20T05:00:00.000Z</t>
+          <t>2026-07-20T08:30:05.000Z</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T06:39:46.390Z</t>
+          <t>2026-10-12T15:10:44.210Z</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/codex-true-education</t>
+          <t>https://www.inflearn.com/course/blender-reboot-basic</t>
         </is>
       </c>
     </row>
@@ -4099,19 +4099,19 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>나도코딩</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>0</v>
@@ -4120,10 +4120,10 @@
         <v>4.9</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1933</v>
+        <v>52</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>40221</v>
+        <v>306</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4132,40 +4132,40 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>api, trading, codex, 바이브코딩</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>358</v>
+        <v>628</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2020-02-24T15:00:00.000Z</t>
+          <t>2026-09-09T01:30:06.000Z</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T06:34:34.311Z</t>
+          <t>2026-10-11T08:59:09.803Z</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+          <t>https://www.inflearn.com/course/create-an-automated</t>
         </is>
       </c>
     </row>
@@ -4175,19 +4175,19 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F49" s="10" t="n">
         <v>0</v>
@@ -4196,52 +4196,52 @@
         <v>5</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>188</v>
+        <v>117</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>6184</v>
+        <v>2974</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, routing</t>
+          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2026-01-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:27:31.006Z</t>
+          <t>2026-02-09T09:50:03.741Z</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
         </is>
       </c>
     </row>
@@ -4251,31 +4251,31 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
+          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>피엠인사이드</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>330000</v>
+        <v>55000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>330000</v>
+        <v>55000</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>20</v>
+        <v>482</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4284,40 +4284,40 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
+          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>프로젝트 관리, PMP</t>
+          <t>SQLD, SQL, Oracle, MSSQL</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>2379</v>
+        <v>501</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T13:00:08.000Z</t>
+          <t>2026-01-13T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T03:05:49.547Z</t>
+          <t>2026-10-12T07:12:46.551Z</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
+          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
         </is>
       </c>
     </row>
@@ -4327,73 +4327,73 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
+          <t>실전! 스프링 부트와 JPA 활용2 - API 개발과 성능 최적화</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>55000</v>
+        <v>88000</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>55000</v>
+        <v>88000</v>
       </c>
       <c r="F51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>42</v>
+        <v>1404</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>481</v>
+        <v>21972</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>SQLD, SQL, Oracle, MSSQL</t>
+          <t>Java, Spring, Spring Boot, JPA</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>501</v>
+        <v>395</v>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13T09:30:00.000Z</t>
+          <t>2019-10-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T07:12:46.551Z</t>
+          <t>2025-05-13T07:23:46.889Z</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
+          <t>https://www.inflearn.com/course/스프링부트-JPA-API개발-성능최적화</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>실전! 스프링 부트와 JPA 활용2 - API 개발과 성능 최적화</t>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
@@ -4424,14 +4424,14 @@
         <v>5</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1404</v>
+        <v>8120</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21971</v>
+        <v>123271</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4446,30 +4446,30 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, Spring Boot, JPA</t>
+          <t>Java, Spring, MVC, Spring Boot</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>395</v>
+        <v>321</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2019-10-30T15:00:00.000Z</t>
+          <t>2020-07-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:23:46.889Z</t>
+          <t>2026-01-30T11:34:33.353Z</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링부트-JPA-API개발-성능최적화</t>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
         </is>
       </c>
     </row>
@@ -4479,73 +4479,73 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>김대현</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>11</v>
+        <v>6187</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 풀스택, 프로그래밍 언어</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>네트워크, tcpip, routing</t>
         </is>
       </c>
       <c r="N53" s="7" t="n">
-        <v>89</v>
+        <v>779</v>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T05:00:07.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T02:52:17.360Z</t>
+          <t>2025-04-29T09:27:31.006Z</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
+          <t>김영한의 실전 자바 - 중급 1편</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>121000</v>
+        <v>66000</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>121000</v>
+        <v>66000</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0</v>
@@ -4576,10 +4576,10 @@
         <v>5</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>117</v>
+        <v>1265</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2973</v>
+        <v>12544</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4588,40 +4588,40 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>797</v>
+        <v>1161</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27T15:00:00.000Z</t>
+          <t>2024-03-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09T09:50:03.741Z</t>
+          <t>2025-11-28T10:04:41.236Z</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
         </is>
       </c>
     </row>
@@ -4631,31 +4631,31 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>330000</v>
+        <v>550000</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>330000</v>
+        <v>550000</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>538</v>
+        <v>606</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
@@ -4664,40 +4664,40 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>임베디드 · IoT, 모빌리티</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
         </is>
       </c>
       <c r="N55" s="7" t="n">
-        <v>1048</v>
+        <v>1017</v>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22T17:00:00.000Z</t>
+          <t>2025-06-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T22:53:04.634Z</t>
+          <t>2026-09-13T09:06:49.556Z</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
         </is>
       </c>
     </row>
@@ -4707,73 +4707,73 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>진짜! 타입스크립트 - 타입 설계부터 타입 레벨 프로그래밍까지</t>
+          <t>리눅스 입문 - 개념으로 탄탄히!!</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>코딩맥스 CodingMax</t>
+          <t>런잇(ProgCoach4U)</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>49500</v>
+        <v>77000</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>7</v>
+        <v>3495</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>시스템 · 운영체제, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, 함수형 프로그래밍, TypeScript, Node.js</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>3475</v>
+        <v>757</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T01:00:07.000Z</t>
+          <t>2021-06-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T01:50:40.027Z</t>
+          <t>2025-05-13T07:44:10.964Z</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/really-typescript-fr</t>
+          <t>https://www.inflearn.com/course/리눅스-입문</t>
         </is>
       </c>
     </row>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+          <t>시스코 CCNA 함께 공부해요</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>ccie_pe_kim</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
@@ -4804,50 +4804,52 @@
         <v>4.9</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>1115</v>
+        <v>1775</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N57" s="7" t="n"/>
+          <t>네트워크, CCNA, routing, tcpip</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="n">
+        <v>1213</v>
+      </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-27T04:00:06.000Z</t>
+          <t>2026-01-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30T07:01:04.312Z</t>
+          <t>2026-03-25T09:44:13.272Z</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
         </is>
       </c>
     </row>
@@ -4857,31 +4859,31 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>베개투자법 완성: 아침이 설레는 AI 주식 완전 자동매매  Claude 바이브코딩</t>
+          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>그랩</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>132000</v>
+        <v>198000</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>132000</v>
+        <v>198000</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>279</v>
+        <v>335</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4890,40 +4892,40 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, FastAPI, 퀀트, cloud-computing, claude</t>
+          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>309</v>
+        <v>896</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T08:30:00.000Z</t>
+          <t>2026-07-23T04:50:00.000Z</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T05:27:04.296Z</t>
+          <t>2026-08-01T16:24:39.937Z</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/automated-trading-th</t>
+          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
         </is>
       </c>
     </row>
@@ -4933,73 +4935,73 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
+          <t>[Chapter 1. 유치원생도 이해하는 파이썬 기초] 설치 없이 시작하는 파이썬 입문</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>숀김</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>787</v>
+        <v>19</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
+          <t>AI 코딩, 프로그래밍 언어, AI 시작하기</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
+          <t>algorithms, data-structure, functions, ioc, python3</t>
         </is>
       </c>
       <c r="N59" s="7" t="n">
-        <v>1266</v>
+        <v>121</v>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07T05:00:33.000Z</t>
+          <t>2026-10-14T03:00:06.000Z</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T22:16:49.715Z</t>
+          <t>2026-10-13T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-llm-servic</t>
+          <t>https://www.inflearn.com/course/python-basics-even-k</t>
         </is>
       </c>
     </row>
@@ -5009,73 +5011,73 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
+          <t>AI 코드를 읽는 게임 개발자 「Unity 6」 「Claude」 「Github Copilot」 「3D」</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>멍슨상</t>
+          <t>알렌</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>36300</v>
+        <v>44000</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>48400</v>
+        <v>88000</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>317</v>
+        <v>2</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>게임 개발, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>게임 프로그래밍, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, database</t>
+          <t>Unity, VSCode, github-copilot, 인공지능(AI), AI Agent, 유니티6, claude</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1553</v>
+        <v>500</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2025-09-24T07:00:00.000Z</t>
+          <t>2026-10-16T06:00:06.000Z</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T06:06:52.494Z</t>
+          <t>2026-10-17T02:15:05.300Z</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
+          <t>https://www.inflearn.com/course/game-developer-who-r</t>
         </is>
       </c>
     </row>
@@ -5085,31 +5087,31 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>시스코 CCNA 함께 공부해요</t>
+          <t>코덱스로 시작하는 실전 하네스 엔지니어링 : AI 에이전트에게 믿고 맡기는 개발</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>ccie_pe_kim</t>
+          <t>Masocampus</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0</v>
+        <v>48510</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>0</v>
+        <v>69300</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>1770</v>
+        <v>11</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
@@ -5118,40 +5120,40 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, routing, tcpip</t>
+          <t>인공지능(AI), codex, AI Agent, 하네스</t>
         </is>
       </c>
       <c r="N61" s="7" t="n">
-        <v>1213</v>
+        <v>205</v>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>2026-01-30T15:00:00.000Z</t>
+          <t>2026-10-14T02:00:06.000Z</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25T09:44:13.272Z</t>
+          <t>2026-10-12T02:36:43.047Z</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+          <t>https://www.inflearn.com/course/practical-harness-en</t>
         </is>
       </c>
     </row>
@@ -5161,19 +5163,19 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>리눅스 입문 - 개념으로 탄탄히!!</t>
+          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>런잇(ProgCoach4U)</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>77000</v>
+        <v>44000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>77000</v>
+        <v>44000</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>0</v>
@@ -5182,10 +5184,10 @@
         <v>4.9</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>301</v>
+        <v>617</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3495</v>
+        <v>8420</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5194,40 +5196,40 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>시스템 · 운영체제, 데브옵스 · 인프라</t>
+          <t>개발 도구</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Git, GitHub, github-actions, git-commands</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
-        <v>757</v>
+        <v>353</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2021-06-02T15:00:00.000Z</t>
+          <t>2022-01-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:44:10.964Z</t>
+          <t>2026-06-03T09:18:28.574Z</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/리눅스-입문</t>
+          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
         </is>
       </c>
     </row>
@@ -5237,31 +5239,31 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
+          <t>옵시디언 마스터 클래스: PKM·AI Second Brain·LLM WiKi 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>남박사</t>
+          <t>조영수(데이먼)</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>68200</v>
+        <v>132000</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>68200</v>
+        <v>132000</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>288</v>
+        <v>168</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>3414</v>
+        <v>1139</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
@@ -5270,40 +5272,40 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>업무 생산성, 기획 · 경영 · 마케팅, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
+          <t>생산성 도구, 기획 · PM· PO, AI 실무 활용</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
+          <t>업무 생산성, obsidian</t>
         </is>
       </c>
       <c r="N63" s="7" t="n">
-        <v>1143</v>
+        <v>455</v>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>2025-05-06T15:00:00.000Z</t>
+          <t>2025-06-25T12:30:00.000Z</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12T11:29:01.075Z</t>
+          <t>2026-05-08T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
+          <t>https://www.inflearn.com/course/옵시디언-마스터-클래스생산성을-바꾸는-1</t>
         </is>
       </c>
     </row>
@@ -5313,73 +5315,71 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 고급편</t>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>879</v>
+        <v>98</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21012</v>
+        <v>1117</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Spring, 디자인 패턴</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="n">
-        <v>1004</v>
-      </c>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2021-10-26T15:00:00.000Z</t>
+          <t>2026-06-27T04:00:06.000Z</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21T11:02:33.060Z</t>
+          <t>2026-06-30T07:01:04.312Z</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-고급편</t>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
         </is>
       </c>
     </row>
@@ -5389,31 +5389,31 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
+          <t>대세는 바이브 코딩 : 클로드 코드와 TDD로 완성하는 AI 풀스택 개발</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>Masocampus</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>69300</v>
+        <v>89100</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>99000</v>
+        <v>89100</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
@@ -5422,40 +5422,40 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
+          <t>AI 개발 활용, 웹 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
+          <t>웹앱, TDD, 인공지능(AI), claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N65" s="7" t="n">
-        <v>73</v>
+        <v>345</v>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08T11:00:10.000Z</t>
+          <t>2026-04-16T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T17:09:46.044Z</t>
+          <t>2026-04-16T07:04:40.971Z</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
+          <t>https://www.inflearn.com/course/the-trend-is-vibe-co-1</t>
         </is>
       </c>
     </row>
@@ -5465,31 +5465,31 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>베개 투자법: 자면서 돈 버는 AI 주식 자동 매매 머신</t>
+          <t>[리뉴얼] 파이썬입문과 크롤링기초 부트캠프 [파이썬, 웹, 데이터 이해 기본까지] (업데이트)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>잔재미코딩 DaveLee</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50</v>
+        <v>739</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>611</v>
+        <v>7615</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5498,40 +5498,40 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 커리어 · 자기계발, 데이터 사이언스</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 금융 ·  재테크, 데이터 분석</t>
+          <t>데이터 분석, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Python, 딥러닝, 데이터 엔지니어링, FastAPI, 빅데이터</t>
+          <t>Python, 웹 크롤링</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>349</v>
+        <v>991</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2025-06-01T15:00:00.000Z</t>
+          <t>2019-06-05T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T03:37:05.105Z</t>
+          <t>2026-08-27T04:37:56.211Z</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/베개투자법-ai주식-자동매매머신</t>
+          <t>https://www.inflearn.com/course/python-crawling-basic</t>
         </is>
       </c>
     </row>
@@ -5541,31 +5541,31 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>정보처리기사 자격증 대비 교육(실기)</t>
+          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>국립안동대학교 SW융합교육원</t>
+          <t>피엠인사이드</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="F67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>2239</v>
+        <v>20</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
@@ -5574,40 +5574,40 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증</t>
+          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>정보처리기사</t>
+          <t>프로젝트 관리, PMP</t>
         </is>
       </c>
       <c r="N67" s="7" t="n">
-        <v>1532</v>
+        <v>2374</v>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>2024-08-13T15:00:00.000Z</t>
+          <t>2026-10-01T13:00:08.000Z</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>2024-08-14T00:00:00.000Z</t>
+          <t>2026-10-16T09:00:13.940Z</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
+          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
         </is>
       </c>
     </row>
@@ -5617,31 +5617,31 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>&lt;밑바닥부터 만들면서 배우는 LLM&gt; 해설 강의</t>
+          <t>대세는 쿠버네티스 (초급~중급편)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>99000</v>
+        <v>44000</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>99000</v>
+        <v>44000</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>26</v>
+        <v>626</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>580</v>
+        <v>8500</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5650,40 +5650,40 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 자연어 처리, 인공지능 기타</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>PyTorch, gpt-2, transformer, LLM, Fine-Tuning</t>
+          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
         </is>
       </c>
       <c r="N68" s="2" t="n">
-        <v>924</v>
+        <v>425</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2025-10-03T09:30:00.000Z</t>
+          <t>2019-09-10T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10T10:01:12.921Z</t>
+          <t>2025-11-19T05:23:15.024Z</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/lt밑바닥부터-만들면서-배우는-llm-1</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
         </is>
       </c>
     </row>
@@ -5693,19 +5693,19 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>한국에서 제일 쉬운 리눅스 커널 강의</t>
+          <t>김영한의 실전 자바 - 중급 2편</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>ojtube5</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>110000</v>
+        <v>66000</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>110000</v>
+        <v>66000</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>0</v>
@@ -5714,10 +5714,10 @@
         <v>5</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>18</v>
+        <v>883</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>537</v>
+        <v>11025</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
@@ -5726,40 +5726,40 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>하드웨어, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 컴퓨터 구조, 시스템 · 운영체제</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>Linux, 운영체제, asm, C, Raspberry Pi, ARM Architecture</t>
+          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
         </is>
       </c>
       <c r="N69" s="7" t="n">
-        <v>1231</v>
+        <v>1165</v>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>2024-10-08T15:00:00.000Z</t>
+          <t>2024-05-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:41:48.813Z</t>
+          <t>2025-11-24T10:17:13.631Z</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한국에서-제일쉬운-리눅스커널-강의</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
         </is>
       </c>
     </row>
@@ -5769,73 +5769,73 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>0</v>
+        <v>440000</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0</v>
+        <v>440000</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21174</v>
+        <v>53</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>823</v>
+        <v>1240</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2023-03-02T15:00:00.000Z</t>
+          <t>2026-10-04T15:00:07.000Z</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T09:43:24.787Z</t>
+          <t>2026-10-05T03:23:49.530Z</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
         </is>
       </c>
     </row>
@@ -5845,19 +5845,19 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
+          <t>하루만에 끝내는 Herdr: 멀티플렉서, 에이전트, SSH 맥미니-모바일 원격 접속</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>82500</v>
+        <v>77000</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>82500</v>
+        <v>77000</v>
       </c>
       <c r="F71" s="10" t="n">
         <v>0</v>
@@ -5866,52 +5866,52 @@
         <v>4.9</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>790</v>
+        <v>9</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>2912</v>
+        <v>123</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>개발 도구, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, argocd, container, helm</t>
+          <t>tmux, claude, codex, terminal, AI Agent, macOS, Git</t>
         </is>
       </c>
       <c r="N71" s="7" t="n">
-        <v>669</v>
+        <v>248</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>2023-09-11T15:00:00.000Z</t>
+          <t>2026-09-13T12:00:06.000Z</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>2026-05-27T08:15:25.352Z</t>
+          <t>2026-09-27T09:02:14.111Z</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
+          <t>https://www.inflearn.com/course/herdr-in-one-day-mul</t>
         </is>
       </c>
     </row>
@@ -5921,19 +5921,19 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>AI 에이전트로 구현하는 RAG 시스템(w. LangGraph)</t>
+          <t>정보처리기사 자격증 대비 교육(실기)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>판다스 스튜디오</t>
+          <t>국립안동대학교 SW융합교육원</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>4.8</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8047</v>
+        <v>2240</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5954,40 +5954,40 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발</t>
+          <t>개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>AI Agent, LangGraph, RAG, LLM, LangChain</t>
+          <t>정보처리기사</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>405</v>
+        <v>1532</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2024-10-22T15:00:00.000Z</t>
+          <t>2024-08-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04T03:56:05.522Z</t>
+          <t>2024-08-14T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai에이전트-구현-rag시스템-랭그래프</t>
+          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
         </is>
       </c>
     </row>
@@ -5997,19 +5997,19 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>BHPT - 호스트 기반 모의해킹 기초</t>
+          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>레드라쿤</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="F73" s="10" t="n">
         <v>0</v>
@@ -6018,52 +6018,52 @@
         <v>4.9</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>134</v>
+        <v>460</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>1161</v>
+        <v>21178</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>보안, 시스템 · 운영체제, 네트워크</t>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>모의해킹, 오펜시브 시큐리티, 네트워크, kali-linux</t>
+          <t>컴퓨터 구조, 운영체제, 기술면접</t>
         </is>
       </c>
       <c r="N73" s="7" t="n">
-        <v>1031</v>
+        <v>823</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>2024-01-01T15:00:00.000Z</t>
+          <t>2023-03-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>2026-03-30T05:39:15.743Z</t>
+          <t>2025-04-29T09:43:24.787Z</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/호스트-기반-모의해킹-기초</t>
+          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
         </is>
       </c>
     </row>
@@ -6073,31 +6073,31 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>토비의 클린 스프링 - 도메인 모델 패턴과 헥사고날 아키텍처 Part 2</t>
+          <t>실전! FastAPI 입문</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>토비</t>
+          <t>신동현</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>99000</v>
+        <v>77000</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>630</v>
+        <v>1059</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6111,35 +6111,35 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>백엔드</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, Spring Boot, JPA, 리팩터링, DDD, hexagonal-architecture</t>
+          <t>Python, SQLAlchemy, ORM, FastAPI, pytest</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>779</v>
+        <v>306</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T08:12:00.000Z</t>
+          <t>2023-07-17T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T00:00:00.000Z</t>
+          <t>2025-08-06T04:34:10.347Z</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/tobys-clean-spring-d</t>
+          <t>https://www.inflearn.com/course/실전-fastapi-입문</t>
         </is>
       </c>
     </row>
@@ -6149,73 +6149,73 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
+          <t>실전! Querydsl</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>44550</v>
+        <v>88000</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>59400</v>
+        <v>88000</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>23</v>
+        <v>1003</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>229</v>
+        <v>17189</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
+          <t>백엔드, 데이터베이스, 웹 개발</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
+          <t>Java, JPA</t>
         </is>
       </c>
       <c r="N75" s="7" t="n">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31T10:30:06.000Z</t>
+          <t>2020-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12T14:30:32.966Z</t>
+          <t>2025-05-13T07:25:35.324Z</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
+          <t>https://www.inflearn.com/course/querydsl-실전</t>
         </is>
       </c>
     </row>
@@ -6225,31 +6225,31 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Decision AI로 에이전트 판단 자동화 설계: Laya와 사람 검토</t>
+          <t>AI 에이전트로 구현하는 RAG 시스템(w. LangGraph)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>판다스 스튜디오</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>22000</v>
+        <v>99000</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>22000</v>
+        <v>99000</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20</v>
+        <v>8047</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6258,40 +6258,40 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
+          <t>AI에이전트 개발</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>infrastructure, agents, 인공지능(AI), 문제해결능력, AI Agent, AX(에이전트 경험)</t>
+          <t>AI Agent, LangGraph, RAG, LLM, LangChain</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>109</v>
+        <v>405</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T05:00:08.000Z</t>
+          <t>2024-10-22T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T19:46:29.290Z</t>
+          <t>2026-03-04T03:56:05.522Z</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-decision-a</t>
+          <t>https://www.inflearn.com/course/ai에이전트-구현-rag시스템-랭그래프</t>
         </is>
       </c>
     </row>
@@ -6301,31 +6301,31 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>대세는 쿠버네티스 (초급~중급편)</t>
+          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>44000</v>
+        <v>64900</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>44000</v>
+        <v>64900</v>
       </c>
       <c r="F77" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>626</v>
+        <v>5</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>8499</v>
+        <v>788</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
@@ -6334,40 +6334,40 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
+          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
         </is>
       </c>
       <c r="N77" s="7" t="n">
-        <v>425</v>
+        <v>1266</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>2019-09-10T15:00:00.000Z</t>
+          <t>2026-09-07T05:00:33.000Z</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T05:23:15.024Z</t>
+          <t>2026-10-13T22:16:49.715Z</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+          <t>https://www.inflearn.com/course/practical-llm-servic</t>
         </is>
       </c>
     </row>
@@ -6377,73 +6377,73 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>[AI 리터러시 저자직강] 모든 직장인이 활용할 수 있는 올인원 AI 활용법(26년 6월 전체 리뉴얼)</t>
+          <t>기획자·마케터를 위한 피그마 배리어블로 SNS 템플릿 제작법</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>김용성</t>
+          <t>알라딘 아카데미</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>110000</v>
+        <v>33000</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>110000</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1138</v>
+        <v>3</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>디자인 · 아트, 기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
+          <t>그래픽 디자인, UX/UI, 마케팅</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, 영상제작, 서비스 기획, 인공지능(AI)</t>
+          <t>콘텐츠 마케팅, Figma, 콘텐츠 제작, autolayout, figma variable</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09T09:30:00.000Z</t>
+          <t>2026-10-15T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07T08:14:11.781Z</t>
+          <t>2026-10-15T08:49:08.171Z</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-리터러시-저자직강-모든-직장인이</t>
+          <t>https://www.inflearn.com/course/how-to-create-sns-te</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
+          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>77000</v>
+        <v>44000</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>77000</v>
+        <v>44000</v>
       </c>
       <c r="F79" s="10" t="n">
         <v>0</v>
@@ -6474,10 +6474,10 @@
         <v>5</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>605</v>
+        <v>4071</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>9781</v>
+        <v>37234</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
@@ -6486,40 +6486,40 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, thread, multithread, 동시성</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="N79" s="7" t="n">
-        <v>1249</v>
+        <v>341</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>2024-07-14T15:00:00.000Z</t>
+          <t>2020-12-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>2025-11-18T01:46:58.908Z</t>
+          <t>2025-05-13T07:23:13.295Z</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
+          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
         </is>
       </c>
     </row>
@@ -6529,73 +6529,73 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>회사에서 바로 쓰는 업무자동화 AI 에이전트 (w. n8n, LangGraph)</t>
+          <t>실리콘밸리 AI 개발자의 LLM 서비스를 위한 RAG</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>79200</v>
+        <v>165000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>79200</v>
+        <v>165000</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>229</v>
+        <v>14</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6762</v>
+        <v>684</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 인공지능 기타, 개발 · 프로그래밍 기타</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), LangChain, LangGraph</t>
+          <t>JavaScript, Python, 인공지능(AI), ChatGPT, RAG</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>357</v>
+        <v>531</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2025-07-11T02:00:00.000Z</t>
+          <t>2026-08-14T08:00:08.000Z</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10T22:31:31.977Z</t>
+          <t>2026-10-02T00:24:12.168Z</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/회사에서-바로쓰는-업무자동화-ai에이전트</t>
+          <t>https://www.inflearn.com/course/mastering-rag-as-tau</t>
         </is>
       </c>
     </row>
@@ -6605,31 +6605,31 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
+          <t>AI 시대의 혁신적인 게임 개발 입문 with Unity6</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>UniCoti</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>38500</v>
+        <v>36300</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>38500</v>
+        <v>36300</v>
       </c>
       <c r="F81" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>64</v>
+        <v>4253</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
@@ -6638,40 +6638,40 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>게임 개발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>게임 프로그래밍, 프로그래밍 언어, AI 코딩</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>SQL, Oracle, database, modeling, SQLD</t>
+          <t>Unity, C#, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N81" s="7" t="n">
-        <v>923</v>
+        <v>259</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02T03:00:00.000Z</t>
+          <t>2025-04-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02T00:00:00.000Z</t>
+          <t>2025-08-11T02:17:36.456Z</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
+          <t>https://www.inflearn.com/course/ai-게임개발-입문-unity6</t>
         </is>
       </c>
     </row>
@@ -6681,19 +6681,19 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>React 완벽 마스터: 기초 개념부터 린캔버스 프로젝트까지</t>
+          <t>[입문자를 위한 UE5] Part4. 언리얼 엔진 C++</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>99000</v>
+        <v>220000</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>99000</v>
+        <v>220000</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0</v>
@@ -6702,10 +6702,10 @@
         <v>4.8</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>963</v>
+        <v>631</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6714,40 +6714,40 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>게임 개발</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>게임 프로그래밍</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>React, react-query, react-router, React Context, TailwindCSS</t>
+          <t>언리얼 C++, Unreal Engine</t>
         </is>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1054</v>
+        <v>1553</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2024-09-11T15:00:00.000Z</t>
+          <t>2024-04-28T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09T02:15:49.950Z</t>
+          <t>2025-05-13T07:32:11.155Z</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/react-완벽가이드-기초-프로젝트</t>
+          <t>https://www.inflearn.com/course/언리얼5-개발의정석-4</t>
         </is>
       </c>
     </row>
@@ -6757,73 +6757,73 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>초보자를 위한 IT 인프라의 이해</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>보물상자</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>66000</v>
+        <v>99000</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>66000</v>
+        <v>99000</v>
       </c>
       <c r="F83" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>1265</v>
+        <v>83</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>12542</v>
+        <v>761</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 하드웨어</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>데브옵스 · 인프라, 백엔드, 컴퓨터 구조</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>네트워크, 컴퓨터 구조</t>
         </is>
       </c>
       <c r="N83" s="7" t="n">
-        <v>1161</v>
+        <v>770</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2022-11-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2025-05-13T07:42:47.379Z</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/it-인프라-이해</t>
         </is>
       </c>
     </row>
@@ -6833,19 +6833,19 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
+          <t>노베이스를 위한 ADsP 생존 가이드</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>nstyxn</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>118800</v>
+        <v>0</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>118800</v>
+        <v>0</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0</v>
@@ -6854,10 +6854,10 @@
         <v>5</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>959</v>
+        <v>769</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6866,40 +6866,40 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>보안, 보안 · 네트워크 자격증</t>
+          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Forensic, 디지털포렌식전문가 2급</t>
+          <t>SQL, R, ADsP</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>6530</v>
+        <v>303</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2022-11-13T15:00:00.000Z</t>
+          <t>2025-11-11T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T02:00:30.898Z</t>
+          <t>2025-11-11T09:14:53.120Z</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
+          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
         </is>
       </c>
     </row>
@@ -6909,31 +6909,31 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>알고리즘 트레이딩의 비밀, AI가 주가를 맞추는 법</t>
+          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>박해선</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>47300</v>
+        <v>69300</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>47300</v>
+        <v>99000</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>484</v>
+        <v>48</v>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
@@ -6942,40 +6942,40 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스, AI 기술, 커리어 · 자기계발</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 엔지니어링, 딥러닝 · 머신러닝, 금융 ·  재테크</t>
+          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, Python, transformer, lstm, 재테크</t>
+          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
         </is>
       </c>
       <c r="N85" s="7" t="n">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>2025-02-20T15:00:00.000Z</t>
+          <t>2026-10-08T11:00:10.000Z</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>2025-08-25T04:22:21.430Z</t>
+          <t>2026-10-11T17:09:46.044Z</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai딥러닝기반-미국주식-분석</t>
+          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
         </is>
       </c>
     </row>
@@ -6985,73 +6985,73 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ②</t>
+          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>멍슨상</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>33000</v>
+        <v>36300</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>66000</v>
+        <v>48400</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>34</v>
+        <v>317</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>백엔드, AI 코딩</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>네트워크, Docker, backend, devops, 인공지능(AI), RAG</t>
+          <t>Python, Java, C, 정보처리기사, database</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>461</v>
+        <v>1553</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T04:30:06.000Z</t>
+          <t>2025-09-24T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T22:23:02.274Z</t>
+          <t>2026-10-11T06:06:52.494Z</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-backend-co-1</t>
+          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
         </is>
       </c>
     </row>
@@ -7061,73 +7061,73 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>AI 에이전트 엔지니어링</t>
+          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>민혁</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="F87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>39</v>
+        <v>605</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>2070</v>
+        <v>9782</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>Python, 인공지능(AI), RAG, AI Agent</t>
+          <t>Java, 객체지향, thread, multithread, 동시성</t>
         </is>
       </c>
       <c r="N87" s="7" t="n">
-        <v>322</v>
+        <v>1249</v>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07T05:00:00.000Z</t>
+          <t>2024-07-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07T02:58:08.781Z</t>
+          <t>2025-11-18T01:46:58.908Z</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
         </is>
       </c>
     </row>
@@ -7137,31 +7137,31 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>서비스기획 &amp; 프로덕트 매니저(PM)의 첫걸음[입문]</t>
+          <t>자바(Java) 알고리즘 문제풀이 입문: 코딩테스트 대비</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>레브(Reve)</t>
+          <t>김태원</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>49500</v>
+        <v>77000</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>55000</v>
+        <v>77000</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>42</v>
+        <v>372</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>300</v>
+        <v>8297</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7170,40 +7170,40 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>기획 · PM· PO, 취업 · 이직</t>
+          <t>알고리즘 · 자료구조, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>서비스 기획, Figma, 프로젝트 관리, 포트폴리오</t>
+          <t>Java, 코딩 테스트</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>321</v>
+        <v>1348</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2025-02-02T15:00:00.000Z</t>
+          <t>2021-03-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2025-08-13T23:51:26.711Z</t>
+          <t>2025-05-13T07:32:20.151Z</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/프로덕트-매니저-본질</t>
+          <t>https://www.inflearn.com/course/자바-알고리즘-문제풀이-코테대비</t>
         </is>
       </c>
     </row>
@@ -7213,31 +7213,31 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>[리뉴얼] 처음하는 SQL과 데이터베이스(MySQL) 부트캠프 [입문부터 활용까지]</t>
+          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>잔재미코딩 DaveLee</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>77000</v>
+        <v>33000</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>77000</v>
+        <v>66000</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>328</v>
+        <v>4</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>4363</v>
+        <v>268</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
@@ -7246,40 +7246,40 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>Python, SQL, MySQL, DBMS/RDBMS, 데이터 엔지니어링</t>
+          <t>Python, LLM, AI Agent, claude</t>
         </is>
       </c>
       <c r="N89" s="7" t="n">
-        <v>528</v>
+        <v>305</v>
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>2019-09-08T15:00:00.000Z</t>
+          <t>2026-09-23T06:30:05.000Z</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27T04:47:42.744Z</t>
+          <t>2026-09-26T17:31:06.856Z</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sql-db-mysql-파이썬-데이터분석</t>
+          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
         </is>
       </c>
     </row>
@@ -7289,19 +7289,19 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>38군데 합격 비법, 2026 코딩테스트 필수 알고리즘</t>
+          <t>스프링 핵심 원리 - 고급편</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>딩코딩코</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>165000</v>
+        <v>121000</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>165000</v>
+        <v>121000</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>0</v>
@@ -7310,52 +7310,52 @@
         <v>5</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>452</v>
+        <v>880</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2887</v>
+        <v>21012</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>알고리즘 · 자료구조, 취업 · 이직</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Python, 코딩 테스트, 알고리즘, data-structure</t>
+          <t>Spring, 디자인 패턴</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>934</v>
+        <v>1004</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2024-11-12T15:00:00.000Z</t>
+          <t>2021-10-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T05:18:11.523Z</t>
+          <t>2025-12-21T11:02:33.060Z</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/38군데-합격비법-코테-필수-알고리즘</t>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-고급편</t>
         </is>
       </c>
     </row>
@@ -7365,31 +7365,31 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>노베이스를 위한 ADsP 생존 가이드</t>
+          <t>AI에게 마음 놓고 맡기는 바이브코딩 : 망쳐도 한 문장으로 되돌리는 Git 버전 관리</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>Masocampus</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0</v>
+        <v>34650</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>767</v>
+        <v>7</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
@@ -7398,40 +7398,40 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
+          <t>AI 실무 활용, AI 개발 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>SQL, R, ADsP</t>
+          <t>인공지능(AI), Git, 바이브코딩, VSCode, codex, GitHub</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
-        <v>303</v>
+        <v>119</v>
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T11:00:00.000Z</t>
+          <t>2026-10-14T02:00:06.000Z</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T09:14:53.120Z</t>
+          <t>2026-10-12T02:14:59.154Z</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
+          <t>https://www.inflearn.com/course/vibe-coding-you-can</t>
         </is>
       </c>
     </row>
@@ -7441,73 +7441,73 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
+          <t>RAG 마스터: 기초부터 고급기법까지 (feat. LangChain)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>최원영</t>
+          <t>판다스 스튜디오</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1576</v>
+        <v>986</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>AI에이전트 개발</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI)</t>
+          <t>RAG, LangChain, LLM, 챗봇, Python</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>32</v>
+        <v>523</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27T05:00:00.000Z</t>
+          <t>2024-09-29T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27T06:18:36.692Z</t>
+          <t>2025-05-13T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
+          <t>https://www.inflearn.com/course/랭체인으로-만드는-rag-활용-평가</t>
         </is>
       </c>
     </row>
@@ -7517,31 +7517,31 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>타입스크립트로 배우는 리액트(React.js) : 기초부터 최신 기술까지 완벽하게</t>
+          <t>웹 개발자와 정보보안 입문자가 꼭 알아야 할 웹 해킹 &amp; 시큐어 코딩</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>수코딩</t>
+          <t>크리핵티브</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>79200</v>
+        <v>55000</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>99000</v>
+        <v>55000</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>86</v>
+        <v>265</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>624</v>
+        <v>2362</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
@@ -7550,40 +7550,40 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발, 모바일 앱 개발</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>React, react-router, redux-toolkit, zustand, react.js</t>
+          <t>모의해킹, 인젝션</t>
         </is>
       </c>
       <c r="N93" s="7" t="n">
-        <v>1615</v>
+        <v>993</v>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>2025-06-08T15:00:00.000Z</t>
+          <t>2020-06-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25T06:25:45.941Z</t>
+          <t>2025-05-13T07:44:01.802Z</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/typescript-react-perfect-course</t>
+          <t>https://www.inflearn.com/course/웹해킹-보안-시큐어코딩</t>
         </is>
       </c>
     </row>
@@ -7593,19 +7593,19 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 AI 개발자의 LLM 서비스를 위한 RAG</t>
+          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>남박사</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>165000</v>
+        <v>68200</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>165000</v>
+        <v>68200</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>0</v>
@@ -7614,10 +7614,10 @@
         <v>4.8</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>14</v>
+        <v>288</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>684</v>
+        <v>3415</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7626,40 +7626,40 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
+          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, Python, 인공지능(AI), ChatGPT, RAG</t>
+          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>531</v>
+        <v>1143</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T08:00:08.000Z</t>
+          <t>2025-05-06T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T00:24:12.168Z</t>
+          <t>2026-06-12T11:29:01.075Z</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-rag-as-tau</t>
+          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
         </is>
       </c>
     </row>
@@ -7669,73 +7669,73 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>나만의 Claude Code  하네스 (SPEC·TDD·CI로 짓는 AI 개발 워크플로우)</t>
+          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>프롱트</t>
+          <t>최원영</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>575</v>
+        <v>1578</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 웹 개발, AI 개발 활용</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>React, TDD, AI Agent, claude, 하네스</t>
+          <t>인공지능(AI)</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
-        <v>438</v>
+        <v>32</v>
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06T09:00:00.000Z</t>
+          <t>2026-02-27T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21T16:24:41.523Z</t>
+          <t>2026-02-27T06:18:36.692Z</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/my-own-claude-code-h</t>
+          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
         </is>
       </c>
     </row>
@@ -7745,73 +7745,73 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>실리콘 밸리 엔지니어와 함께하는 Local LLM 완전 정복 (LM Studio &amp; Ollama &amp; Ollaya)</t>
+          <t>홍정모의 따라하며 배우는 C++</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>홍정모</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>55000</v>
+        <v>176000</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>55000</v>
+        <v>176000</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>42</v>
+        <v>395</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>690</v>
+        <v>7126</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 게임 개발</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
+          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), LLM, AI Agent</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>270</v>
+        <v>2907</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17T18:00:00.000Z</t>
+          <t>2018-09-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T05:15:20.298Z</t>
+          <t>2025-08-10T19:46:59.750Z</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-local-llm</t>
+          <t>https://www.inflearn.com/course/following-c-plus</t>
         </is>
       </c>
     </row>
@@ -7821,31 +7821,31 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>독하게 시작하는 C 프로그래밍</t>
+          <t>진짜! 타입스크립트 - 타입 설계부터 타입 레벨 프로그래밍까지</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>코딩맥스 CodingMax</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>99000</v>
+        <v>49500</v>
       </c>
       <c r="E97" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>3145</v>
+        <v>7</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
@@ -7854,40 +7854,40 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 시스템 · 운영체제</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>C, 컴퓨터 구조, assembly-language, vc++</t>
+          <t>JavaScript, 함수형 프로그래밍, TypeScript, Node.js</t>
         </is>
       </c>
       <c r="N97" s="7" t="n">
-        <v>1739</v>
+        <v>3475</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>2023-09-26T15:00:00.000Z</t>
+          <t>2026-10-13T01:00:07.000Z</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:29:20.937Z</t>
+          <t>2026-10-13T01:50:40.027Z</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/독하게-시작하는-c프로그래밍</t>
+          <t>https://www.inflearn.com/course/really-typescript-fr</t>
         </is>
       </c>
     </row>
@@ -7897,31 +7897,31 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>한시간만에 끝내는 영어 : 시드니개발자의 영어PT</t>
+          <t>[AI 리터러시 저자직강] 모든 직장인이 활용할 수 있는 올인원 AI 활용법(26년 6월 전체 리뉴얼)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>시드니개발자의 영어PT</t>
+          <t>김용성</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>220000</v>
+        <v>110000</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>220000</v>
+        <v>110000</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>63</v>
+        <v>223</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2198</v>
+        <v>1141</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7930,40 +7930,40 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>외국어</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>업무 생산성, 영상제작, 서비스 기획, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N98" s="2" t="n">
-        <v>49</v>
+        <v>274</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2023-01-12T15:00:00.000Z</t>
+          <t>2025-09-09T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T05:15:40.989Z</t>
+          <t>2026-06-07T08:14:11.781Z</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한달-문법이해-개발자-영어</t>
+          <t>https://www.inflearn.com/course/ai-리터러시-저자직강-모든-직장인이</t>
         </is>
       </c>
     </row>
@@ -7973,12 +7973,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>외워서 끝내는 네트워크 핵심이론 - 기초</t>
+          <t>[리뉴얼] 처음하는 SQL과 데이터베이스(MySQL) 부트캠프 [입문부터 활용까지]</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>잔재미코딩 DaveLee</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
@@ -7991,55 +7991,55 @@
         <v>0</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>798</v>
+        <v>328</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>8579</v>
+        <v>4364</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>네트워크, 개발 · 프로그래밍 기타, 웹 개발</t>
+          <t>데이터베이스, 데이터 분석</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>네트워크, 프로토콜</t>
+          <t>Python, SQL, MySQL, DBMS/RDBMS, 데이터 엔지니어링</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
-        <v>431</v>
+        <v>528</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>2022-09-26T15:00:00.000Z</t>
+          <t>2019-09-08T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:25:51.956Z</t>
+          <t>2026-08-27T04:47:42.744Z</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/네트워크-핵심이론-기초</t>
+          <t>https://www.inflearn.com/course/sql-db-mysql-파이썬-데이터분석</t>
         </is>
       </c>
     </row>
@@ -8049,31 +8049,31 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>자바 ORM 표준 JPA 프로그래밍 - 기본편</t>
+          <t>[Next 바이브코딩] 2단계: AI가 짠 코드, 믿기 전에 확인하는 구현·리뷰·PR 흐름</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>121000</v>
+        <v>33000</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>121000</v>
+        <v>66000</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>2154</v>
+        <v>0</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>25680</v>
+        <v>20</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -8082,40 +8082,40 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데이터베이스</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Java, JPA</t>
+          <t>Git, GitHub, codex, 인공지능(AI), AI Agent, claude</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>963</v>
+        <v>285</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2019-06-25T15:00:00.000Z</t>
+          <t>2026-09-18T04:30:06.000Z</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2025-04-29T09:40:24.471Z</t>
+          <t>2026-09-24T04:23:48.617Z</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ORM-JPA-Basic</t>
+          <t>https://www.inflearn.com/course/next-vibe-coding-ste-1</t>
         </is>
       </c>
     </row>
@@ -8125,31 +8125,31 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>실습으로 손에 잡히는 SQLD(2과목)</t>
+          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>땃지</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>49500</v>
+        <v>82500</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>49500</v>
+        <v>82500</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>86</v>
+        <v>790</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>913</v>
+        <v>2912</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
@@ -8158,40 +8158,40 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 개발 · 프로그래밍 자격증, 데이터 분석</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>SQL, Oracle, MSSQL, SQLD</t>
+          <t>Kubernetes, devops, argocd, container, helm</t>
         </is>
       </c>
       <c r="N101" s="7" t="n">
-        <v>518</v>
+        <v>669</v>
       </c>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>2024-07-17T15:00:00.000Z</t>
+          <t>2023-09-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27T14:29:36.409Z</t>
+          <t>2026-05-27T08:15:25.352Z</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqld-완성-2과목</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16T13:34:20+09:00</t>
+          <t>2026-10-17T13:29:21+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -605,31 +605,31 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Spring AI LLM 비용 모니터링 — Actuator 한 줄로 만드는 토큰 대시보드</t>
+          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>52470</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>174900</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>263</v>
+        <v>498</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -638,40 +638,40 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, AI에이전트 개발</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Spring AI, Prometheus, grafana, spring-boot-actuator, 인공지능(AI), Spring Boot, IntelliJ IDEA</t>
+          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>73</v>
+        <v>520</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T23:30:05.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T22:06:45.263Z</t>
+          <t>2026-08-26T10:28:07.736Z</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/spring-ai-llm-cost-m</t>
+          <t>https://www.inflearn.com/course/building-embeddings</t>
         </is>
       </c>
     </row>
@@ -681,31 +681,31 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 임베딩과 Mini GPT</t>
+          <t>Spring AI LLM 비용 모니터링 — Actuator 한 줄로 만드는 토큰 대시보드</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>52470</v>
+        <v>0</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>174900</v>
+        <v>0</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>487</v>
+        <v>290</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -714,40 +714,40 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
+          <t>AI 개발 활용, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>Python, 업무 생산성, 인공지능(AI), ChatGPT, AI Agent</t>
+          <t>Spring AI, Prometheus, grafana, spring-boot-actuator, 인공지능(AI), Spring Boot, IntelliJ IDEA</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>520</v>
+        <v>73</v>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-10-13T23:30:05.000Z</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26T10:28:07.736Z</t>
+          <t>2026-10-13T22:06:45.263Z</t>
         </is>
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-embeddings</t>
+          <t>https://www.inflearn.com/course/spring-ai-llm-cost-m</t>
         </is>
       </c>
     </row>
@@ -778,10 +778,10 @@
         <v>4.9</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2661</v>
+        <v>2686</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -851,13 +851,13 @@
         <v>0.1</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
@@ -889,12 +889,12 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T15:43:03.831Z</t>
+          <t>2026-10-18T03:26:00.226Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -909,73 +909,73 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
+          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>43560</v>
+        <v>198000</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>108900</v>
+        <v>198000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10</v>
+        <v>1655</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>462</v>
+        <v>11351</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
+          <t>React, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>321</v>
+        <v>1254</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2025-11-19T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29T06:47:12.230Z</t>
+          <t>2026-08-18T03:54:49.011Z</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
+          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
         </is>
       </c>
     </row>
@@ -985,73 +985,73 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
+          <t>실리콘밸리 개발자가 알려주는 LLM 평가 하네스 엔지니어링</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>198000</v>
+        <v>43560</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>198000</v>
+        <v>108900</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>4.9</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1654</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11346</v>
+        <v>465</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>AI 실무 활용, 백엔드, AI 개발 활용</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>React, 인공지능(AI), claude</t>
+          <t>JavaScript, TypeScript, 업무 생산성, 인공지능(AI), ChatGPT, LLM, AI Agent</t>
         </is>
       </c>
       <c r="N7" s="7" t="n">
-        <v>1254</v>
+        <v>321</v>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>2025-11-19T09:00:00.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18T03:54:49.011Z</t>
+          <t>2026-08-29T06:47:12.230Z</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
+          <t>https://www.inflearn.com/course/is-your-llm-safe-llm</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
         <v>931</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6032</v>
+        <v>6041</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -1137,31 +1137,31 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
+          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>88000</v>
+        <v>484000</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>88000</v>
+        <v>484000</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>732</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>5731</v>
+        <v>34</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
@@ -1170,40 +1170,40 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
+          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>2108</v>
+        <v>224</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2024-06-13T15:00:00.000Z</t>
+          <t>2026-10-04T05:30:05.000Z</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T14:55:46.048Z</t>
+          <t>2026-10-16T04:14:58.414Z</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
+          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
         </is>
       </c>
     </row>
@@ -1213,31 +1213,31 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
+          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>49500</v>
+        <v>88000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10</v>
+        <v>732</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>165</v>
+        <v>5730</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1246,40 +1246,40 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Linux, AWS, bash, ubuntu, nginx</t>
+          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>712</v>
+        <v>2108</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T07:00:10.000Z</t>
+          <t>2024-06-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T00:04:40.038Z</t>
+          <t>2026-10-01T14:55:46.048Z</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
+          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
         </is>
       </c>
     </row>
@@ -1289,31 +1289,31 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
+          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>한빛미디어</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>731</v>
+        <v>10</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>13515</v>
+        <v>165</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
@@ -1322,40 +1322,40 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
+          <t>데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), 바이브코딩</t>
+          <t>Linux, AWS, bash, ubuntu, nginx</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>259</v>
+        <v>712</v>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>2025-12-22T08:00:00.000Z</t>
+          <t>2026-10-06T07:00:10.000Z</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-01-07T07:20:44.145Z</t>
+          <t>2026-10-17T00:04:40.038Z</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
+          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
         </is>
       </c>
     </row>
@@ -1365,73 +1365,73 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
+          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>한조각</t>
+          <t>한빛미디어</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>19800</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3</v>
+        <v>732</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>246</v>
+        <v>13530</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
+          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
+          <t>인공지능(AI), 바이브코딩</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>538</v>
+        <v>259</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T20:30:05.000Z</t>
+          <t>2025-12-22T08:00:00.000Z</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T18:51:20.390Z</t>
+          <t>2026-01-07T07:20:44.145Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-service-deploym</t>
+          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
         </is>
       </c>
     </row>
@@ -1441,73 +1441,73 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
+          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>한조각</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>440000</v>
+        <v>19800</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>484000</v>
+        <v>66000</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.7</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
+          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
+          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>224</v>
+        <v>538</v>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T05:30:05.000Z</t>
+          <t>2026-09-29T20:30:05.000Z</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T04:14:58.414Z</t>
+          <t>2026-09-29T18:51:20.390Z</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
+          <t>https://www.inflearn.com/course/from-service-deploym</t>
         </is>
       </c>
     </row>
@@ -1517,31 +1517,31 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>198000</v>
+        <v>37950</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>198000</v>
+        <v>75900</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1620</v>
+        <v>222</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1550,40 +1550,40 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1649</v>
+        <v>641</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2026-09-28T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T09:10:56.894Z</t>
+          <t>2026-09-29T01:52:33.960Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
         </is>
       </c>
     </row>
@@ -1593,73 +1593,73 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>316</v>
+        <v>173</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>4039</v>
+        <v>1622</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>90</v>
+        <v>1649</v>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2026-10-15T09:10:56.894Z</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -1687,13 +1687,13 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>416</v>
+        <v>316</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4692</v>
+        <v>4051</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1702,38 +1702,40 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n"/>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>90</v>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27T10:00:00.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T00:59:39.967Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -1743,31 +1745,31 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>알고런 데이터코드 연구소</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>77</v>
+        <v>416</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>600</v>
+        <v>4698</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
@@ -1776,40 +1778,38 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>785</v>
-      </c>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n"/>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2025-04-07T15:00:00.000Z</t>
+          <t>2026-01-27T10:00:00.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02T07:40:07.999Z</t>
+          <t>2026-06-30T00:59:39.967Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
         </is>
       </c>
     </row>
@@ -1819,31 +1819,31 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
+          <t>김영한의 실전 자바 - 기본편</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>37950</v>
+        <v>44000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>75900</v>
+        <v>44000</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
+        <v>2404</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>219</v>
+        <v>28229</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1857,35 +1857,35 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>641</v>
+        <v>1012</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:30:06.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T01:52:33.960Z</t>
+          <t>2025-12-23T06:52:23.926Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
         </is>
       </c>
     </row>
@@ -1895,73 +1895,73 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>엔지니어를 위한 AI 독해력 [입문편] — 모델 카드 · API 문서 · 논문이 읽히는 48강</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Hiro Son</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>49500</v>
+        <v>55000</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>198000</v>
+        <v>55000</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>24</v>
+        <v>663</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T17:30:06.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T02:35:12.680Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -1971,31 +1971,31 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>[Next 바이브코딩] 2단계: AI가 짠 코드, 믿기 전에 확인하는 구현·리뷰·PR 흐름</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>55000</v>
+        <v>66000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>55000</v>
+        <v>66000</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>662</v>
+        <v>24</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -2004,40 +2004,40 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>Git, GitHub, codex, 인공지능(AI), AI Agent, claude</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>196</v>
+        <v>305</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2026-09-18T04:30:06.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2026-10-17T09:18:36.438Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/next-vibe-coding-ste-1</t>
         </is>
       </c>
     </row>
@@ -2047,73 +2047,73 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>알고런 데이터코드 연구소</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>88000</v>
+        <v>79200</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>88000</v>
+        <v>79200</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1369</v>
+        <v>601</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>309</v>
+        <v>785</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2025-04-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:44.702Z</t>
+          <t>2026-07-02T07:40:07.999Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
         </is>
       </c>
     </row>
@@ -2123,73 +2123,73 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
+          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>회로설계 멘토 삼코치</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>99000</v>
+        <v>269500</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>99000</v>
+        <v>269500</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>91</v>
+        <v>703</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>임베디드 · IoT, 반도체</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>363</v>
+        <v>918</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2025-03-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2026-09-11T13:20:57.892Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>89100</v>
+        <v>88000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>89100</v>
+        <v>88000</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>0</v>
@@ -2220,52 +2220,52 @@
         <v>4.9</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1740</v>
+        <v>1370</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>727</v>
+        <v>309</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2026-08-30T11:28:44.702Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -2275,73 +2275,73 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>330000</v>
+        <v>89100</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>330000</v>
+        <v>89100</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>539</v>
+        <v>1741</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>security, CPPG(개인정보관리사)</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1048</v>
+        <v>727</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T17:00:00.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T22:53:04.634Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -2351,73 +2351,73 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
+          <t>엔지니어를 위한 AI 독해력 [입문편] — AI 논문을 읽을 수 있게</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>회로설계 멘토 삼코치</t>
+          <t>Hiro Son</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>269500</v>
+        <v>49500</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>269500</v>
+        <v>198000</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>702</v>
+        <v>24</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 반도체</t>
+          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
+          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>918</v>
+        <v>228</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2025-03-25T15:00:00.000Z</t>
+          <t>2026-10-07T17:30:06.000Z</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11T13:20:57.892Z</t>
+          <t>2026-10-17T14:12:56.231Z</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
+          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
         </is>
       </c>
     </row>
@@ -2427,31 +2427,31 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 기본편</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ②</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>2404</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28226</v>
+        <v>39</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2465,35 +2465,35 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>네트워크, Docker, backend, devops, 인공지능(AI), RAG</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1012</v>
+        <v>461</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-09-18T04:30:06.000Z</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23T06:52:23.926Z</t>
+          <t>2026-09-17T22:23:02.274Z</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+          <t>https://www.inflearn.com/course/essential-backend-co-1</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 기본편</t>
+          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
@@ -2524,14 +2524,14 @@
         <v>5</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>518</v>
+        <v>747</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>5400</v>
+        <v>11860</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>821</v>
+        <v>517</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
@@ -2559,17 +2559,17 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06T12:14:20.961Z</t>
+          <t>2025-08-31T09:28:51.006Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
         </is>
       </c>
     </row>
@@ -2579,73 +2579,73 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
+          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>김대현</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>6600</v>
+        <v>99000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>11000</v>
+        <v>99000</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 풀스택, 프로그래밍 언어</t>
+          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>89</v>
+        <v>363</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:00:07.000Z</t>
+          <t>2026-09-16T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T02:52:17.360Z</t>
+          <t>2026-09-30T03:16:06.187Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
+          <t>https://www.inflearn.com/course/ai-automated-trading</t>
         </is>
       </c>
     </row>
@@ -2655,19 +2655,19 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
+          <t>자바 ORM 표준 JPA 프로그래밍 - 기본편</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>99000</v>
+        <v>121000</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>99000</v>
+        <v>121000</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
@@ -2676,10 +2676,10 @@
         <v>5</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>2</v>
+        <v>2154</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>33</v>
+        <v>25682</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
@@ -2688,40 +2688,40 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>백엔드, 웹 개발, 데이터베이스</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
+          <t>Java, JPA</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>370</v>
+        <v>963</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T10:00:08.000Z</t>
+          <t>2019-06-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T07:55:47.247Z</t>
+          <t>2025-04-29T09:40:24.471Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-latest</t>
+          <t>https://www.inflearn.com/course/ORM-JPA-Basic</t>
         </is>
       </c>
     </row>
@@ -2731,31 +2731,31 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>인프런</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>747</v>
+        <v>1403</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11851</v>
+        <v>34404</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2764,40 +2764,40 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>517</v>
+        <v>857</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2019-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2025-08-31T09:28:51.006Z</t>
+          <t>2026-09-18T05:48:10.725Z</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
         </is>
       </c>
     </row>
@@ -2807,19 +2807,19 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>자바 ORM 표준 JPA 프로그래밍 - 기본편</t>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>121000</v>
+        <v>99000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>121000</v>
+        <v>99000</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0</v>
@@ -2828,52 +2828,52 @@
         <v>5</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>2154</v>
+        <v>156</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>25681</v>
+        <v>1113</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데이터베이스</t>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>Java, JPA</t>
+          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>963</v>
+        <v>516</v>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>2019-06-25T15:00:00.000Z</t>
+          <t>2026-05-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:40:24.471Z</t>
+          <t>2026-09-21T01:35:54.874Z</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ORM-JPA-Basic</t>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
         </is>
       </c>
     </row>
@@ -2883,73 +2883,73 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1112</v>
+        <v>1471</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
+          <t>업무 생산성, wiki, obsidian, claude</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>516</v>
+        <v>368</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12T00:00:00.000Z</t>
+          <t>2026-04-25T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T01:35:54.874Z</t>
+          <t>2026-10-08T14:26:56.788Z</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
         </is>
       </c>
     </row>
@@ -2959,35 +2959,35 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>인프런</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>33000</v>
+        <v>48400</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>33000</v>
+        <v>48400</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>1403</v>
+        <v>1561</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>34402</v>
+        <v>15632</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
@@ -2997,35 +2997,35 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript, React, Node.js</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>857</v>
+        <v>1114</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2019-06-01T15:00:00.000Z</t>
+          <t>2022-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18T05:48:10.725Z</t>
+          <t>2026-06-13T00:57:34.805Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
         </is>
       </c>
     </row>
@@ -3035,73 +3035,73 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ①</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>66000</v>
+        <v>330000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>66000</v>
+        <v>330000</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>194</v>
+        <v>540</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>백엔드, AI 코딩</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>네트워크, REST API, DBMS/RDBMS, 동시성, JWT, backend, 인공지능(AI)</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>461</v>
+        <v>1048</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T02:01:06.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T15:11:35.275Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-backend-co</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -3111,73 +3111,73 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
+          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>154000</v>
+        <v>99000</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>154000</v>
+        <v>99000</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>2053</v>
+        <v>909</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 풀스택</t>
+          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
+          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>1270</v>
+        <v>657</v>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00.000Z</t>
+          <t>2026-07-20T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28T00:00:00.000Z</t>
+          <t>2026-10-11T06:39:46.390Z</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
+          <t>https://www.inflearn.com/course/codex-true-education</t>
         </is>
       </c>
     </row>
@@ -3187,73 +3187,73 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
+          <t>김영한의 실전 데이터베이스 - 기본편</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>128700</v>
+        <v>88000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>128700</v>
+        <v>88000</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>42</v>
+        <v>518</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>581</v>
+        <v>5400</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 오피스, 업무 자동화</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05T16:00:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T06:36:11.731Z</t>
+          <t>2026-08-06T12:14:20.961Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/starting-with-claude</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 기본편</t>
+          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>88000</v>
+        <v>121000</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>0</v>
@@ -3284,10 +3284,10 @@
         <v>5</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>4934</v>
+        <v>117</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>50483</v>
+        <v>2974</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
@@ -3296,40 +3296,40 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>Spring, 객체지향</t>
+          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>725</v>
+        <v>797</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2020-09-20T15:00:00.000Z</t>
+          <t>2026-01-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2025-06-04T15:00:00.555Z</t>
+          <t>2026-02-09T09:50:03.741Z</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
         </is>
       </c>
     </row>
@@ -3339,31 +3339,31 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+          <t>[Next 바이브코딩] 3단계: 지침·Skills·Hooks·MCP로 AI가 일하기 좋은 개발 시스템 만들기</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>48400</v>
+        <v>33000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>48400</v>
+        <v>66000</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15631</v>
+        <v>23</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3372,40 +3372,40 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>codex, claude, AI Agent, 인공지능(AI), MCP, Git</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1114</v>
+        <v>304</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2022-01-26T15:00:00.000Z</t>
+          <t>2026-09-20T13:00:06.000Z</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13T00:57:34.805Z</t>
+          <t>2026-10-17T09:27:01.129Z</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-리액트</t>
+          <t>https://www.inflearn.com/course/next-vibe-coding-sta</t>
         </is>
       </c>
     </row>
@@ -3415,73 +3415,73 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
+          <t>AI 코드를 읽는 게임 개발자 「Unity 6」 「Claude」 「Github Copilot」 「3D」</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>김형태</t>
+          <t>알렌</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>138600</v>
+        <v>44000</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>198000</v>
+        <v>88000</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>486</v>
+        <v>3</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
+          <t>게임 개발, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
+          <t>게임 프로그래밍, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
+          <t>Unity, VSCode, github-copilot, 인공지능(AI), AI Agent, 유니티6, claude</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>2026-05-29T02:00:00.000Z</t>
+          <t>2026-10-16T06:00:06.000Z</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26T10:39:08.073Z</t>
+          <t>2026-10-17T17:44:29.872Z</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-a-marketing</t>
+          <t>https://www.inflearn.com/course/game-developer-who-r</t>
         </is>
       </c>
     </row>
@@ -3491,31 +3491,31 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>195</v>
+        <v>42</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1467</v>
+        <v>484</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3524,40 +3524,40 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>SQLD, SQL, Oracle, MSSQL</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>368</v>
+        <v>501</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2026-01-13T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2026-10-12T07:12:46.551Z</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
         </is>
       </c>
     </row>
@@ -3567,19 +3567,19 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>조회수 터지는 AI 강아지 영상만들기</t>
+          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>마이업AI</t>
+          <t>YoungJea Oh</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F41" s="10" t="n">
         <v>0</v>
@@ -3591,49 +3591,49 @@
         <v>2</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 커리어 · 자기계발</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>AI 크리에이티브, AI 시작하기, 창업 · 부업</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), gemini, gpt, 영상제작, AI 영상, AI 이미지</t>
+          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>10</v>
+        <v>370</v>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T08:00:07.000Z</t>
+          <t>2026-10-02T10:00:08.000Z</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T05:45:43.069Z</t>
+          <t>2026-10-02T07:55:47.247Z</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/creating-ai-dog-vide</t>
+          <t>https://www.inflearn.com/course/mastering-the-latest</t>
         </is>
       </c>
     </row>
@@ -3643,19 +3643,19 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>마일드코드</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>239800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>239800</v>
+        <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>0</v>
@@ -3664,10 +3664,10 @@
         <v>5</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>3</v>
+        <v>3143</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>52</v>
+        <v>57323</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3676,40 +3676,40 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>480</v>
+        <v>771</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:00:33.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:25:37.776Z</t>
+          <t>2026-01-28T11:59:57.298Z</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-for-non</t>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
         </is>
       </c>
     </row>
@@ -3719,31 +3719,31 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0</v>
+        <v>128700</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0</v>
+        <v>128700</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>3142</v>
+        <v>42</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>57319</v>
+        <v>582</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
@@ -3752,40 +3752,40 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI 실무 활용, 오피스, 업무 자동화</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>771</v>
+        <v>832</v>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-06-05T16:00:00.000Z</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28T11:59:57.298Z</t>
+          <t>2026-08-07T06:36:11.731Z</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+          <t>https://www.inflearn.com/course/starting-with-claude</t>
         </is>
       </c>
     </row>
@@ -3795,73 +3795,73 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
+          <t>김영한의 실전 자바 - 중급 1편</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>144</v>
+        <v>1265</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>908</v>
+        <v>12545</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>657</v>
+        <v>1161</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T05:00:00.000Z</t>
+          <t>2024-03-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T06:39:46.390Z</t>
+          <t>2025-11-28T10:04:41.236Z</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/codex-true-education</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
         </is>
       </c>
     </row>
@@ -3871,73 +3871,73 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>나도코딩</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="F45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>1933</v>
+        <v>51</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>40225</v>
+        <v>2054</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>데이터베이스, 데이터 분석, 풀스택</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>358</v>
+        <v>1270</v>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>2020-02-24T15:00:00.000Z</t>
+          <t>2026-07-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T06:34:34.311Z</t>
+          <t>2026-07-28T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
         </is>
       </c>
     </row>
@@ -3947,73 +3947,73 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ②</t>
+          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>마일드코드</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>33000</v>
+        <v>239800</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>66000</v>
+        <v>239800</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>백엔드, AI 코딩</t>
+          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>네트워크, Docker, backend, devops, 인공지능(AI), RAG</t>
+          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T04:30:06.000Z</t>
+          <t>2026-09-21T09:00:33.000Z</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T22:23:02.274Z</t>
+          <t>2026-10-13T14:25:37.776Z</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-backend-co-1</t>
+          <t>https://www.inflearn.com/course/claude-code-for-non</t>
         </is>
       </c>
     </row>
@@ -4023,19 +4023,19 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>블렌더 리부트 베이직: AI와 새로운 UI로 다시 시작하는 블렌더</t>
+          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>런타임</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>148500</v>
+        <v>44000</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>148500</v>
+        <v>44000</v>
       </c>
       <c r="F47" s="10" t="n">
         <v>0</v>
@@ -4044,10 +4044,10 @@
         <v>4.9</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>23</v>
+        <v>617</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>435</v>
+        <v>8421</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
@@ -4056,40 +4056,40 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 디자인 · 아트</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, CAD · 3D 모델링, AI 크리에이티브</t>
+          <t>개발 도구</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>Blender, 콘텐츠 제작, 3d-modeling, 인공지능(AI), ChatGPT, MCP, claude</t>
+          <t>Git, GitHub, github-actions, git-commands</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>568</v>
+        <v>353</v>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20T08:30:05.000Z</t>
+          <t>2022-01-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T15:10:44.210Z</t>
+          <t>2026-06-03T09:18:28.574Z</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/blender-reboot-basic</t>
+          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
         </is>
       </c>
     </row>
@@ -4099,19 +4099,19 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
+          <t>블렌더 리부트 베이직: AI와 새로운 UI로 다시 시작하는 블렌더</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>런타임</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>198000</v>
+        <v>148500</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>198000</v>
+        <v>148500</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>0</v>
@@ -4120,10 +4120,10 @@
         <v>4.9</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>306</v>
+        <v>435</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4132,40 +4132,40 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 디자인 · 아트</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
+          <t>AI 실무 활용, CAD · 3D 모델링, AI 크리에이티브</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>api, trading, codex, 바이브코딩</t>
+          <t>Blender, 콘텐츠 제작, 3d-modeling, 인공지능(AI), ChatGPT, MCP, claude</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>628</v>
+        <v>568</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T01:30:06.000Z</t>
+          <t>2026-07-20T08:30:05.000Z</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T08:59:09.803Z</t>
+          <t>2026-10-12T15:10:44.210Z</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/create-an-automated</t>
+          <t>https://www.inflearn.com/course/blender-reboot-basic</t>
         </is>
       </c>
     </row>
@@ -4175,73 +4175,73 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>나도코딩</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>117</v>
+        <v>1933</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>2974</v>
+        <v>40228</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>797</v>
+        <v>358</v>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27T15:00:00.000Z</t>
+          <t>2020-02-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09T09:50:03.741Z</t>
+          <t>2025-04-29T06:34:34.311Z</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
         </is>
       </c>
     </row>
@@ -4251,73 +4251,73 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
+          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>김형태</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>55000</v>
+        <v>138600</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>55000</v>
+        <v>198000</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>SQLD, SQL, Oracle, MSSQL</t>
+          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13T09:30:00.000Z</t>
+          <t>2026-05-29T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T07:12:46.551Z</t>
+          <t>2026-09-26T10:39:08.073Z</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
+          <t>https://www.inflearn.com/course/building-a-marketing</t>
         </is>
       </c>
     </row>
@@ -4327,73 +4327,73 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>실전! 스프링 부트와 JPA 활용2 - API 개발과 성능 최적화</t>
+          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>88000</v>
+        <v>44550</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>88000</v>
+        <v>59400</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>1404</v>
+        <v>24</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>21972</v>
+        <v>234</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>Java, Spring, Spring Boot, JPA</t>
+          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>395</v>
+        <v>311</v>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>2019-10-30T15:00:00.000Z</t>
+          <t>2026-07-31T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:23:46.889Z</t>
+          <t>2026-08-12T14:30:32.966Z</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링부트-JPA-API개발-성능최적화</t>
+          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
         </is>
       </c>
     </row>
@@ -4403,31 +4403,31 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ①</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>123271</v>
+        <v>194</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4441,35 +4441,35 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, MVC, Spring Boot</t>
+          <t>네트워크, REST API, DBMS/RDBMS, 동시성, JWT, backend, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>321</v>
+        <v>508</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2020-07-19T15:00:00.000Z</t>
+          <t>2026-09-17T02:01:06.000Z</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T11:34:33.353Z</t>
+          <t>2026-10-18T02:24:47.861Z</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+          <t>https://www.inflearn.com/course/essential-backend-co</t>
         </is>
       </c>
     </row>
@@ -4479,19 +4479,19 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="F53" s="10" t="n">
         <v>0</v>
@@ -4500,10 +4500,10 @@
         <v>5</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>6187</v>
+        <v>67</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
@@ -4512,40 +4512,40 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, routing</t>
+          <t>SQL, Oracle, database, modeling, SQLD</t>
         </is>
       </c>
       <c r="N53" s="7" t="n">
-        <v>779</v>
+        <v>923</v>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2026-09-02T03:00:00.000Z</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:27:31.006Z</t>
+          <t>2026-09-02T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
         </is>
       </c>
     </row>
@@ -4555,35 +4555,35 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>김대현</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>66000</v>
+        <v>6600</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>66000</v>
+        <v>11000</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1265</v>
+        <v>0</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12544</v>
+        <v>12</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4593,35 +4593,35 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>백엔드, 풀스택, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1161</v>
+        <v>89</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2026-10-13T05:00:07.000Z</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2026-10-13T02:52:17.360Z</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
         </is>
       </c>
     </row>
@@ -4631,31 +4631,31 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
+          <t>하루만에 끝내는 Herdr: 멀티플렉서, 에이전트, SSH 맥미니-모바일 원격 접속</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>제어쟁이</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>550000</v>
+        <v>77000</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>550000</v>
+        <v>77000</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>606</v>
+        <v>124</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
@@ -4664,40 +4664,40 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 모빌리티</t>
+          <t>개발 도구, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>임베디드, stm32, hardware, motordriver, artwork</t>
+          <t>tmux, claude, codex, terminal, AI Agent, macOS, Git</t>
         </is>
       </c>
       <c r="N55" s="7" t="n">
-        <v>1017</v>
+        <v>248</v>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>2025-06-15T15:00:00.000Z</t>
+          <t>2026-09-13T12:00:06.000Z</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13T09:06:49.556Z</t>
+          <t>2026-09-27T09:02:14.111Z</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
+          <t>https://www.inflearn.com/course/herdr-in-one-day-mul</t>
         </is>
       </c>
     </row>
@@ -4707,19 +4707,19 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>리눅스 입문 - 개념으로 탄탄히!!</t>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>런잇(ProgCoach4U)</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>0</v>
@@ -4728,10 +4728,10 @@
         <v>4.9</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>301</v>
+        <v>99</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3495</v>
+        <v>1124</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4740,40 +4740,38 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>시스템 · 운영체제, 데브옵스 · 인프라</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Linux</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="n">
-        <v>757</v>
-      </c>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2021-06-02T15:00:00.000Z</t>
+          <t>2026-06-27T04:00:06.000Z</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:44:10.964Z</t>
+          <t>2026-06-30T07:01:04.312Z</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/리눅스-입문</t>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
         </is>
       </c>
     </row>
@@ -4783,31 +4781,31 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>시스코 CCNA 함께 공부해요</t>
+          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>ccie_pe_kim</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0</v>
+        <v>64900</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>0</v>
+        <v>64900</v>
       </c>
       <c r="F57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>1775</v>
+        <v>788</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
@@ -4816,40 +4814,40 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, routing, tcpip</t>
+          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
         </is>
       </c>
       <c r="N57" s="7" t="n">
-        <v>1213</v>
+        <v>1266</v>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>2026-01-30T15:00:00.000Z</t>
+          <t>2026-09-07T05:00:33.000Z</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25T09:44:13.272Z</t>
+          <t>2026-10-13T22:16:49.715Z</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+          <t>https://www.inflearn.com/course/practical-llm-servic</t>
         </is>
       </c>
     </row>
@@ -4859,73 +4857,73 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
+          <t>Claude Code로 배우는 AI 개발 워크플로우 완벽 가이드 (실전 프로젝트 포함)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>그랩</t>
+          <t>kimw24072</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>198000</v>
+        <v>33000</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>198000</v>
+        <v>33000</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>335</v>
+        <v>91</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
+          <t>AI 개발 활용, 프로그래밍 언어, 웹 개발</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>claude, JavaScript, TypeScript, Next.js, Firebase</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>896</v>
+        <v>412</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T04:50:00.000Z</t>
+          <t>2026-04-28T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T16:24:39.937Z</t>
+          <t>2026-05-03T22:51:17.474Z</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
+          <t>https://www.inflearn.com/course/pytorch-deep-learnin</t>
         </is>
       </c>
     </row>
@@ -4935,19 +4933,19 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>[Chapter 1. 유치원생도 이해하는 파이썬 기초] 설치 없이 시작하는 파이썬 입문</t>
+          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0</v>
+        <v>440000</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>0</v>
+        <v>440000</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>0</v>
@@ -4959,49 +4957,49 @@
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, 프로그래밍 언어, AI 시작하기</t>
+          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>algorithms, data-structure, functions, ioc, python3</t>
+          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
         </is>
       </c>
       <c r="N59" s="7" t="n">
-        <v>121</v>
+        <v>1240</v>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T03:00:06.000Z</t>
+          <t>2026-10-04T15:00:07.000Z</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T00:00:00.000Z</t>
+          <t>2026-10-05T03:23:49.530Z</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/python-basics-even-k</t>
+          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
         </is>
       </c>
     </row>
@@ -5011,31 +5009,31 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>AI 코드를 읽는 게임 개발자 「Unity 6」 「Claude」 「Github Copilot」 「3D」</t>
+          <t>김영한의 실전 자바 - 중급 2편</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>알렌</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>88000</v>
+        <v>66000</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0</v>
+        <v>884</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
+        <v>11027</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5044,40 +5042,40 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>게임 개발, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>게임 프로그래밍, AI 코딩, AI 개발 활용</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Unity, VSCode, github-copilot, 인공지능(AI), AI Agent, 유니티6, claude</t>
+          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>500</v>
+        <v>1165</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T06:00:06.000Z</t>
+          <t>2024-05-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T02:15:05.300Z</t>
+          <t>2025-11-24T10:17:13.631Z</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/game-developer-who-r</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
         </is>
       </c>
     </row>
@@ -5087,73 +5085,73 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>코덱스로 시작하는 실전 하네스 엔지니어링 : AI 에이전트에게 믿고 맡기는 개발</t>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Masocampus</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>48510</v>
+        <v>550000</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>69300</v>
+        <v>550000</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>11</v>
+        <v>606</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 개발 활용</t>
+          <t>임베디드 · IoT, 모빌리티</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), codex, AI Agent, 하네스</t>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
         </is>
       </c>
       <c r="N61" s="7" t="n">
-        <v>205</v>
+        <v>1017</v>
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T02:00:06.000Z</t>
+          <t>2025-06-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T02:36:43.047Z</t>
+          <t>2026-09-13T09:06:49.556Z</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-harness-en</t>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
         </is>
       </c>
     </row>
@@ -5163,35 +5161,35 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>617</v>
+        <v>8120</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8420</v>
+        <v>123273</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5201,35 +5199,35 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>Java, Spring, MVC, Spring Boot</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2020-07-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2026-01-30T11:34:33.353Z</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
         </is>
       </c>
     </row>
@@ -5239,19 +5237,19 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>옵시디언 마스터 클래스: PKM·AI Second Brain·LLM WiKi 기초부터 실전까지</t>
+          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>조영수(데이먼)</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>132000</v>
+        <v>198000</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>132000</v>
+        <v>198000</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>0</v>
@@ -5260,10 +5258,10 @@
         <v>4.9</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>1139</v>
+        <v>306</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
@@ -5272,40 +5270,40 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, 기획 · 경영 · 마케팅, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>생산성 도구, 기획 · PM· PO, AI 실무 활용</t>
+          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, obsidian</t>
+          <t>api, trading, codex, 바이브코딩</t>
         </is>
       </c>
       <c r="N63" s="7" t="n">
-        <v>455</v>
+        <v>628</v>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>2025-06-25T12:30:00.000Z</t>
+          <t>2026-09-09T01:30:06.000Z</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08T00:00:00.000Z</t>
+          <t>2026-10-11T08:59:09.803Z</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/옵시디언-마스터-클래스생산성을-바꾸는-1</t>
+          <t>https://www.inflearn.com/course/create-an-automated</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5313,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+          <t>시스코 CCNA 함께 공부해요</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>ccie_pe_kim</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
@@ -5336,50 +5334,52 @@
         <v>4.9</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1117</v>
+        <v>1777</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="n"/>
+          <t>네트워크, CCNA, routing, tcpip</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>1213</v>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T04:00:06.000Z</t>
+          <t>2026-01-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T07:01:04.312Z</t>
+          <t>2026-03-25T09:44:13.272Z</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
         </is>
       </c>
     </row>
@@ -5389,73 +5389,73 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>대세는 바이브 코딩 : 클로드 코드와 TDD로 완성하는 AI 풀스택 개발</t>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Masocampus</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>89100</v>
+        <v>0</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>89100</v>
+        <v>0</v>
       </c>
       <c r="F65" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>96</v>
+        <v>6188</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 코딩</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>웹앱, TDD, 인공지능(AI), claude, 바이브코딩</t>
+          <t>네트워크, tcpip, routing</t>
         </is>
       </c>
       <c r="N65" s="7" t="n">
-        <v>345</v>
+        <v>779</v>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>2026-04-16T09:30:00.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>2026-04-16T07:04:40.971Z</t>
+          <t>2025-04-29T09:27:31.006Z</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-trend-is-vibe-co-1</t>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
         </is>
       </c>
     </row>
@@ -5465,19 +5465,19 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>[리뉴얼] 파이썬입문과 크롤링기초 부트캠프 [파이썬, 웹, 데이터 이해 기본까지] (업데이트)</t>
+          <t>채널톡 면접관이 직접 알려주는 CS 면접 대비 - 데이터베이스 편</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>잔재미코딩 DaveLee</t>
+          <t>JSCODE 제이온</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>77000</v>
+        <v>66000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>77000</v>
+        <v>66000</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0</v>
@@ -5486,52 +5486,52 @@
         <v>4.9</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>739</v>
+        <v>29</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7615</v>
+        <v>304</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석, 프로그래밍 언어</t>
+          <t>취업 · 이직, 개발 · 프로그래밍 기타, 데이터베이스</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Python, 웹 크롤링</t>
+          <t>DBMS/RDBMS, NoSQL, computer-science</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>991</v>
+        <v>174</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2019-06-05T15:00:00.000Z</t>
+          <t>2026-04-27T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T04:37:56.211Z</t>
+          <t>2026-08-30T11:26:35.540Z</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/python-crawling-basic</t>
+          <t>https://www.inflearn.com/course/cs-interview-prepara-1</t>
         </is>
       </c>
     </row>
@@ -5541,19 +5541,19 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>PMP(프로젝트 관리 전문가) 자격 취득과정(PMBOK 8판 기준)</t>
+          <t>[Chapter 1. 유치원생도 이해하는 파이썬 기초] 설치 없이 시작하는 파이썬 입문</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>피엠인사이드</t>
+          <t>숀김</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="F67" s="10" t="n">
         <v>0</v>
@@ -5565,49 +5565,49 @@
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
+          <t>AI 코딩, 프로그래밍 언어, AI 시작하기</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 관리, PMP</t>
+          <t>algorithms, data-structure, functions, ioc, python3</t>
         </is>
       </c>
       <c r="N67" s="7" t="n">
-        <v>2374</v>
+        <v>121</v>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01T13:00:08.000Z</t>
+          <t>2026-10-14T03:00:06.000Z</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T09:00:13.940Z</t>
+          <t>2026-10-13T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
+          <t>https://www.inflearn.com/course/python-basics-even-k</t>
         </is>
       </c>
     </row>
@@ -5617,73 +5617,73 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>대세는 쿠버네티스 (초급~중급편)</t>
+          <t>실전! 스프링 부트와 JPA 활용2 - API 개발과 성능 최적화</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>44000</v>
+        <v>88000</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>44000</v>
+        <v>88000</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>626</v>
+        <v>1404</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>8500</v>
+        <v>21972</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
+          <t>Java, Spring, Spring Boot, JPA</t>
         </is>
       </c>
       <c r="N68" s="2" t="n">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2019-09-10T15:00:00.000Z</t>
+          <t>2019-10-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2025-11-19T05:23:15.024Z</t>
+          <t>2025-05-13T07:23:46.889Z</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+          <t>https://www.inflearn.com/course/스프링부트-JPA-API개발-성능최적화</t>
         </is>
       </c>
     </row>
@@ -5693,73 +5693,73 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 2편</t>
+          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>883</v>
+        <v>460</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>11025</v>
+        <v>21179</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+          <t>컴퓨터 구조, 운영체제, 기술면접</t>
         </is>
       </c>
       <c r="N69" s="7" t="n">
-        <v>1165</v>
+        <v>823</v>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>2024-05-07T15:00:00.000Z</t>
+          <t>2023-03-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>2025-11-24T10:17:13.631Z</t>
+          <t>2025-04-29T09:43:24.787Z</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
         </is>
       </c>
     </row>
@@ -5769,73 +5769,73 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
+          <t>스프링 핵심 원리 - 기본편</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>440000</v>
+        <v>88000</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>440000</v>
+        <v>88000</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0</v>
+        <v>4934</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>53</v>
+        <v>50483</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
+          <t>Spring, 객체지향</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1240</v>
+        <v>725</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T15:00:07.000Z</t>
+          <t>2020-09-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T03:23:49.530Z</t>
+          <t>2025-06-04T15:00:00.555Z</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
+          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>하루만에 끝내는 Herdr: 멀티플렉서, 에이전트, SSH 맥미니-모바일 원격 접속</t>
+          <t>리눅스 입문 - 개념으로 탄탄히!!</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>런잇(ProgCoach4U)</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
@@ -5866,52 +5866,52 @@
         <v>4.9</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>9</v>
+        <v>301</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>123</v>
+        <v>3495</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>개발 도구, AI에이전트 개발, AI 개발 활용</t>
+          <t>시스템 · 운영체제, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>tmux, claude, codex, terminal, AI Agent, macOS, Git</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="N71" s="7" t="n">
-        <v>248</v>
+        <v>757</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13T12:00:06.000Z</t>
+          <t>2021-06-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27T09:02:14.111Z</t>
+          <t>2025-05-13T07:44:10.964Z</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/herdr-in-one-day-mul</t>
+          <t>https://www.inflearn.com/course/리눅스-입문</t>
         </is>
       </c>
     </row>
@@ -5921,31 +5921,31 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>정보처리기사 자격증 대비 교육(실기)</t>
+          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>국립안동대학교 SW융합교육원</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>56</v>
+        <v>4071</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2240</v>
+        <v>37235</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5954,40 +5954,40 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증</t>
+          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>정보처리기사</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1532</v>
+        <v>341</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2024-08-13T15:00:00.000Z</t>
+          <t>2020-12-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2024-08-14T00:00:00.000Z</t>
+          <t>2025-05-13T07:23:13.295Z</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
+          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
         </is>
       </c>
     </row>
@@ -5997,31 +5997,31 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+          <t>초당 1,000,000++ RPS를 처리하는 네이버 개발자의 Valkey</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0</v>
+        <v>56760</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>0</v>
+        <v>141900</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>460</v>
+        <v>6</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>21178</v>
+        <v>146</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
@@ -6030,40 +6030,40 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+          <t>백엔드, 알고리즘 · 자료구조, 데이터베이스</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+          <t>JavaScript, 빅데이터, TypeScript, DBMS/RDBMS, Redis, MSA, 데이터 엔지니어링</t>
         </is>
       </c>
       <c r="N73" s="7" t="n">
-        <v>823</v>
+        <v>422</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>2023-03-02T15:00:00.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:43:24.787Z</t>
+          <t>2026-08-29T21:47:01.350Z</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+          <t>https://www.inflearn.com/course/valkey-vs-redis-a-na</t>
         </is>
       </c>
     </row>
@@ -6073,31 +6073,31 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>실전! FastAPI 입문</t>
+          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>신동현</t>
+          <t>그랩</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>77000</v>
+        <v>198000</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>77000</v>
+        <v>198000</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1059</v>
+        <v>335</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6106,40 +6106,40 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Python, SQLAlchemy, ORM, FastAPI, pytest</t>
+          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>306</v>
+        <v>896</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2023-07-17T15:00:00.000Z</t>
+          <t>2026-07-23T04:50:00.000Z</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2025-08-06T04:34:10.347Z</t>
+          <t>2026-08-01T16:24:39.937Z</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/실전-fastapi-입문</t>
+          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
         </is>
       </c>
     </row>
@@ -6149,19 +6149,19 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>실전! Querydsl</t>
+          <t>채널톡 면접관이 직접 알려주는 CS 면접 대비 - 네트워크 &amp; 웹 편</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>JSCODE 제이온</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>88000</v>
+        <v>77000</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>88000</v>
+        <v>77000</v>
       </c>
       <c r="F75" s="10" t="n">
         <v>0</v>
@@ -6170,52 +6170,52 @@
         <v>5</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>1003</v>
+        <v>21</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>17189</v>
+        <v>265</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 데이터베이스, 웹 개발</t>
+          <t>취업 · 이직, 웹 개발, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>Java, JPA</t>
+          <t>네트워크, websocket, https, dns, computer-science</t>
         </is>
       </c>
       <c r="N75" s="7" t="n">
-        <v>385</v>
+        <v>210</v>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>2020-01-14T15:00:00.000Z</t>
+          <t>2026-06-27T10:00:07.000Z</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:25:35.324Z</t>
+          <t>2026-08-30T11:26:35.131Z</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/querydsl-실전</t>
+          <t>https://www.inflearn.com/course/cs-interview-prepara-2</t>
         </is>
       </c>
     </row>
@@ -6225,73 +6225,73 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>AI 에이전트로 구현하는 RAG 시스템(w. LangGraph)</t>
+          <t>비전공자도 쉽게 배우는 클로드 디자인</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>판다스 스튜디오</t>
+          <t>범쌤</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>99000</v>
+        <v>49500</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>99000</v>
+        <v>49500</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>172</v>
+        <v>33</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8047</v>
+        <v>366</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 활용(AX), 디자인 · 아트, 업무 생산성</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발</t>
+          <t>AI 크리에이티브, UX/UI, 생산성 도구</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>AI Agent, LangGraph, RAG, LLM, LangChain</t>
+          <t>Figma, terminal, figma-plugin, AI Agent, claude</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>405</v>
+        <v>249</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2024-10-22T15:00:00.000Z</t>
+          <t>2026-06-09T12:00:00.000Z</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04T03:56:05.522Z</t>
+          <t>2026-08-12T08:13:15.389Z</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai에이전트-구현-rag시스템-랭그래프</t>
+          <t>https://www.inflearn.com/course/claude-design-for-no</t>
         </is>
       </c>
     </row>
@@ -6301,19 +6301,19 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
+          <t>조회수 터지는 AI 강아지 영상만들기</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>마이업AI</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="F77" s="10" t="n">
         <v>0</v>
@@ -6322,52 +6322,52 @@
         <v>5</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>788</v>
+        <v>22</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
+          <t>AI 크리에이티브, AI 시작하기, 창업 · 부업</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
+          <t>인공지능(AI), gemini, gpt, 영상제작, AI 영상, AI 이미지</t>
         </is>
       </c>
       <c r="N77" s="7" t="n">
-        <v>1266</v>
+        <v>10</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07T05:00:33.000Z</t>
+          <t>2026-10-14T08:00:07.000Z</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T22:16:49.715Z</t>
+          <t>2026-10-14T05:45:43.069Z</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-llm-servic</t>
+          <t>https://www.inflearn.com/course/creating-ai-dog-vide</t>
         </is>
       </c>
     </row>
@@ -6377,31 +6377,31 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>기획자·마케터를 위한 피그마 배리어블로 SNS 템플릿 제작법</t>
+          <t>트래픽 급증을 견디는 서버 시스템 설계 - Coupon 발급 서비스</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>알라딘 아카데미</t>
+          <t>한조각</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>33000</v>
+        <v>41250</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>110000</v>
+        <v>55000</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3</v>
+        <v>813</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6410,40 +6410,40 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>디자인 · 아트, 기획 · 경영 · 마케팅</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>그래픽 디자인, UX/UI, 마케팅</t>
+          <t>백엔드, 웹 개발, 데이터베이스</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>콘텐츠 마케팅, Figma, 콘텐츠 제작, autolayout, figma variable</t>
+          <t>Java, Kotlin, MySQL, Docker, Spring Boot, Kafka, Redis</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>183</v>
+        <v>618</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T10:30:06.000Z</t>
+          <t>2026-08-09T17:00:05.000Z</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:49:08.171Z</t>
+          <t>2026-08-27T15:21:43.118Z</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-sns-te</t>
+          <t>https://www.inflearn.com/course/designing-a-server-s</t>
         </is>
       </c>
     </row>
@@ -6453,73 +6453,73 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
+          <t>비개발자 직장인을 위한 Claude (Cowork + N8N + Claude Design)</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>딩코딩코</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>44000</v>
+        <v>165000</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>44000</v>
+        <v>165000</v>
       </c>
       <c r="F79" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>4071</v>
+        <v>59</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>37234</v>
+        <v>575</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
+          <t>AI 실무 활용, 업무 자동화</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>claude, 인공지능(AI), AI Agent, n8n</t>
         </is>
       </c>
       <c r="N79" s="7" t="n">
-        <v>341</v>
+        <v>694</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>2020-12-19T15:00:00.000Z</t>
+          <t>2026-04-26T02:30:00.000Z</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:23:13.295Z</t>
+          <t>2026-07-24T14:36:39.327Z</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
+          <t>https://www.inflearn.com/course/claude-for-non-devel</t>
         </is>
       </c>
     </row>
@@ -6529,31 +6529,31 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>실리콘밸리 AI 개발자의 LLM 서비스를 위한 RAG</t>
+          <t>옵시디언 마스터 클래스: PKM·AI Second Brain·LLM WiKi 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>조영수(데이먼)</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>165000</v>
+        <v>132000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>165000</v>
+        <v>132000</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>684</v>
+        <v>1139</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6562,40 +6562,40 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>업무 생산성, 기획 · 경영 · 마케팅, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
+          <t>생산성 도구, 기획 · PM· PO, AI 실무 활용</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>JavaScript, Python, 인공지능(AI), ChatGPT, RAG</t>
+          <t>업무 생산성, obsidian</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>531</v>
+        <v>455</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T08:00:08.000Z</t>
+          <t>2025-06-25T12:30:00.000Z</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T00:24:12.168Z</t>
+          <t>2026-05-08T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-rag-as-tau</t>
+          <t>https://www.inflearn.com/course/옵시디언-마스터-클래스생산성을-바꾸는-1</t>
         </is>
       </c>
     </row>
@@ -6605,73 +6605,73 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>AI 시대의 혁신적인 게임 개발 입문 with Unity6</t>
+          <t>밑바닥부터 만드는 AI 에이전트 — RAG · 멀티 에이전트 · MCP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>UniCoti</t>
+          <t>단테</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>36300</v>
+        <v>44000</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>36300</v>
+        <v>88000</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>4253</v>
+        <v>8</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>게임 개발, 개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>게임 프로그래밍, 프로그래밍 언어, AI 코딩</t>
+          <t>AI에이전트 개발, 백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>Unity, C#, 인공지능(AI)</t>
+          <t>Python, FastAPI, LLM, openAI API, AI Agent</t>
         </is>
       </c>
       <c r="N81" s="7" t="n">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>2025-04-02T15:00:00.000Z</t>
+          <t>2026-10-05T18:00:08.000Z</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>2025-08-11T02:17:36.456Z</t>
+          <t>2026-10-18T04:36:20.813Z</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-게임개발-입문-unity6</t>
+          <t>https://www.inflearn.com/course/introduction-to-buil-2</t>
         </is>
       </c>
     </row>
@@ -6681,73 +6681,71 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>[입문자를 위한 UE5] Part4. 언리얼 엔진 C++</t>
+          <t>개발자 개념 장착 - 프로그래밍 개발에 필요한 필수 개념과 핵심 이론정리</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>코딩하는기술사</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>631</v>
+        <v>1651</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>게임 개발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>게임 프로그래밍</t>
+          <t>개발 · 프로그래밍 기타, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>언리얼 C++, Unreal Engine</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>1553</v>
-      </c>
+          <t>아키텍처, 컴퓨터 구조, 기술면접, 소프트웨어 설계, 문제해결능력</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2024-04-28T15:00:00.000Z</t>
+          <t>2026-01-19T13:00:00.000Z</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:32:11.155Z</t>
+          <t>2026-01-30T22:11:57.790Z</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/언리얼5-개발의정석-4</t>
+          <t>https://www.inflearn.com/course/개발자-개념-장착-프로그래밍-개발에</t>
         </is>
       </c>
     </row>
@@ -6757,31 +6755,31 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>초보자를 위한 IT 인프라의 이해</t>
+          <t>피그마(Figma)를 활용한 UI디자인 입문부터 실전까지 A to Z</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>보물상자</t>
+          <t>에릭</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>99000</v>
+        <v>82500</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>99000</v>
+        <v>82500</v>
       </c>
       <c r="F83" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>83</v>
+        <v>518</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>761</v>
+        <v>3679</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
@@ -6790,40 +6788,40 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 하드웨어</t>
+          <t>디자인 · 아트</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 백엔드, 컴퓨터 구조</t>
+          <t>UX/UI, 그래픽 디자인</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>네트워크, 컴퓨터 구조</t>
+          <t>Figma, 웹 디자인, 모바일 디자인, 프로덕트디자인</t>
         </is>
       </c>
       <c r="N83" s="7" t="n">
-        <v>770</v>
+        <v>545</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>2022-11-14T15:00:00.000Z</t>
+          <t>2020-11-04T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:42:47.379Z</t>
+          <t>2026-05-04T11:22:20.563Z</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/it-인프라-이해</t>
+          <t>https://www.inflearn.com/course/피그마-ui디자인</t>
         </is>
       </c>
     </row>
@@ -6833,73 +6831,73 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>노베이스를 위한 ADsP 생존 가이드</t>
+          <t>실전! 언리얼 소울라이크 개발: A to Z</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>Spector</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>0</v>
+        <v>176000</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>0</v>
+        <v>176000</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>769</v>
+        <v>254</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>게임 개발</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
+          <t>게임 프로그래밍</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>SQL, R, ADsP</t>
+          <t>Unreal Engine, 언리얼 C++, C++</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>303</v>
+        <v>1189</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11T11:00:00.000Z</t>
+          <t>2025-04-28T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11T09:14:53.120Z</t>
+          <t>2025-10-28T07:29:59.986Z</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
+          <t>https://www.inflearn.com/course/언리얼-소울라이크-개발</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6968,7 @@
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
@@ -6985,73 +6983,73 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
+          <t>대세는 바이브 코딩 : 클로드 코드와 TDD로 완성하는 AI 풀스택 개발</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>멍슨상</t>
+          <t>Masocampus</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>36300</v>
+        <v>89100</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>48400</v>
+        <v>89100</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>317</v>
+        <v>96</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>AI 개발 활용, 웹 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, database</t>
+          <t>웹앱, TDD, 인공지능(AI), claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>1553</v>
+        <v>345</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2025-09-24T07:00:00.000Z</t>
+          <t>2026-04-16T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T06:06:52.494Z</t>
+          <t>2026-04-16T07:04:40.971Z</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
+          <t>https://www.inflearn.com/course/the-trend-is-vibe-co-1</t>
         </is>
       </c>
     </row>
@@ -7061,31 +7059,31 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
+          <t>정보처리기사 자격증 대비 교육(실기)</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>국립안동대학교 SW융합교육원</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="F87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>605</v>
+        <v>56</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>9782</v>
+        <v>2241</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
@@ -7099,35 +7097,35 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, thread, multithread, 동시성</t>
+          <t>정보처리기사</t>
         </is>
       </c>
       <c r="N87" s="7" t="n">
-        <v>1249</v>
+        <v>1532</v>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>2024-07-14T15:00:00.000Z</t>
+          <t>2024-08-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>2025-11-18T01:46:58.908Z</t>
+          <t>2024-08-14T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
+          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
         </is>
       </c>
     </row>
@@ -7137,73 +7135,73 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>자바(Java) 알고리즘 문제풀이 입문: 코딩테스트 대비</t>
+          <t>PMP(프로젝트 관리 전문가) 자격 취득과정- PMBOK 8판 기준</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>김태원</t>
+          <t>피엠인사이드</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>77000</v>
+        <v>330000</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>77000</v>
+        <v>330000</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>8297</v>
+        <v>20</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>알고리즘 · 자료구조, 프로그래밍 언어</t>
+          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Java, 코딩 테스트</t>
+          <t>프로젝트 관리, PMP</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>1348</v>
+        <v>2374</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2021-03-24T15:00:00.000Z</t>
+          <t>2026-10-01T13:00:08.000Z</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:32:20.151Z</t>
+          <t>2026-10-16T09:00:13.940Z</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/자바-알고리즘-문제풀이-코테대비</t>
+          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
         </is>
       </c>
     </row>
@@ -7213,31 +7211,31 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
+          <t>나만의 Claude Code  하네스 (SPEC·TDD·CI로 짓는 AI 개발 워크플로우)</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>미쿡엔지니어</t>
+          <t>프롱트</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>33000</v>
+        <v>66000</v>
       </c>
       <c r="E89" s="9" t="n">
         <v>66000</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>268</v>
+        <v>577</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
@@ -7246,40 +7244,40 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
+          <t>AI에이전트 개발, 웹 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>Python, LLM, AI Agent, claude</t>
+          <t>React, TDD, AI Agent, claude, 하네스</t>
         </is>
       </c>
       <c r="N89" s="7" t="n">
-        <v>305</v>
+        <v>438</v>
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23T06:30:05.000Z</t>
+          <t>2026-05-06T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26T17:31:06.856Z</t>
+          <t>2026-05-21T16:24:41.523Z</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
+          <t>https://www.inflearn.com/course/my-own-claude-code-h</t>
         </is>
       </c>
     </row>
@@ -7289,73 +7287,73 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 고급편</t>
+          <t>대세는 쿠버네티스 (초급~중급편)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>121000</v>
+        <v>44000</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>121000</v>
+        <v>44000</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>880</v>
+        <v>626</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>21012</v>
+        <v>8500</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Spring, 디자인 패턴</t>
+          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>1004</v>
+        <v>425</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2021-10-26T15:00:00.000Z</t>
+          <t>2019-09-10T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21T11:02:33.060Z</t>
+          <t>2025-11-19T05:23:15.024Z</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-고급편</t>
+          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
         </is>
       </c>
     </row>
@@ -7365,73 +7363,73 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>AI에게 마음 놓고 맡기는 바이브코딩 : 망쳐도 한 문장으로 되돌리는 Git 버전 관리</t>
+          <t>38군데 합격 비법, 2026 코딩테스트 필수 알고리즘</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Masocampus</t>
+          <t>딩코딩코</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>34650</v>
+        <v>165000</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>49500</v>
+        <v>165000</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>4</v>
+        <v>453</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>7</v>
+        <v>2888</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI에이전트 개발</t>
+          <t>알고리즘 · 자료구조, 취업 · 이직</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), Git, 바이브코딩, VSCode, codex, GitHub</t>
+          <t>Python, 코딩 테스트, 알고리즘, data-structure</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
-        <v>119</v>
+        <v>934</v>
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T02:00:06.000Z</t>
+          <t>2024-11-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T02:14:59.154Z</t>
+          <t>2026-09-10T05:18:11.523Z</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/vibe-coding-you-can</t>
+          <t>https://www.inflearn.com/course/38군데-합격비법-코테-필수-알고리즘</t>
         </is>
       </c>
     </row>
@@ -7441,73 +7439,73 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>RAG 마스터: 기초부터 고급기법까지 (feat. LangChain)</t>
+          <t>[리뉴얼] 파이썬입문과 크롤링기초 부트캠프 [파이썬, 웹, 데이터 이해 기본까지] (업데이트)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>판다스 스튜디오</t>
+          <t>잔재미코딩 DaveLee</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>121000</v>
+        <v>77000</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>121000</v>
+        <v>77000</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>986</v>
+        <v>7615</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발</t>
+          <t>데이터 분석, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>RAG, LangChain, LLM, 챗봇, Python</t>
+          <t>Python, 웹 크롤링</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>523</v>
+        <v>991</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2024-09-29T15:00:00.000Z</t>
+          <t>2019-06-05T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T00:00:00.000Z</t>
+          <t>2026-08-27T04:37:56.211Z</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/랭체인으로-만드는-rag-활용-평가</t>
+          <t>https://www.inflearn.com/course/python-crawling-basic</t>
         </is>
       </c>
     </row>
@@ -7517,73 +7515,73 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>웹 개발자와 정보보안 입문자가 꼭 알아야 할 웹 해킹 &amp; 시큐어 코딩</t>
+          <t>노베이스를 위한 ADsP 생존 가이드</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>크리핵티브</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="F93" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>265</v>
+        <v>22</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>2362</v>
+        <v>772</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>모의해킹, 인젝션</t>
+          <t>SQL, R, ADsP</t>
         </is>
       </c>
       <c r="N93" s="7" t="n">
-        <v>993</v>
+        <v>303</v>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>2020-06-16T15:00:00.000Z</t>
+          <t>2025-11-11T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:44:01.802Z</t>
+          <t>2025-11-11T09:14:53.120Z</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/웹해킹-보안-시큐어코딩</t>
+          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
         </is>
       </c>
     </row>
@@ -7593,73 +7591,73 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
+          <t>한 입 크기로 잘라먹는 타입스크립트(TypeScript)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>남박사</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>68200</v>
+        <v>48400</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>68200</v>
+        <v>48400</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>288</v>
+        <v>783</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3415</v>
+        <v>14566</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
+          <t>프로그래밍 언어, 웹 개발, 프론트엔드</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>1143</v>
+        <v>632</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2025-05-06T15:00:00.000Z</t>
+          <t>2023-05-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12T11:29:01.075Z</t>
+          <t>2026-04-16T00:41:51.879Z</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
+          <t>https://www.inflearn.com/course/한입-크기-타입스크립트</t>
         </is>
       </c>
     </row>
@@ -7669,73 +7667,73 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>30분 만에 나만의 AI 에이전트 만들기 (Antigravity 실습)</t>
+          <t>Claude Code로 만드는 1인 개발자 자동화 시스템 - Sidabari 프로젝트</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>최원영</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0</v>
+        <v>187000</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>0</v>
+        <v>187000</v>
       </c>
       <c r="F95" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>1578</v>
+        <v>465</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>데브옵스 · 인프라, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI)</t>
+          <t>devops, tauri, 프롬프트엔지니어링, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
-        <v>32</v>
+        <v>598</v>
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27T05:00:00.000Z</t>
+          <t>2026-05-15T08:30:00.000Z</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27T06:18:36.692Z</t>
+          <t>2026-07-21T02:16:22.604Z</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/30분-만에-나만의-ai-에이전트-만</t>
+          <t>https://www.inflearn.com/course/solo-developer-autom</t>
         </is>
       </c>
     </row>
@@ -7745,73 +7743,73 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>홍정모의 따라하며 배우는 C++</t>
+          <t>AI 에이전트 엔지니어링</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>홍정모</t>
+          <t>민혁</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>176000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>176000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>395</v>
+        <v>39</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>7126</v>
+        <v>2077</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 게임 개발</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 게임 프로그래밍, AI 코딩</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Python, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>2907</v>
+        <v>322</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2018-09-30T15:00:00.000Z</t>
+          <t>2026-04-07T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2025-08-10T19:46:59.750Z</t>
+          <t>2026-04-07T02:58:08.781Z</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/following-c-plus</t>
+          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
         </is>
       </c>
     </row>
@@ -7821,31 +7819,31 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>진짜! 타입스크립트 - 타입 설계부터 타입 레벨 프로그래밍까지</t>
+          <t>AI 에이전트로 구현하는 RAG 시스템(w. LangGraph)</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>코딩맥스 CodingMax</t>
+          <t>판다스 스튜디오</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
       <c r="E97" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>7</v>
+        <v>8047</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
@@ -7854,40 +7852,40 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>AI에이전트 개발</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, 함수형 프로그래밍, TypeScript, Node.js</t>
+          <t>AI Agent, LangGraph, RAG, LLM, LangChain</t>
         </is>
       </c>
       <c r="N97" s="7" t="n">
-        <v>3475</v>
+        <v>405</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T01:00:07.000Z</t>
+          <t>2024-10-22T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T01:50:40.027Z</t>
+          <t>2026-03-04T03:56:05.522Z</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/really-typescript-fr</t>
+          <t>https://www.inflearn.com/course/ai에이전트-구현-rag시스템-랭그래프</t>
         </is>
       </c>
     </row>
@@ -7897,31 +7895,31 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>[AI 리터러시 저자직강] 모든 직장인이 활용할 수 있는 올인원 AI 활용법(26년 6월 전체 리뉴얼)</t>
+          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>김용성</t>
+          <t>nstyxn</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>110000</v>
+        <v>118800</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>110000</v>
+        <v>118800</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>223</v>
+        <v>88</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1141</v>
+        <v>960</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7930,40 +7928,40 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
+          <t>보안, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, 영상제작, 서비스 기획, 인공지능(AI)</t>
+          <t>Forensic, 디지털포렌식전문가 2급</t>
         </is>
       </c>
       <c r="N98" s="2" t="n">
-        <v>274</v>
+        <v>6530</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09T09:30:00.000Z</t>
+          <t>2022-11-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07T08:14:11.781Z</t>
+          <t>2026-07-15T02:00:30.898Z</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-리터러시-저자직강-모든-직장인이</t>
+          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
         </is>
       </c>
     </row>
@@ -7973,31 +7971,31 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>[리뉴얼] 처음하는 SQL과 데이터베이스(MySQL) 부트캠프 [입문부터 활용까지]</t>
+          <t>Docker가 쉬워지는 운영체제 이야기</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>잔재미코딩 DaveLee</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>77000</v>
+        <v>88000</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>77000</v>
+        <v>88000</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>328</v>
+        <v>46</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>4364</v>
+        <v>951</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
@@ -8006,40 +8004,40 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석</t>
+          <t>데브옵스 · 인프라, 시스템 · 운영체제, 클라우드</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>Python, SQL, MySQL, DBMS/RDBMS, 데이터 엔지니어링</t>
+          <t>네트워크, Linux, Docker, 운영체제, linux-containers, cloud-computing</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
-        <v>528</v>
+        <v>723</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>2019-09-08T15:00:00.000Z</t>
+          <t>2026-07-30T04:00:57.000Z</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27T04:47:42.744Z</t>
+          <t>2026-08-04T00:38:47.888Z</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sql-db-mysql-파이썬-데이터분석</t>
+          <t>https://www.inflearn.com/course/operating-system-sto</t>
         </is>
       </c>
     </row>
@@ -8049,31 +8047,31 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>[Next 바이브코딩] 2단계: AI가 짠 코드, 믿기 전에 확인하는 구현·리뷰·PR 흐름</t>
+          <t>김영한의 실전 데이터베이스 - 설계 1편, 현대적 데이터 모델링 완전 정복</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>33000</v>
+        <v>99000</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>66000</v>
+        <v>99000</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20</v>
+        <v>4184</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -8082,40 +8080,40 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, codex, 인공지능(AI), AI Agent, claude</t>
+          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>285</v>
+        <v>972</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T04:30:06.000Z</t>
+          <t>2025-09-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T04:23:48.617Z</t>
+          <t>2026-02-09T09:36:10.311Z</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/next-vibe-coding-ste-1</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계1편</t>
         </is>
       </c>
     </row>
@@ -8125,19 +8123,19 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>쿠버네티스 어나더 클래스-Sprint 1, 2 (#실무기초 #설치 #배포 #Jenkins #Helm #ArgoCD)</t>
+          <t>LangGraph를 활용한 AI Agent 개발 (feat. MCP)</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>82500</v>
+        <v>69300</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>82500</v>
+        <v>69300</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>0</v>
@@ -8146,10 +8144,10 @@
         <v>4.9</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>790</v>
+        <v>263</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>2912</v>
+        <v>2967</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
@@ -8158,40 +8156,40 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>AI에이전트 개발</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, argocd, container, helm</t>
+          <t>프롬프트엔지니어링, LLM, AI Agent, LangGraph, MCP</t>
         </is>
       </c>
       <c r="N101" s="7" t="n">
-        <v>669</v>
+        <v>381</v>
       </c>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>2023-09-11T15:00:00.000Z</t>
+          <t>2025-01-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>2026-05-27T08:15:25.352Z</t>
+          <t>2026-06-23T10:57:36.230Z</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-어나더-클래스-지상편-sprint1</t>
+          <t>https://www.inflearn.com/course/랭그래프-활용한-llm에이전트-개발</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8346,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17T13:29:21+09:00</t>
+          <t>2026-10-18T13:36:38+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -626,10 +626,10 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Claude Code 실전 업무 자동화 : 코드 없이 나만의 AI 에이전트 만들기</t>
+          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>일잘러 장피엠</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>4.9</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67</v>
+        <v>1664</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2686</v>
+        <v>11361</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -790,40 +790,40 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>claude, codex, MCP, No-code</t>
+          <t>React, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>306</v>
+        <v>1254</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T05:00:08.000Z</t>
+          <t>2025-11-19T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T01:55:19.117Z</t>
+          <t>2026-08-18T03:54:49.011Z</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-workflow-a</t>
+          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
         </is>
       </c>
     </row>
@@ -854,10 +854,10 @@
         <v>5</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
@@ -889,12 +889,12 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T03:26:00.226Z</t>
+          <t>2026-10-18T04:41:50.010Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -909,19 +909,19 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
+          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>퇴근후딴짓</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>198000</v>
+        <v>121000</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>198000</v>
+        <v>121000</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -930,10 +930,10 @@
         <v>4.9</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1655</v>
+        <v>931</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11351</v>
+        <v>6048</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -942,40 +942,40 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>데이터 사이언스 자격증, 데이터 분석</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>React, 인공지능(AI), claude</t>
+          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1254</v>
+        <v>1618</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2025-11-19T09:00:00.000Z</t>
+          <t>2022-12-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T03:54:49.011Z</t>
+          <t>2026-10-18T16:36:18.265Z</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
+          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1061,31 +1061,31 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
+          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>퇴근후딴짓</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>121000</v>
+        <v>484000</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>121000</v>
+        <v>484000</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>931</v>
+        <v>11</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6041</v>
+        <v>38</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1094,40 +1094,40 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 데이터 분석</t>
+          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
+          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1576</v>
+        <v>224</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2022-12-12T15:00:00.000Z</t>
+          <t>2026-10-04T05:30:05.000Z</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T10:04:18.317Z</t>
+          <t>2026-10-16T04:14:58.414Z</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
+          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>GPT·바이브코딩으로 만드는 자동 수익형 사주 서비스 제작법</t>
+          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>484000</v>
+        <v>88000</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>484000</v>
+        <v>88000</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>9</v>
+        <v>733</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>34</v>
+        <v>5735</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
@@ -1170,40 +1170,40 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 실무 활용</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>HTML/CSS, ChatGPT, AI Agent, claude, 바이브코딩</t>
+          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
         </is>
       </c>
       <c r="N9" s="7" t="n">
-        <v>224</v>
+        <v>2108</v>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T05:30:05.000Z</t>
+          <t>2024-06-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T04:14:58.414Z</t>
+          <t>2026-10-18T06:15:41.801Z</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/how-to-create-an-aut</t>
+          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
         </is>
       </c>
     </row>
@@ -1213,31 +1213,31 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>(2026 최신!) 일주일만에 합격하는 정보처리기사 실기</t>
+          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>한빛미디어</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5730</v>
+        <v>13558</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1246,40 +1246,40 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
+          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Python, Java, C, 정보처리기사, 정보처리산업기사</t>
+          <t>인공지능(AI), 바이브코딩</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2108</v>
+        <v>259</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2024-06-13T15:00:00.000Z</t>
+          <t>2025-12-22T08:00:00.000Z</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T14:55:46.048Z</t>
+          <t>2026-01-07T07:20:44.145Z</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/일주일만에-합격하는-정보처리기사-실기</t>
+          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
         </is>
       </c>
     </row>
@@ -1289,73 +1289,73 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>49500</v>
+        <v>198000</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>99000</v>
+        <v>198000</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>165</v>
+        <v>1627</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>Linux, AWS, bash, ubuntu, nginx</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>712</v>
+        <v>1649</v>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06T07:00:10.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T00:04:40.038Z</t>
+          <t>2026-10-15T09:10:56.894Z</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
+          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>한빛미디어</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>732</v>
+        <v>10</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13530</v>
+        <v>167</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1398,40 +1398,40 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
+          <t>데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), 바이브코딩</t>
+          <t>Linux, AWS, bash, ubuntu, nginx</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>259</v>
+        <v>710</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22T08:00:00.000Z</t>
+          <t>2026-10-06T07:00:10.000Z</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07T07:20:44.145Z</t>
+          <t>2026-10-18T17:50:09.486Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
+          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -1593,31 +1593,31 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>김영한의 실전 자바 - 기본편</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>198000</v>
+        <v>44000</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>198000</v>
+        <v>44000</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>173</v>
+        <v>2406</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1622</v>
+        <v>28233</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
@@ -1626,40 +1626,40 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>1649</v>
+        <v>1012</v>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T09:10:56.894Z</t>
+          <t>2025-12-23T06:52:23.926Z</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
         </is>
       </c>
     </row>
@@ -1669,73 +1669,73 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>클로드 코드 실전 — 설치부터 하네스까지</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>단테</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4051</v>
+        <v>6</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>Git, supabase, AI Agent, MCP, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>90</v>
+        <v>690</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2026-10-17T18:00:04.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2026-10-18T02:05:05.992Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/claude-code-in-pract</t>
         </is>
       </c>
     </row>
@@ -1745,71 +1745,73 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+          <t>LangChain, LangGraph, LangSmith 기초부터 총정리</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>bradkim</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0</v>
+        <v>69300</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>4698</v>
+        <v>3</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+          <t>AI에이전트 개발, 인공지능 기타, AI 개발 활용</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n"/>
+          <t>FastAPI, vector-database, 인공지능(AI), LLM, LangChain, openAI API, LangGraph</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>526</v>
+      </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27T10:00:00.000Z</t>
+          <t>2026-10-18T13:30:05.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30T00:59:39.967Z</t>
+          <t>2026-10-18T11:54:49.913Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+          <t>https://www.inflearn.com/course/a-complete-overview</t>
         </is>
       </c>
     </row>
@@ -1819,19 +1821,19 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 기본편</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>44000</v>
+        <v>55000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>44000</v>
+        <v>55000</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0</v>
@@ -1840,10 +1842,10 @@
         <v>5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2404</v>
+        <v>114</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>28229</v>
+        <v>666</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1852,40 +1854,40 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1012</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23T06:52:23.926Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -1895,73 +1897,73 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="F19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>113</v>
+        <v>317</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>663</v>
+        <v>4061</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -1971,73 +1973,71 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>[Next 바이브코딩] 2단계: AI가 짠 코드, 믿기 전에 확인하는 구현·리뷰·PR 흐름</t>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24</v>
+        <v>4708</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, codex, 인공지능(AI), AI Agent, claude</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>305</v>
-      </c>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T04:30:06.000Z</t>
+          <t>2026-01-27T10:00:00.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:18:36.438Z</t>
+          <t>2026-06-30T00:59:39.967Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/next-vibe-coding-ste-1</t>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
         </is>
       </c>
     </row>
@@ -2047,73 +2047,73 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
+          <t>김영한의 실전 자바 - 중급 2편</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>알고런 데이터코드 연구소</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>79200</v>
+        <v>66000</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>79200</v>
+        <v>66000</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>77</v>
+        <v>885</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>601</v>
+        <v>11031</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
+          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>785</v>
+        <v>1165</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2025-04-07T15:00:00.000Z</t>
+          <t>2024-05-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02T07:40:07.999Z</t>
+          <t>2025-11-24T10:17:13.631Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
         </is>
       </c>
     </row>
@@ -2123,73 +2123,73 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
+          <t>AWS로 배우는 네트워크: 이론부터 실무까지</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>회로설계 멘토 삼코치</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>269500</v>
+        <v>154000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>269500</v>
+        <v>154000</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>703</v>
+        <v>1212</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>AI 활용(AX), 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 반도체</t>
+          <t>AI 실무 활용, 네트워크, 클라우드</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
+          <t>네트워크, tcpip, aws-vpc, aws-alb, 바이브코딩</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2025-03-25T15:00:00.000Z</t>
+          <t>2026-02-26T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:20:57.892Z</t>
+          <t>2026-02-28T06:03:09.161Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
+          <t>https://www.inflearn.com/course/aws로-배우는-네트워크-이론부터-실</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>0</v>
@@ -2220,10 +2220,10 @@
         <v>4.9</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>270</v>
+        <v>42</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1370</v>
+        <v>489</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
@@ -2232,40 +2232,40 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+          <t>SQLD, SQL, Oracle, MSSQL</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>309</v>
+        <v>501</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2026-01-13T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:28:44.702Z</t>
+          <t>2026-10-12T07:12:46.551Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
         </is>
       </c>
     </row>
@@ -2275,73 +2275,73 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>89100</v>
+        <v>154000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>89100</v>
+        <v>154000</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>237</v>
+        <v>52</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1741</v>
+        <v>2059</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>데이터베이스, 데이터 분석, 풀스택</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
+          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>727</v>
+        <v>1270</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2026-07-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2026-07-28T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
         </is>
       </c>
     </row>
@@ -2351,73 +2351,73 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>엔지니어를 위한 AI 독해력 [입문편] — AI 논문을 읽을 수 있게</t>
+          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Hiro Son</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>49500</v>
+        <v>44550</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>198000</v>
+        <v>59400</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
+          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>228</v>
+        <v>311</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07T17:30:06.000Z</t>
+          <t>2026-07-31T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T14:12:56.231Z</t>
+          <t>2026-08-12T14:30:32.966Z</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
+          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
         </is>
       </c>
     </row>
@@ -2427,73 +2427,73 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ②</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>66000</v>
+        <v>89100</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>66000</v>
+        <v>89100</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>39</v>
+        <v>1744</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>백엔드, AI 코딩</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>네트워크, Docker, backend, devops, 인공지능(AI), RAG</t>
+          <t>security, CPPG(개인정보관리사)</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>461</v>
+        <v>727</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T04:30:06.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T22:23:02.274Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-backend-co-1</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -2503,73 +2503,73 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>747</v>
+        <v>272</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>11860</v>
+        <v>1374</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>517</v>
+        <v>309</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2025-08-31T09:28:51.006Z</t>
+          <t>2026-10-19T01:45:14.770Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -2579,73 +2579,73 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
+          <t>김영한의 실전 자바 - 중급 1편</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>91</v>
+        <v>12548</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>363</v>
+        <v>1161</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2024-03-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2025-11-28T10:04:41.236Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
         </is>
       </c>
     </row>
@@ -2655,31 +2655,31 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>자바 ORM 표준 JPA 프로그래밍 - 기본편</t>
+          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>121000</v>
+        <v>88000</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>121000</v>
+        <v>88000</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>2154</v>
+        <v>195</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>25682</v>
+        <v>1473</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
@@ -2688,40 +2688,40 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데이터베이스</t>
+          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>Java, JPA</t>
+          <t>업무 생산성, wiki, obsidian, claude</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>963</v>
+        <v>368</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2019-06-25T15:00:00.000Z</t>
+          <t>2026-04-25T18:30:00.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:40:24.471Z</t>
+          <t>2026-10-08T14:26:56.788Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ORM-JPA-Basic</t>
+          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
         </is>
       </c>
     </row>
@@ -2731,73 +2731,73 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
+          <t>김영한의 실전 데이터베이스 - 기본편</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>인프런</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>33000</v>
+        <v>88000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>33000</v>
+        <v>88000</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1403</v>
+        <v>520</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>34404</v>
+        <v>5403</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>857</v>
+        <v>821</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2019-06-01T15:00:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T05:48:10.725Z</t>
+          <t>2026-08-06T12:14:20.961Z</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
         </is>
       </c>
     </row>
@@ -2807,19 +2807,19 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
+          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>99000</v>
+        <v>121000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>99000</v>
+        <v>121000</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0</v>
@@ -2828,52 +2828,52 @@
         <v>5</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1113</v>
+        <v>2977</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
+          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>516</v>
+        <v>797</v>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12T00:00:00.000Z</t>
+          <t>2026-01-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-21T01:35:54.874Z</t>
+          <t>2026-02-09T09:50:03.741Z</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
         </is>
       </c>
     </row>
@@ -2883,73 +2883,73 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>195</v>
+        <v>617</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1471</v>
+        <v>8424</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>개발 도구</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>Git, GitHub, github-actions, git-commands</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2022-01-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2026-06-03T09:18:28.574Z</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
         </is>
       </c>
     </row>
@@ -2959,73 +2959,73 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
+          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>48400</v>
+        <v>99000</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>48400</v>
+        <v>99000</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>1561</v>
+        <v>7</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>15632</v>
+        <v>93</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>프론트엔드, 웹 개발</t>
+          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, React, Node.js</t>
+          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>1114</v>
+        <v>363</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2022-01-26T15:00:00.000Z</t>
+          <t>2026-09-16T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13T00:57:34.805Z</t>
+          <t>2026-09-30T03:16:06.187Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-리액트</t>
+          <t>https://www.inflearn.com/course/ai-automated-trading</t>
         </is>
       </c>
     </row>
@@ -3035,19 +3035,19 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
+          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>0</v>
@@ -3056,52 +3056,52 @@
         <v>5</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>42</v>
+        <v>747</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>540</v>
+        <v>11872</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1048</v>
+        <v>517</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T17:00:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T22:53:04.634Z</t>
+          <t>2025-08-31T09:28:51.006Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
         <v>145</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -3187,73 +3187,73 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 기본편</t>
+          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>알고런 데이터코드 연구소</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>88000</v>
+        <v>79200</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>88000</v>
+        <v>79200</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>518</v>
+        <v>77</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5400</v>
+        <v>601</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>821</v>
+        <v>785</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2025-04-07T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06T12:14:20.961Z</t>
+          <t>2026-07-02T07:40:07.999Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
+          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
         </is>
       </c>
     </row>
@@ -3263,31 +3263,31 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
+          <t>Docker가 쉬워지는 운영체제 이야기</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>121000</v>
+        <v>88000</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>121000</v>
+        <v>88000</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>2974</v>
+        <v>956</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
@@ -3296,40 +3296,40 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>데브옵스 · 인프라, 시스템 · 운영체제, 클라우드</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
+          <t>네트워크, Linux, Docker, 운영체제, linux-containers, cloud-computing</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>797</v>
+        <v>723</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27T15:00:00.000Z</t>
+          <t>2026-07-30T04:00:57.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09T09:50:03.741Z</t>
+          <t>2026-08-04T00:38:47.888Z</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
+          <t>https://www.inflearn.com/course/operating-system-sto</t>
         </is>
       </c>
     </row>
@@ -3339,73 +3339,73 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>[Next 바이브코딩] 3단계: 지침·Skills·Hooks·MCP로 AI가 일하기 좋은 개발 시스템 만들기</t>
+          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>마일드코드</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>33000</v>
+        <v>239800</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>66000</v>
+        <v>239800</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>codex, claude, AI Agent, 인공지능(AI), MCP, Git</t>
+          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>304</v>
+        <v>480</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T13:00:06.000Z</t>
+          <t>2026-09-21T09:00:33.000Z</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:27:01.129Z</t>
+          <t>2026-10-13T14:25:37.776Z</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/next-vibe-coding-sta</t>
+          <t>https://www.inflearn.com/course/claude-code-for-non</t>
         </is>
       </c>
     </row>
@@ -3415,73 +3415,73 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>AI 코드를 읽는 게임 개발자 「Unity 6」 「Claude」 「Github Copilot」 「3D」</t>
+          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>알렌</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0</v>
+        <v>3145</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>3</v>
+        <v>57334</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>게임 개발, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>게임 프로그래밍, AI 코딩, AI 개발 활용</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>Unity, VSCode, github-copilot, 인공지능(AI), AI Agent, 유니티6, claude</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N39" s="7" t="n">
-        <v>498</v>
+        <v>771</v>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16T06:00:06.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T17:44:29.872Z</t>
+          <t>2026-01-28T11:59:57.298Z</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/game-developer-who-r</t>
+          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
         </is>
       </c>
     </row>
@@ -3491,73 +3491,73 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
+          <t>PCB HW설계 실무 : STM32를 활용한 Mixed-signal 보드 설계 프로젝트</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>회로설계 멘토 삼코치</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>55000</v>
+        <v>269500</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>55000</v>
+        <v>269500</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>484</v>
+        <v>703</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>임베디드 · IoT, 반도체</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SQLD, SQL, Oracle, MSSQL</t>
+          <t>orcad, kicad, artwork, stm32, hardware, MCU</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>501</v>
+        <v>918</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13T09:30:00.000Z</t>
+          <t>2025-03-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T07:12:46.551Z</t>
+          <t>2026-09-11T13:20:57.892Z</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
+          <t>https://www.inflearn.com/course/pcb-hw설계실무-stm32</t>
         </is>
       </c>
     </row>
@@ -3567,19 +3567,19 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>YoungJea Oh</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>99000</v>
+        <v>330000</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>99000</v>
+        <v>330000</v>
       </c>
       <c r="F41" s="10" t="n">
         <v>0</v>
@@ -3588,52 +3588,52 @@
         <v>5</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>33</v>
+        <v>547</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N41" s="7" t="n">
-        <v>370</v>
+        <v>1048</v>
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T10:00:08.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02T07:55:47.247Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-latest</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>김영한의 자바 입문 - 코드로 시작하는 자바 첫걸음</t>
+          <t>김영한의 실전 자바 - 고급 1편, 멀티스레드와 동시성</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>0</v>
@@ -3664,14 +3664,14 @@
         <v>5</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>3143</v>
+        <v>607</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>57323</v>
+        <v>9786</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3681,35 +3681,35 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>Java, 객체지향, thread, multithread, 동시성</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>771</v>
+        <v>1249</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2024-07-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28T11:59:57.298Z</t>
+          <t>2025-11-18T01:46:58.908Z</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-자바-입문</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-1</t>
         </is>
       </c>
     </row>
@@ -3719,73 +3719,73 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
+          <t>[Next 바이브코딩] 2단계: AI가 짠 코드, 믿기 전에 확인하는 구현·리뷰·PR 흐름</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Rookiss</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>128700</v>
+        <v>66000</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>128700</v>
+        <v>66000</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>582</v>
+        <v>23</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 오피스, 업무 자동화</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
+          <t>Git, GitHub, codex, 인공지능(AI), AI Agent, claude</t>
         </is>
       </c>
       <c r="N43" s="7" t="n">
-        <v>832</v>
+        <v>305</v>
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05T16:00:00.000Z</t>
+          <t>2026-09-18T04:30:06.000Z</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07T06:36:11.731Z</t>
+          <t>2026-10-17T09:18:36.438Z</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/starting-with-claude</t>
+          <t>https://www.inflearn.com/course/next-vibe-coding-ste-1</t>
         </is>
       </c>
     </row>
@@ -3795,73 +3795,73 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>챗봇을 만들며 배우는 ai agent 개발의 모든것(fastapi, RAG, vector, LangChain, sLLM/파인튜닝)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>bradkim</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
         <v>66000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>66000</v>
+        <v>88000</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1265</v>
+        <v>13</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12545</v>
+        <v>339</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>AI에이전트 개발, 인공지능 기타, AI 개발 활용</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>RAG, vector-database, FastAPI, LLM, Llama, Fine-Tuning, openAI API</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1161</v>
+        <v>507</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2026-07-01T06:30:06.000Z</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2026-07-01T07:03:29.747Z</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/everything-about-ai</t>
         </is>
       </c>
     </row>
@@ -3871,19 +3871,19 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>154000</v>
+        <v>99000</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>154000</v>
+        <v>99000</v>
       </c>
       <c r="F45" s="10" t="n">
         <v>0</v>
@@ -3892,52 +3892,52 @@
         <v>5</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2054</v>
+        <v>1117</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 풀스택</t>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
+          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N45" s="7" t="n">
-        <v>1270</v>
+        <v>516</v>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00.000Z</t>
+          <t>2026-05-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28T00:00:00.000Z</t>
+          <t>2026-09-21T01:35:54.874Z</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
         </is>
       </c>
     </row>
@@ -3947,19 +3947,19 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>모두의 클로드 코드: 바이브코딩 바닥부터 프로 개발자처럼 서비스 운영하는 법과 수익화까지</t>
+          <t>김영한의 실전 자바 - 고급 3편, 람다, 스트림, 함수형 프로그래밍</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>마일드코드</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>239800</v>
+        <v>77000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>239800</v>
+        <v>77000</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>0</v>
@@ -3968,52 +3968,52 @@
         <v>5</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>3</v>
+        <v>349</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>52</v>
+        <v>5465</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX), 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>AI 코딩, AI 개발 활용, 창업 · 부업</t>
+          <t>웹 개발, 프로그래밍 언어, 백엔드</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>GitHub, Next.js, expo, vercel, supabase, claude, 바이브코딩</t>
+          <t>Java, 함수형 프로그래밍, Lambda, optional</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>480</v>
+        <v>1001</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:00:33.000Z</t>
+          <t>2025-03-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T14:25:37.776Z</t>
+          <t>2025-09-14T05:27:02.800Z</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-for-non</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-3</t>
         </is>
       </c>
     </row>
@@ -4023,19 +4023,19 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>채널톡 면접관이 직접 알려주는 CS 면접 대비 - 데이터베이스 편</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>JSCODE 제이온</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="F47" s="10" t="n">
         <v>0</v>
@@ -4044,52 +4044,52 @@
         <v>4.9</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>617</v>
+        <v>29</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>8421</v>
+        <v>306</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>취업 · 이직, 개발 · 프로그래밍 기타, 데이터베이스</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>DBMS/RDBMS, NoSQL, computer-science</t>
         </is>
       </c>
       <c r="N47" s="7" t="n">
-        <v>353</v>
+        <v>174</v>
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2026-04-27T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2026-08-30T11:26:35.540Z</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/cs-interview-prepara-1</t>
         </is>
       </c>
     </row>
@@ -4099,73 +4099,73 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>블렌더 리부트 베이직: AI와 새로운 UI로 다시 시작하는 블렌더</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ②</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>런타임</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>148500</v>
+        <v>66000</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>148500</v>
+        <v>66000</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>435</v>
+        <v>39</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 디자인 · 아트</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, CAD · 3D 모델링, AI 크리에이티브</t>
+          <t>백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Blender, 콘텐츠 제작, 3d-modeling, 인공지능(AI), ChatGPT, MCP, claude</t>
+          <t>네트워크, Docker, backend, devops, 인공지능(AI), RAG</t>
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>568</v>
+        <v>461</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T08:30:05.000Z</t>
+          <t>2026-09-18T04:30:06.000Z</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:10:44.210Z</t>
+          <t>2026-09-17T22:23:02.274Z</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/blender-reboot-basic</t>
+          <t>https://www.inflearn.com/course/essential-backend-co-1</t>
         </is>
       </c>
     </row>
@@ -4175,35 +4175,35 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
+          <t>김영한의 실전 자바 - 고급 2편, I/O, 네트워크, 리플렉션</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>나도코딩</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="F49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>1933</v>
+        <v>395</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>40228</v>
+        <v>7224</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
@@ -4213,35 +4213,35 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어</t>
+          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java, 네트워크, 객체지향</t>
         </is>
       </c>
       <c r="N49" s="7" t="n">
-        <v>358</v>
+        <v>1296</v>
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>2020-02-24T15:00:00.000Z</t>
+          <t>2024-10-06T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T06:34:34.311Z</t>
+          <t>2025-06-08T10:29:28.205Z</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-고급-2</t>
         </is>
       </c>
     </row>
@@ -4251,73 +4251,73 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
+          <t>베개투자법 완성: 아침이 설레는 AI 주식 완전 자동매매  Claude 바이브코딩</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>김형태</t>
+          <t>치알남 cheatkeyman</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>138600</v>
+        <v>132000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>198000</v>
+        <v>132000</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>487</v>
+        <v>281</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
+          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
+          <t>AI 개발 활용, 데이터 분석, 금융 ·  재테크</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
+          <t>Python, 머신러닝, AWS, FastAPI, 퀀트, cloud-computing, claude</t>
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>483</v>
+        <v>309</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29T02:00:00.000Z</t>
+          <t>2026-05-17T08:30:00.000Z</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T10:39:08.073Z</t>
+          <t>2026-06-29T05:27:04.296Z</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/building-a-marketing</t>
+          <t>https://www.inflearn.com/course/automated-trading-th</t>
         </is>
       </c>
     </row>
@@ -4327,73 +4327,73 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
+          <t>엔지니어를 위한 AI 독해력 [입문편] — AI 논문을 읽을 수 있게</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>Hiro Son</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>44550</v>
+        <v>49500</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>59400</v>
+        <v>198000</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>234</v>
+        <v>25</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
+          <t>취업 · 이직, 자연어 처리, AI 시작하기</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
+          <t>딥러닝, 인공지능(AI), transformer, LLM, RAG, AI Agent, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N51" s="7" t="n">
-        <v>311</v>
+        <v>228</v>
       </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31T10:30:06.000Z</t>
+          <t>2026-10-07T17:30:06.000Z</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12T14:30:32.966Z</t>
+          <t>2026-10-17T14:12:56.231Z</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
+          <t>https://www.inflearn.com/course/ai-reading-comprehen</t>
         </is>
       </c>
     </row>
@@ -4403,73 +4403,73 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ①</t>
+          <t>비전공자도 쉽게 배우는 클로드 디자인</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>해여</t>
+          <t>범쌤</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>66000</v>
+        <v>49500</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>66000</v>
+        <v>49500</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>194</v>
+        <v>368</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 디자인 · 아트, 업무 생산성</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>백엔드, AI 코딩</t>
+          <t>AI 크리에이티브, UX/UI, 생산성 도구</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>네트워크, REST API, DBMS/RDBMS, 동시성, JWT, backend, 인공지능(AI)</t>
+          <t>Figma, terminal, figma-plugin, AI Agent, claude</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>508</v>
+        <v>249</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T02:01:06.000Z</t>
+          <t>2026-06-09T12:00:00.000Z</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T02:24:47.861Z</t>
+          <t>2026-08-12T08:13:15.389Z</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/essential-backend-co</t>
+          <t>https://www.inflearn.com/course/claude-design-for-no</t>
         </is>
       </c>
     </row>
@@ -4479,19 +4479,19 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
+          <t>김영한의 실전 데이터베이스 - 설계 1편, 현대적 데이터 모델링 완전 정복</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>38500</v>
+        <v>99000</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>38500</v>
+        <v>99000</v>
       </c>
       <c r="F53" s="10" t="n">
         <v>0</v>
@@ -4500,14 +4500,14 @@
         <v>5</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>4</v>
+        <v>308</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>67</v>
+        <v>4186</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
@@ -4517,35 +4517,35 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>SQL, Oracle, database, modeling, SQLD</t>
+          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
         </is>
       </c>
       <c r="N53" s="7" t="n">
-        <v>923</v>
+        <v>972</v>
       </c>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02T03:00:00.000Z</t>
+          <t>2025-09-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02T00:00:00.000Z</t>
+          <t>2026-02-09T09:36:10.311Z</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계1편</t>
         </is>
       </c>
     </row>
@@ -4555,73 +4555,73 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>우아한 Rust 중급 (5) - Option &amp; Result</t>
+          <t>채널톡 면접관이 직접 알려주는 CS 면접 대비 - 네트워크 &amp; 웹 편</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>김대현</t>
+          <t>JSCODE 제이온</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>6600</v>
+        <v>77000</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>11000</v>
+        <v>77000</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12</v>
+        <v>266</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 풀스택, 프로그래밍 언어</t>
+          <t>취업 · 이직, 웹 개발, 개발 · 프로그래밍 기타</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>네트워크, websocket, https, dns, computer-science</t>
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:00:07.000Z</t>
+          <t>2026-06-27T10:00:07.000Z</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T02:52:17.360Z</t>
+          <t>2026-08-30T11:26:35.131Z</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/elegant-rust-interme-3</t>
+          <t>https://www.inflearn.com/course/cs-interview-prepara-2</t>
         </is>
       </c>
     </row>
@@ -4631,73 +4631,73 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>하루만에 끝내는 Herdr: 멀티플렉서, 에이전트, SSH 맥미니-모바일 원격 접속</t>
+          <t>[인프런어워드 베스트셀러] 코딩 없이 AI 자동화 전문가가 되는 법, n8n 완벽 가이드</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>주말코딩</t>
+          <t>남박사</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>77000</v>
+        <v>68200</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>77000</v>
+        <v>68200</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>10</v>
+        <v>289</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>124</v>
+        <v>3419</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>개발 도구, AI에이전트 개발, AI 개발 활용</t>
+          <t>AI 시작하기, AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>tmux, claude, codex, terminal, AI Agent, macOS, Git</t>
+          <t>n8n, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N55" s="7" t="n">
-        <v>248</v>
+        <v>1143</v>
       </c>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13T12:00:06.000Z</t>
+          <t>2025-05-06T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27T09:02:14.111Z</t>
+          <t>2026-06-12T11:29:01.075Z</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/herdr-in-one-day-mul</t>
+          <t>https://www.inflearn.com/course/ai-자동화-n8n</t>
         </is>
       </c>
     </row>
@@ -4707,31 +4707,31 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>인프런</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>99</v>
+        <v>1403</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1124</v>
+        <v>34413</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4740,38 +4740,40 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="n"/>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>857</v>
+      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T04:00:06.000Z</t>
+          <t>2019-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T07:01:04.312Z</t>
+          <t>2026-09-18T05:48:10.725Z</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
         </is>
       </c>
     </row>
@@ -4781,31 +4783,31 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Spring 개발자를 위한 실전 LLM 서비스 개발</t>
+          <t>시스코 CCNA 함께 공부해요</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>ccie_pe_kim</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>64900</v>
+        <v>0</v>
       </c>
       <c r="F57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>788</v>
+        <v>1788</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
@@ -4814,40 +4816,40 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>백엔드, AI에이전트 개발, AI 실무 활용</t>
+          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>openai, vector-database, 프롬프트엔지니어링, RAG, Spring AI</t>
+          <t>네트워크, CCNA, routing, tcpip</t>
         </is>
       </c>
       <c r="N57" s="7" t="n">
-        <v>1266</v>
+        <v>1213</v>
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07T05:00:33.000Z</t>
+          <t>2026-01-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T22:16:49.715Z</t>
+          <t>2026-03-25T09:44:13.272Z</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-llm-servic</t>
+          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
         </is>
       </c>
     </row>
@@ -4857,73 +4859,73 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Claude Code로 배우는 AI 개발 워크플로우 완벽 가이드 (실전 프로젝트 포함)</t>
+          <t>자바 ORM 표준 JPA 프로그래밍 - 기본편</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>kimw24072</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>33000</v>
+        <v>121000</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>33000</v>
+        <v>121000</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>13</v>
+        <v>2155</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>91</v>
+        <v>25685</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 프로그래밍 언어, 웹 개발</t>
+          <t>백엔드, 웹 개발, 데이터베이스</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>claude, JavaScript, TypeScript, Next.js, Firebase</t>
+          <t>Java, JPA</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>412</v>
+        <v>963</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28T07:00:00.000Z</t>
+          <t>2019-06-25T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03T22:51:17.474Z</t>
+          <t>2025-04-29T09:40:24.471Z</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pytorch-deep-learnin</t>
+          <t>https://www.inflearn.com/course/ORM-JPA-Basic</t>
         </is>
       </c>
     </row>
@@ -4933,73 +4935,73 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>데이터와사람들과 함께하는 SQLP  자격대비반</t>
+          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>데이터와사람들 서윤식</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>53</v>
+        <v>123282</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 엔지니어링, 개발 도구</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>SQL, DBMS/RDBMS, database-tuning, sqlpp11</t>
+          <t>Java, Spring, MVC, Spring Boot</t>
         </is>
       </c>
       <c r="N59" s="7" t="n">
-        <v>1240</v>
+        <v>321</v>
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T15:00:07.000Z</t>
+          <t>2020-07-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T03:23:49.530Z</t>
+          <t>2026-01-30T11:34:33.353Z</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqlp-certification-p</t>
+          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
         </is>
       </c>
     </row>
@@ -5009,73 +5011,73 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 2편</t>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>66000</v>
+        <v>550000</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>66000</v>
+        <v>550000</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>884</v>
+        <v>85</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11027</v>
+        <v>608</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>임베디드 · IoT, 모빌리티</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
         </is>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1165</v>
+        <v>1017</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2024-05-07T15:00:00.000Z</t>
+          <t>2025-06-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2025-11-24T10:17:13.631Z</t>
+          <t>2026-09-13T09:06:49.556Z</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
         </is>
       </c>
     </row>
@@ -5085,19 +5087,19 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
+          <t>[Codex + Ollama] 온디바이스 바이브코딩: 무료 &amp; 무제한 토큰과 보안까지</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>제어쟁이</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="F61" s="10" t="n">
         <v>0</v>
@@ -5106,52 +5108,50 @@
         <v>4.9</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>606</v>
+        <v>1130</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>하드웨어</t>
+          <t>AI 기술, AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>임베디드 · IoT, 모빌리티</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 코딩</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>임베디드, stm32, hardware, motordriver, artwork</t>
-        </is>
-      </c>
-      <c r="N61" s="7" t="n">
-        <v>1017</v>
-      </c>
+          <t>codex, 인공지능(AI), LLM, 바이브코딩</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="n"/>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>2025-06-15T15:00:00.000Z</t>
+          <t>2026-06-27T04:00:06.000Z</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13T09:06:49.556Z</t>
+          <t>2026-06-30T07:01:04.312Z</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
+          <t>https://www.inflearn.com/course/on-device-vibe-codin</t>
         </is>
       </c>
     </row>
@@ -5161,31 +5161,31 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>스프링 입문 - 코드로 배우는 스프링 부트, 웹 MVC, DB 접근 기술</t>
+          <t>PMP(프로젝트 관리 전문가) 자격 취득과정- PMBOK 8판 기준</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>피엠인사이드</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>123273</v>
+        <v>22</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5194,40 +5194,40 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>기획 · 경영 · 마케팅</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, MVC, Spring Boot</t>
+          <t>프로젝트 관리, PMP</t>
         </is>
       </c>
       <c r="N62" s="2" t="n">
-        <v>321</v>
+        <v>2374</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2020-07-19T15:00:00.000Z</t>
+          <t>2026-10-01T13:00:08.000Z</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T11:34:33.353Z</t>
+          <t>2026-10-16T09:00:13.940Z</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-입문-스프링부트</t>
+          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
         </is>
       </c>
     </row>
@@ -5237,73 +5237,73 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>국내·미국 주식 자동매매 프로그램 만들기 - 컴맹도 따라하는 코덱스 바이브코딩</t>
+          <t>Kaggle Competition Project Practice</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>제조 지능화 전문가</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>198000</v>
+        <v>33000</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>198000</v>
+        <v>110000</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>306</v>
+        <v>2</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 업무 생산성, 커리어 · 자기계발</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스, AI 기술</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, 업무 자동화, 금융 ·  재테크</t>
+          <t>AI 코딩, 데이터 분석, 딥러닝 · 머신러닝</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>api, trading, codex, 바이브코딩</t>
+          <t>Python, 인공지능(AI), 머신러닝, 빅데이터, 데이터 엔지니어링, 문제해결능력, 확률과 통계</t>
         </is>
       </c>
       <c r="N63" s="7" t="n">
-        <v>628</v>
+        <v>1180</v>
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09T01:30:06.000Z</t>
+          <t>2026-10-17T18:00:04.000Z</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T08:59:09.803Z</t>
+          <t>2026-10-17T11:32:25.892Z</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/create-an-automated</t>
+          <t>https://www.inflearn.com/course/kaggle-competition-p</t>
         </is>
       </c>
     </row>
@@ -5313,19 +5313,19 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>시스코 CCNA 함께 공부해요</t>
+          <t>한 입 크기로 잘라 먹는 리액트(React.js) : 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ccie_pe_kim</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>0</v>
@@ -5334,10 +5334,10 @@
         <v>4.9</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>58</v>
+        <v>1565</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1777</v>
+        <v>15634</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5346,40 +5346,40 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 네트워크, 보안 · 네트워크 기타</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>네트워크, CCNA, routing, tcpip</t>
+          <t>JavaScript, React, Node.js</t>
         </is>
       </c>
       <c r="N64" s="2" t="n">
-        <v>1213</v>
+        <v>1114</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T15:00:00.000Z</t>
+          <t>2022-01-26T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25T09:44:13.272Z</t>
+          <t>2026-06-13T00:57:34.805Z</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/시스코-ccna-함께-공부해요</t>
+          <t>https://www.inflearn.com/course/한입-리액트</t>
         </is>
       </c>
     </row>
@@ -5389,19 +5389,19 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
+          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>그랩</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F65" s="10" t="n">
         <v>0</v>
@@ -5410,52 +5410,52 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>188</v>
+        <v>31</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>6188</v>
+        <v>336</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 활용(AX)</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, routing</t>
+          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N65" s="7" t="n">
-        <v>779</v>
+        <v>896</v>
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>2025-01-14T15:00:00.000Z</t>
+          <t>2026-07-23T04:50:00.000Z</t>
         </is>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:27:31.006Z</t>
+          <t>2026-08-01T16:24:39.937Z</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
+          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
         </is>
       </c>
     </row>
@@ -5465,19 +5465,19 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>채널톡 면접관이 직접 알려주는 CS 면접 대비 - 데이터베이스 편</t>
+          <t>파이썬 무료 강의 (기본편) - 6시간 뒤면 나도 개발자</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>JSCODE 제이온</t>
+          <t>나도코딩</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0</v>
@@ -5486,52 +5486,52 @@
         <v>4.9</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>29</v>
+        <v>1934</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>304</v>
+        <v>40232</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>취업 · 이직, 개발 · 프로그래밍 기타, 데이터베이스</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>DBMS/RDBMS, NoSQL, computer-science</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N66" s="2" t="n">
-        <v>174</v>
+        <v>358</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27T05:00:00.000Z</t>
+          <t>2020-02-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:35.540Z</t>
+          <t>2025-04-29T06:34:34.311Z</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cs-interview-prepara-1</t>
+          <t>https://www.inflearn.com/course/나도코딩-파이썬-기본</t>
         </is>
       </c>
     </row>
@@ -5541,73 +5541,73 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>[Chapter 1. 유치원생도 이해하는 파이썬 기초] 설치 없이 시작하는 파이썬 입문</t>
+          <t>React 완벽 마스터: 기초 개념부터 린캔버스 프로젝트까지</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>숀김</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>21</v>
+        <v>965</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>AI 코딩, 프로그래밍 언어, AI 시작하기</t>
+          <t>프론트엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>algorithms, data-structure, functions, ioc, python3</t>
+          <t>React, react-query, react-router, React Context, TailwindCSS</t>
         </is>
       </c>
       <c r="N67" s="7" t="n">
-        <v>121</v>
+        <v>1054</v>
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T03:00:06.000Z</t>
+          <t>2024-09-11T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T00:00:00.000Z</t>
+          <t>2025-09-09T02:15:49.950Z</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/python-basics-even-k</t>
+          <t>https://www.inflearn.com/course/react-완벽가이드-기초-프로젝트</t>
         </is>
       </c>
     </row>
@@ -5617,73 +5617,73 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>실전! 스프링 부트와 JPA 활용2 - API 개발과 성능 최적화</t>
+          <t>처음 시작하는 클로드 코워크 — 사무직을 위한 노코드 업무 자동화</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>Rookiss</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>88000</v>
+        <v>128700</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>88000</v>
+        <v>128700</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1404</v>
+        <v>43</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21972</v>
+        <v>583</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>AI 실무 활용, 오피스, 업무 자동화</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Java, Spring, Spring Boot, JPA</t>
+          <t>업무 생산성, 인공지능(AI), claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N68" s="2" t="n">
-        <v>395</v>
+        <v>832</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2019-10-30T15:00:00.000Z</t>
+          <t>2026-06-05T16:00:00.000Z</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:23:46.889Z</t>
+          <t>2026-08-07T06:36:11.731Z</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링부트-JPA-API개발-성능최적화</t>
+          <t>https://www.inflearn.com/course/starting-with-claude</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>개발자를 위한 컴퓨터공학 1: 혼자 공부하는 컴퓨터구조 + 운영체제</t>
+          <t>노베이스를 위한 ADsP 생존 가이드</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>강민철</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
@@ -5711,13 +5711,13 @@
         <v>0</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>460</v>
+        <v>22</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>21179</v>
+        <v>778</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
@@ -5726,40 +5726,40 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크, 하드웨어, 대학 교육</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제, 컴퓨터 구조, 공학</t>
+          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>컴퓨터 구조, 운영체제, 기술면접</t>
+          <t>SQL, R, ADsP</t>
         </is>
       </c>
       <c r="N69" s="7" t="n">
-        <v>823</v>
+        <v>303</v>
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>2023-03-02T15:00:00.000Z</t>
+          <t>2025-11-11T11:00:00.000Z</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>2025-04-29T09:43:24.787Z</t>
+          <t>2025-11-11T09:14:53.120Z</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/혼자-공부하는-컴퓨터구조-운영체제</t>
+          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
         </is>
       </c>
     </row>
@@ -5769,19 +5769,19 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>스프링 핵심 원리 - 기본편</t>
+          <t>면접 전에 알고 가면 좋을 것들 - 신입 Java 백엔드 개발자편</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>88000</v>
+        <v>66000</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>88000</v>
+        <v>66000</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>0</v>
@@ -5790,10 +5790,10 @@
         <v>5</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>4934</v>
+        <v>69</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>50483</v>
+        <v>1631</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5802,40 +5802,40 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발</t>
+          <t>취업 · 이직, 웹 개발, 백엔드, 풀스택</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Spring, 객체지향</t>
+          <t>기술면접, 이력서, DBMS/RDBMS, tcpip</t>
         </is>
       </c>
       <c r="N70" s="2" t="n">
-        <v>725</v>
+        <v>306</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2020-09-20T15:00:00.000Z</t>
+          <t>2023-08-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2025-06-04T15:00:00.555Z</t>
+          <t>2025-05-13T07:42:51.608Z</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/스프링-핵심-원리-기본편</t>
+          <t>https://www.inflearn.com/course/면접-신입-java-백앤드-개발자</t>
         </is>
       </c>
     </row>
@@ -5845,31 +5845,31 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>리눅스 입문 - 개념으로 탄탄히!!</t>
+          <t>실리콘밸리 AI 개발자의 LLM 서비스를 위한 RAG</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>런잇(ProgCoach4U)</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>77000</v>
+        <v>123750</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>77000</v>
+        <v>165000</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>301</v>
+        <v>14</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>3495</v>
+        <v>687</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
@@ -5878,40 +5878,40 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>시스템 · 운영체제, 데브옵스 · 인프라</t>
+          <t>AI 시작하기, 백엔드, AI 실무 활용</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>JavaScript, Python, 인공지능(AI), ChatGPT, RAG</t>
         </is>
       </c>
       <c r="N71" s="7" t="n">
-        <v>757</v>
+        <v>531</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>2021-06-02T15:00:00.000Z</t>
+          <t>2026-08-14T08:00:08.000Z</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>2025-05-13T07:44:10.964Z</t>
+          <t>2026-10-02T00:24:12.168Z</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/리눅스-입문</t>
+          <t>https://www.inflearn.com/course/mastering-rag-as-tau</t>
         </is>
       </c>
     </row>
@@ -5921,73 +5921,73 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>모든 개발자를 위한 HTTP 웹 기본 지식</t>
+          <t>맥북 처음 샀을 때 꼭 해야 할 세팅 A to Z (Claude Code · OpenClaw · Hermes Agent  | macOS 올인원)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>44000</v>
+        <v>67100</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>44000</v>
+        <v>67100</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>4071</v>
+        <v>32</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>37235</v>
+        <v>475</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>웹 개발, 네트워크, 개발 · 프로그래밍 기타</t>
+          <t>AI 실무 활용, 개발 도구, AI 코딩</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>macOS, homebrew, 인공지능(AI), AI Agent, claude</t>
         </is>
       </c>
       <c r="N72" s="2" t="n">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2020-12-19T15:00:00.000Z</t>
+          <t>2026-03-11T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2025-05-13T07:23:13.295Z</t>
+          <t>2026-06-24T14:33:58.313Z</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/http-웹-네트워크</t>
+          <t>https://www.inflearn.com/course/all-in-one-macbook-s</t>
         </is>
       </c>
     </row>
@@ -5997,73 +5997,73 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>초당 1,000,000++ RPS를 처리하는 네이버 개발자의 Valkey</t>
+          <t>2026 최신 Codex 완전 정복 : 기초부터 에이전틱 개발 자동화까지</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>YoungJea Oh</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>56760</v>
+        <v>99000</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>141900</v>
+        <v>99000</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>146</v>
+        <v>33</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 알고리즘 · 자료구조, 데이터베이스</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>JavaScript, 빅데이터, TypeScript, DBMS/RDBMS, Redis, MSA, 데이터 엔지니어링</t>
+          <t>Python, codex, 인공지능(AI), ChatGPT, AI Agent, 바이브코딩</t>
         </is>
       </c>
       <c r="N73" s="7" t="n">
-        <v>422</v>
+        <v>370</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22T11:00:07.000Z</t>
+          <t>2026-10-02T10:00:08.000Z</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29T21:47:01.350Z</t>
+          <t>2026-10-02T07:55:47.247Z</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/valkey-vs-redis-a-na</t>
+          <t>https://www.inflearn.com/course/mastering-the-latest</t>
         </is>
       </c>
     </row>
@@ -6073,31 +6073,31 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>진짜 바이브코딩 올인원 클래스: Claude Code 기초부터 런칭, 운영, 에이전트 자동화까지</t>
+          <t>정보처리기사 자격증 대비 교육(실기)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>그랩</t>
+          <t>국립안동대학교 SW융합교육원</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>335</v>
+        <v>2248</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6106,40 +6106,40 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI 개발 활용, AI 시작하기</t>
+          <t>개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, Next.js, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
+          <t>정보처리기사</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>896</v>
+        <v>1532</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T04:50:00.000Z</t>
+          <t>2024-08-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T16:24:39.937Z</t>
+          <t>2024-08-14T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-올인원-클래스-claudecode</t>
+          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
         </is>
       </c>
     </row>
@@ -6149,31 +6149,31 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>채널톡 면접관이 직접 알려주는 CS 면접 대비 - 네트워크 &amp; 웹 편</t>
+          <t>[백문이불여일타] 데이터 분석을 위한 중급 SQL</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 제이온</t>
+          <t>데이터리안</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>77000</v>
+        <v>38500</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>77000</v>
+        <v>38500</v>
       </c>
       <c r="F75" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>21</v>
+        <v>997</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>265</v>
+        <v>5707</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
@@ -6182,40 +6182,40 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>취업 · 이직, 웹 개발, 개발 · 프로그래밍 기타</t>
+          <t>데이터 분석, 데이터베이스</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>네트워크, websocket, https, dns, computer-science</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="N75" s="7" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-27T10:00:07.000Z</t>
+          <t>2020-02-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:35.131Z</t>
+          <t>2025-11-27T07:45:36.152Z</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cs-interview-prepara-2</t>
+          <t>https://www.inflearn.com/course/데이터-분석-중급-sql</t>
         </is>
       </c>
     </row>
@@ -6225,31 +6225,31 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>비전공자도 쉽게 배우는 클로드 디자인</t>
+          <t>개발자를 위한 컴퓨터공학 2: 혼자 공부하는 네트워크</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>범쌤</t>
+          <t>강민철</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>33</v>
+        <v>188</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>366</v>
+        <v>6192</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6258,40 +6258,40 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 디자인 · 아트, 업무 생산성</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>AI 크리에이티브, UX/UI, 생산성 도구</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Figma, terminal, figma-plugin, AI Agent, claude</t>
+          <t>네트워크, tcpip, routing</t>
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>249</v>
+        <v>779</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T12:00:00.000Z</t>
+          <t>2025-01-14T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T08:13:15.389Z</t>
+          <t>2025-04-29T09:27:31.006Z</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-design-for-no</t>
+          <t>https://www.inflearn.com/course/개발자-컴퓨터공학-혼자공부하는-네트워크</t>
         </is>
       </c>
     </row>
@@ -6301,73 +6301,73 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>조회수 터지는 AI 강아지 영상만들기</t>
+          <t>[Next 바이브코딩] 3단계: 지침·Skills·Hooks·MCP로 AI가 일하기 좋은 개발 시스템 만들기</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>마이업AI</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 커리어 · 자기계발</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>AI 크리에이티브, AI 시작하기, 창업 · 부업</t>
+          <t>AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), gemini, gpt, 영상제작, AI 영상, AI 이미지</t>
+          <t>codex, claude, AI Agent, 인공지능(AI), MCP, Git</t>
         </is>
       </c>
       <c r="N77" s="7" t="n">
-        <v>10</v>
+        <v>304</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T08:00:07.000Z</t>
+          <t>2026-09-20T13:00:06.000Z</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14T05:45:43.069Z</t>
+          <t>2026-10-17T09:27:01.129Z</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/creating-ai-dog-vide</t>
+          <t>https://www.inflearn.com/course/next-vibe-coding-sta</t>
         </is>
       </c>
     </row>
@@ -6377,31 +6377,31 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>트래픽 급증을 견디는 서버 시스템 설계 - Coupon 발급 서비스</t>
+          <t>실리콘밸리 엔지니어와 함께하는 OpenRouter</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>한조각</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>41250</v>
+        <v>33000</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>55000</v>
+        <v>66000</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>813</v>
+        <v>271</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6410,40 +6410,40 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데이터베이스</t>
+          <t>AI에이전트 개발, AI 실무 활용, AI 개발 활용</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Java, Kotlin, MySQL, Docker, Spring Boot, Kafka, Redis</t>
+          <t>Python, LLM, AI Agent, claude</t>
         </is>
       </c>
       <c r="N78" s="2" t="n">
-        <v>618</v>
+        <v>305</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09T17:00:05.000Z</t>
+          <t>2026-09-23T06:30:05.000Z</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T15:21:43.118Z</t>
+          <t>2026-09-26T17:31:06.856Z</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/designing-a-server-s</t>
+          <t>https://www.inflearn.com/course/openrouter-with-a-si</t>
         </is>
       </c>
     </row>
@@ -6453,19 +6453,19 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>비개발자 직장인을 위한 Claude (Cowork + N8N + Claude Design)</t>
+          <t>나만의 Claude Code  하네스 (SPEC·TDD·CI로 짓는 AI 개발 워크플로우)</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>딩코딩코</t>
+          <t>프롱트</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>165000</v>
+        <v>66000</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>165000</v>
+        <v>66000</v>
       </c>
       <c r="F79" s="10" t="n">
         <v>0</v>
@@ -6474,52 +6474,52 @@
         <v>4.8</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화</t>
+          <t>AI에이전트 개발, 웹 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>claude, 인공지능(AI), AI Agent, n8n</t>
+          <t>React, TDD, AI Agent, claude, 하네스</t>
         </is>
       </c>
       <c r="N79" s="7" t="n">
-        <v>694</v>
+        <v>438</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>2026-04-26T02:30:00.000Z</t>
+          <t>2026-05-06T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24T14:36:39.327Z</t>
+          <t>2026-05-21T16:24:41.523Z</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-for-non-devel</t>
+          <t>https://www.inflearn.com/course/my-own-claude-code-h</t>
         </is>
       </c>
     </row>
@@ -6529,73 +6529,73 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>옵시디언 마스터 클래스: PKM·AI Second Brain·LLM WiKi 기초부터 실전까지</t>
+          <t>밑바닥부터 만드는 AI 에이전트 — RAG · 멀티 에이전트 · MCP</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>조영수(데이먼)</t>
+          <t>단테</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>132000</v>
+        <v>44000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>132000</v>
+        <v>88000</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1139</v>
+        <v>10</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, 기획 · 경영 · 마케팅, AI 활용(AX)</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>생산성 도구, 기획 · PM· PO, AI 실무 활용</t>
+          <t>AI에이전트 개발, 백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>업무 생산성, obsidian</t>
+          <t>Python, FastAPI, LLM, openAI API, AI Agent</t>
         </is>
       </c>
       <c r="N80" s="2" t="n">
-        <v>455</v>
+        <v>317</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2025-06-25T12:30:00.000Z</t>
+          <t>2026-10-05T18:00:08.000Z</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08T00:00:00.000Z</t>
+          <t>2026-10-18T21:51:13.562Z</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/옵시디언-마스터-클래스생산성을-바꾸는-1</t>
+          <t>https://www.inflearn.com/course/introduction-to-buil-2</t>
         </is>
       </c>
     </row>
@@ -6605,22 +6605,22 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>밑바닥부터 만드는 AI 에이전트 — RAG · 멀티 에이전트 · MCP</t>
+          <t>AI로 코드 짤 때 꼭 알아야 할 백엔드 개념 ①</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>단테</t>
+          <t>해여</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>88000</v>
+        <v>66000</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>8</v>
+        <v>194</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
@@ -6638,40 +6638,40 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 백엔드, AI 코딩</t>
+          <t>백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>Python, FastAPI, LLM, openAI API, AI Agent</t>
+          <t>네트워크, REST API, DBMS/RDBMS, 동시성, JWT, backend, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N81" s="7" t="n">
-        <v>317</v>
+        <v>508</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05T18:00:08.000Z</t>
+          <t>2026-09-17T02:01:06.000Z</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T04:36:20.813Z</t>
+          <t>2026-10-18T02:24:47.861Z</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/introduction-to-buil-2</t>
+          <t>https://www.inflearn.com/course/essential-backend-co</t>
         </is>
       </c>
     </row>
@@ -6681,19 +6681,19 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>개발자 개념 장착 - 프로그래밍 개발에 필요한 필수 개념과 핵심 이론정리</t>
+          <t>Claude로 시작하는 AI 실무 활용 입문</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>코딩하는기술사</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0</v>
@@ -6702,10 +6702,10 @@
         <v>4.9</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1651</v>
+        <v>430</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6714,38 +6714,40 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 기타, 웹 개발, 백엔드</t>
+          <t>AI 실무 활용, AI 코딩, AI 시작하기</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>아키텍처, 컴퓨터 구조, 기술면접, 소프트웨어 설계, 문제해결능력</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="n"/>
+          <t>인공지능(AI), claude, LLM, 바이브코딩, AX(에이전트 경험)</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>161</v>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2026-01-19T13:00:00.000Z</t>
+          <t>2026-09-22T09:30:06.000Z</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30T22:11:57.790Z</t>
+          <t>2026-09-22T05:01:00.947Z</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/개발자-개념-장착-프로그래밍-개발에</t>
+          <t>https://www.inflearn.com/course/introduction-to-prac-2</t>
         </is>
       </c>
     </row>
@@ -6755,31 +6757,31 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>피그마(Figma)를 활용한 UI디자인 입문부터 실전까지 A to Z</t>
+          <t>클로드 코드로 알잘딱깔센 성과내는 마케팅 OS 시스템 구축하기</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>에릭</t>
+          <t>김형태</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>82500</v>
+        <v>138600</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>82500</v>
+        <v>198000</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>518</v>
+        <v>32</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>3679</v>
+        <v>487</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
@@ -6788,40 +6790,40 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>디자인 · 아트</t>
+          <t>AI 활용(AX), 기획 · 경영 · 마케팅, AI 기술</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>UX/UI, 그래픽 디자인</t>
+          <t>AI 실무 활용, 마케팅, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>Figma, 웹 디자인, 모바일 디자인, 프로덕트디자인</t>
+          <t>콘텐츠 마케팅, 디지털 마케팅, AI Agent, claude, AX(에이전트 경험)</t>
         </is>
       </c>
       <c r="N83" s="7" t="n">
-        <v>545</v>
+        <v>483</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>2020-11-04T15:00:00.000Z</t>
+          <t>2026-05-29T02:00:00.000Z</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>2026-05-04T11:22:20.563Z</t>
+          <t>2026-09-26T10:39:08.073Z</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/피그마-ui디자인</t>
+          <t>https://www.inflearn.com/course/building-a-marketing</t>
         </is>
       </c>
     </row>
@@ -6831,73 +6833,73 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>실전! 언리얼 소울라이크 개발: A to Z</t>
+          <t>30년 차 DBA에게 배우는 SQLD 1·2과목 올인원 : 왕초보 합격 코스</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Spector</t>
+          <t>데이터와사람들 서윤식</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>176000</v>
+        <v>38500</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>176000</v>
+        <v>38500</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>254</v>
+        <v>66</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>게임 개발</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>게임 프로그래밍</t>
+          <t>데이터베이스, 데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Unreal Engine, 언리얼 C++, C++</t>
+          <t>SQL, Oracle, database, modeling, SQLD</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1189</v>
+        <v>923</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2025-04-28T15:00:00.000Z</t>
+          <t>2026-09-02T03:00:00.000Z</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28T07:29:59.986Z</t>
+          <t>2026-09-02T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/언리얼-소울라이크-개발</t>
+          <t>https://www.inflearn.com/course/complete-beginner-ta</t>
         </is>
       </c>
     </row>
@@ -6907,73 +6909,73 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>&lt;케라스 창시자에게 배우는 딥러닝 3판&gt; 예제 코드 해설</t>
+          <t>실리콘 밸리 엔지니어와 함께하는 Local LLM 완전 정복 (LM Studio &amp; Ollama &amp; Ollaya)</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>박해선</t>
+          <t>미쿡엔지니어</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>69300</v>
+        <v>55000</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>99000</v>
+        <v>55000</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>48</v>
+        <v>692</v>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>딥러닝 · 머신러닝, 컴퓨터 비전, 자연어 처리</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 시작하기</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>딥러닝, Keras, Tensorflow, Stable Diffusion, LLM</t>
+          <t>인공지능(AI), LLM, AI Agent</t>
         </is>
       </c>
       <c r="N85" s="7" t="n">
-        <v>73</v>
+        <v>270</v>
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08T11:00:10.000Z</t>
+          <t>2026-04-17T18:00:00.000Z</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T17:09:46.044Z</t>
+          <t>2026-10-01T05:15:20.298Z</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/explanation-of-the-e</t>
+          <t>https://www.inflearn.com/course/mastering-local-llm</t>
         </is>
       </c>
     </row>
@@ -6983,73 +6985,73 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>대세는 바이브 코딩 : 클로드 코드와 TDD로 완성하는 AI 풀스택 개발</t>
+          <t>블렌더 리부트 베이직: AI와 새로운 UI로 다시 시작하는 블렌더</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Masocampus</t>
+          <t>런타임</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>89100</v>
+        <v>148500</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>89100</v>
+        <v>148500</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>96</v>
+        <v>436</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), 디자인 · 아트</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, 웹 개발, AI 코딩</t>
+          <t>AI 실무 활용, CAD · 3D 모델링, AI 크리에이티브</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>웹앱, TDD, 인공지능(AI), claude, 바이브코딩</t>
+          <t>Blender, 콘텐츠 제작, 3d-modeling, 인공지능(AI), ChatGPT, MCP, claude</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>345</v>
+        <v>568</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16T09:30:00.000Z</t>
+          <t>2026-07-20T08:30:05.000Z</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16T07:04:40.971Z</t>
+          <t>2026-10-12T15:10:44.210Z</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/the-trend-is-vibe-co-1</t>
+          <t>https://www.inflearn.com/course/blender-reboot-basic</t>
         </is>
       </c>
     </row>
@@ -7059,31 +7061,31 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>정보처리기사 자격증 대비 교육(실기)</t>
+          <t>제대로 파는 자바스크립트(JavaScript) - by 얄코</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>국립안동대학교 SW융합교육원</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="F87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>56</v>
+        <v>165</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>2241</v>
+        <v>3107</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
@@ -7097,35 +7099,35 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증</t>
+          <t>프로그래밍 언어, 웹 개발</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>정보처리기사</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N87" s="7" t="n">
-        <v>1532</v>
+        <v>762</v>
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>2024-08-13T15:00:00.000Z</t>
+          <t>2022-11-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>2024-08-14T00:00:00.000Z</t>
+          <t>2026-05-27T00:32:23.339Z</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/정보처리기사-자격증-대비교육-실기</t>
+          <t>https://www.inflearn.com/course/제대로-파는-자바스크립트</t>
         </is>
       </c>
     </row>
@@ -7135,73 +7137,73 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>PMP(프로젝트 관리 전문가) 자격 취득과정- PMBOK 8판 기준</t>
+          <t>2026 벼락치기 합격! 기출문제 집중 정보처리기사 실기</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>피엠인사이드</t>
+          <t>멍슨상</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>330000</v>
+        <v>36300</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>330000</v>
+        <v>48400</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>20</v>
+        <v>319</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>기획 · 경영 · 마케팅</t>
+          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>경영 · 전략, 기획 · PM· PO, 기획 · 경영 · 마케팅 자격증</t>
+          <t>개발 · 프로그래밍 자격증, 개발 · 프로그래밍 기타, 커리어 · 자기계발 기타</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>프로젝트 관리, PMP</t>
+          <t>Python, Java, C, 정보처리기사, database</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>2374</v>
+        <v>1553</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T13:00:08.000Z</t>
+          <t>2025-09-24T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T09:00:13.940Z</t>
+          <t>2026-10-11T06:06:52.494Z</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/pmp-project-manageme</t>
+          <t>https://www.inflearn.com/course/벼락치기-합격-기출문제-집중-정보처리</t>
         </is>
       </c>
     </row>
@@ -7211,73 +7213,73 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>나만의 Claude Code  하네스 (SPEC·TDD·CI로 짓는 AI 개발 워크플로우)</t>
+          <t>하루만에 끝내는 Herdr: 멀티플렉서, 에이전트, SSH 맥미니-모바일 원격 접속</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>프롱트</t>
+          <t>주말코딩</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="F89" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>577</v>
+        <v>125</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 웹 개발, AI 개발 활용</t>
+          <t>개발 도구, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>React, TDD, AI Agent, claude, 하네스</t>
+          <t>tmux, claude, codex, terminal, AI Agent, macOS, Git</t>
         </is>
       </c>
       <c r="N89" s="7" t="n">
-        <v>438</v>
+        <v>248</v>
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06T09:00:00.000Z</t>
+          <t>2026-09-13T12:00:06.000Z</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21T16:24:41.523Z</t>
+          <t>2026-09-27T09:02:14.111Z</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/my-own-claude-code-h</t>
+          <t>https://www.inflearn.com/course/herdr-in-one-day-mul</t>
         </is>
       </c>
     </row>
@@ -7287,73 +7289,73 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>대세는 쿠버네티스 (초급~중급편)</t>
+          <t>초당 1,000,000++ RPS를 처리하는 네이버 개발자의 Valkey</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>44000</v>
+        <v>56760</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>44000</v>
+        <v>141900</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>626</v>
+        <v>6</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8500</v>
+        <v>147</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 풀스택, 시스템 · 운영체제</t>
+          <t>백엔드, 알고리즘 · 자료구조, 데이터베이스</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, devops, container, infrastructure-as-a-code</t>
+          <t>JavaScript, 빅데이터, TypeScript, DBMS/RDBMS, Redis, MSA, 데이터 엔지니어링</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2019-09-10T15:00:00.000Z</t>
+          <t>2026-09-22T11:00:07.000Z</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2025-11-19T05:23:15.024Z</t>
+          <t>2026-08-29T21:47:01.350Z</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/쿠버네티스-기초</t>
+          <t>https://www.inflearn.com/course/valkey-vs-redis-a-na</t>
         </is>
       </c>
     </row>
@@ -7363,73 +7365,73 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>38군데 합격 비법, 2026 코딩테스트 필수 알고리즘</t>
+          <t>AI 에이전트 엔지니어링</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>딩코딩코</t>
+          <t>민혁</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="F91" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>453</v>
+        <v>39</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>2888</v>
+        <v>2080</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 커리어 · 자기계발</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>알고리즘 · 자료구조, 취업 · 이직</t>
+          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>Python, 코딩 테스트, 알고리즘, data-structure</t>
+          <t>Python, 인공지능(AI), RAG, AI Agent</t>
         </is>
       </c>
       <c r="N91" s="7" t="n">
-        <v>934</v>
+        <v>322</v>
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>2024-11-12T15:00:00.000Z</t>
+          <t>2026-04-07T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10T05:18:11.523Z</t>
+          <t>2026-04-07T02:58:08.781Z</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/38군데-합격비법-코테-필수-알고리즘</t>
+          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7441,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>[리뉴얼] 파이썬입문과 크롤링기초 부트캠프 [파이썬, 웹, 데이터 이해 기본까지] (업데이트)</t>
+          <t>자바(Java) 알고리즘 문제풀이 입문: 코딩테스트 대비</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>잔재미코딩 DaveLee</t>
+          <t>김태원</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
@@ -7457,13 +7459,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>739</v>
+        <v>372</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>7615</v>
+        <v>8298</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7472,40 +7474,40 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>데이터 분석, 프로그래밍 언어</t>
+          <t>알고리즘 · 자료구조, 프로그래밍 언어</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Python, 웹 크롤링</t>
+          <t>Java, 코딩 테스트</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>991</v>
+        <v>1348</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2019-06-05T15:00:00.000Z</t>
+          <t>2021-03-24T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T04:37:56.211Z</t>
+          <t>2025-05-13T07:32:20.151Z</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/python-crawling-basic</t>
+          <t>https://www.inflearn.com/course/자바-알고리즘-문제풀이-코테대비</t>
         </is>
       </c>
     </row>
@@ -7515,31 +7517,31 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>노베이스를 위한 ADsP 생존 가이드</t>
+          <t>곰책으로 쉽게 배우는 최소한의 운영체제론</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="F93" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>772</v>
+        <v>2754</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
@@ -7548,40 +7550,40 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 데이터 사이언스 자격증, 데이터 사이언스 기타</t>
+          <t>개발 · 프로그래밍 기타, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>SQL, R, ADsP</t>
+          <t>운영체제</t>
         </is>
       </c>
       <c r="N93" s="7" t="n">
-        <v>303</v>
+        <v>449</v>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T11:00:00.000Z</t>
+          <t>2022-11-02T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>2025-11-11T09:14:53.120Z</t>
+          <t>2025-05-13T07:42:42.712Z</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/노베이스를-위한-adsp-생존-가이드</t>
+          <t>https://www.inflearn.com/course/곰책-쉽게-배우는-운영체제</t>
         </is>
       </c>
     </row>
@@ -7591,31 +7593,31 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기로 잘라먹는 타입스크립트(TypeScript)</t>
+          <t>기출로 대비하는 개발자 전공면접 [CS 완전정복]</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>이정환 Winterlood</t>
+          <t>개발남노씨</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>48400</v>
+        <v>165000</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>48400</v>
+        <v>165000</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>783</v>
+        <v>114</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14566</v>
+        <v>2237</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7624,40 +7626,40 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 프론트엔드</t>
+          <t>취업 · 이직, 개발 · 프로그래밍 기타, 알고리즘 · 자료구조</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>면접, 기술면접, 운영체제</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>632</v>
+        <v>370</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>2023-05-21T15:00:00.000Z</t>
+          <t>2022-03-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16T00:41:51.879Z</t>
+          <t>2025-05-13T07:50:45.128Z</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/한입-크기-타입스크립트</t>
+          <t>https://www.inflearn.com/course/개발자-전공면접-cs-완전정복</t>
         </is>
       </c>
     </row>
@@ -7667,73 +7669,73 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Claude Code로 만드는 1인 개발자 자동화 시스템 - Sidabari 프로젝트</t>
+          <t>AI로 만드는 KR/US 퀀트 트레이딩 노드 분석 시스템 (바이브코딩)</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>호두감자</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>187000</v>
+        <v>385000</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>187000</v>
+        <v>385000</v>
       </c>
       <c r="F95" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>465</v>
+        <v>65</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>AI 활용(AX), 데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, AI 실무 활용, AI 코딩</t>
+          <t>AI 실무 활용, 데이터 분석, AI 코딩</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>devops, tauri, 프롬프트엔지니어링, claude, 바이브코딩</t>
+          <t>투자, 퀀트, router, n8n, 백테스팅, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N95" s="7" t="n">
-        <v>598</v>
+        <v>188</v>
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15T08:30:00.000Z</t>
+          <t>2026-06-15T12:00:00.000Z</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21T02:16:22.604Z</t>
+          <t>2026-10-15T13:52:36.162Z</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/solo-developer-autom</t>
+          <t>https://www.inflearn.com/course/ai-powered-krus-quan</t>
         </is>
       </c>
     </row>
@@ -7743,31 +7745,31 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>AI 에이전트 엔지니어링</t>
+          <t>실전! 스프링 부트와 JPA 활용2 - API 개발과 성능 최적화</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>민혁</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>39</v>
+        <v>1405</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2077</v>
+        <v>21973</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7776,40 +7778,40 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용, AI 실무 활용</t>
+          <t>백엔드, 웹 개발</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Python, 인공지능(AI), RAG, AI Agent</t>
+          <t>Java, Spring, Spring Boot, JPA</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>322</v>
+        <v>395</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07T05:00:00.000Z</t>
+          <t>2019-10-30T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07T02:58:08.781Z</t>
+          <t>2025-05-13T07:23:46.889Z</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-agent-engineering</t>
+          <t>https://www.inflearn.com/course/스프링부트-JPA-API개발-성능최적화</t>
         </is>
       </c>
     </row>
@@ -7819,31 +7821,31 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>AI 에이전트로 구현하는 RAG 시스템(w. LangGraph)</t>
+          <t>채널톡 면접관이 직접 알려주는 CS 면접 대비 - 운영체제 편</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>판다스 스튜디오</t>
+          <t>JSCODE 제이온</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
       <c r="F97" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>172</v>
+        <v>12</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>8047</v>
+        <v>193</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
@@ -7852,40 +7854,40 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>커리어 · 자기계발, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발</t>
+          <t>취업 · 이직, 개발 · 프로그래밍 기타, 백엔드</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>AI Agent, LangGraph, RAG, LLM, LangChain</t>
+          <t>운영체제, 동시성, memory-management, cpu, computer-science</t>
         </is>
       </c>
       <c r="N97" s="7" t="n">
-        <v>405</v>
+        <v>187</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>2024-10-22T15:00:00.000Z</t>
+          <t>2026-08-23T07:00:34.000Z</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>2026-03-04T03:56:05.522Z</t>
+          <t>2026-08-30T11:25:15.161Z</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai에이전트-구현-rag시스템-랭그래프</t>
+          <t>https://www.inflearn.com/course/cs-interview-prepara-3</t>
         </is>
       </c>
     </row>
@@ -7895,19 +7897,19 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
+          <t>조회수 터지는 AI 강아지 영상만들기</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>nstyxn</t>
+          <t>마이업AI</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>118800</v>
+        <v>0</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>118800</v>
+        <v>0</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>0</v>
@@ -7916,10 +7918,10 @@
         <v>5</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>960</v>
+        <v>26</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7928,40 +7930,40 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크</t>
+          <t>AI 활용(AX), 커리어 · 자기계발</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>보안, 보안 · 네트워크 자격증</t>
+          <t>AI 크리에이티브, AI 시작하기, 창업 · 부업</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Forensic, 디지털포렌식전문가 2급</t>
+          <t>인공지능(AI), gemini, gpt, 영상제작, AI 영상, AI 이미지</t>
         </is>
       </c>
       <c r="N98" s="2" t="n">
-        <v>6530</v>
+        <v>10</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>2022-11-13T15:00:00.000Z</t>
+          <t>2026-10-14T08:00:07.000Z</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T02:00:30.898Z</t>
+          <t>2026-10-14T05:45:43.069Z</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
+          <t>https://www.inflearn.com/course/creating-ai-dog-vide</t>
         </is>
       </c>
     </row>
@@ -7971,19 +7973,19 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>Docker가 쉬워지는 운영체제 이야기</t>
+          <t>AWS Certified Solutions Architect - Associate 자격증 준비하기</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>코드바나나</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>88000</v>
+        <v>148500</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>88000</v>
+        <v>148500</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>0</v>
@@ -7992,10 +7994,10 @@
         <v>4.9</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>46</v>
+        <v>320</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>951</v>
+        <v>3757</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
@@ -8009,35 +8011,35 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 시스템 · 운영체제, 클라우드</t>
+          <t>데브옵스 · 인프라, 보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>네트워크, Linux, Docker, 운영체제, linux-containers, cloud-computing</t>
+          <t>AWS, 네트워크, AWS SAA</t>
         </is>
       </c>
       <c r="N99" s="7" t="n">
-        <v>723</v>
+        <v>1450</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30T04:00:57.000Z</t>
+          <t>2022-06-21T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04T00:38:47.888Z</t>
+          <t>2026-10-12T03:07:28.063Z</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/operating-system-sto</t>
+          <t>https://www.inflearn.com/course/aws-자격증-어소시에이트</t>
         </is>
       </c>
     </row>
@@ -8047,31 +8049,31 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 설계 1편, 현대적 데이터 모델링 완전 정복</t>
+          <t>실무자를 위한 구글애널리틱스(GA4+GTM) 활용법(26년 Update)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>GA4 Guide</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>99000</v>
+        <v>173800</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>99000</v>
+        <v>173800</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>308</v>
+        <v>88</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>4184</v>
+        <v>1361</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -8080,40 +8082,40 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>기획 · 경영 · 마케팅, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>마케팅, 데이터 분석</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
+          <t>Google Analytics, Google Tag Manager, 데이터 리터러시, GA4</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>972</v>
+        <v>1440</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>2025-09-15T15:00:00.000Z</t>
+          <t>2023-06-20T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09T09:36:10.311Z</t>
+          <t>2026-09-15T07:09:42.889Z</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계1편</t>
+          <t>https://www.inflearn.com/course/실무자-ga4-활용법</t>
         </is>
       </c>
     </row>
@@ -8123,19 +8125,19 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>LangGraph를 활용한 AI Agent 개발 (feat. MCP)</t>
+          <t>개발자 개념 장착 - 프로그래밍 개발에 필요한 필수 개념과 핵심 이론정리</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>제이쓴</t>
+          <t>코딩하는기술사</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>0</v>
@@ -8144,52 +8146,50 @@
         <v>4.9</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>263</v>
+        <v>31</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>2967</v>
+        <v>1656</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발</t>
+          <t>개발 · 프로그래밍 기타, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>프롬프트엔지니어링, LLM, AI Agent, LangGraph, MCP</t>
-        </is>
-      </c>
-      <c r="N101" s="7" t="n">
-        <v>381</v>
-      </c>
+          <t>아키텍처, 컴퓨터 구조, 기술면접, 소프트웨어 설계, 문제해결능력</t>
+        </is>
+      </c>
+      <c r="N101" s="7" t="n"/>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>2025-01-19T15:00:00.000Z</t>
+          <t>2026-01-19T13:00:00.000Z</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23T10:57:36.230Z</t>
+          <t>2026-01-30T22:11:57.790Z</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/랭그래프-활용한-llm에이전트-개발</t>
+          <t>https://www.inflearn.com/course/개발자-개념-장착-프로그래밍-개발에</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-18T13:36:38+09:00</t>
+          <t>2026-10-19T13:43:08+09:00</t>
         </is>
       </c>
     </row>

--- a/inflearn/output/inflearn_main_latest.xlsx
+++ b/inflearn/output/inflearn_main_latest.xlsx
@@ -626,10 +626,10 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -681,73 +681,73 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Spring AI LLM 비용 모니터링 — Actuator 한 줄로 만드는 토큰 대시보드</t>
+          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>짐코딩</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="F3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>0</v>
+        <v>1667</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>323</v>
+        <v>11385</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, AI에이전트 개발</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>Spring AI, Prometheus, grafana, spring-boot-actuator, 인공지능(AI), Spring Boot, IntelliJ IDEA</t>
+          <t>React, 인공지능(AI), claude</t>
         </is>
       </c>
       <c r="N3" s="7" t="n">
-        <v>73</v>
+        <v>1254</v>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T23:30:05.000Z</t>
+          <t>2025-11-19T09:00:00.000Z</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13T22:06:45.263Z</t>
+          <t>2026-08-18T03:54:49.011Z</t>
         </is>
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/spring-ai-llm-cost-m</t>
+          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
         </is>
       </c>
     </row>
@@ -757,19 +757,19 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>클로드 코드 완벽 마스터: AI 개발 워크플로우 기초부터 실전까지</t>
+          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>짐코딩</t>
+          <t>퇴근후딴짓</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>198000</v>
+        <v>121000</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>198000</v>
+        <v>121000</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>4.9</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1664</v>
+        <v>932</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11361</v>
+        <v>6061</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -790,40 +790,40 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
+          <t>데이터 사이언스</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
+          <t>데이터 사이언스 자격증, 데이터 분석</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>React, 인공지능(AI), claude</t>
+          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1254</v>
+        <v>1618</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2025-11-19T09:00:00.000Z</t>
+          <t>2022-12-12T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T03:54:49.011Z</t>
+          <t>2026-10-18T16:36:18.265Z</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/클로드-코드-완벽-마스터-ai-개발</t>
+          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
         </is>
       </c>
     </row>
@@ -833,73 +833,73 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
+          <t>Spring AI LLM 비용 모니터링 — Actuator 한 줄로 만드는 토큰 대시보드</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>108900</v>
+        <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>271</v>
+        <v>356</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화</t>
+          <t>AI 개발 활용, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
+          <t>Spring AI, Prometheus, grafana, spring-boot-actuator, 인공지능(AI), Spring Boot, IntelliJ IDEA</t>
         </is>
       </c>
       <c r="N5" s="7" t="n">
-        <v>182</v>
+        <v>73</v>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04T09:30:05.000Z</t>
+          <t>2026-10-13T23:30:05.000Z</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T04:41:50.010Z</t>
+          <t>2026-10-13T22:06:45.263Z</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
+          <t>https://www.inflearn.com/course/spring-ai-llm-cost-m</t>
         </is>
       </c>
     </row>
@@ -909,31 +909,31 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>[퇴근후딴짓] 빅데이터 분석기사 실기 (작업형1,2,3)</t>
+          <t>Claude Code 실전 업무 자동화 : 코드 없이 나만의 AI 에이전트 만들기</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>퇴근후딴짓</t>
+          <t>일잘러 장피엠</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>121000</v>
+        <v>44880</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>121000</v>
+        <v>149600</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>931</v>
+        <v>78</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6048</v>
+        <v>2733</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -942,40 +942,40 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스 자격증, 데이터 분석</t>
+          <t>AI 실무 활용, 업무 자동화, AI 시작하기</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>빅데이터분석기사, 빅데이터, Python, Pandas, 머신러닝</t>
+          <t>claude, codex, MCP, No-code</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1618</v>
+        <v>306</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2022-12-12T15:00:00.000Z</t>
+          <t>2026-10-01T05:00:00.000Z</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T16:36:18.265Z</t>
+          <t>2026-10-05T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/빅데이터-분석기사-실기</t>
+          <t>https://www.inflearn.com/course/practical-workflow-a</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1085,7 +1085,7 @@
         <v>11</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         <v>4.8</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>5735</v>
+        <v>5738</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -1213,31 +1213,31 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
+          <t>[단테랩스] Hermes Bot × OpenAI Dots: AI 봇 플랫폼 완전정복</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>한빛미디어</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0</v>
+        <v>108900</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>734</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13558</v>
+        <v>273</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1251,35 +1251,35 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
+          <t>AI 실무 활용, 업무 자동화</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), 바이브코딩</t>
+          <t>업무 생산성, No-code, ChatGPT, AI Agent</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22T08:00:00.000Z</t>
+          <t>2026-10-04T09:30:05.000Z</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07T07:20:44.145Z</t>
+          <t>2026-10-19T13:05:57.408Z</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
+          <t>https://www.inflearn.com/course/dante-labs-hermes-bo</t>
         </is>
       </c>
     </row>
@@ -1289,19 +1289,19 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
+          <t>[무료 바이브 코딩 강의 / 입문편] 혼자 공부하는 바이브 코딩 with 클로드 코드</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>단테랩스 Dante</t>
+          <t>한빛미디어</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0</v>
@@ -1310,52 +1310,52 @@
         <v>4.9</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>173</v>
+        <v>738</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1627</v>
+        <v>13591</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>AI 활용(AX), 업무 생산성</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 실무 활용</t>
+          <t>AI 시작하기, 생산성 도구, AI 개발 활용</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
+          <t>인공지능(AI), 바이브코딩</t>
         </is>
       </c>
       <c r="N11" s="7" t="n">
-        <v>1649</v>
+        <v>259</v>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>2026-05-13T06:30:00.000Z</t>
+          <t>2025-12-22T08:00:00.000Z</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15T09:10:56.894Z</t>
+          <t>2026-01-07T07:20:44.145Z</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
+          <t>https://www.inflearn.com/course/바이브-코딩-입문-강의-혼자-공부하는</t>
         </is>
       </c>
     </row>
@@ -1365,73 +1365,73 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
+          <t>[단테랩스] Hermes × Codex 로 세우는 나만의 AI 가상 오피스 (8주 마스터 과정)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>단테랩스 Dante</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>49500</v>
+        <v>198000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>99000</v>
+        <v>198000</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>167</v>
+        <v>1632</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라</t>
+          <t>AI에이전트 개발, AI 실무 활용</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Linux, AWS, bash, ubuntu, nginx</t>
+          <t>인공지능(AI), AI Agent</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>710</v>
+        <v>1649</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T07:00:10.000Z</t>
+          <t>2026-05-13T06:30:00.000Z</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T17:50:09.486Z</t>
+          <t>2026-10-15T09:10:56.894Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
+          <t>https://www.inflearn.com/course/hermes-agent-advance</t>
         </is>
       </c>
     </row>
@@ -1441,31 +1441,31 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
+          <t>한입 리액트 실전 라이브러리 키트 - Zustand, Tanstack Query, TailwindCSS</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>한조각</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
         <v>19800</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>66000</v>
+        <v>19800</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>253</v>
+        <v>423</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
@@ -1474,40 +1474,40 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
+          <t>웹 개발, 개발 도구, 프론트엔드</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
+          <t>React, 웹앱, TailwindCSS, react-query, zustand</t>
         </is>
       </c>
       <c r="N13" s="7" t="n">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T20:30:05.000Z</t>
+          <t>2026-03-16T22:00:00.000Z</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29T18:51:20.390Z</t>
+          <t>2026-03-28T01:38:34.068Z</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/from-service-deploym</t>
+          <t>https://www.inflearn.com/course/one-bite-react-pract</t>
         </is>
       </c>
     </row>
@@ -1517,22 +1517,22 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
+          <t>밑바닥부터 만드는 AI 에이전트 — RAG · 멀티 에이전트 · MCP</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Dowon Lee</t>
+          <t>단테</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>37950</v>
+        <v>110000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>75900</v>
+        <v>110000</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1550,40 +1550,40 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
+          <t>AI에이전트 개발, 백엔드, AI 코딩</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
+          <t>Python, FastAPI, LLM, openAI API, AI Agent</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>641</v>
+        <v>427</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:30:06.000Z</t>
+          <t>2026-10-05T18:00:08.000Z</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T01:52:33.960Z</t>
+          <t>2026-10-19T22:06:23.303Z</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
+          <t>https://www.inflearn.com/course/introduction-to-buil-2</t>
         </is>
       </c>
     </row>
@@ -1593,31 +1593,31 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 기본편</t>
+          <t>배포부터 운영 장애 대응까지 - GitOps, 옵저버빌리티, AI 에이전트</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>한조각</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>44000</v>
+        <v>19800</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>44000</v>
+        <v>66000</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>2406</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>28233</v>
+        <v>258</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
@@ -1626,40 +1626,40 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, AI 기술</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
+          <t>백엔드, 데브옵스 · 인프라, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>Spring Boot, Kubernetes, CI/CD, github-actions, argocd, gitops, AI Agent</t>
         </is>
       </c>
       <c r="N15" s="7" t="n">
-        <v>1012</v>
+        <v>538</v>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>2023-11-27T15:00:00.000Z</t>
+          <t>2026-09-29T20:30:05.000Z</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2025-12-23T06:52:23.926Z</t>
+          <t>2026-10-19T13:49:51.036Z</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
+          <t>https://www.inflearn.com/course/from-service-deploym</t>
         </is>
       </c>
     </row>
@@ -1669,73 +1669,73 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>클로드 코드 실전 — 설치부터 하네스까지</t>
+          <t>프로그래밍 시작하기 : 파이썬 입문 (Inflearn Original)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>단테</t>
+          <t>인프런</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>77000</v>
+        <v>33000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>154000</v>
+        <v>33000</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
+        <v>1404</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6</v>
+        <v>34422</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, AI 개발 활용</t>
+          <t>프로그래밍 언어</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Git, supabase, AI Agent, MCP, claude, 바이브코딩</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>690</v>
+        <v>857</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T18:00:04.000Z</t>
+          <t>2019-06-01T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T02:05:05.992Z</t>
+          <t>2026-09-18T05:48:10.725Z</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/claude-code-in-pract</t>
+          <t>https://www.inflearn.com/course/프로그래밍-파이썬-입문-인프런-오리지널</t>
         </is>
       </c>
     </row>
@@ -1745,73 +1745,73 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>LangChain, LangGraph, LangSmith 기초부터 총정리</t>
+          <t>한 입 크기로 잘라먹는 바이브코딩 - 기초부터 실전 배포까지 (클로드 &amp; 코덱스)</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>bradkim</t>
+          <t>이정환 Winterlood</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>69300</v>
+        <v>99000</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>99000</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>3</v>
+        <v>1127</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>AI 기술, AI 활용(AX)</t>
+          <t>개발 · 프로그래밍, AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>AI에이전트 개발, 인공지능 기타, AI 개발 활용</t>
+          <t>AI 코딩, AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>FastAPI, vector-database, 인공지능(AI), LLM, LangChain, openAI API, LangGraph</t>
+          <t>웹앱, claude, 바이브코딩, codex, 인공지능(AI)</t>
         </is>
       </c>
       <c r="N17" s="7" t="n">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T13:30:05.000Z</t>
+          <t>2026-05-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T11:54:49.913Z</t>
+          <t>2026-09-21T01:35:54.874Z</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/a-complete-overview</t>
+          <t>https://www.inflearn.com/course/bite-sized-vibe-codi</t>
         </is>
       </c>
     </row>
@@ -1821,31 +1821,31 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
+          <t>클로드 코드 실전 — 설치부터 하네스까지</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>일프로</t>
+          <t>단테</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>55000</v>
+        <v>77000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>55000</v>
+        <v>154000</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>666</v>
+        <v>11</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1854,40 +1854,40 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>AI 기술, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
+          <t>AI에이전트 개발, AI 개발 활용</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Kubernetes, devops, certificates, container, CKA</t>
+          <t>Git, supabase, AI Agent, MCP, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>196</v>
+        <v>740</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19T22:30:00.000Z</t>
+          <t>2026-10-17T18:00:04.000Z</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T08:32:14.551Z</t>
+          <t>2026-10-19T18:23:18.376Z</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/certified-kubernetes</t>
+          <t>https://www.inflearn.com/course/claude-code-in-pract</t>
         </is>
       </c>
     </row>
@@ -1897,73 +1897,73 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
+          <t>Jenkins와 ArgoCD로 배우는 실전 GitOps CI/CD</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>FlowCoder</t>
+          <t>Dowon Lee</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0</v>
+        <v>37950</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0</v>
+        <v>75900</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>4061</v>
+        <v>229</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
+          <t>백엔드, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
+          <t>Docker, Jenkins, Kubernetes, CI/CD, devops, argocd, Spring Boot</t>
         </is>
       </c>
       <c r="N19" s="7" t="n">
-        <v>90</v>
+        <v>641</v>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:00:00.000Z</t>
+          <t>2026-09-28T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24T16:57:29.088Z</t>
+          <t>2026-09-29T01:52:33.960Z</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
+          <t>https://www.inflearn.com/course/practical-gitops-cic</t>
         </is>
       </c>
     </row>
@@ -1973,31 +1973,31 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
+          <t>리눅스 참교육 - AWS Ubuntu로 Linux 기초부터 서버 운영까지</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>AI 지식 전달자</t>
+          <t>얄코</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>418</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4708</v>
+        <v>171</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -2006,38 +2006,40 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
+          <t>데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>인공지능(AI), AI Agent</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n"/>
+          <t>Linux, AWS, bash, ubuntu, nginx</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>710</v>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27T10:00:00.000Z</t>
+          <t>2026-10-06T07:00:10.000Z</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T00:59:39.967Z</t>
+          <t>2026-10-18T17:50:09.486Z</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
+          <t>https://www.inflearn.com/course/linux-mastery-from-t</t>
         </is>
       </c>
     </row>
@@ -2047,73 +2049,73 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 2편</t>
+          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>컴공로드맵</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>66000</v>
+        <v>89100</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>66000</v>
+        <v>89100</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>885</v>
+        <v>238</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>11031</v>
+        <v>1747</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Java, 객체지향, 알고리즘, 코딩 테스트</t>
+          <t>security, CPPG(개인정보관리사)</t>
         </is>
       </c>
       <c r="N21" s="7" t="n">
-        <v>1165</v>
+        <v>727</v>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>2024-05-07T15:00:00.000Z</t>
+          <t>2023-11-16T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2025-11-24T10:17:13.631Z</t>
+          <t>2026-07-15T12:04:39.450Z</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-2</t>
+          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
         </is>
       </c>
     </row>
@@ -2123,31 +2125,31 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>AWS로 배우는 네트워크: 이론부터 실무까지</t>
+          <t>김영한의 실전 자바 - 기본편</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>154000</v>
+        <v>44000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>154000</v>
+        <v>44000</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50</v>
+        <v>2409</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1212</v>
+        <v>28239</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2156,40 +2158,40 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 보안 · 네트워크</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 네트워크, 클라우드</t>
+          <t>프로그래밍 언어, 웹 개발, 백엔드</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>네트워크, tcpip, aws-vpc, aws-alb, 바이브코딩</t>
+          <t>Java, 객체지향</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>917</v>
+        <v>1012</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26T07:00:00.000Z</t>
+          <t>2023-11-27T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28T06:03:09.161Z</t>
+          <t>2025-12-23T06:52:23.926Z</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws로-배우는-네트워크-이론부터-실</t>
+          <t>https://www.inflearn.com/course/김영한의-실전-자바-기본편</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2201,19 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
+          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>정미나</t>
+          <t>JSCODE 박재성</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>55000</v>
+        <v>88000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>55000</v>
+        <v>88000</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>0</v>
@@ -2220,10 +2222,10 @@
         <v>4.9</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>42</v>
+        <v>273</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>489</v>
+        <v>1377</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
@@ -2232,40 +2234,40 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>데이터 사이언스, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
+          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>SQLD, SQL, Oracle, MSSQL</t>
+          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
         </is>
       </c>
       <c r="N23" s="7" t="n">
-        <v>501</v>
+        <v>309</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13T09:30:00.000Z</t>
+          <t>2026-01-06T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12T07:12:46.551Z</t>
+          <t>2026-10-19T01:45:14.770Z</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
+          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
         </is>
       </c>
     </row>
@@ -2275,19 +2277,19 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 성능 최적화, 실행 계획과 인덱스 완전 정복</t>
+          <t>Certified Kubernetes Administrator (CKA) – Practical Exam Guide</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>일프로</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>154000</v>
+        <v>55000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>154000</v>
+        <v>55000</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
@@ -2296,52 +2298,52 @@
         <v>5</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2059</v>
+        <v>669</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 데이터 분석, 풀스택</t>
+          <t>보안 · 네트워크 자격증, 데브옵스 · 인프라, 시스템 · 운영체제</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, sql-tuning, SQLD</t>
+          <t>Kubernetes, devops, certificates, container, CKA</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1270</v>
+        <v>196</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T15:00:00.000Z</t>
+          <t>2026-02-19T22:30:00.000Z</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28T00:00:00.000Z</t>
+          <t>2026-09-22T08:32:14.551Z</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-성능최적화</t>
+          <t>https://www.inflearn.com/course/certified-kubernetes</t>
         </is>
       </c>
     </row>
@@ -2351,73 +2353,73 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
+          <t>AI 처음으로 일 시키기 — Claude Code 에이전틱 자동화</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>코드브릿지</t>
+          <t>FlowCoder</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>44550</v>
+        <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>59400</v>
+        <v>0</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>4.8</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>24</v>
+        <v>323</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>238</v>
+        <v>4087</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
+          <t>AI 시작하기, AI 실무 활용, AI에이전트 개발</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
+          <t>인공지능(AI), AI Agent, claude, 바이브코딩, 업무 생산성</t>
         </is>
       </c>
       <c r="N25" s="7" t="n">
-        <v>311</v>
+        <v>90</v>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31T10:30:06.000Z</t>
+          <t>2026-04-21T04:00:00.000Z</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12T14:30:32.966Z</t>
+          <t>2026-09-24T16:57:29.088Z</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
+          <t>https://www.inflearn.com/course/giving-ai-its-first</t>
         </is>
       </c>
     </row>
@@ -2427,73 +2429,73 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026년 CPPG 개인정보관리사 자격증 취득하기 (개정안 반영)</t>
+          <t>파이썬 라즈베리파이 IoT프로젝트-원격모니터링 자동차</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>컴공로드맵</t>
+          <t>노마드크리에이터</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>89100</v>
+        <v>33000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>89100</v>
+        <v>33000</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>237</v>
+        <v>28</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1744</v>
+        <v>340</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크, 개발 · 프로그래밍</t>
+          <t>하드웨어, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>보안 · 네트워크 자격증, 개발 · 프로그래밍 자격증, 보안</t>
+          <t>임베디드 · IoT, 프로그래밍 언어, 모빌리티</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>security, CPPG(개인정보관리사)</t>
+          <t>Python, Linux, Raspberry Pi, IoT</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>727</v>
+        <v>148</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2023-11-16T15:00:00.000Z</t>
+          <t>2019-02-23T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T12:04:39.450Z</t>
+          <t>2025-05-13T07:51:40.535Z</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/cppg-개인정보관리사-취득하기</t>
+          <t>https://www.inflearn.com/course/iot</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2505,19 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>AWS SAA-C03 자격증 벼락치기 - 딱 163문제로 2주만에 합격하기</t>
+          <t>전동킥보드로 배우는 임베디드 실전 프로젝트</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>JSCODE 박재성</t>
+          <t>제어쟁이</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>88000</v>
+        <v>550000</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>88000</v>
+        <v>550000</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>0</v>
@@ -2524,52 +2526,52 @@
         <v>4.9</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>272</v>
+        <v>85</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1374</v>
+        <v>611</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>하드웨어</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍 자격증, 웹 개발, 데브옵스 · 인프라</t>
+          <t>임베디드 · IoT, 모빌리티</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>AWS, devops, infrastructure, AWS SAA, backend</t>
+          <t>임베디드, stm32, hardware, motordriver, artwork</t>
         </is>
       </c>
       <c r="N27" s="7" t="n">
-        <v>309</v>
+        <v>1017</v>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>2026-01-06T22:30:00.000Z</t>
+          <t>2025-06-15T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T01:45:14.770Z</t>
+          <t>2026-09-13T09:06:49.556Z</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/aws-saa-c03-자격증-벼락치기</t>
+          <t>https://www.inflearn.com/course/전동킥보드개발-임베디드-개발자</t>
         </is>
       </c>
     </row>
@@ -2579,31 +2581,31 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 자바 - 중급 1편</t>
+          <t>하네스•루프•그래프 엔지니어링 - 프롬프트 다음의 AI 에이전트 다섯 단계</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>코드브릿지</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>66000</v>
+        <v>46200</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>66000</v>
+        <v>59400</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1266</v>
+        <v>24</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>12548</v>
+        <v>240</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2612,40 +2614,40 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 활용(AX), AI 기술, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>프로그래밍 언어, 백엔드, 웹 개발</t>
+          <t>AI 실무 활용, AI에이전트 개발, AI 코딩</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Java, 객체지향</t>
+          <t>multi-agent, context-switching, AutoGPT, AI Agent</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1161</v>
+        <v>311</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2024-03-27T15:00:00.000Z</t>
+          <t>2026-07-31T10:30:06.000Z</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2025-11-28T10:04:41.236Z</t>
+          <t>2026-08-12T14:30:32.966Z</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한의-실전-자바-중급-1</t>
+          <t>https://www.inflearn.com/course/mastering-the-5-stag</t>
         </is>
       </c>
     </row>
@@ -2655,31 +2657,31 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Obsidian x Claude Code 나만의 LLM Wiki 만들기</t>
+          <t>SQLD의 정석: 노랭이 문제집 씹어먹기</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>실용주의개발</t>
+          <t>정미나</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>88000</v>
+        <v>55000</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>195</v>
+        <v>42</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1473</v>
+        <v>489</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
@@ -2688,40 +2690,40 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, AI 활용(AX), 개발 · 프로그래밍</t>
+          <t>데이터 사이언스, 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>생산성 도구, AI 실무 활용, AI 코딩</t>
+          <t>데이터 분석, 개발 · 프로그래밍 자격증</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>업무 생산성, wiki, obsidian, claude</t>
+          <t>SQLD, SQL, Oracle, MSSQL</t>
         </is>
       </c>
       <c r="N29" s="7" t="n">
-        <v>368</v>
+        <v>501</v>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25T18:30:00.000Z</t>
+          <t>2026-01-13T09:30:00.000Z</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08T14:26:56.788Z</t>
+          <t>2026-10-12T07:12:46.551Z</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/obsidian-x-claude-co</t>
+          <t>https://www.inflearn.com/course/sqld의-정석-노랭이-문제집-씹어먹</t>
         </is>
       </c>
     </row>
@@ -2731,73 +2733,71 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 기본편</t>
+          <t>[바이브코딩] Google AntiGravity 마스터 클래스 - Basic</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>AI 지식 전달자</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5403</v>
+        <v>4719</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>입문</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 활용(AX), 개발 · 프로그래밍</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>AI 개발 활용, AI 실무 활용, 풀스택</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>821</v>
-      </c>
+          <t>인공지능(AI), AI Agent</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2026-01-27T10:00:00.000Z</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06T12:14:20.961Z</t>
+          <t>2026-06-30T00:59:39.967Z</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
+          <t>https://www.inflearn.com/course/바이브코딩-google-antigra</t>
         </is>
       </c>
     </row>
@@ -2807,19 +2807,19 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 - 설계 2편, 실무에서 반드시 마주치는 9가지 설계 패턴</t>
+          <t>네카라쿠배 시니어의 실무 하네스 엔지니어링 : 실전 Spring Boot 환경에서 사용하는 클로드 코드</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>실용주의개발</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>121000</v>
+        <v>330000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>121000</v>
+        <v>330000</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>0</v>
@@ -2828,52 +2828,52 @@
         <v>5</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>2977</v>
+        <v>549</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>초급</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 기술, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>AI에이전트 개발, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, 소프트웨어 설계, SQLD</t>
+          <t>Java, Spring, 소프트웨어 설계, 인공지능(AI), AI Agent, claude, 바이브코딩</t>
         </is>
       </c>
       <c r="N31" s="7" t="n">
-        <v>797</v>
+        <v>1048</v>
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27T15:00:00.000Z</t>
+          <t>2026-06-22T17:00:00.000Z</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09T09:50:03.741Z</t>
+          <t>2026-09-16T22:53:04.634Z</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-설계2편</t>
+          <t>https://www.inflearn.com/course/the-standard-of-clau</t>
         </is>
       </c>
     </row>
@@ -2883,19 +2883,19 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>제대로 파는 Git &amp; GitHub - by 얄코</t>
+          <t>LangGraph를 활용한 AI Agent 개발 (feat. MCP)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>제이쓴</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>44000</v>
+        <v>69300</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>44000</v>
+        <v>69300</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>0</v>
@@ -2904,52 +2904,52 @@
         <v>4.9</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>617</v>
+        <v>263</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8424</v>
+        <v>2978</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍</t>
+          <t>AI 기술</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>개발 도구</t>
+          <t>AI에이전트 개발</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Git, GitHub, github-actions, git-commands</t>
+          <t>프롬프트엔지니어링, LLM, AI Agent, LangGraph, MCP</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2022-01-20T15:00:00.000Z</t>
+          <t>2025-01-19T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03T09:18:28.574Z</t>
+          <t>2026-06-23T10:57:36.230Z</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/제대로-파는-깃</t>
+          <t>https://www.inflearn.com/course/랭그래프-활용한-llm에이전트-개발</t>
         </is>
       </c>
     </row>
@@ -2959,31 +2959,31 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>한국주식 AI 자동매매 - 외국인·기관 수급 완전정복 (베개투자법) NEW</t>
+          <t>디지털포렌식 입문자를 위한 디지털포렌식 전문가 2급 실기 시험대비 강의(Encase/Autopsy)</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>치알남 cheatkeyman</t>
+          <t>nstyxn</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>99000</v>
+        <v>118800</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>99000</v>
+        <v>118800</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>93</v>
+        <v>965</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
@@ -2992,40 +2992,40 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 데이터 사이언스, 커리어 · 자기계발</t>
+          <t>보안 · 네트워크</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 데이터 분석, 금융 ·  재테크</t>
+          <t>보안, 보안 · 네트워크 자격증</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>Python, 머신러닝, AWS, PostgreSQL, FastAPI, 인공지능(AI), claude</t>
+          <t>Forensic, 디지털포렌식전문가 2급</t>
         </is>
       </c>
       <c r="N33" s="7" t="n">
-        <v>363</v>
+        <v>6530</v>
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:07.000Z</t>
+          <t>2022-11-13T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30T03:16:06.187Z</t>
+          <t>2026-07-15T02:00:30.898Z</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/ai-automated-trading</t>
+          <t>https://www.inflearn.com/course/입문-디지털포렌식-2급-실기</t>
         </is>
       </c>
     </row>
@@ -3035,73 +3035,73 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>김영한의 실전 데이터베이스 입문 - 모든 IT인을 위한 SQL 첫걸음(SQL부터 차근차근)</t>
+          <t>AWS로 배우는 네트워크: 이론부터 실무까지</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>김영한</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>747</v>
+        <v>50</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11872</v>
+        <v>1217</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 데이터 사이언스</t>
+          <t>AI 활용(AX), 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>데이터베이스, 백엔드, 데이터 분석</t>
+          <t>AI 실무 활용, 네트워크, 클라우드</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
+          <t>네트워크, tcpip, aws-vpc, aws-alb, 바이브코딩</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>517</v>
+        <v>917</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2025-07-31T15:00:00.000Z</t>
+          <t>2026-02-26T07:00:00.000Z</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2025-08-31T09:28:51.006Z</t>
+          <t>2026-02-28T06:03:09.161Z</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-입문</t>
+          <t>https://www.inflearn.com/course/aws로-배우는-네트워크-이론부터-실</t>
         </is>
       </c>
     </row>
@@ -3111,73 +3111,73 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>코덱스 참교육 - Codex 업무 자동화부터 바이브 코딩까지</t>
+          <t>김영한의 실전 데이터베이스 - 기본편</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>얄코</t>
+          <t>김영한</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>145</v>
+        <v>520</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>915</v>
+        <v>5406</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>AI 활용(AX), 업무 생산성, 개발 · 프로그래밍</t>
+          <t>개발 · 프로그래밍, 데이터 사이언스</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>AI 실무 활용, 업무 자동화, AI 코딩</t>
+          <t>데이터베이스, 백엔드, 데이터 분석</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>agents, codex, 프롬프트엔지니어링, 바이브코딩, 하네스</t>
+          <t>SQL, MySQL, DBMS/RDBMS, SQLD</t>
         </is>
       </c>
       <c r="N35" s="7" t="n">
-        <v>657</v>
+        <v>821</v>
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20T05:00:00.000Z</t>
+          <t>2025-07-31T15:00:00.000Z</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11T06:39:46.390Z</t>
+          <t>2026-08-06T12:14:20.961Z</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/codex-true-education</t>
+          <t>https://www.inflearn.com/course/김영한-실전-데이터베이스-기본편</t>
         </is>
       </c>
     </row>
@@ -3187,73 +3187,73 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>[2026] 비전공자도 한 번에 합격하는 SQLD 올인원</t>
+          <t>Docker가 쉬워지는 운영체제 이야기</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>알고런 데이터코드 연구소</t>
+          <t>널널한 개발자</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>79200</v>
+        <v>88000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>79200</v>
+        <v>88000</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>601</v>
+        <v>959</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>초급</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>데이터 사이언스</t>
+          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>데이터 엔지니어링, 데이터 분석, 데이터 사이언스 자격증</t>
+          <t>데브옵스 · 인프라, 시스템 · 운영체제, 클라우드</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SQL, 빅데이터, 데이터 엔지니어링, SQLD, 코딩 테스트</t>
+          <t>네트워크, Linux, Docker, 운영체제, linux-containers, cloud-computing</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>785</v>
+        <v>723</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2025-04-07T15:00:00.000Z</t>
+          <t>2026-07-30T04:00:57.000Z</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T07:40:07.999Z</t>
+          <t>2026-08-04T00:38:47.888Z</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:43:08+09:00</t>
+          <t>2026-10-20T13:52:50+09:00</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>https://www.inflearn.com/course/비전공자-sqld-자격증</t>
+          <t>https://www.inflearn.com/course/operating-system-sto</t>
         </is>
       </c>
     </row>
@@ -3263,31 +3263,31 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Docker가 쉬워지는 운영체제 이야기</t>
+          <t>AI 코드를 읽는 게임 개발자 「Unity 6」 「Claude」 「Github Copilot」 「3D」</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>널널한 개발자</t>
+          <t>알렌</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="E37" s="9" t="n">
         <v>88000</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>956</v>
+        <v>6</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
@@ -3296,40 +3296,40 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>개발 · 프로그래밍, 보안 · 네트워크</t>
+          <t>게임 개발, 개발 · 프로그래밍, AI 활용(AX)</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>데브옵스 · 인프라, 시스템 · 운영체제, 클라우드</t>
+          <t>게임 프로그래밍, AI 코딩, AI 개발 활용</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>네트워크, Linux, Docker, 운영체제, linux-containers, cloud-computing</t>
+          <t>Unity, VSCode, github-copilot, 인공지능(AI), AI Agent, 유니티6, claude</t>
         </is>
       </c>
       <c r="N37" s="7" t="n">
-        <v>723</v>
+        <v>498</v>
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30T04:00:57.000Z</t>
+          <t>2026-10-16T06:00:06.000Z</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04T00:38:47.888Z</t>
+          <t>2026-10-17T17:44:29.872Z</t>
         </is>
       </c>
 